--- a/data/processed/pssi_form_data_altered.xlsx
+++ b/data/processed/pssi_form_data_altered.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ennsj\Documents\PSSI-final-tech-report\data\processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C44190-B37D-4273-BC40-F836A69EA022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{912B8EAF-0CE7-443F-872A-ED495F3C6D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="641">
   <si>
     <t>source_file</t>
   </si>
@@ -391,9 +391,6 @@
     <t>San Juan Chinook</t>
   </si>
   <si>
-    <t>WCVI Fall Chinook</t>
-  </si>
-  <si>
     <t>- San Juan Chinook are a unique population part of the WCVI Fall Chinook CU that has recently received a rebuilding plan. Risk assessments have noted knowledge gaps related to juvenile life stages in the freshwater, estuary and early marine stages. This project aims to fill some of these data gaps.
 - The results from this project will inform a revised risk assessment process for WCVI Chinook in 2026, as well as provide Pacheedaht First Nation with data upon which to base their rebuilding plan for San Juan Chinook and to inform restoration efforts in the watershed.</t>
   </si>
@@ -401,10 +398,6 @@
     <t>These activities will all inform the San Juan Chinook Rebuilding Plan in development by PFN, which will be linked to the broader WCVI Chinook Rebuilding Plan recently developed by DFO (required under the Fish Stock Provisions Act for naturally-produced WCVI Chinook) (DFO 2025). This project will also inform a risk assessment re-scoring expected to happen in 2026, where new information from PSSI projects will be used to re-evaluate the most prominent bottlenecks to WCVI Chinook survival and recovery. The first round WCVI Chinook risk assessment process identified several knowledge gaps, mostly related to early freshwater and marine life cycle stages. For San Juan Chinook specifically, juvenile data from these life stages (and interactions between hatchery and wild juveniles) are sparse, and biological data on natural spawners (e.g., age, origin) are limited.
 These reasons made the San Juan River a good candidate to develop an integrated life history monitoring program in alignment with the larger Follow The Fish program. We focused on activities complemented Pacheedaht First Nation's established juvenile monitoring programs. First, we operated a rotary screw trap program to enumerate and sample naturally-produced out-migrating juveniles (all species, but focused on juvenile Chinook migration timing) in the freshwater environment, allowing us to compare natural migration timing to hatchery release timing, gather baseline biological traits relative to hatchery releases (e.g., size, condition), and estimate fry outmigration abundance. Otolith and stomach samples are also collected from a sub-sample of individuals to assess size-specific survival and diet contents. Second, we collected samples from Pacheedaht's estuary beach seine program to continue examining diet differences and estuary residency (via otolith microchemistry) between hatchery and natural-origin Chinook. Finally, we conducted biweekly purse seining in Port San Juan (PFMA 20-2) through the late spring, summer and fall months (~May-October) to collect mixed-stock information, including hatchery/natural-origin of juvenile Chinook, stock ID, biological traits, relative abundance, and information on other species schooling with Chinook (e.g., Coho, Pacific Herring). As with the RST and beach seine, we also collected otoliths and stomach contents from a sub-sample of Chinook encountered. Finally, we developed a biosampling plan to assess age and stock composition of naturally-spawning adult Chinook (a deadpitch program). Current information on the Proportion of Natural Influence (PNI) is limited only to broodstock sampling, but it is unknown whether these samples are biased and whether they are representative of the river spawning component of the population. It is critical to have an accurate representation of PNI and age and composition-at-return to assess productivity trends and hatchery release strategies for rebuilding San Juan Chinook.
 All work was done in collaboration with Pacheedaht First Nation. Their Fisheries Team lead the majority of the field work and sample collection, as well as advised on sampling designs and salmon dynamics to improve the study design of the project.</t>
-  </si>
-  <si>
-    <t>The key finding of this project will be the specific differences in dynamics between hatchery and natural-origin San Juan Chinook, and using this information to both improve the survival and health of natural-origin juveniles while producing hatchery fish that complement, rather than compete with, the natural population. These findings may be applicable to other systems, although collecting stock-specific information is critical to ensure that any future "indicator" populations are in fact indicative of dynamics in other systems.
-Future studies should further examine specific indicators of early mortality in juvenile salmon, primarily in the freshwater and estuarine stages which are largely unmonitored by DFO. In addition, consideration should be given as to how hatchery release strategies change the life history dynamics of juvenile salmon</t>
   </si>
   <si>
     <t>2404 PSSI Science Project Reporting_Bianucci.docx</t>
@@ -1068,9 +1061,6 @@
   </si>
   <si>
     <t>2425 PSSI Science Project Report - Geospatial Indicators - Jan232026.docx</t>
-  </si>
-  <si>
-    <t>Geospatial Indicators and Metrics for Threats to Fish Habitat in the Fraser River Basin with Thompson-Nicola as a Case Study</t>
   </si>
   <si>
     <t>Josephine Iacarella, Keegan Paterson, Daniel Weller</t>
@@ -2354,39 +2344,6 @@
 CTD PROFILES AND WATER SAMPLING: Profile data were collected using a SeaBird SBE911 CTD with sensors for temperature, salinity, dissolved oxygen, transmissivity (red: 660nm, green: 550 nm) and chlorophyll fluorescence. Water samples were collected using a standard 24-bottle rosette collected on the up-cast. Water samples were analyzed unfiltered for nutrients (nitrate, phosphate, silicate) at the Institute of Ocean Sciences, using a Technicon AutoAnalyzerâ„¢ II (Barwell-Clarke and Whitney, 1996). Nutrient data will be interpreted by calculating molar ratios of Si:N:P and comparing the ratios with those calculated for the Strait of Georgia and Puget Sound. (In Puget Sound, the Si:N ratio has declined since the 1990s, affecting the phytoplankton species assemblage, while the ratio has remained stable in the Strait of Georgia (unpublished data)).
 DATA ARCHIVING: Following quality control, data were archived in the OSD Data Archive at the Institute of Ocean Sciences and made available through the Waterproperties.ca website.
 DELAYS: There were some unforeseen delays in field work and sample analysis. Two sampling cruises were cancelled, and a change in Coast Guard policy that made it impossible to collect sediment cores and water samples during the same cruise, which meant that the field work portion of the project took longer than anticipated. In addition, three labs that had previously analyzed stable isotopes all stopped offering that service, and it took some time to identify a new lab. As a result, some data were only received this month, with the rest of the outstanding data due by March 31. Consequently, only a preliminary interpretation is possible at this time. Interpretation will be completed in the coming fiscal year.</t>
-  </si>
-  <si>
-    <t>â€¢Ahousaht First Nation
-â€¢ Coal Harbour Ltd.
-â€¢ British Columbia Conservation Foundation
-â€¢ Cedar Coast Field Station
-â€¢ Charter Tofino
-â€¢ Ditidaht First Nation
-â€¢ Ehattesaht/Chinehkint First Nation
-â€¢ Ha'oom Fisheries Society
-â€¢ Hesquiaht First Nation
-â€¢ HupaÄasath First Nation
-â€¢ Huu-ay-aht First Nations
-â€¢ The Juanes Lab (University of Victoria)
-â€¢ Ka:'yu:'k't'h'/Che:k:tles7et'h' First Nations
-â€¢ LGL Limited
-â€¢ Maaqutusiis Hahoulthee Stewardship Society
-â€¢ M.C. Wright and Associates Ltd.
-â€¢ Mowachaht-Muchalaht First Nations
-â€¢ Nootka Sound Watershed Society
-â€¢ Nuu-Chah-Nulth Tribal Council
-â€¢ Nuchatlaht Tribe
-â€¢ Pacheedaht First Nation
-â€¢ Pacific Salmon Foundation
-â€¢ Quatsino First Nation
-â€¢ Redd Fish Restoration Society
-â€¢ Thornton Creek Enhancement Society
-â€¢ Tla-o-qui-aht First Nation
-â€¢ Toquaht Nation
-â€¢ Tseshaht First Nation
-â€¢ T'Sou-ke Nation
-â€¢ Uchucklesaht Tribe
-â€¢ YuuÅ‚uÊ”iÅ‚Ê”athÌ£ Government</t>
   </si>
   <si>
     <t>Figure 1. Chinook-bearing river systems on the WCVI that have been genetically sequenced and included in the library for stock assignment with GSI and PBT. Color coding indicates how populations were aggregated for individual stock assignments and shapes indicate how river systems fall in the South-West Vancouver Island (SWVI), Nootka-Kyuquot (NoKy) and North-West Vancouver Island (NWVI) Conservation Units.
@@ -2789,12 +2746,6 @@
 The broodfish-thiamine-injection method appeared to effectively improve the total thiamine levels, mostly in form of TH, in Chinook salmon eggs. Although there were no untreated, control eggs available as a comparison at Shuswap River Hatchery, the injection-treated eggs (20.5 Â± 4.8 nmol/g, range from 16 - 27 nmol/g) contained up to 2 - 3 times the usual thiamine amount in untreated eggs of other Chinook salmon stocks (Figure 2 and 3, 6 - 13 nmol/g). The total thiamine levels in eggs from these injection-treated fish are within the range reported for similar studies on coho salmon (21.925 Â±1.694 nmol/g, Fitzsimons et al., 2005) and steelhead trout *Oncorhynchus mykiss* (total thiamine 20.4 Â± 11.3 nmol/g; Futia et al 2017; mean total thiamine: 33.5 nmol/g, range: 15.4 - 51.1 nmol/g; Reed et al 2023). Unfortunately, our study could not resolve the effectiveness of thiamine bath-treated eggs because of supra-biological and varying levels measured in eggs sampled immediately after the 1 h treatment bath (e.g. 302.5 Â± 31.2 nmol/g in Chinook salmon at Tenderfoot Creek hatchery; 0.95 - 291.20 nmol/g in mid Coho salmon eggs at Capilano Hatchery). Thus, it was unknown how much of the thiamine was actually retained and biologically available to the eggs over time. Future work should resolve the effectiveness and necessity of these thiamine treatments, as these methods could prove highly valuable in both minimizing the potential negative impacts of TDC on early fry and optimizing hatchery salmon production (Futia et al. 2017; Reed et al. 2023; Harder et al. 2025).</t>
   </si>
   <si>
-    <t>Table 1. Results of total thiamine levels detected in chinook salmon eggs treated or untreated with thiamine.
-Figure 1. Results of linear regression analysis on the total mean thiamine level results reported by SUNY Brockport and PSEC on the same set of chinook salmon eggs. Each dot represents an individual sample.
-Figure 2. Results of the total thiamine levels in untreated and unfertilized eggs collected from Capilano mid coho (Cap-mid-Coho, n=5), Chilliwack mid coho (Cwk-mid-Coho, n=10), Tenderfoot Cheakamus Chinook (Tdf-Chinook, n=4), Chilliwack fall Chinook (Cwk-Chinook, n=10), Harrison sockeye (Har-Sockeye, n=10), Chilko sockeye (Cko-Sockeye, n=10), Weaver sockeye (Wvr-Sockeye, n=9) and Chehalis pink (Chs-Pink, n=11). Note that the Harrison sockeye eggs were considered not ripe during sample collection; Tenderfoot Cheakamus Chinook data came from results of untreated eggs reported in Table 1. The dash lines represent thiamine level thresholds established by Mantua et al. (2025) to illustrate the likelihood of being impacted by thiamine deficiency: high - unlikely impacted (&gt; 7.7 nmol/g), intermediate - likely impacted (5.9-7.7 nmol/g), low - impacted (2.7-5.9 nmol/g) and critically low - severely impacted (&lt; 2.7 nmol/g). The cross symbol (Ã—) in the box plot indicates mean values within each group.
-Figure 3. Proportion of salmon eggs from different populations measured by the thiamine level thresholds established by Mantua et al. (2025). Different category of total thiamine level represents different likelihood of being impacted by thiamine deficiency: high - unlikely impacted (&gt; 7.7 nmol/g), intermediate - likely impacted (5.9-7.7 nmol/g), low - impacted (2.7-5.9 nmol/g) and critically low - severely impacted (&lt; 2.7 nmol/g). Eggs were collected from different salmon species and population: Capilano mid coho (n=5), Chilliwack mid coho (n=10), Tenderfoot Cheakamus Chinook (n=4), Chilliwack fall Chinook (n=10), Harrison sockeye (n=10), Chilko sockeye (n=10), Weaver sockeye (n=9) and Chehalis pink (n=11).</t>
-  </si>
-  <si>
     <t>Amcoff, P., BÃ¶rjeson, H., Landergren, P., Vallin, L., and Norrgren, L. 1999. Thiamine (vitamin B1) concentrations in salmon (*Salmo salar*), brown trout (Salmo trutta) and cod (Gadus morhua) from the Baltic Sea. Ambio 28(1): 48-54.
 BÃ¢, A. 2008. Metabolic and structural role of thiamine in nervous tissues. Cell. Mol. Neurobiol. 28(7): 923-931. doi:10.1007/s10571-008-9297-7.
 Brown, S.B., Fitzsimons, J.D., Honeyfield, D.C., and Tillitt, D.E. 2005a. Implications of thiamine deficiency in Great Lakes salmonines. J. Aquat. Anim. Health 17(1): 113-124. doi:10.1577/H04-015.1.
@@ -3219,13 +3170,32 @@
 Figure 2. 2023 daily estimates of Chilko River Sockeye smolt passage: side-looking SONAR estimates versus fence counts.
 Figure 3. 2022 daily estimates of Chilko River Sockeye smolt passage: side-looking SONAR estimates versus fence counts.</t>
   </si>
+  <si>
+    <t>Ahousaht First Nation; Coal Harbour Ltd.; British Columbia Conservation Foundation; Cedar Coast Field Station; Charter Tofino; Ditidaht First Nation; Ehattesaht/Chinehkint First Nation; Ha'oom Fisheries Society; Hesquiaht First Nation; HupaÄasath First Nation; Huu-ay-aht First Nations; The Juanes Lab (University of Victoria); Ka:'yu:'k't'h'/Che:k:tles7et'h' First Nations; LGL Limited; Maaqutusiis Hahoulthee Stewardship Society; M.C. Wright and Associates Ltd.; Mowachaht-Muchalaht First Nations; Nootka Sound Watershed Society; Nuu-Chah-Nulth Tribal Council; Nuchatlaht Tribe; Pacheedaht First Nation; Pacific Salmon Foundation; Quatsino First Nation; Redd Fish Restoration Society; Thornton Creek Enhancement Society; Tla-o-qui-aht First Nation; Toquaht Nation; Tseshaht First Nation; T'Sou-ke Nation; Uchucklesaht Tribe; and YuuÅ‚uÊ”iÅ‚Ê”athÌ£ Government</t>
+  </si>
+  <si>
+    <t>Geospatial indicators and metrics for threats to fish habitat in the Fraser River Basin with Thompson-Nicola as a case study</t>
+  </si>
+  <si>
+    <t>West Coast Vancouver Island Fall Chinook</t>
+  </si>
+  <si>
+    <t>The key finding of this project will be the specific differences in dynamics between hatchery and natural-origin San Juan Chinook, and using this information to both improve the survival and health of natural-origin juveniles while producing hatchery fish that complement, rather than compete with, the natural population. These findings may be applicable to other systems, although collecting stock-specific information is critical to ensure that any future "indicator" populations are in fact indicative of dynamics in other systems.
+Future studies should further examine specific indicators of early mortality in juvenile salmon, primarily in the freshwater and estuarine stages which are largely unmonitored by DFO. In addition, consideration should be given as to how hatchery release strategies change the life history dynamics of juvenile salmon.</t>
+  </si>
+  <si>
+    <t>Table 1. Results of total thiamine levels detected in chinook salmon eggs treated or untreated with thiamine. The results shown were the mean of duplicates. Each test represented results of eggs collected from an individual fish of each population. Note that for Cheakamus chinook salmon, each pair of control and treated eggs (same row) was collected from the same fish. All Middle Shuswap chinook salmon were treated with injection prior to spawning, and thus untreated eggs were not available for sampling. The bath-treated eggs were all fertilized, while the untreated eggs, and the injection-treated eggs were not fertilized. 
+Figure 1. Results of linear regression analysis on the total mean thiamine level results reported by SUNY Brockport and PSEC on the same set of chinook salmon eggs. Each dot represents an individual sample. 
+Figure 2. Results of the total thiamine levels in untreated and unfertilized eggs collected from Capilano mid coho (Cap-mid-Coho, n=5), Chilliwack mid coho (Cwk-mid-Coho, n=10), Tenderfoot Cheakamus Chinook (Tdf-Chinook, n=4), Chilliwack fall Chinook (Cwk-Chinook, n=10), Harrison sockeye (Har-Sockeye, n=10), Chilko sockeye (Cko-Sockeye, n=10), Weaver sockeye (Wvr-Sockeye, n=9) and Chehalis pink (Chs-Pink, n=11). Note that the Harrison sockeye eggs were considered not ripe during sample collection; Tenderfoot Cheakamus Chinook data came from results of untreated eggs reported in Table 1. The dash lines represent thiamine level thresholds established by Mantua et al. (2025) to illustrate the likelihood of being impacted by thiamine deficiency: high - unlikely impacted (&gt; 7.7 nmol/g), intermediate - likely impacted (5.9-7.7 nmol/g), low - impacted (2.7-5.9 nmol/g) and critically low - severely impacted (&lt; 2.7 nmol/g). The cross symbol (Ã—) in the box plot indicates mean values within each group.
+Figure 3. Proportion of salmon eggs from different populations measured by the thiamine level thresholds established by Mantua et al. (2025). Different category of total thiamine level represents different likelihood of being impacted by thiamine deficiency: high - unlikely impacted (&gt; 7.7 nmol/g), intermediate - likely impacted (5.9-7.7 nmol/g), low - impacted (2.7-5.9 nmol/g) and critically low - severely impacted (&lt; 2.7 nmol/g). Eggs were collected from different salmon species and population: Capilano mid coho (n=5), Chilliwack mid coho (n=10), Tenderfoot Cheakamus Chinook (n=4), Chilliwack fall Chinook (n=10), Harrison sockeye (n=10), Chilko sockeye (n=10), Weaver sockeye (n=9) and Chehalis pink (n=11).</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -3267,39 +3237,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="23">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3658,6 +3614,24 @@
         <name val="Calibri"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
@@ -3696,29 +3670,35 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C1235FC-468F-46C3-9676-E136DE729105}" name="Table1" displayName="Table1" ref="A1:U44" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
-  <autoFilter ref="A1:U44" xr:uid="{9C1235FC-468F-46C3-9676-E136DE729105}"/>
+  <autoFilter ref="A1:U44" xr:uid="{9C1235FC-468F-46C3-9676-E136DE729105}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="2418"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{21F25E78-D457-418F-9F78-7DE13AE8CD93}" name="source_file" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{B8BCB027-8A7D-4FCE-803F-A296662A280E}" name="extraction_date" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{683393A0-8045-467F-9A16-95D1CB0C532F}" name="project_id" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{5331C13B-A3FC-484A-95E7-7EAD3A2BB00D}" name="project_title" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{65143B71-B457-4DF3-96FB-A320AE4152BD}" name="project_leads" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{0B1052C0-47F1-41AA-B13F-BE70DF38178E}" name="collaborations" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{1204734C-F170-44F7-B4B4-5C53DC28A923}" name="location" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{DB4F19D6-FCB3-4A48-B206-A993711C4060}" name="species" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{3B9CC560-9650-4F10-B6EB-A8BB6D19FD2B}" name="waterbodies" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{3B74A0C4-6035-471F-BA59-5E5296130A6C}" name="life_history" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{83EB77D8-FF38-4BA7-8B8A-C5EB6609BA41}" name="region" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{B5F0F367-295F-4C21-8EF2-8D796262B584}" name="stock" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{592AD976-80C9-41A3-904D-28E27F957093}" name="population" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{0841A155-6170-4816-B52F-62D315F16BB4}" name="cu" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{6A19023B-7495-49F1-A1EC-B098C5E333CF}" name="highlights" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{E075E454-2C61-4348-A20B-0C745E2EC565}" name="background" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{F232593A-A943-4A2F-A957-77EB6182BDA8}" name="methods_findings" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{2F87C396-47EA-4A13-9083-A6C4F71287B3}" name="insights" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{E3203637-205F-4D67-8A5B-15606B06B96D}" name="next_steps" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{71B5C06F-A10D-4B50-AAD8-E218E0D666CD}" name="tables_figures" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{671D065B-E9D7-4645-BF8D-C6523418AA9F}" name="references" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{B8BCB027-8A7D-4FCE-803F-A296662A280E}" name="extraction_date" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{683393A0-8045-467F-9A16-95D1CB0C532F}" name="project_id" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{5331C13B-A3FC-484A-95E7-7EAD3A2BB00D}" name="project_title" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{65143B71-B457-4DF3-96FB-A320AE4152BD}" name="project_leads" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{0B1052C0-47F1-41AA-B13F-BE70DF38178E}" name="collaborations" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{1204734C-F170-44F7-B4B4-5C53DC28A923}" name="location" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{DB4F19D6-FCB3-4A48-B206-A993711C4060}" name="species" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{3B9CC560-9650-4F10-B6EB-A8BB6D19FD2B}" name="waterbodies" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{3B74A0C4-6035-471F-BA59-5E5296130A6C}" name="life_history" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{83EB77D8-FF38-4BA7-8B8A-C5EB6609BA41}" name="region" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{B5F0F367-295F-4C21-8EF2-8D796262B584}" name="stock" dataDxfId="9"/>
+    <tableColumn id="13" xr3:uid="{592AD976-80C9-41A3-904D-28E27F957093}" name="population" dataDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{0841A155-6170-4816-B52F-62D315F16BB4}" name="cu" dataDxfId="7"/>
+    <tableColumn id="15" xr3:uid="{6A19023B-7495-49F1-A1EC-B098C5E333CF}" name="highlights" dataDxfId="6"/>
+    <tableColumn id="16" xr3:uid="{E075E454-2C61-4348-A20B-0C745E2EC565}" name="background" dataDxfId="5"/>
+    <tableColumn id="17" xr3:uid="{F232593A-A943-4A2F-A957-77EB6182BDA8}" name="methods_findings" dataDxfId="4"/>
+    <tableColumn id="18" xr3:uid="{2F87C396-47EA-4A13-9083-A6C4F71287B3}" name="insights" dataDxfId="3"/>
+    <tableColumn id="19" xr3:uid="{E3203637-205F-4D67-8A5B-15606B06B96D}" name="next_steps" dataDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{71B5C06F-A10D-4B50-AAD8-E218E0D666CD}" name="tables_figures" dataDxfId="1"/>
+    <tableColumn id="21" xr3:uid="{671D065B-E9D7-4645-BF8D-C6523418AA9F}" name="references" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4009,7 +3989,7 @@
     <col min="1" max="1" width="13" style="2" customWidth="1"/>
     <col min="2" max="2" width="17.140625" style="6" customWidth="1"/>
     <col min="3" max="3" width="12.140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="96.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="15.140625" style="2" customWidth="1"/>
     <col min="6" max="6" width="15.7109375" style="2" customWidth="1"/>
     <col min="7" max="8" width="11.42578125" style="2"/>
@@ -4093,7 +4073,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
@@ -4134,7 +4114,7 @@
         <v>32</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>33</v>
@@ -4158,7 +4138,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>40</v>
       </c>
@@ -4184,7 +4164,7 @@
         <v>45</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>46</v>
@@ -4193,13 +4173,13 @@
         <v>47</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>48</v>
@@ -4223,7 +4203,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>55</v>
       </c>
@@ -4240,7 +4220,7 @@
         <v>57</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>58</v>
@@ -4249,7 +4229,7 @@
         <v>59</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>60</v>
@@ -4261,19 +4241,19 @@
         <v>61</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="P4" s="1" t="s">
         <v>62</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="R4" s="1" t="s">
         <v>63</v>
@@ -4282,13 +4262,13 @@
         <v>64</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>65</v>
       </c>
@@ -4305,10 +4285,10 @@
         <v>67</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>68</v>
@@ -4340,10 +4320,10 @@
         <v>75</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>76</v>
       </c>
@@ -4381,7 +4361,7 @@
         <v>84</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>85</v>
@@ -4393,7 +4373,7 @@
         <v>87</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="R6" s="1" t="s">
         <v>88</v>
@@ -4408,74 +4388,74 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:21" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="8">
         <v>46083</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="4">
         <v>2403</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="L7" s="1" t="s">
+      <c r="K7" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="L7" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="M7" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="N7" s="5" t="s">
+        <v>638</v>
+      </c>
+      <c r="O7" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="O7" s="1" t="s">
+      <c r="P7" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="P7" s="1" t="s">
+      <c r="Q7" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="R7" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="S7" s="5" t="s">
+        <v>639</v>
+      </c>
+      <c r="T7" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="U7" s="4" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="U7" s="1" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="B8" s="7">
         <v>46083</v>
@@ -4484,63 +4464,63 @@
         <v>2404</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="H8" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="J8" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="U8" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="R8" s="1" t="s">
+    </row>
+    <row r="9" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="B9" s="7">
         <v>46083</v>
@@ -4549,63 +4529,63 @@
         <v>2405</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="G9" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>68</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="J9" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="O9" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="P9" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="L9" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="O9" s="1" t="s">
+      <c r="Q9" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="R9" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="P9" s="1" t="s">
+      <c r="S9" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="Q9" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="R9" s="1" t="s">
+      <c r="T9" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="S9" s="1" t="s">
+      <c r="U9" s="1" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="U9" s="1" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="B10" s="7">
         <v>46083</v>
@@ -4614,63 +4594,63 @@
         <v>2406</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="H10" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="G10" s="1" t="s">
+      <c r="J10" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="I10" s="1" t="s">
+      <c r="L10" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="P10" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="K10" s="1" t="s">
+      <c r="Q10" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="R10" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="L10" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>546</v>
-      </c>
-      <c r="P10" s="1" t="s">
+      <c r="S10" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="Q10" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="R10" s="1" t="s">
+      <c r="T10" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="S10" s="1" t="s">
+      <c r="U10" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="T10" s="1" t="s">
+    </row>
+    <row r="11" spans="1:21" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="U10" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="B11" s="8">
         <v>46083</v>
@@ -4679,63 +4659,63 @@
         <v>2407</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>561</v>
-      </c>
-      <c r="G11" s="4" t="s">
+      <c r="I11" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="J11" s="4" t="s">
         <v>141</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>143</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>58</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="N11" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="P11" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="O11" s="4" t="s">
+      <c r="Q11" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="P11" s="4" t="s">
+      <c r="R11" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="Q11" s="4" t="s">
+      <c r="S11" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="R11" s="4" t="s">
+      <c r="T11" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="U11" s="4" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="S11" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="T11" s="4" t="s">
-        <v>562</v>
-      </c>
-      <c r="U11" s="4" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="B12" s="7">
         <v>46083</v>
@@ -4744,19 +4724,19 @@
         <v>2408</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>57</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>58</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
@@ -4766,35 +4746,35 @@
         <v>58</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="R12" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="P12" s="1" t="s">
+      <c r="S12" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="Q12" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="R12" s="1" t="s">
+      <c r="T12" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="S12" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="T12" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="U12" s="1" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>158</v>
       </c>
       <c r="B13" s="7">
         <v>46083</v>
@@ -4803,61 +4783,61 @@
         <v>2409</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>161</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
         <v>68</v>
       </c>
       <c r="I13" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="M13" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="N13" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="O13" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="M13" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="N13" s="1" t="s">
+      <c r="P13" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="O13" s="1" t="s">
+      <c r="Q13" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="P13" s="1" t="s">
+      <c r="R13" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="Q13" s="1" t="s">
+      <c r="S13" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="R13" s="1" t="s">
+      <c r="T13" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="S13" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="T13" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="U13" s="1" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="B14" s="7">
         <v>46083</v>
@@ -4866,22 +4846,22 @@
         <v>2410</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>32</v>
@@ -4893,36 +4873,36 @@
         <v>32</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="N14" s="1" t="s">
         <v>32</v>
       </c>
       <c r="O14" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q14" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="P14" s="1" t="s">
+      <c r="R14" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="Q14" s="1" t="s">
+      <c r="S14" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="R14" s="1" t="s">
+      <c r="T14" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="S14" s="1" t="s">
+      <c r="U14" s="1" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="T14" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="U14" s="1" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>182</v>
       </c>
       <c r="B15" s="7">
         <v>46083</v>
@@ -4931,63 +4911,63 @@
         <v>2412</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="H15" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="I15" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="J15" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>58</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="O15" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="S15" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="P15" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="R15" s="1" t="s">
+      <c r="T15" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>191</v>
       </c>
       <c r="B16" s="7">
         <v>46083</v>
@@ -4996,63 +4976,63 @@
         <v>2413</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="G16" s="1" t="s">
+      <c r="I16" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="K16" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="I16" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="J16" s="1" t="s">
+      <c r="L16" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="O16" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="P16" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="L16" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="O16" s="1" t="s">
+      <c r="Q16" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="P16" s="1" t="s">
+      <c r="R16" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="Q16" s="1" t="s">
+      <c r="S16" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="R16" s="1" t="s">
+      <c r="T16" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="U16" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="S16" s="1" t="s">
+    </row>
+    <row r="17" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="U16" s="1" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>204</v>
       </c>
       <c r="B17" s="7">
         <v>46083</v>
@@ -5061,63 +5041,63 @@
         <v>2416</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="G17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="K17" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L17" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="M17" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="P17" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="L17" s="1" t="s">
+      <c r="Q17" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="M17" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="O17" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="P17" s="1" t="s">
+      <c r="R17" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="Q17" s="1" t="s">
+      <c r="S17" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="R17" s="1" t="s">
+      <c r="T17" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="S17" s="1" t="s">
+      <c r="U17" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="T17" s="1" t="s">
+    </row>
+    <row r="18" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="U17" s="1" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>218</v>
       </c>
       <c r="B18" s="7">
         <v>46083</v>
@@ -5126,63 +5106,63 @@
         <v>2417</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="G18" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="I18" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="J18" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="K18" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="I18" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="J18" s="1" t="s">
+      <c r="L18" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="M18" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="O18" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="L18" s="1" t="s">
+      <c r="P18" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="M18" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="O18" s="1" t="s">
+      <c r="Q18" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="S18" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="P18" s="1" t="s">
+      <c r="T18" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>228</v>
-      </c>
-      <c r="Q18" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="R18" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="S18" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="T18" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="U18" s="1" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>230</v>
       </c>
       <c r="B19" s="7">
         <v>46083</v>
@@ -5191,63 +5171,63 @@
         <v>2418</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="F19" s="1" t="s">
+      <c r="I19" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="T19" s="10" t="s">
+        <v>640</v>
+      </c>
+      <c r="U19" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="O19" s="1" t="s">
+    </row>
+    <row r="20" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="P19" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="Q19" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="R19" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="S19" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="T19" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="U19" s="1" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>238</v>
       </c>
       <c r="B20" s="7">
         <v>46083</v>
@@ -5256,63 +5236,63 @@
         <v>2421</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="J20" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>241</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>58</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="O20" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="R20" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="P20" s="1" t="s">
+      <c r="S20" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="Q20" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="R20" s="1" t="s">
+      <c r="T20" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>244</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="T20" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="U20" s="1" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>246</v>
       </c>
       <c r="B21" s="7">
         <v>46083</v>
@@ -5321,63 +5301,63 @@
         <v>2422</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="J21" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="I21" s="1" t="s">
+      <c r="K21" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L21" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="M21" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="O21" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="L21" s="1" t="s">
+      <c r="P21" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="M21" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="O21" s="1" t="s">
+      <c r="Q21" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="P21" s="1" t="s">
+      <c r="R21" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="Q21" s="1" t="s">
+      <c r="S21" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="R21" s="1" t="s">
+      <c r="T21" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="S21" s="1" t="s">
+      <c r="U21" s="1" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="T21" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="U21" s="1" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>258</v>
       </c>
       <c r="B22" s="7">
         <v>46083</v>
@@ -5386,63 +5366,63 @@
         <v>2424</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="I22" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="H22" s="1" t="s">
+      <c r="J22" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="K22" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="L22" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="O22" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="P22" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="R22" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="L22" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="O22" s="1" t="s">
+      <c r="S22" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="P22" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="Q22" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="R22" s="1" t="s">
+      <c r="T22" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="S22" s="1" t="s">
+      <c r="U22" s="1" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>267</v>
-      </c>
-      <c r="T22" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="U22" s="1" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>269</v>
       </c>
       <c r="B23" s="7">
         <v>46083</v>
@@ -5450,62 +5430,64 @@
       <c r="C23" s="1">
         <v>2425</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="9" t="s">
+        <v>637</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>544</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="I23" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="J23" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1" t="s">
+      <c r="K23" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="L23" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="N23" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="I23" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="J23" s="1" t="s">
+      <c r="O23" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="P23" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="L23" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="N23" s="1" t="s">
+      <c r="Q23" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="O23" s="1" t="s">
+      <c r="R23" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="P23" s="1" t="s">
+      <c r="S23" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="Q23" s="1" t="s">
+      <c r="T23" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="U23" s="1" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="S23" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="T23" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="U23" s="1" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>282</v>
       </c>
       <c r="B24" s="7">
         <v>46083</v>
@@ -5514,63 +5496,63 @@
         <v>2426</v>
       </c>
       <c r="D24" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="I24" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="G24" s="1" t="s">
+      <c r="J24" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="K24" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="L24" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="M24" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="N24" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="L24" s="1" t="s">
+      <c r="O24" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="M24" s="1" t="s">
+      <c r="P24" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="R24" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="N24" s="1" t="s">
+      <c r="S24" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="O24" s="1" t="s">
+      <c r="T24" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="P24" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="Q24" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="R24" s="1" t="s">
+      <c r="U24" s="1" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="S24" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="T24" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="U24" s="1" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>297</v>
       </c>
       <c r="B25" s="7">
         <v>46083</v>
@@ -5579,63 +5561,63 @@
         <v>2427</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="K25" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="G25" s="1" t="s">
+      <c r="L25" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="O25" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="H25" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="J25" s="1" t="s">
+      <c r="P25" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="Q25" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="R25" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="L25" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="O25" s="1" t="s">
+      <c r="S25" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="P25" s="1" t="s">
+      <c r="T25" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="Q25" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="R25" s="1" t="s">
+      <c r="U25" s="1" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="S25" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="T25" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="U25" s="1" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>307</v>
       </c>
       <c r="B26" s="7">
         <v>46083</v>
@@ -5644,63 +5626,63 @@
         <v>2430</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="K26" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="I26" s="1" t="s">
+      <c r="L26" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="M26" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="N26" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="O26" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="L26" s="1" t="s">
+      <c r="P26" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="S26" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="M26" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="N26" s="1" t="s">
+      <c r="T26" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="O26" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="P26" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="Q26" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="R26" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="S26" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="T26" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="U26" s="1" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>316</v>
       </c>
       <c r="B27" s="7">
         <v>46083</v>
@@ -5709,63 +5691,63 @@
         <v>2432</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="P27" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>611</v>
-      </c>
-      <c r="G27" s="1" t="s">
+      <c r="Q27" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="H27" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="O27" s="1" t="s">
+      <c r="R27" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="P27" s="1" t="s">
+      <c r="S27" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="Q27" s="1" t="s">
+      <c r="T27" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="R27" s="1" t="s">
+      <c r="U27" s="1" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="S27" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="T27" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="U27" s="1" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>325</v>
       </c>
       <c r="B28" s="7">
         <v>46083</v>
@@ -5774,63 +5756,63 @@
         <v>2433</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="P28" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="F28" s="1" t="s">
+      <c r="Q28" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="R28" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="H28" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="M28" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="O28" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="P28" s="1" t="s">
+      <c r="S28" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="Q28" s="1" t="s">
+      <c r="T28" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="R28" s="1" t="s">
+      <c r="U28" s="1" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="S28" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="T28" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="U28" s="1" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>334</v>
       </c>
       <c r="B29" s="7">
         <v>46083</v>
@@ -5839,63 +5821,63 @@
         <v>2434</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="H29" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="I29" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="J29" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="K29" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="L29" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="H29" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="I29" s="1" t="s">
+      <c r="M29" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="N29" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="K29" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="L29" s="1" t="s">
+      <c r="O29" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="P29" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="M29" s="1" t="s">
+      <c r="Q29" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="N29" s="1" t="s">
+      <c r="R29" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="O29" s="1" t="s">
-        <v>613</v>
-      </c>
-      <c r="P29" s="1" t="s">
+      <c r="S29" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="Q29" s="1" t="s">
+      <c r="T29" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="R29" s="1" t="s">
+      <c r="U29" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="S29" s="1" t="s">
+    </row>
+    <row r="30" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="T29" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="U29" s="1" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>350</v>
       </c>
       <c r="B30" s="7">
         <v>46083</v>
@@ -5904,63 +5886,63 @@
         <v>2435</v>
       </c>
       <c r="D30" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="H30" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="I30" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="J30" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="K30" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="L30" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="M30" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="N30" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="L30" s="1" t="s">
+      <c r="O30" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="M30" s="1" t="s">
+      <c r="P30" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="N30" s="1" t="s">
+      <c r="Q30" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="O30" s="1" t="s">
+      <c r="R30" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="P30" s="1" t="s">
+      <c r="S30" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="Q30" s="1" t="s">
+      <c r="T30" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="R30" s="1" t="s">
+      <c r="U30" s="1" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>365</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="T30" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="U30" s="1" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>368</v>
       </c>
       <c r="B31" s="7">
         <v>46083</v>
@@ -5969,63 +5951,63 @@
         <v>2436</v>
       </c>
       <c r="D31" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="I31" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="G31" s="1" t="s">
+      <c r="J31" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="K31" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="L31" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="N31" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="O31" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="P31" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="L31" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="N31" s="1" t="s">
+      <c r="Q31" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="O31" s="1" t="s">
+      <c r="R31" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="P31" s="1" t="s">
+      <c r="S31" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="Q31" s="1" t="s">
+      <c r="T31" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="R31" s="1" t="s">
+      <c r="U31" s="1" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="S31" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="T31" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="U31" s="1" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>383</v>
       </c>
       <c r="B32" s="7">
         <v>46083</v>
@@ -6034,63 +6016,63 @@
         <v>2437</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="I32" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="J32" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="H32" s="1" t="s">
+      <c r="K32" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="L32" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="M32" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="N32" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="L32" s="1" t="s">
+      <c r="O32" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="P32" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="M32" s="1" t="s">
+      <c r="Q32" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="N32" s="1" t="s">
+      <c r="R32" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="O32" s="1" t="s">
-        <v>616</v>
-      </c>
-      <c r="P32" s="1" t="s">
+      <c r="S32" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="Q32" s="1" t="s">
+      <c r="T32" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="R32" s="1" t="s">
+      <c r="U32" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="S32" s="1" t="s">
+    </row>
+    <row r="33" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>396</v>
-      </c>
-      <c r="T32" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="U32" s="1" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>399</v>
       </c>
       <c r="B33" s="7">
         <v>46083</v>
@@ -6099,63 +6081,63 @@
         <v>2439</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="H33" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="I33" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="K33" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="F33" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="G33" s="1" t="s">
+      <c r="L33" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="O33" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="P33" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="Q33" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="I33" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="K33" s="1" t="s">
+      <c r="R33" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="L33" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="M33" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="O33" s="1" t="s">
+      <c r="S33" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="P33" s="1" t="s">
-        <v>618</v>
-      </c>
-      <c r="Q33" s="1" t="s">
+      <c r="T33" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="R33" s="1" t="s">
+      <c r="U33" s="1" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>407</v>
-      </c>
-      <c r="S33" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="T33" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="U33" s="1" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>410</v>
       </c>
       <c r="B34" s="7">
         <v>46083</v>
@@ -6164,63 +6146,63 @@
         <v>2442</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="J34" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="K34" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="F34" s="1" t="s">
-        <v>620</v>
-      </c>
-      <c r="G34" s="1" t="s">
+      <c r="L34" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="H34" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="I34" s="1" t="s">
+      <c r="M34" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="J34" s="1" t="s">
+      <c r="N34" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="K34" s="1" t="s">
+      <c r="O34" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="L34" s="1" t="s">
+      <c r="P34" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="M34" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="N34" s="1" t="s">
+      <c r="Q34" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="R34" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="O34" s="1" t="s">
+      <c r="S34" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="P34" s="1" t="s">
+      <c r="T34" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="Q34" s="1" t="s">
-        <v>621</v>
-      </c>
-      <c r="R34" s="1" t="s">
+      <c r="U34" s="1" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="S34" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="T34" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="U34" s="1" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>423</v>
       </c>
       <c r="B35" s="7">
         <v>46083</v>
@@ -6229,63 +6211,63 @@
         <v>2443</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>68</v>
       </c>
       <c r="I35" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="O35" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="J35" s="1" t="s">
+      <c r="P35" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="K35" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="M35" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="N35" s="1" t="s">
+      <c r="Q35" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="O35" s="1" t="s">
+      <c r="R35" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="P35" s="1" t="s">
+      <c r="S35" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="Q35" s="1" t="s">
+      <c r="T35" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="U35" s="1" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>432</v>
-      </c>
-      <c r="R35" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="S35" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="T35" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="U35" s="1" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>435</v>
       </c>
       <c r="B36" s="7">
         <v>46083</v>
@@ -6294,63 +6276,63 @@
         <v>2447</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>81</v>
       </c>
       <c r="I36" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="O36" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="J36" s="1" t="s">
+      <c r="P36" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="K36" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="M36" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="N36" s="1" t="s">
+      <c r="Q36" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="O36" s="1" t="s">
+      <c r="R36" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="P36" s="1" t="s">
+      <c r="S36" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="Q36" s="1" t="s">
+      <c r="T36" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="R36" s="1" t="s">
+      <c r="U36" s="1" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
         <v>444</v>
-      </c>
-      <c r="S36" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="T36" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="U36" s="1" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>447</v>
       </c>
       <c r="B37" s="7">
         <v>46083</v>
@@ -6359,63 +6341,63 @@
         <v>2448</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>58</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I37" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="M37" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="J37" s="1" t="s">
+      <c r="N37" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="O37" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="P37" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="L37" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="M37" s="1" t="s">
+      <c r="Q37" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="N37" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="O37" s="1" t="s">
+      <c r="R37" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="S37" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="P37" s="1" t="s">
+      <c r="T37" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="Q37" s="1" t="s">
+      <c r="U37" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="R37" s="1" t="s">
-        <v>626</v>
-      </c>
-      <c r="S37" s="1" t="s">
+    </row>
+    <row r="38" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
         <v>458</v>
-      </c>
-      <c r="T37" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="U37" s="1" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>461</v>
       </c>
       <c r="B38" s="7">
         <v>46083</v>
@@ -6424,63 +6406,63 @@
         <v>2449</v>
       </c>
       <c r="D38" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="J38" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="K38" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="H38" s="1" t="s">
+      <c r="L38" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="I38" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="J38" s="1" t="s">
+      <c r="M38" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="N38" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="L38" s="1" t="s">
+      <c r="O38" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="M38" s="1" t="s">
+      <c r="P38" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="N38" s="1" t="s">
+      <c r="Q38" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="O38" s="1" t="s">
+      <c r="R38" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="P38" s="1" t="s">
+      <c r="S38" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="Q38" s="1" t="s">
+      <c r="T38" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="R38" s="1" t="s">
+      <c r="U38" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="S38" s="1" t="s">
+    </row>
+    <row r="39" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
         <v>474</v>
-      </c>
-      <c r="T38" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="U38" s="1" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>477</v>
       </c>
       <c r="B39" s="7">
         <v>46083</v>
@@ -6489,63 +6471,63 @@
         <v>2451</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>81</v>
       </c>
       <c r="I39" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="P39" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="J39" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="M39" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="N39" s="1" t="s">
+      <c r="Q39" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="O39" s="1" t="s">
+      <c r="R39" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="S39" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="P39" s="1" t="s">
+      <c r="T39" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="Q39" s="1" t="s">
+      <c r="U39" s="1" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
         <v>483</v>
-      </c>
-      <c r="R39" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="S39" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="T39" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="U39" s="1" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>486</v>
       </c>
       <c r="B40" s="7">
         <v>46083</v>
@@ -6554,63 +6536,63 @@
         <v>2452</v>
       </c>
       <c r="D40" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="L40" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="I40" s="1" t="s">
+      <c r="M40" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="J40" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="K40" s="1" t="s">
+      <c r="N40" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="L40" s="1" t="s">
+      <c r="O40" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="M40" s="1" t="s">
+      <c r="P40" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="N40" s="1" t="s">
+      <c r="Q40" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="R40" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="O40" s="1" t="s">
+      <c r="S40" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="P40" s="1" t="s">
+      <c r="T40" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="Q40" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="R40" s="1" t="s">
+      <c r="U40" s="1" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
         <v>495</v>
-      </c>
-      <c r="S40" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="T40" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="U40" s="1" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>498</v>
       </c>
       <c r="B41" s="7">
         <v>46083</v>
@@ -6619,63 +6601,63 @@
         <v>2504</v>
       </c>
       <c r="D41" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="H41" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="I41" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="G41" s="1" t="s">
+      <c r="J41" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="K41" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="L41" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="J41" s="1" t="s">
+      <c r="M41" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="K41" s="1" t="s">
+      <c r="N41" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="O41" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="L41" s="1" t="s">
+      <c r="P41" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="M41" s="1" t="s">
+      <c r="Q41" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="N41" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="O41" s="1" t="s">
+      <c r="R41" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="P41" s="1" t="s">
+      <c r="S41" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="Q41" s="1" t="s">
+      <c r="T41" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="R41" s="1" t="s">
+      <c r="U41" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="S41" s="1" t="s">
+    </row>
+    <row r="42" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
         <v>512</v>
-      </c>
-      <c r="T41" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="U41" s="1" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>515</v>
       </c>
       <c r="B42" s="7">
         <v>46083</v>
@@ -6684,63 +6666,63 @@
         <v>2513</v>
       </c>
       <c r="D42" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="O42" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="E42" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="G42" s="1" t="s">
+      <c r="P42" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="H42" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="L42" s="1" t="s">
+      <c r="Q42" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="R42" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="S42" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="M42" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="N42" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="O42" s="1" t="s">
+      <c r="T42" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="P42" s="1" t="s">
+      <c r="U42" s="1" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
         <v>520</v>
-      </c>
-      <c r="Q42" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="R42" s="1" t="s">
-        <v>634</v>
-      </c>
-      <c r="S42" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="T42" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="U42" s="1" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>523</v>
       </c>
       <c r="B43" s="7">
         <v>46083</v>
@@ -6749,22 +6731,22 @@
         <v>2545</v>
       </c>
       <c r="D43" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="H43" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="I43" s="1" t="s">
         <v>526</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>529</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>32</v>
@@ -6782,30 +6764,30 @@
         <v>32</v>
       </c>
       <c r="O43" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="P43" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="Q43" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="R43" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="P43" s="1" t="s">
+      <c r="S43" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="Q43" s="1" t="s">
+      <c r="T43" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="R43" s="1" t="s">
+      <c r="U43" s="1" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
         <v>533</v>
-      </c>
-      <c r="S43" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="T43" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="U43" s="1" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>536</v>
       </c>
       <c r="B44" s="7">
         <v>46083</v>
@@ -6814,13 +6796,13 @@
         <v>3682</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
@@ -6833,25 +6815,25 @@
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
       <c r="O44" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="P44" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="Q44" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="R44" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="P44" s="1" t="s">
+      <c r="S44" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="Q44" s="1" t="s">
+      <c r="T44" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="R44" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="S44" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="T44" s="1" t="s">
-        <v>545</v>
-      </c>
       <c r="U44" s="1" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/pssi_form_data_altered.xlsx
+++ b/data/processed/pssi_form_data_altered.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ennsj\Documents\PSSI-final-tech-report\data\processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{912B8EAF-0CE7-443F-872A-ED495F3C6D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87A352C6-1346-4785-B4B8-3962E1484FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,9 +104,6 @@
     <t>0000</t>
   </si>
   <si>
-    <t>Enhanced Mark Selective Fishery (MSF) Monitoring (including a Chinook Reference Fishery)</t>
-  </si>
-  <si>
     <t>Erin Rechisky; Philip Lemp</t>
   </si>
   <si>
@@ -222,9 +219,6 @@
   </si>
   <si>
     <t>2400 PSSI Science Project Reporting_Long_Project.docx</t>
-  </si>
-  <si>
-    <t>Assessment of SEP Chinook and Coho broodstock ELISA screening data by modelling for explanatory variables, and yearling DFAT prevalence data by modelling for predictive variables.</t>
   </si>
   <si>
     <t>Amy Long</t>
@@ -260,9 +254,6 @@
   </si>
   <si>
     <t>2401 PSSI final report-Garver.docx</t>
-  </si>
-  <si>
-    <t>Epidemiological modeling of infectious hematopoietic necrosis virus in Sockeye salmon</t>
   </si>
   <si>
     <t>Kyle Garver</t>
@@ -367,9 +358,6 @@
     <t>2403 PSSI Science Project Reporting - San Juan.docx</t>
   </si>
   <si>
-    <t>San Juan River Adult and Juvenile Assessment Program</t>
-  </si>
-  <si>
     <t>Katie Davidson</t>
   </si>
   <si>
@@ -440,9 +428,6 @@
   </si>
   <si>
     <t>Biological models to support prioritizing salmon stocks under future climates</t>
-  </si>
-  <si>
-    <t>Jan Finke, Travis Tai, Brendan Connors, Cameron Freshwater, Patrick Thompson</t>
   </si>
   <si>
     <t>Amber Holdsworth and Angelica Pena (Ocean Sciences Division); Dan Selbie, Howard Stiff, Greig Oldford, and Josie Iacarella (Ecosystem Science Division)</t>
@@ -580,9 +565,6 @@
   </si>
   <si>
     <t>2408 PSSI Science Project Reporting_Long_Project.docx</t>
-  </si>
-  <si>
-    <t>Improvement, Expansion and Modernization of Salmonid Health Diagnostic Services For Optimizing Salmonid Hatchery Health Management</t>
   </si>
   <si>
     <t>See Supplemental Table 1</t>
@@ -719,9 +701,6 @@
     <t>2412 PSSI Science Project Reporting_Pearce_Mackenzie_Forster_Neville.docx</t>
   </si>
   <si>
-    <t>Investigation of the impacts of singular and coinciding acute climate stressors on the nutritional quality of the pteropod *Limacina helicina*, a juvenile Pacific salmon dietary species</t>
-  </si>
-  <si>
     <t>Chris Pearce, Clara Mackenzie, Ian Forster (DFO, Nearshore Ecosystems Section)</t>
   </si>
   <si>
@@ -1108,11 +1087,6 @@
     <t>2426 PSSI Science Project Reporting Template Oct2025_Sakinaw Sockeye_KP-KF.docx</t>
   </si>
   <si>
-    <t>Sakinaw sockeye juvenile research on measures to increase marine survival
----
-Sakinaw Sockeye Juvenile Research on Measures to Increase Marine Survival</t>
-  </si>
-  <si>
     <t>Kevin Pellett, Karalea Filipovic, Nicolette Watson</t>
   </si>
   <si>
@@ -1362,10 +1336,6 @@
   </si>
   <si>
     <t>2435 PSSI Science Project Reporting - 2453 and 2435.docx</t>
-  </si>
-  <si>
-    <t>Epigenetic variation between hatchery- and natural-origin Canadian Chinook salmon
-intergeneration transfer and parental origins of DNA methylation variation in coho and Chinook salmon (2435 and 2453)</t>
   </si>
   <si>
     <t>Timothy Healy, Kyle Wellband, Eric Rondeau</t>
@@ -1881,9 +1851,6 @@
   </si>
   <si>
     <t>2449 PSSI Science Project Reporting- salmonMSE.docx</t>
-  </si>
-  <si>
-    <t>A decision-support tool that considers harvest, hatchery, and habitat management levers to support implementation of the *Fisheries Act* for Pacific salmon</t>
   </si>
   <si>
     <t>Carrie Holt, Catarina Wor and Brendan Connors</t>
@@ -2847,9 +2814,6 @@
     <t>Chinook Salmon *OncorhynchusÂ tshawytscha*</t>
   </si>
   <si>
-    <t>Doug Braun, Josephine Iacarella, SecwÃ©pemc Fisheries Commission</t>
-  </si>
-  <si>
     <t>Low flows during summer months can be an important bottleneck for stream-rearing rearing salmon. Determining how much water fish need is therefore a critical management question, especially given rising human water use and climate warming. Elevated water temperature is another threat facing stream-rearing salmon that is often linked to low flows. However, conventional modelling tools for determining instream flow needs have generally not explicitly considered temperature. This is a gap for management as it is unclear if current instream flow assessments will apply in a warmer future.
 This project developed an analytical framework to integrate water temperature into habitat simulation models, a widely used tool for determining instream flow needs. We used a bioenergetics framework that relates channel hydraulics (e.g., depth and velocity) and temperature to the daily energy balance of juvenile salmonids. We then applied the approach to 17 coho-rearing streams across the North Thompson watershed, interior BC. This work was collaborative with SecwÃ©pemc Fisheries Commission and Simpcw First Nation and will inform instream flow management through the lens of climate change.</t>
   </si>
@@ -2875,9 +2839,6 @@
 Iacarella, J.C. and Weller, J.D., 2023. Predicting favourable streams for anadromous salmon spawning and natal rearing under climate change.Â Can. J. Fish. Aquat. Sci.,Â 81(1), pp.1-13. doi:10.1139/cjfas-2023-0096
 Iacarella, J.C., Paterson, K., Potapova, A., and Weller, J.D. 2025. Geospatial Indicators and Metrics for Threats to Fish Habitat in the Fraser River Basin with Thompson-Nicola as a Case Study. DFO Can. Sci. Advis. Sec. Res. Doc. 2025/013. xiii + 126 p.
 Rosenfeld, J., Gonzalez-Espinosa, P., Jarvis, L., Enders, E., Bayly, M., Paul, A., MacPherson, L., Moore, J., Sullivan, M., Ulaski, M., and Wilson, K. 2022. Stressor-response functions as a generalizable model for context dependence. Trends Ecol. Evolut. 37: 1032-1035. doi:10.1016/j.tree.2022.09.010</t>
-  </si>
-  <si>
-    <t>shÃ­shÃ¡lh Nation</t>
   </si>
   <si>
     <t>Sakinaw sockeye have been listed as endangered with COSEWIC since 2003, and a *Species at Risk Act* Recovery Potential Assessment (RPA) was completed in 2017 (Ramshaw et al. 2019). The RPA cited low marine survival as the greatest limiting factor in recovery, with predator abundance and assumed predation on smolts and adults ranked as high risk, with a critical level of impact. Perpetually low marine survivals are preventing recovery such that the persistence of the population is entirely dependent on a captive brood program.
@@ -2935,9 +2896,6 @@
 SONAR data was manually reviewed and edited using Echoview software to remove noise, and echo integrated in 1 hour x 1 m range cells (side-looking) or 1 hour x 0.2 m range cells (up-looking). The results were exported as csv files, and all echo integration csv files belonging to the same transducer and site were concatenated for further analysis in Microsoft Excel. Excel was then used to convert the echo integration results to smolt passage estimates, which were then compared to the estimates generated at the Chilko River smolt enumeration fence.
 In 2023 and 2024 (2025 results pending), daily estimates of smolt passage showed close correspondence (5% in 2023, 9% in 2024) between fence counts and independent acoustic estimates both in time and magnitude. In the first year of the study (2022), daily SONAR estimates were in good agreement with the fence counts over the first 9 days of the study, but consistently higher over the last 9 days (May 3rd and thereafter). At present, the source of this divergence is unclear.
 This project is one of few that have used split-beam SONARs configured in this manner to enumerate outmigrating salmon smolts. While further testing needs to be conducted in both the Chilko River where the study was conducted, and in other candidate systems, the preliminary results of this study are promising. These methods could be modified and applied to a variety of salmon stock assessment programs to gain crucial information on survival in the early freshwater life stages (egg to smolt survival), however, considerable planning and care needs to be taken when selecting a suitable site.</t>
-  </si>
-  <si>
-    <t>StÃ©phane Gauthier</t>
   </si>
   <si>
     <t>Follow The fish team</t>
@@ -3171,9 +3129,6 @@
 Figure 3. 2022 daily estimates of Chilko River Sockeye smolt passage: side-looking SONAR estimates versus fence counts.</t>
   </si>
   <si>
-    <t>Ahousaht First Nation; Coal Harbour Ltd.; British Columbia Conservation Foundation; Cedar Coast Field Station; Charter Tofino; Ditidaht First Nation; Ehattesaht/Chinehkint First Nation; Ha'oom Fisheries Society; Hesquiaht First Nation; HupaÄasath First Nation; Huu-ay-aht First Nations; The Juanes Lab (University of Victoria); Ka:'yu:'k't'h'/Che:k:tles7et'h' First Nations; LGL Limited; Maaqutusiis Hahoulthee Stewardship Society; M.C. Wright and Associates Ltd.; Mowachaht-Muchalaht First Nations; Nootka Sound Watershed Society; Nuu-Chah-Nulth Tribal Council; Nuchatlaht Tribe; Pacheedaht First Nation; Pacific Salmon Foundation; Quatsino First Nation; Redd Fish Restoration Society; Thornton Creek Enhancement Society; Tla-o-qui-aht First Nation; Toquaht Nation; Tseshaht First Nation; T'Sou-ke Nation; Uchucklesaht Tribe; and YuuÅ‚uÊ”iÅ‚Ê”athÌ£ Government</t>
-  </si>
-  <si>
     <t>Geospatial indicators and metrics for threats to fish habitat in the Fraser River Basin with Thompson-Nicola as a case study</t>
   </si>
   <si>
@@ -3188,6 +3143,70 @@
 Figure 1. Results of linear regression analysis on the total mean thiamine level results reported by SUNY Brockport and PSEC on the same set of chinook salmon eggs. Each dot represents an individual sample. 
 Figure 2. Results of the total thiamine levels in untreated and unfertilized eggs collected from Capilano mid coho (Cap-mid-Coho, n=5), Chilliwack mid coho (Cwk-mid-Coho, n=10), Tenderfoot Cheakamus Chinook (Tdf-Chinook, n=4), Chilliwack fall Chinook (Cwk-Chinook, n=10), Harrison sockeye (Har-Sockeye, n=10), Chilko sockeye (Cko-Sockeye, n=10), Weaver sockeye (Wvr-Sockeye, n=9) and Chehalis pink (Chs-Pink, n=11). Note that the Harrison sockeye eggs were considered not ripe during sample collection; Tenderfoot Cheakamus Chinook data came from results of untreated eggs reported in Table 1. The dash lines represent thiamine level thresholds established by Mantua et al. (2025) to illustrate the likelihood of being impacted by thiamine deficiency: high - unlikely impacted (&gt; 7.7 nmol/g), intermediate - likely impacted (5.9-7.7 nmol/g), low - impacted (2.7-5.9 nmol/g) and critically low - severely impacted (&lt; 2.7 nmol/g). The cross symbol (Ã—) in the box plot indicates mean values within each group.
 Figure 3. Proportion of salmon eggs from different populations measured by the thiamine level thresholds established by Mantua et al. (2025). Different category of total thiamine level represents different likelihood of being impacted by thiamine deficiency: high - unlikely impacted (&gt; 7.7 nmol/g), intermediate - likely impacted (5.9-7.7 nmol/g), low - impacted (2.7-5.9 nmol/g) and critically low - severely impacted (&lt; 2.7 nmol/g). Eggs were collected from different salmon species and population: Capilano mid coho (n=5), Chilliwack mid coho (n=10), Tenderfoot Cheakamus Chinook (n=4), Chilliwack fall Chinook (n=10), Harrison sockeye (n=10), Chilko sockeye (n=10), Weaver sockeye (n=9) and Chehalis pink (n=11).</t>
+  </si>
+  <si>
+    <t>shíshálh Nation</t>
+  </si>
+  <si>
+    <t>Sakinaw sockeye juvenile research on measures to increase marine survival</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Investigation of the impacts of singular and coinciding acute climate stressors on the nutritional quality of the pteropod </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Limacina helicina</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>, a juvenile Pacific salmon dietary species</t>
+    </r>
+  </si>
+  <si>
+    <t>Epigenetic variation between hatchery- and natural-origin Canadian Chinook salmon intergeneration transfer and parental origins of DNA methylation variation in coho and Chinook salmon (2435 and 2453)</t>
+  </si>
+  <si>
+    <t>A decision-support tool that considers harvest, hatchery, and habitat management levers to support implementation of the Fisheries Act for Pacific salmon</t>
+  </si>
+  <si>
+    <t>Jan Finke, Travis Tai, Brendan Connors, 
+Cameron Freshwater, Patrick Thompson</t>
+  </si>
+  <si>
+    <t>Stéphane Gauthier</t>
+  </si>
+  <si>
+    <t>Ahousaht First Nation; Coal Harbour Ltd.; British Columbia Conservation Foundation; Cedar Coast Field Station; Charter Tofino; Ditidaht First Nation; Ehattesaht/Chinehkint First Nation; Ha’oom Fisheries Society; Hesquiaht First Nation; Hupačasath First Nation; Huu-ay-aht First Nations; The Juanes Lab (University of Victoria); Ka:’yu:’k’t’h’/Che:k:tles7et’h’ First Nations; LGL Limited; Maaqutusiis Hahoulthee Stewardship Society; M.C. Wright and Associates Ltd.; Mowachaht-Muchalaht First Nations; Nootka Sound Watershed Society; Nuu-Chah-Nulth Tribal Council; Nuchatlaht Tribe; Pacheedaht First Nation; Pacific Salmon Foundation; Quatsino First Nation; Redd Fish Restoration Society; Thornton Creek Enhancement Society; Tla-o-qui-aht First Nation; Toquaht Nation; Tseshaht First Nation; T’Sou-ke Nation; Uchucklesaht Tribe; Yuułuʔiłʔatḥ Government</t>
+  </si>
+  <si>
+    <t>Doug Braun, Josephine Iacarella, Secwépemc Fisheries Commission</t>
+  </si>
+  <si>
+    <t>Enhanced Mark Selective Fishery (MSF) monitoring (including a Chinook Reference Fishery)</t>
+  </si>
+  <si>
+    <t>Assessment of SEP Chinook and coho broodstock ELISA screening data by modelling for explanatory variables, and yearling DFAT prevalence data by modelling for predictive variables.</t>
+  </si>
+  <si>
+    <t>Epidemiological modeling of infectious hematopoietic necrosis virus in sockeye salmon</t>
+  </si>
+  <si>
+    <t>San Juan River adult and juvenile assessment program</t>
+  </si>
+  <si>
+    <t>Improvement, expansion and modernization of salmonid health diagnostic services for optimizing salmonid hatchery health management</t>
   </si>
 </sst>
 </file>
@@ -3197,7 +3216,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -3211,6 +3230,13 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -3237,7 +3263,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3248,9 +3274,6 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3670,13 +3693,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C1235FC-468F-46C3-9676-E136DE729105}" name="Table1" displayName="Table1" ref="A1:U44" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
-  <autoFilter ref="A1:U44" xr:uid="{9C1235FC-468F-46C3-9676-E136DE729105}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="2418"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:U44" xr:uid="{9C1235FC-468F-46C3-9676-E136DE729105}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{21F25E78-D457-418F-9F78-7DE13AE8CD93}" name="source_file" dataDxfId="20"/>
     <tableColumn id="2" xr3:uid="{B8BCB027-8A7D-4FCE-803F-A296662A280E}" name="extraction_date" dataDxfId="19"/>
@@ -4073,7 +4090,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
@@ -4083,64 +4100,64 @@
       <c r="C2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="U2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="B3" s="7">
         <v>46083</v>
@@ -4149,63 +4166,63 @@
         <v>2394</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="U3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="B4" s="7">
         <v>46083</v>
@@ -4213,64 +4230,64 @@
       <c r="C4" s="1">
         <v>2400</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="9" t="s">
+        <v>637</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="G4" s="1" t="s">
+      <c r="I4" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="K4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="J4" s="1" t="s">
+      <c r="M4" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="P4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="L4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="R4" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="M4" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="P4" s="1" t="s">
+      <c r="S4" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="Q4" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="R4" s="1" t="s">
+      <c r="T4" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="B5" s="7">
         <v>46083</v>
@@ -4278,23 +4295,23 @@
       <c r="C5" s="1">
         <v>2401</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="9" t="s">
+        <v>638</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
@@ -4302,30 +4319,30 @@
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="R5" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="P5" s="1" t="s">
+      <c r="S5" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="Q5" s="1" t="s">
+      <c r="T5" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="R5" s="1" t="s">
+      <c r="U5" s="1" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="U5" s="1" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="B6" s="7">
         <v>46083</v>
@@ -4334,63 +4351,63 @@
         <v>2402</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="K6" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="L6" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="M6" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="O6" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="L6" s="1" t="s">
+      <c r="P6" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="M6" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="N6" s="1" t="s">
+      <c r="Q6" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="R6" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="O6" s="1" t="s">
+      <c r="S6" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="P6" s="1" t="s">
+      <c r="T6" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="Q6" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="R6" s="1" t="s">
+      <c r="U6" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="S6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>92</v>
       </c>
       <c r="B7" s="8">
         <v>46083</v>
@@ -4398,64 +4415,64 @@
       <c r="C7" s="4">
         <v>2403</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
+        <v>639</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="I7" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="J7" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="K7" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="L7" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="M7" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>624</v>
+      </c>
+      <c r="O7" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="P7" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="Q7" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="R7" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="S7" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="T7" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="U7" s="4" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>544</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>638</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q7" s="4" t="s">
-        <v>544</v>
-      </c>
-      <c r="R7" s="4" t="s">
-        <v>544</v>
-      </c>
-      <c r="S7" s="5" t="s">
-        <v>639</v>
-      </c>
-      <c r="T7" s="4" t="s">
-        <v>544</v>
-      </c>
-      <c r="U7" s="4" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="B8" s="7">
         <v>46083</v>
@@ -4464,63 +4481,63 @@
         <v>2404</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="L8" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="O8" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="G8" s="1" t="s">
+      <c r="P8" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="Q8" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="U8" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="O8" s="1" t="s">
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="B9" s="7">
         <v>46083</v>
@@ -4529,63 +4546,63 @@
         <v>2405</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="O9" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="P9" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="Q9" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="R9" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="J9" s="1" t="s">
+      <c r="S9" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="T9" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="L9" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="O9" s="1" t="s">
+      <c r="U9" s="1" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="U9" s="1" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="B10" s="7">
         <v>46083</v>
@@ -4594,63 +4611,63 @@
         <v>2406</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="P10" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="Q10" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="R10" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="G10" s="1" t="s">
+      <c r="S10" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="I10" s="1" t="s">
+      <c r="T10" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="K10" s="1" t="s">
+      <c r="U10" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="L10" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>543</v>
-      </c>
-      <c r="P10" s="1" t="s">
+    </row>
+    <row r="11" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="T10" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="U10" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>135</v>
       </c>
       <c r="B11" s="8">
         <v>46083</v>
@@ -4659,63 +4676,63 @@
         <v>2407</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="J11" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="K11" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="N11" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>636</v>
-      </c>
-      <c r="G11" s="4" t="s">
+      <c r="O11" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="P11" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="Q11" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="R11" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="K11" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>544</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>544</v>
-      </c>
-      <c r="N11" s="4" t="s">
+      <c r="S11" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="O11" s="4" t="s">
+      <c r="T11" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="U11" s="4" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="P11" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q11" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="R11" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="S11" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="T11" s="4" t="s">
-        <v>558</v>
-      </c>
-      <c r="U11" s="4" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>148</v>
       </c>
       <c r="B12" s="7">
         <v>46083</v>
@@ -4723,58 +4740,58 @@
       <c r="C12" s="1">
         <v>2408</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>149</v>
+      <c r="D12" s="9" t="s">
+        <v>640</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
     </row>
-    <row r="13" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B13" s="7">
         <v>46083</v>
@@ -4783,61 +4800,61 @@
         <v>2409</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I13" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="P13" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="Q13" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="R13" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="S13" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="M13" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="N13" s="1" t="s">
+      <c r="T13" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="P13" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="R13" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="S13" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="T13" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="U13" s="1" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>170</v>
       </c>
       <c r="B14" s="7">
         <v>46083</v>
@@ -4846,63 +4863,63 @@
         <v>2410</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="R14" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="S14" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="1" t="s">
+      <c r="T14" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="O14" s="1" t="s">
+      <c r="U14" s="1" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="P14" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q14" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="R14" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="S14" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="T14" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="U14" s="1" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>180</v>
       </c>
       <c r="B15" s="7">
         <v>46083</v>
@@ -4910,64 +4927,64 @@
       <c r="C15" s="1">
         <v>2412</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="9" t="s">
+        <v>629</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="S15" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="T15" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="B16" s="7">
         <v>46083</v>
@@ -4976,63 +4993,63 @@
         <v>2413</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="P16" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="Q16" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="G16" s="1" t="s">
+      <c r="R16" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="S16" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="I16" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J16" s="1" t="s">
+      <c r="T16" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="U16" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="K16" s="1" t="s">
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="O16" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="P16" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q16" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="R16" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="U16" s="1" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>202</v>
       </c>
       <c r="B17" s="7">
         <v>46083</v>
@@ -5041,63 +5058,63 @@
         <v>2416</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="P17" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="Q17" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="G17" s="1" t="s">
+      <c r="R17" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="S17" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="T17" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="U17" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="L17" s="1" t="s">
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="O17" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="P17" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q17" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="R17" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="S17" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="T17" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="U17" s="1" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>216</v>
       </c>
       <c r="B18" s="7">
         <v>46083</v>
@@ -5106,63 +5123,63 @@
         <v>2417</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="L18" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="M18" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="O18" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="P18" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="Q18" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="S18" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="T18" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="O18" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="P18" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="Q18" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="R18" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="S18" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="T18" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="U18" s="1" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>228</v>
       </c>
       <c r="B19" s="7">
         <v>46083</v>
@@ -5171,63 +5188,63 @@
         <v>2418</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="T19" s="5" t="s">
+        <v>626</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="O19" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="P19" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="Q19" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="R19" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="S19" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="T19" s="10" t="s">
-        <v>640</v>
-      </c>
-      <c r="U19" s="1" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>236</v>
       </c>
       <c r="B20" s="7">
         <v>46083</v>
@@ -5236,63 +5253,63 @@
         <v>2421</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="R20" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="T20" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="U20" s="1" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>244</v>
       </c>
       <c r="B21" s="7">
         <v>46083</v>
@@ -5301,63 +5318,63 @@
         <v>2422</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q21" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="R21" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="I21" s="1" t="s">
+      <c r="S21" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="T21" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="L21" s="1" t="s">
+      <c r="U21" s="1" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="O21" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="P21" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="Q21" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="T21" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="U21" s="1" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>256</v>
       </c>
       <c r="B22" s="7">
         <v>46083</v>
@@ -5366,63 +5383,63 @@
         <v>2424</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="R22" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="S22" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="H22" s="1" t="s">
+      <c r="T22" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="U22" s="1" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="P22" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="Q22" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="S22" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="T22" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="U22" s="1" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>267</v>
       </c>
       <c r="B23" s="7">
         <v>46083</v>
@@ -5431,63 +5448,63 @@
         <v>2425</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>637</v>
+        <v>623</v>
       </c>
       <c r="E23" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="P23" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="F23" s="9" t="s">
-        <v>544</v>
-      </c>
-      <c r="G23" s="1" t="s">
+      <c r="Q23" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="R23" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="I23" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="J23" s="1" t="s">
+      <c r="S23" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="T23" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="U23" s="1" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="O23" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="P23" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q23" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="S23" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="T23" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="U23" s="1" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>279</v>
       </c>
       <c r="B24" s="7">
         <v>46083</v>
@@ -5495,64 +5512,64 @@
       <c r="C24" s="1">
         <v>2426</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="9" t="s">
+        <v>628</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>627</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="M24" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="N24" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="G24" s="1" t="s">
+      <c r="O24" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="P24" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="R24" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="S24" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="T24" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="U24" s="1" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="O24" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="P24" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="Q24" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="R24" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="S24" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="T24" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="U24" s="1" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>294</v>
       </c>
       <c r="B25" s="7">
         <v>46083</v>
@@ -5561,63 +5578,63 @@
         <v>2427</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="T25" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="G25" s="1" t="s">
+      <c r="U25" s="1" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="O25" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="P25" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q25" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="R25" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="S25" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="T25" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="U25" s="1" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>304</v>
       </c>
       <c r="B26" s="7">
         <v>46083</v>
@@ -5626,63 +5643,63 @@
         <v>2430</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>305</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="O26" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="P26" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="Q26" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="R26" s="1" t="s">
-        <v>634</v>
-      </c>
-      <c r="S26" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="T26" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="U26" s="1" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>313</v>
       </c>
       <c r="B27" s="7">
         <v>46083</v>
@@ -5691,63 +5708,63 @@
         <v>2432</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>633</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="R27" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="S27" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="T27" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="U27" s="1" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>605</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="O27" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="P27" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="Q27" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="R27" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="S27" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="T27" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="U27" s="1" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>322</v>
       </c>
       <c r="B28" s="7">
         <v>46083</v>
@@ -5756,63 +5773,63 @@
         <v>2433</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>633</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="R28" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="S28" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="T28" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="U28" s="1" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>605</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="M28" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="O28" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="P28" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="Q28" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="R28" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="S28" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="T28" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="U28" s="1" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>331</v>
       </c>
       <c r="B29" s="7">
         <v>46083</v>
@@ -5821,63 +5838,63 @@
         <v>2434</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="N29" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="O29" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="P29" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="Q29" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="R29" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="H29" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="I29" s="1" t="s">
+      <c r="S29" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="T29" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="K29" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="L29" s="1" t="s">
+      <c r="U29" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="M29" s="1" t="s">
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="N29" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="O29" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="P29" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="Q29" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="R29" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="T29" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="U29" s="1" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>347</v>
       </c>
       <c r="B30" s="7">
         <v>46083</v>
@@ -5885,64 +5902,64 @@
       <c r="C30" s="1">
         <v>2435</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="9" t="s">
+        <v>630</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="M30" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="N30" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="O30" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="P30" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="Q30" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="R30" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="S30" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="T30" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="L30" s="1" t="s">
+      <c r="U30" s="1" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>356</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="N30" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="O30" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="P30" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="Q30" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="R30" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="T30" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="U30" s="1" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>365</v>
       </c>
       <c r="B31" s="7">
         <v>46083</v>
@@ -5951,63 +5968,63 @@
         <v>2436</v>
       </c>
       <c r="D31" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="P31" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="Q31" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="G31" s="1" t="s">
+      <c r="R31" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="S31" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="T31" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="U31" s="1" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="N31" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="O31" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="P31" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="Q31" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="R31" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="S31" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="T31" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="U31" s="1" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>380</v>
       </c>
       <c r="B32" s="7">
         <v>46083</v>
@@ -6016,63 +6033,63 @@
         <v>2437</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="P32" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="Q32" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="H32" s="1" t="s">
+      <c r="R32" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="S32" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="T32" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="U32" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="L32" s="1" t="s">
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>387</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="O32" s="1" t="s">
-        <v>611</v>
-      </c>
-      <c r="P32" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="Q32" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="R32" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="S32" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="T32" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="U32" s="1" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="33" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>396</v>
       </c>
       <c r="B33" s="7">
         <v>46083</v>
@@ -6081,63 +6098,63 @@
         <v>2439</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="S33" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="T33" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="U33" s="1" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="M33" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="P33" s="1" t="s">
-        <v>613</v>
-      </c>
-      <c r="Q33" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="R33" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="S33" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="T33" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="U33" s="1" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>407</v>
       </c>
       <c r="B34" s="7">
         <v>46083</v>
@@ -6146,63 +6163,63 @@
         <v>2442</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="Q34" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="R34" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="S34" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="F34" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="G34" s="1" t="s">
+      <c r="T34" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="H34" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="J34" s="1" t="s">
+      <c r="U34" s="1" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>411</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="M34" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="N34" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="O34" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="P34" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="Q34" s="1" t="s">
-        <v>616</v>
-      </c>
-      <c r="R34" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="S34" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="T34" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="U34" s="1" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>420</v>
       </c>
       <c r="B35" s="7">
         <v>46083</v>
@@ -6211,63 +6228,63 @@
         <v>2443</v>
       </c>
       <c r="D35" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="Q35" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R35" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="S35" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="F35" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="G35" s="1" t="s">
+      <c r="T35" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="U35" s="1" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>423</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="M35" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="O35" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="P35" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="Q35" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="R35" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="S35" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="T35" s="1" t="s">
-        <v>618</v>
-      </c>
-      <c r="U35" s="1" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="36" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>432</v>
       </c>
       <c r="B36" s="7">
         <v>46083</v>
@@ -6276,63 +6293,63 @@
         <v>2447</v>
       </c>
       <c r="D36" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="R36" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="S36" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="T36" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="F36" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="G36" s="1" t="s">
+      <c r="U36" s="1" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="M36" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="N36" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="O36" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="P36" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="Q36" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="R36" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="S36" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="T36" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="U36" s="1" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>444</v>
       </c>
       <c r="B37" s="7">
         <v>46083</v>
@@ -6341,63 +6358,63 @@
         <v>2448</v>
       </c>
       <c r="D37" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="Q37" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="R37" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="S37" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="T37" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="G37" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="I37" s="1" t="s">
+      <c r="U37" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="J37" s="1" t="s">
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
         <v>449</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="M37" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="O37" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="P37" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="Q37" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="R37" s="1" t="s">
-        <v>621</v>
-      </c>
-      <c r="S37" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="T37" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="U37" s="1" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>458</v>
       </c>
       <c r="B38" s="7">
         <v>46083</v>
@@ -6405,64 +6422,64 @@
       <c r="C38" s="1">
         <v>2449</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" s="9" t="s">
+        <v>631</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="P38" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="Q38" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="R38" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>622</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="H38" s="1" t="s">
+      <c r="S38" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="I38" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="J38" s="1" t="s">
+      <c r="T38" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="U38" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="L38" s="1" t="s">
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
         <v>464</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="N38" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="O38" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="P38" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="Q38" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="R38" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="S38" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="T38" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="U38" s="1" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>474</v>
       </c>
       <c r="B39" s="7">
         <v>46083</v>
@@ -6471,63 +6488,63 @@
         <v>2451</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="Q39" s="1" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>623</v>
+        <v>610</v>
       </c>
       <c r="S39" s="1" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="U39" s="1" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
     </row>
-    <row r="40" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="B40" s="7">
         <v>46083</v>
@@ -6536,63 +6553,63 @@
         <v>2452</v>
       </c>
       <c r="D40" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="P40" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="Q40" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="R40" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="S40" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="T40" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="I40" s="1" t="s">
+      <c r="U40" s="1" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
         <v>485</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="M40" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="N40" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="O40" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="P40" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="Q40" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="R40" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="S40" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="T40" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="U40" s="1" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="41" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>495</v>
       </c>
       <c r="B41" s="7">
         <v>46083</v>
@@ -6601,63 +6618,63 @@
         <v>2504</v>
       </c>
       <c r="D41" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="P41" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="Q41" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>626</v>
-      </c>
-      <c r="G41" s="1" t="s">
+      <c r="R41" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="S41" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="T41" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="J41" s="1" t="s">
+      <c r="U41" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="K41" s="1" t="s">
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
         <v>502</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="M41" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="N41" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="O41" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="P41" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="Q41" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="R41" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="S41" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="T41" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="U41" s="1" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="42" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>512</v>
       </c>
       <c r="B42" s="7">
         <v>46083</v>
@@ -6666,63 +6683,63 @@
         <v>2513</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="Q42" s="1" t="s">
-        <v>628</v>
+        <v>615</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>629</v>
+        <v>616</v>
       </c>
       <c r="S42" s="1" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="U42" s="1" t="s">
-        <v>630</v>
+        <v>617</v>
       </c>
     </row>
-    <row r="43" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="B43" s="7">
         <v>46083</v>
@@ -6731,63 +6748,63 @@
         <v>2545</v>
       </c>
       <c r="D43" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="P43" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="Q43" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="R43" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="S43" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="T43" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="U43" s="1" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
         <v>523</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="L43" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M43" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="O43" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="P43" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="Q43" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="R43" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="S43" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="T43" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="U43" s="1" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="44" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>533</v>
       </c>
       <c r="B44" s="7">
         <v>46083</v>
@@ -6796,44 +6813,44 @@
         <v>3682</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
       <c r="O44" s="1" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="Q44" s="1" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="S44" s="1" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="U44" s="1" t="s">
-        <v>631</v>
+        <v>618</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/pssi_form_data_altered.xlsx
+++ b/data/processed/pssi_form_data_altered.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ennsj\Documents\PSSI-final-tech-report\data\processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87A352C6-1346-4785-B4B8-3962E1484FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4831C3B-A3B3-4693-AC55-B6C40BC527ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -520,9 +520,6 @@
     <t>2407 PSSI Science Project Reporting Template_JessyBokvist_Final.docx</t>
   </si>
   <si>
-    <t>Characterizing juvenile Chinook salmon distribution, diet and health on the West Coast of Vancouver Island.</t>
-  </si>
-  <si>
     <t>Jessy Bokvist</t>
   </si>
   <si>
@@ -727,9 +724,6 @@
     <t>2413 PSSI Science Project Reporting BarkleyClayoquot.docx</t>
   </si>
   <si>
-    <t>Barkley Sound and Clayoquot Sound Krill Monitoring</t>
-  </si>
-  <si>
     <t>Akash Sastri, Kelly Young</t>
   </si>
   <si>
@@ -895,9 +889,6 @@
     <t>2418 PSSI Science Project Reporting-thiamine analysis-final-BC_EE.docx</t>
   </si>
   <si>
-    <t>Prediction of reproductive success of Chinook salmon based on Thiamine concentrations in returning adults</t>
-  </si>
-  <si>
     <t>Pacific Science Enterprise Centre</t>
   </si>
   <si>
@@ -919,9 +910,6 @@
   </si>
   <si>
     <t>2421 PSSI Science Project Reporting Johnson.docx</t>
-  </si>
-  <si>
-    <t>Measurement of stress hormones in scales and its application for the identification of conditions causing chronic stress in Pacific Salmon</t>
   </si>
   <si>
     <t>Stewart Johnson</t>
@@ -1522,9 +1510,6 @@
   </si>
   <si>
     <t>2439 PSSI Science Project Reporting.docx</t>
-  </si>
-  <si>
-    <t>Modernizing Fish Age Estimation using Fourier Transform-Near Infrared and Neural Network Techniques</t>
   </si>
   <si>
     <t>Stephen Wischniowski</t>
@@ -1675,9 +1660,6 @@
   </si>
   <si>
     <t>2447 PSSI Reporting - Fit-Chips and eDNA Project .docx</t>
-  </si>
-  <si>
-    <t>Innovative Ecosystem Based Approaches to identify cumulative stressors: Salmon Fit-Chips and eDNA</t>
   </si>
   <si>
     <t>Kristi Saunders (retired), Christoph Deeg, Arthur Bass, Carl Llewellyn</t>
@@ -1774,9 +1756,6 @@
     <t>2448 PSSI_Science_Project_Reporting.docx</t>
   </si>
   <si>
-    <t>Developing a proactive, modernized, holistic approach to ensure optimal health and condition of Hatchery Production.</t>
-  </si>
-  <si>
     <t>Christoph Deeg, Kristi Miller-Saunders (retired), Karia Kaukinen, Arthur Bass</t>
   </si>
   <si>
@@ -2272,10 +2251,6 @@
 Figure 2. Maps of Clayoquot Sound showing the percentage of the top 5m of the water column exceeding 17Â°C in summer (July, August and September) in the (a) simulation for 2024 and (b) future scenario. Panel (c) shows the difference between both (future scenario minus 2024 simulation), highlighting the additional percentage of the surface waters that can exceed the temperature threshold in the future scenario.
 Figure 3. Time series of the percentage of water volume that exceeds 17Â°C in Tofino inlet at different depth ranges and different simulations. Bold colours indicate the future scenario, while paler colours indicate the 2024 simulation. Green colours indicate the volume in the surface depth range (0 to 5 m), blue colours represent upper waters below the surface (5 to 20 m) and black/grey represent deep waters (20 to 100 m). At surface, both simulations exceed the threshold between spring and autumn, while below 5 m the threshold is exceeded mostly in the future scenario.
 Figure 4. Location of the CTD profiles with oxygen data from 2024. The oxygen histograms show the distribution of oxygen data for the whole 2024 year and four seasons (winter: Jan-Mar, spring: Apr-Jun, summer: Jul-Sep, and winter: Oct-Dec). The different colours show the histograms for four different depth ranges: the whole water column (blue), top 50 meters (orange), top 20 meters (yellow) and top 5 meters (purple).</t>
-  </si>
-  <si>
-    <t>Rosen, S., Bianucci, L., Jackson, J.M., Hare, A., Greengrove, C., Monks, R., Bartlett, M. and Dick, J., 2022. Seasonal near-surface hypoxia in a temperate fjord in Clayoquot Sound, British Columbia.Â *Frontiers in Marine Science*,Â *9*, p.1000041.
-Foreman, M.G.G., Chandler, P.C., Bianucci, L., Wan, D., Krassovski, M.V., Thupaki, P., Cooper, G. and Lin, Y., 2024. A circulation model for inlets along the central West Coast of Vancouver Island.Â *Atmosphere-Ocean*,Â *62*(1), pp.58-89.</t>
   </si>
   <si>
     <t>*Overview of the model*
@@ -2550,32 +2525,6 @@
     <t>Province of British Columbia, Pacific Salmon Commission</t>
   </si>
   <si>
-    <t>Chan, F.T., Beatty, S.J., Gilles Jr, A.S., Hill, J.E., Kozic, S., Luo, D., Morgan, D.L., Pavia Jr, R.T., Therriault, T.W., Verreycken, H. and Vilizzi, L., 2019. Leaving the fish bowl: the ornamental trade as a global vector for freshwater fish invasions.Â *Aquatic Ecosystem Health &amp; Management*,Â *22*(4), pp.417-439.
-Deacon, J.E., Hubbs, C. and Zahuranec, B.J., 1964. Some effects of introduced fishes on the native fish fauna of southern Nevada.Â *Copeia*, pp.384-388.
-Dextrase, A.J. and Mandrak, N.E., 2006. Impacts of alien invasive species on freshwater fauna at risk in Canada.Â *Biological Invasions*,Â *8*(1), pp.13-24.
-Egertson, C.J. and Downing, J.A., 2004. Relationship of fish catch and composition to water quality in a suite of agriculturally eutrophic lakes.Â *Canadian Journal of Fisheries and Aquatic Sciences*,Â *61*(9), pp.1784-1796.
-Faisal, M., Shavalier, M., Kim, R.K., Millard, E.V., Gunn, M.R., Winters, A.D., Schulz, C.A., Eissa, A., Thomas, M.V., Wolgamood, M. and Whelan, G.E., 2012. Spread of the emerging viral hemorrhagic septicemia virus strain, genotype IVb, in Michigan, USA.Â *Viruses*,Â *4*(5), pp.734-760.
-Gilad, O., Yun, S., Zagmutt-Vergara, F.J., Leutenegger, C.M., Bercovier, H. and Hedrick, R.P., 2004. Concentrations of a Koi herpesvirus (KHV) in tissues of experimentally-infected Cyprinus carpio koi as assessed by real-time TaqMan PCR.Â *Diseases of aquatic organisms*,Â *60*, pp.179-187.
-Jackson, Z.J., Quist, M.C., Downing, J.A. and Larscheid, J.G., 2010. Common carp (Cyprinus carpio), sport fishes, and water quality: ecological thresholds in agriculturally eutrophic lakes.Â *Lake and Reservoir Management*,Â *26*(1), pp.14-22.
-Jalbert, C.S., Falke, J.A., LÃ³pez, J.A., Dunker, K.J., Sepulveda, A.J. and Westley, P.A., 2021. Vulnerability of Pacific salmon to invasion of northern pike (Esox lucius) in Southcentral Alaska.Â *PLoS One*,Â *16*(7), p.e0254097.
-Jones, P.W. and Martin, F.D., 1978.Â *Development of Fishes of the Mid-Atlantic Bight: Acipenseridae Through Ictaluridae*. pp 323.
-Lentsch, L.D., Muth, R., Thompson, P.D., Crowl, T.A. and Hoskins, B.G., 1996. Options for selectively controlling non-indigenous fish in the Upper Colorado River Basin.Â *Final Report. Publication*, pp.96-14.
-Marsh, P.C. and Douglas, M.E., 1997. Predation by introduced fishes on endangered humpback chub and other native species in the Little Colorado River, Arizona.Â *Transactions of the American Fisheries Society*,Â *126*(2), pp.343-346.
-Miller, A.I. and Beckman, L.G., 1996. First record of predation on white sturgeon eggs by sympatric fishes.Â *Transactions of the American Fisheries Society*,Â *125*(2), pp.338-340.
-Moyle, P.B. 1976. Inland fishes of California. University of California Press, Berkeley, CA.
-Nowosad, D.M. and Taylor, E.B., 2013. Habitat variation and invasive species as factors influencing the distribution of native fishes in the lower Fraser River Valley, British Columbia, with an emphasis on brassy minnow (*Hybognathus hankinsoni*).Â *Canadian journal of zoology*,Â *91*(2), pp.71-81.
-Poelen, J.H., Simons, J.D. and Mungall, C.J., 2014. Global biotic interactions: An open infrastructure to share and analyze species-interaction datasets.Â *Ecological informatics*,Â *24*, pp.148-159.
-Richardson, M.J., Whoriskey, F.G. and Roy, L.H., 1995. Turbidity generation and biological impacts of an exotic fish Carassius auratus, introduced into shallow seasonally anoxic ponds.Â *Journal of fish biology*,Â *47*(4), pp.576-585.
-Robinette, H.R. and Knight, S.S., 1981. Food of channel catfish during flooding of the Tombigbee River, Mississippi. InÂ *Proceedings of the Southeastern Association of Fish and Wildlife Agencies*Â (Vol. 35, pp. 598-606).
-Sala, O.E., Stuart Chapin, F.I.I.I., Armesto, J.J., Berlow, E., Bloomfield, J., Dirzo, R., Huber-Sanwald, E., Huenneke, L.F., Jackson, R.B., Kinzig, A. and Leemans, R., 2000. Global biodiversity scenarios for the year 2100.Â *science*,Â *287*(5459), pp.1770-1774.
-Sanderson, B.L., Barnas, K.A. and Rub, A.M.W., 2009. Nonindigenous species of the Pacific Northwest: an overlooked risk to endangered salmon?.Â *BioScience*,Â *59*(3), pp.245-256.
-Schwoerer, T., Little, J.M. and Adkison, M.D., 2019. Aquatic invasive species change ecosystem services from the world's largest wild sockeye salmon fisheries in Alaska.Â *Journal of Ocean and Coastal Economics*,Â *6*(1), p.2.
-Scott, W.B., 1973. Freshwater fishes of Canada.Â *Fish. Res. Board Can. Bull.*,Â *184*, pp.1-966.
-Vigg, S., Poe, T.P., Prendergast, L.A. and Hansel, H.C., 1991. Rates of consumption of juvenile salmonids and alternative prey fish by northern squawfish, walleyes, smallmouth bass, and channel catfish in John Day Reservoir, Columbia River.Â *Transactions of the American Fisheries Society*,Â *120*(4), pp.421-438.
-Weber, M.J. and Brown, M.L., 2009. Effects of common carp on aquatic ecosystems 80 years after "carp as a dominant": ecological insights for fisheries management.Â *Reviews in Fisheries Science*,Â *17*(4), pp.524-537.
-Wilcox, M.A., Johnson, D., Dyke, K., Gunsch, D., Lyons, D.A., DiBacco, C. and Therriault, T.W., 2025. Identifying higher risk invaders to the Columbia Glaciated Freshwater Ecoregion using a new screening tool: the Non-Indigenous Species Screening Tool (NISST).Â *Management of Biological Invasions*,Â *16*(1), pp.187-210.</t>
-  </si>
-  <si>
     <t>Under global climate change, co-occurrence of gradual physical changes in seawater and extreme events pose a substantial threat to marine ecosystems (IPCC, 2023). This PSSI-funded project focused on the Strait of Georgia (SOG) within the Northeast Pacific coastal region where steady rises in mean seasonal seawater temperatures and *p*CO2 levels, and increasingly prevalent acute stressor events such as heatwaves and low-pH upwellings, are already occurring (Bylhouwer et al., 2013; Evans et al., 2019; Okey et al., 2024; Raymond et al., 2022; Talloni-Alvarez et al., 2014). Moreover, the SOG is distinctive as conditions of high *p*CO2 and aragonite undersaturation persist year-round across a wide extent of the water column (Moore-Maley et al., 2016; Simpson et al., 2024). *Limacina helicina*, a cold-water pteropod well-represented within the region's zooplankton communities, is highly susceptible to climate change stressors, with documented impacts of ocean warming and ocean acidification (OA) on shell development, growth, and survival (BednarÅ¡ek et al., 2016, 2022; Lischka et al., 2022; Lischka &amp; Riebesell, 2012). However, there has been minimal investigation of climate change effects on the species' nutritional status (*e.g.* fatty acid (FA) composition) under regionally-relevant conditions. Given the importance of *L. helicina* as a dietary item for some populations of juvenile Pacific salmon species in the Northeast Pacific (Brodeur et al., 2007; Doubleday &amp; Hopcroft, 2015; Sturdevant et al., 2012), it was proposed that any change in the nutritive status of *L. helicina* under climate stressor conditions could have carry-over impacts to juvenile salmon growth, health, and survival.
 The project involved cross-program collaboration between DFO researchers based at the Pacific Biological Station (PBS) and the Pacific Science Enterprise Centre (PSEC) for investigation of the impacts of warming and OA conditions (representative of future conditions in the SOG) on FA profiles of *L. helicina* populations in the region. *Limacina helicina* samples were collected and processed as part of juvenile Pacific salmon survey fieldwork carried out in the SOG during 2014âˆ’2023 by the *Salmon Marine Interactions Program* at PBS (Lead: Neville). The program also supported live collection (within the SOG) of *L. helicina* for a climate change experiment (2023). Subsequent field sample sorting (*i.e.* extraction of whole pteropods from historical size-fractionated plankton samples) and laboratory experimentation (*i.e.* conducting of a climate change experiment in the Fisheries and Oceans Climate Change and Ocean Acidification Laboratory (FOCCOAL)), and nutritional analyses (*i.e.* FA analyses via gas chromatography) were carried out by the *Sustainable Invertebrate Aquaculture Program* at PBS (Lead: Pearce) and *Nutrition Program* at PSEC (Lead: Forster), respectively.</t>
   </si>
@@ -3197,9 +3146,6 @@
     <t>Enhanced Mark Selective Fishery (MSF) monitoring (including a Chinook Reference Fishery)</t>
   </si>
   <si>
-    <t>Assessment of SEP Chinook and coho broodstock ELISA screening data by modelling for explanatory variables, and yearling DFAT prevalence data by modelling for predictive variables.</t>
-  </si>
-  <si>
     <t>Epidemiological modeling of infectious hematopoietic necrosis virus in sockeye salmon</t>
   </si>
   <si>
@@ -3207,6 +3153,60 @@
   </si>
   <si>
     <t>Improvement, expansion and modernization of salmonid health diagnostic services for optimizing salmonid hatchery health management</t>
+  </si>
+  <si>
+    <t>Barkley Sound and Clayoquot Sound krill monitoring</t>
+  </si>
+  <si>
+    <t>Prediction of reproductive success of Chinook salmon based on thiamine concentrations in returning adults</t>
+  </si>
+  <si>
+    <t>Measurement of stress hormones in scales and its application for the identification of conditions causing chronic stress in Pacific salmon</t>
+  </si>
+  <si>
+    <t>Modernizing fish age estimation using Fourier transform-near infrared and neural network techniques</t>
+  </si>
+  <si>
+    <t>Innovative ecosystem based approaches to identify cumulative stressors: Salmon Fit-Chips and eDNA</t>
+  </si>
+  <si>
+    <t>Developing a proactive, modernized, holistic approach to ensure optimal health and condition of hatchery production</t>
+  </si>
+  <si>
+    <t>Assessment of SEP Chinook and coho broodstock ELISA screening data by modelling for explanatory variables, and yearling DFAT prevalence data by modelling for predictive variables</t>
+  </si>
+  <si>
+    <t>Characterizing juvenile Chinook salmon distribution, diet and health on the West Coast of Vancouver Island</t>
+  </si>
+  <si>
+    <t>Chan, F.T., Beatty, S.J., Gilles Jr, A.S., Hill, J.E., Kozic, S., Luo, D., Morgan, D.L., Pavia Jr, R.T., Therriault, T.W., Verreycken, H. and Vilizzi, L., 2019. Leaving the fish bowl: the ornamental trade as a global vector for freshwater fish invasions. Aquatic Ecosystem Health &amp; Management, 22(4), pp.417-439.
+Deacon, J.E., Hubbs, C. and Zahuranec, B.J., 1964. Some effects of introduced fishes on the native fish fauna of southern Nevada. Copeia, pp.384-388.
+Dextrase, A.J. and Mandrak, N.E., 2006. Impacts of alien invasive species on freshwater fauna at risk in Canada. Biological Invasions, 8(1), pp.13-24.
+Egertson, C.J. and Downing, J.A., 2004. Relationship of fish catch and composition to water quality in a suite of agriculturally eutrophic lakes. Canadian Journal of Fisheries and Aquatic Sciences, 61(9), pp.1784-1796.
+Faisal, M., Shavalier, M., Kim, R.K., Millard, E.V., Gunn, M.R., Winters, A.D., Schulz, C.A., Eissa, A., Thomas, M.V., Wolgamood, M. and Whelan, G.E., 2012. Spread of the emerging viral hemorrhagic septicemia virus strain, genotype IVb, in Michigan, USA. Viruses, 4(5), pp.734-760.
+Gilad, O., Yun, S., Zagmutt-Vergara, F.J., Leutenegger, C.M., Bercovier, H. and Hedrick, R.P., 2004. Concentrations of a Koi herpesvirus (KHV) in tissues of experimentally-infected Cyprinus carpio koi as assessed by real-time TaqMan PCR. Diseases of aquatic organisms, 60, pp.179-187.
+Jackson, Z.J., Quist, M.C., Downing, J.A. and Larscheid, J.G., 2010. Common carp (Cyprinus carpio), sport fishes, and water quality: ecological thresholds in agriculturally eutrophic lakes. Lake and Reservoir Management, 26(1), pp.14-22.
+Jalbert, C.S., Falke, J.A., López, J.A., Dunker, K.J., Sepulveda, A.J. and Westley, P.A., 2021. Vulnerability of Pacific salmon to invasion of northern pike (Esox lucius) in Southcentral Alaska. PLoS One, 16(7), p.e0254097.
+Jones, P.W. and Martin, F.D., 1978. Development of Fishes of the Mid-Atlantic Bight: Acipenseridae Through Ictaluridae. pp 323. 
+Lentsch, L.D., Muth, R., Thompson, P.D., Crowl, T.A. and Hoskins, B.G., 1996. Options for selectively controlling non-indigenous fish in the Upper Colorado River Basin. Final Report. Publication, pp.96-14.
+Marsh, P.C. and Douglas, M.E., 1997. Predation by introduced fishes on endangered humpback chub and other native species in the Little Colorado River, Arizona. Transactions of the American Fisheries Society, 126(2), pp.343-346.
+Miller, A.I. and Beckman, L.G., 1996. First record of predation on white sturgeon eggs by sympatric fishes. Transactions of the American Fisheries Society, 125(2), pp.338-340.
+Moyle, P.B. 1976. Inland fishes of California. University of California Press, Berkeley, CA.
+Nowosad, D.M. and Taylor, E.B., 2013. Habitat variation and invasive species as factors influencing the distribution of native fishes in the lower Fraser River Valley, British Columbia, with an emphasis on brassy minnow (Hybognathus hankinsoni). Canadian journal of zoology, 91(2), pp.71-81.
+Poelen, J.H., Simons, J.D. and Mungall, C.J., 2014. Global biotic interactions: An open infrastructure to share and analyze species-interaction datasets. Ecological informatics, 24, pp.148-159.
+Richardson, M.J., Whoriskey, F.G. and Roy, L.H., 1995. Turbidity generation and biological impacts of an exotic fish Carassius auratus, introduced into shallow seasonally anoxic ponds. Journal of fish biology, 47(4), pp.576-585.
+Robinette, H.R. and Knight, S.S., 1981. Food of channel catfish during flooding of the Tombigbee River, Mississippi. In Proceedings of the Southeastern Association of Fish and Wildlife Agencies (Vol. 35, pp. 598-606).
+Sala, O.E., Stuart Chapin, F.I.I.I., Armesto, J.J., Berlow, E., Bloomfield, J., Dirzo, R., Huber-Sanwald, E., Huenneke, L.F., Jackson, R.B., Kinzig, A. and Leemans, R., 2000. Global biodiversity scenarios for the year 2100. science, 287(5459), pp.1770-1774.
+Sanderson, B.L., Barnas, K.A. and Rub, A.M.W., 2009. Nonindigenous species of the Pacific Northwest: an overlooked risk to endangered salmon?. BioScience, 59(3), pp.245-256.
+Schwoerer, T., Little, J.M. and Adkison, M.D., 2019. Aquatic invasive species change ecosystem services from the world's largest wild sockeye salmon fisheries in Alaska. Journal of Ocean and Coastal Economics, 6(1), p.2.
+Scott, W.B., 1973. Freshwater fishes of Canada. Fish. Res. Board Can. Bull., 184, pp.1-966.
+Vigg, S., Poe, T.P., Prendergast, L.A. and Hansel, H.C., 1991. Rates of consumption of juvenile salmonids and alternative prey fish by northern squawfish, walleyes, smallmouth bass, and channel catfish in John Day Reservoir, Columbia River. Transactions of the American Fisheries Society, 120(4), pp.421-438.
+Weber, M.J. and Brown, M.L., 2009. Effects of common carp on aquatic ecosystems 80 years after “carp as a dominant”: ecological insights for fisheries management. Reviews in Fisheries Science, 17(4), pp.524-537.
+Wilcox, M.A., Johnson, D., Dyke, K., Gunsch, D., Lyons, D.A., DiBacco, C. and Therriault, T.W., 2025. Identifying higher risk invaders to the Columbia Glaciated Freshwater Ecoregion using a new screening tool: the Non-Indigenous Species Screening Tool (NISST). Management of Biological Invasions, 16(1), pp.187-210.</t>
+  </si>
+  <si>
+    <t>Rosen, S., Bianucci, L., Jackson, J.M., Hare, A., Greengrove, C., Monks, R., Bartlett, M. and Dick, J., 2022. Seasonal near-surface hypoxia in a temperate fjord in Clayoquot Sound, British Columbia. Frontiers in Marine Science, 9, p.1000041.
+Foreman, M.G.G., Chandler, P.C., Bianucci, L., Wan, D., Krassovski, M.V., Thupaki, P., Cooper, G. and Lin, Y., 2024. A circulation model for inlets along the central West Coast of Vancouver Island. Atmosphere-Ocean, 62(1), pp.58-89.</t>
   </si>
 </sst>
 </file>
@@ -3263,7 +3263,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3274,6 +3274,9 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4021,7 +4024,7 @@
     <col min="18" max="18" width="11.42578125" style="2"/>
     <col min="19" max="19" width="12.85546875" style="2" customWidth="1"/>
     <col min="20" max="20" width="15.7109375" style="2" customWidth="1"/>
-    <col min="21" max="21" width="12.7109375" style="2" customWidth="1"/>
+    <col min="21" max="21" width="126.85546875" style="10" customWidth="1"/>
     <col min="22" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
@@ -4086,7 +4089,7 @@
       <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="10" t="s">
         <v>20</v>
       </c>
     </row>
@@ -4101,7 +4104,7 @@
         <v>22</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>23</v>
@@ -4131,7 +4134,7 @@
         <v>31</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>32</v>
@@ -4181,7 +4184,7 @@
         <v>44</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>45</v>
@@ -4190,13 +4193,13 @@
         <v>46</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>47</v>
@@ -4237,7 +4240,7 @@
         <v>55</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>56</v>
@@ -4246,7 +4249,7 @@
         <v>57</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>58</v>
@@ -4258,19 +4261,19 @@
         <v>59</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="P4" s="1" t="s">
         <v>60</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="R4" s="1" t="s">
         <v>61</v>
@@ -4279,10 +4282,10 @@
         <v>62</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -4296,16 +4299,16 @@
         <v>2401</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>65</v>
@@ -4337,7 +4340,7 @@
         <v>72</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -4378,7 +4381,7 @@
         <v>81</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>82</v>
@@ -4390,7 +4393,7 @@
         <v>84</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="R6" s="1" t="s">
         <v>85</v>
@@ -4416,7 +4419,7 @@
         <v>2403</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>90</v>
@@ -4437,7 +4440,7 @@
         <v>95</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="L7" s="4" t="s">
         <v>96</v>
@@ -4446,7 +4449,7 @@
         <v>96</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="O7" s="4" t="s">
         <v>97</v>
@@ -4455,84 +4458,84 @@
         <v>98</v>
       </c>
       <c r="Q7" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="R7" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="S7" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="T7" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="U7" s="4" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" s="8">
+        <v>46083</v>
+      </c>
+      <c r="C8" s="4">
+        <v>2404</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="R7" s="4" t="s">
-        <v>534</v>
-      </c>
-      <c r="S7" s="5" t="s">
-        <v>625</v>
-      </c>
-      <c r="T7" s="4" t="s">
-        <v>534</v>
-      </c>
-      <c r="U7" s="4" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B8" s="7">
-        <v>46083</v>
-      </c>
-      <c r="C8" s="1">
-        <v>2404</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="I8" s="1" t="s">
+      <c r="H8" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="K8" s="1" t="s">
+      <c r="J8" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="K8" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="L8" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="O8" s="1" t="s">
+      <c r="L8" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="O8" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="P8" s="1" t="s">
+      <c r="P8" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="Q8" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="R8" s="1" t="s">
+      <c r="Q8" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="R8" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="S8" s="1" t="s">
+      <c r="S8" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="T8" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>544</v>
+      <c r="T8" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="U8" s="5" t="s">
+        <v>640</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -4549,19 +4552,19 @@
         <v>110</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>111</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>65</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>112</v>
@@ -4570,13 +4573,13 @@
         <v>113</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>114</v>
@@ -4585,7 +4588,7 @@
         <v>115</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="R9" s="1" t="s">
         <v>116</v>
@@ -4597,7 +4600,7 @@
         <v>118</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -4617,40 +4620,40 @@
         <v>121</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>122</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>123</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>124</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>125</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="R10" s="1" t="s">
         <v>126</v>
@@ -4675,64 +4678,64 @@
       <c r="C11" s="4">
         <v>2407</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
+        <v>638</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="F11" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>634</v>
-      </c>
-      <c r="G11" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="I11" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="J11" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>136</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>56</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="N11" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="O11" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="O11" s="4" t="s">
+      <c r="P11" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="P11" s="4" t="s">
+      <c r="Q11" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="Q11" s="4" t="s">
+      <c r="R11" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="R11" s="4" t="s">
+      <c r="S11" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="S11" s="4" t="s">
-        <v>142</v>
-      </c>
       <c r="T11" s="4" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="U11" s="4" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B12" s="7">
         <v>46083</v>
@@ -4741,19 +4744,19 @@
         <v>2408</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>56</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
@@ -4763,35 +4766,35 @@
         <v>56</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="P12" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="P12" s="1" t="s">
+      <c r="Q12" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="R12" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="Q12" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="R12" s="1" t="s">
+      <c r="S12" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="S12" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="T12" s="1" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B13" s="7">
         <v>46083</v>
@@ -4800,61 +4803,61 @@
         <v>2409</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>153</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
         <v>65</v>
       </c>
       <c r="I13" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J13" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="K13" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="M13" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="N13" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="M13" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="N13" s="1" t="s">
+      <c r="O13" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="O13" s="1" t="s">
+      <c r="P13" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="P13" s="1" t="s">
+      <c r="Q13" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="Q13" s="1" t="s">
+      <c r="R13" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="R13" s="1" t="s">
+      <c r="S13" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="S13" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="T13" s="1" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B14" s="7">
         <v>46083</v>
@@ -4863,22 +4866,22 @@
         <v>2410</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>166</v>
-      </c>
       <c r="F14" s="1" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>31</v>
@@ -4890,36 +4893,36 @@
         <v>31</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="N14" s="1" t="s">
         <v>31</v>
       </c>
       <c r="O14" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="P14" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="P14" s="1" t="s">
+      <c r="Q14" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="Q14" s="1" t="s">
+      <c r="R14" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="R14" s="1" t="s">
+      <c r="S14" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="S14" s="1" t="s">
+      <c r="T14" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="T14" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="U14" s="1" t="s">
-        <v>557</v>
+      <c r="U14" s="5" t="s">
+        <v>639</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B15" s="7">
         <v>46083</v>
@@ -4928,63 +4931,63 @@
         <v>2412</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="H15" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="I15" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>178</v>
-      </c>
       <c r="J15" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>56</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="O15" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="R15" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="P15" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="R15" s="1" t="s">
+      <c r="S15" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="S15" s="1" t="s">
-        <v>181</v>
-      </c>
       <c r="T15" s="1" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B16" s="7">
         <v>46083</v>
@@ -4992,64 +4995,64 @@
       <c r="C16" s="1">
         <v>2413</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="9" t="s">
+        <v>631</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="G16" s="1" t="s">
+      <c r="I16" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="K16" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="I16" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="J16" s="1" t="s">
+      <c r="L16" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="O16" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="P16" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="L16" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="O16" s="1" t="s">
+      <c r="Q16" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="P16" s="1" t="s">
+      <c r="R16" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="Q16" s="1" t="s">
+      <c r="S16" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="R16" s="1" t="s">
+      <c r="T16" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="U16" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="U16" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B17" s="7">
         <v>46083</v>
@@ -5058,63 +5061,63 @@
         <v>2416</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="G17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>201</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>104</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>104</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="P17" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="R17" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="Q17" s="1" t="s">
+      <c r="S17" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="R17" s="1" t="s">
+      <c r="T17" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="S17" s="1" t="s">
+      <c r="U17" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="T17" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="U17" s="1" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B18" s="7">
         <v>46083</v>
@@ -5123,63 +5126,63 @@
         <v>2417</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="G18" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="I18" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="J18" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="K18" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="I18" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="J18" s="1" t="s">
+      <c r="L18" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="M18" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="O18" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="L18" s="1" t="s">
+      <c r="P18" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="M18" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="O18" s="1" t="s">
+      <c r="Q18" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="S18" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="P18" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q18" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="R18" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="S18" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="T18" s="1" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B19" s="7">
         <v>46083</v>
@@ -5187,64 +5190,64 @@
       <c r="C19" s="1">
         <v>2418</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="9" t="s">
+        <v>632</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="J19" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="G19" s="1" t="s">
+      <c r="K19" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="L19" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="M19" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="O19" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="I19" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="J19" s="1" t="s">
+      <c r="P19" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="S19" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="O19" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="P19" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="Q19" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="R19" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="S19" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="T19" s="5" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B20" s="7">
         <v>46083</v>
@@ -5252,64 +5255,64 @@
       <c r="C20" s="1">
         <v>2421</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>230</v>
+      <c r="D20" s="9" t="s">
+        <v>633</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>56</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B21" s="7">
         <v>46083</v>
@@ -5318,63 +5321,63 @@
         <v>2422</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>104</v>
       </c>
       <c r="L21" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="R21" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="M21" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="O21" s="1" t="s">
+      <c r="S21" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="P21" s="1" t="s">
+      <c r="T21" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="Q21" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="T21" s="1" t="s">
-        <v>248</v>
-      </c>
       <c r="U21" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B22" s="7">
         <v>46083</v>
@@ -5383,63 +5386,63 @@
         <v>2424</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="J22" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="K22" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="F22" s="9" t="s">
-        <v>635</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="H22" s="1" t="s">
+      <c r="L22" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="O22" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="P22" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="R22" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="S22" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="T22" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="L22" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="P22" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="Q22" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="S22" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="T22" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="U22" s="1" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B23" s="7">
         <v>46083</v>
@@ -5448,63 +5451,63 @@
         <v>2425</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="E23" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="K23" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="F23" s="9" t="s">
-        <v>534</v>
-      </c>
-      <c r="G23" s="1" t="s">
+      <c r="L23" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="N23" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="O23" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="I23" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="J23" s="1" t="s">
+      <c r="P23" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="Q23" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="L23" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="N23" s="1" t="s">
+      <c r="R23" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="O23" s="1" t="s">
+      <c r="S23" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="P23" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q23" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="S23" s="1" t="s">
-        <v>271</v>
-      </c>
       <c r="T23" s="1" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B24" s="7">
         <v>46083</v>
@@ -5513,63 +5516,63 @@
         <v>2426</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="E24" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="J24" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="F24" s="9" t="s">
-        <v>627</v>
-      </c>
-      <c r="G24" s="1" t="s">
+      <c r="K24" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="L24" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="M24" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="N24" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="O24" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="L24" s="1" t="s">
+      <c r="P24" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="R24" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="M24" s="1" t="s">
+      <c r="S24" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="N24" s="1" t="s">
+      <c r="T24" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="O24" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="P24" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="Q24" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="R24" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="S24" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="T24" s="1" t="s">
-        <v>285</v>
-      </c>
       <c r="U24" s="1" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B25" s="7">
         <v>46083</v>
@@ -5578,63 +5581,63 @@
         <v>2427</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="O25" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="G25" s="1" t="s">
+      <c r="P25" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="H25" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="J25" s="1" t="s">
+      <c r="Q25" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="R25" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="S25" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="L25" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="O25" s="1" t="s">
+      <c r="T25" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="P25" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="Q25" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="R25" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="S25" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="T25" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="U25" s="1" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B26" s="7">
         <v>46083</v>
@@ -5643,63 +5646,63 @@
         <v>2430</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="L26" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="I26" s="1" t="s">
+      <c r="M26" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="N26" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="O26" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="P26" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="S26" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="L26" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="O26" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="P26" s="1" t="s">
-        <v>620</v>
-      </c>
-      <c r="Q26" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="R26" s="1" t="s">
-        <v>621</v>
-      </c>
-      <c r="S26" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="T26" s="1" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="U26" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B27" s="7">
         <v>46083</v>
@@ -5708,63 +5711,63 @@
         <v>2432</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>624</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q27" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="E27" s="9" t="s">
-        <v>633</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="G27" s="1" t="s">
+      <c r="R27" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="H27" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="O27" s="1" t="s">
+      <c r="S27" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="P27" s="1" t="s">
+      <c r="T27" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="Q27" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="R27" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="S27" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="T27" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="U27" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B28" s="7">
         <v>46083</v>
@@ -5773,63 +5776,63 @@
         <v>2433</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>624</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q28" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="E28" s="9" t="s">
-        <v>633</v>
-      </c>
-      <c r="F28" s="1" t="s">
+      <c r="R28" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="S28" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="H28" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="K28" s="9" t="s">
-        <v>534</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="M28" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="O28" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="P28" s="1" t="s">
+      <c r="T28" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="Q28" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="R28" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="S28" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="T28" s="1" t="s">
-        <v>322</v>
-      </c>
       <c r="U28" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B29" s="7">
         <v>46083</v>
@@ -5838,63 +5841,63 @@
         <v>2434</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="I29" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="J29" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="K29" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="L29" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="M29" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="H29" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="I29" s="1" t="s">
+      <c r="N29" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="O29" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="P29" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="K29" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="L29" s="1" t="s">
+      <c r="Q29" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="M29" s="1" t="s">
+      <c r="R29" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="N29" s="1" t="s">
+      <c r="S29" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="O29" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="P29" s="1" t="s">
+      <c r="T29" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="Q29" s="1" t="s">
+      <c r="U29" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="R29" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="T29" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="U29" s="1" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B30" s="7">
         <v>46083</v>
@@ -5903,63 +5906,63 @@
         <v>2435</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="E30" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="I30" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="J30" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="K30" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="L30" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="M30" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="N30" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="O30" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="L30" s="1" t="s">
+      <c r="P30" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="M30" s="1" t="s">
+      <c r="Q30" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="N30" s="1" t="s">
+      <c r="R30" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="O30" s="1" t="s">
+      <c r="S30" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="P30" s="1" t="s">
+      <c r="T30" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="Q30" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="R30" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="T30" s="1" t="s">
-        <v>355</v>
-      </c>
       <c r="U30" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B31" s="7">
         <v>46083</v>
@@ -5968,63 +5971,63 @@
         <v>2436</v>
       </c>
       <c r="D31" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="I31" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="J31" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="G31" s="1" t="s">
+      <c r="K31" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="L31" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="N31" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="O31" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="P31" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="Q31" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="L31" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="N31" s="1" t="s">
+      <c r="R31" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="O31" s="1" t="s">
+      <c r="S31" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="P31" s="1" t="s">
+      <c r="T31" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="Q31" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="R31" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="S31" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="T31" s="1" t="s">
-        <v>370</v>
-      </c>
       <c r="U31" s="1" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B32" s="7">
         <v>46083</v>
@@ -6033,63 +6036,63 @@
         <v>2437</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="J32" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="K32" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="H32" s="1" t="s">
+      <c r="L32" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="M32" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="N32" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="O32" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="P32" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="L32" s="1" t="s">
+      <c r="Q32" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="M32" s="1" t="s">
+      <c r="R32" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="N32" s="1" t="s">
+      <c r="S32" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="O32" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="P32" s="1" t="s">
+      <c r="T32" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="Q32" s="1" t="s">
+      <c r="U32" s="1" t="s">
         <v>382</v>
-      </c>
-      <c r="R32" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="S32" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="T32" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="U32" s="1" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B33" s="7">
         <v>46083</v>
@@ -6097,64 +6100,64 @@
       <c r="C33" s="1">
         <v>2439</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="O33" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="P33" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="Q33" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="F33" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="G33" s="1" t="s">
+      <c r="R33" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="S33" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="I33" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="K33" s="1" t="s">
+      <c r="T33" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="L33" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="M33" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="P33" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="Q33" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="R33" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="S33" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="T33" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="U33" s="1" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B34" s="7">
         <v>46083</v>
@@ -6163,63 +6166,63 @@
         <v>2442</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="L34" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="M34" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="N34" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="F34" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="G34" s="1" t="s">
+      <c r="O34" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="H34" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="J34" s="1" t="s">
+      <c r="P34" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="K34" s="1" t="s">
+      <c r="Q34" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="R34" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="L34" s="1" t="s">
+      <c r="S34" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="M34" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="N34" s="1" t="s">
+      <c r="T34" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="O34" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="P34" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="Q34" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="R34" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="S34" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="T34" s="1" t="s">
-        <v>410</v>
-      </c>
       <c r="U34" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B35" s="7">
         <v>46083</v>
@@ -6227,64 +6230,64 @@
       <c r="C35" s="1">
         <v>2443</v>
       </c>
-      <c r="D35" s="1" t="s">
-        <v>412</v>
+      <c r="D35" s="9" t="s">
+        <v>407</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>65</v>
       </c>
       <c r="I35" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="Q35" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="J35" s="1" t="s">
+      <c r="R35" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="K35" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="M35" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="N35" s="1" t="s">
+      <c r="S35" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="O35" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="P35" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="Q35" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="R35" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="S35" s="1" t="s">
-        <v>422</v>
-      </c>
       <c r="T35" s="1" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="U35" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="B36" s="7">
         <v>46083</v>
@@ -6292,26 +6295,26 @@
       <c r="C36" s="1">
         <v>2447</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>424</v>
+      <c r="D36" s="9" t="s">
+        <v>635</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>78</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>104</v>
@@ -6320,36 +6323,36 @@
         <v>104</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="N36" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="R36" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="S36" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="T36" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="O36" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="P36" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="Q36" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="R36" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="S36" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="T36" s="1" t="s">
-        <v>434</v>
-      </c>
       <c r="U36" s="1" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="B37" s="7">
         <v>46083</v>
@@ -6357,64 +6360,64 @@
       <c r="C37" s="1">
         <v>2448</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>436</v>
+      <c r="D37" s="9" t="s">
+        <v>636</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>56</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I37" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="Q37" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="R37" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="S37" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="J37" s="1" t="s">
+      <c r="T37" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="U37" s="1" t="s">
         <v>441</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="M37" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="O37" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="P37" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="Q37" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="R37" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="S37" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="T37" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="U37" s="1" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="B38" s="7">
         <v>46083</v>
@@ -6423,63 +6426,63 @@
         <v>2449</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="E38" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="O38" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="H38" s="1" t="s">
+      <c r="P38" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="I38" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="J38" s="1" t="s">
+      <c r="Q38" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="R38" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="L38" s="1" t="s">
+      <c r="S38" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="M38" s="1" t="s">
+      <c r="T38" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="N38" s="1" t="s">
+      <c r="U38" s="1" t="s">
         <v>456</v>
-      </c>
-      <c r="O38" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="P38" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="Q38" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="R38" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="S38" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="T38" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="U38" s="1" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="B39" s="7">
         <v>46083</v>
@@ -6488,63 +6491,63 @@
         <v>2451</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>78</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="Q39" s="1" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="S39" s="1" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="U39" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="B40" s="7">
         <v>46083</v>
@@ -6553,63 +6556,63 @@
         <v>2452</v>
       </c>
       <c r="D40" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="P40" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="I40" s="1" t="s">
+      <c r="Q40" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="R40" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="J40" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="K40" s="1" t="s">
+      <c r="S40" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="L40" s="1" t="s">
+      <c r="T40" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="M40" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="N40" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="O40" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="P40" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="Q40" s="1" t="s">
-        <v>611</v>
-      </c>
-      <c r="R40" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="S40" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="T40" s="1" t="s">
-        <v>484</v>
-      </c>
       <c r="U40" s="1" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="B41" s="7">
         <v>46083</v>
@@ -6618,63 +6621,63 @@
         <v>2504</v>
       </c>
       <c r="D41" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="L41" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="M41" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>613</v>
-      </c>
-      <c r="G41" s="1" t="s">
+      <c r="N41" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="O41" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="P41" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="Q41" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="J41" s="1" t="s">
+      <c r="R41" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="K41" s="1" t="s">
+      <c r="S41" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="L41" s="1" t="s">
+      <c r="T41" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="M41" s="1" t="s">
+      <c r="U41" s="1" t="s">
         <v>494</v>
-      </c>
-      <c r="N41" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="O41" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="P41" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="Q41" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="R41" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="S41" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="T41" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="U41" s="1" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="B42" s="7">
         <v>46083</v>
@@ -6683,63 +6686,63 @@
         <v>2513</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="K42" s="1" t="s">
         <v>104</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="Q42" s="1" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="S42" s="1" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="U42" s="1" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="B43" s="7">
         <v>46083</v>
@@ -6748,22 +6751,22 @@
         <v>2545</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>31</v>
@@ -6781,30 +6784,30 @@
         <v>31</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="Q43" s="1" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="S43" s="1" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="U43" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="B44" s="7">
         <v>46083</v>
@@ -6813,13 +6816,13 @@
         <v>3682</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
@@ -6832,25 +6835,25 @@
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
       <c r="O44" s="1" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="Q44" s="1" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="S44" s="1" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="U44" s="1" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/pssi_form_data_altered.xlsx
+++ b/data/processed/pssi_form_data_altered.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ennsj\Documents\PSSI-final-tech-report\data\processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4831C3B-A3B3-4693-AC55-B6C40BC527ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FF8C8F2-6170-4789-9100-586184E57A0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1640,12 +1640,6 @@
     <t>Smallmouth bass (Micropterus dolomieu), a piscivorous fish species native to eastern North America, have been introduced into Cultus Lake, British Columbia. Cultus Lake is home to endangered sockeye salmon (*Oncorhynchus nerka*) as well as endemic Cultus pygmy sculpin (*Cottus aleuticus*). Smallmouth bass introduced in other salmon-bearing habitat have been observed to exert substantial mortality on salmon fry and smolts, suggesting a similar impact may be possible in Cultus Lake. Observations of sockeye salmon, and Cultus pygmy sculpin in the diet of captured smallmouth bass, demonstrates predation upon two native species at risk. While smallmouth bass represent a threat to the Cultus Lake native fish community and species at risk specifically, they are also highly valued by some anglers. Importantly, as a source population, they also represent a real and present threat to other ecosystems in the Lower Mainland. Smallmouth bass are often found in streams and rivers; in fact, they have already been found downstream of Cultus Lake. Additionally, there is the threat of anglers moving smallmouth bass to other waterbodies in the Lower Mainland to create new bass fisheries, which themselves would create risk to receiving environments. While there are largemouth bass (*M. salmoides*) populations in various waterbodies throughout the Lower Mainland, this is the first verified smallmouth bass population, and has drawn a lot of attention from the angling community. Early work on this population has identified a divergence of public opinions: some value native species (especially sockeye salmon) and want to see bass suppressed; other values angling opportunities for smallmouth bass and will strongly oppose any measures to affect this valued fishery resource.
 There are two issues that this project addresses: (1) understanding which suppression options will result in the lowest opposition from anglers and community members, thereby identifying the risk of unintended consequences (e.g., additional transfers to other lakes); and (2) determining the suppression strategy (combination of different suppression options) which will best inform estimates of effectiveness for each suppression option so as to maximize effective suppression moving forward to reduce impacts on sockeye salmon recruitment.
 This project was conducted in collaboration with the Province of British Columbia (Ministry of Water, Land and Resource Stewardship), and Simon Fraser University.</t>
-  </si>
-  <si>
-    <t>Electrofishing and angling was conducted in the spring to target SMB as they move to near-shore habitat to build nests and spawn. The perimeter of Cultus Lake was divided into quadrants (Figure 1) and swept with a boat electrofishing unit to target spawning SMB. In 2023, ten consecutive days of electrofishing were conducted (June 1-10, 2023), and all SMB captured (by electrofishing and angling) were implanted with a PIT tag and released to get an initial baseline of the population in 2024. A subset of SMB (n=25) were also implanted with acoustic transmitters to track movements within the lake, and downstream movement from the lake (acoustic receivers also deployed in 2023 in various locations). In 2024, two consecutive days (east side of lake day one; west side of lake day two) of electrofishing and angling were conducted for six consecutive weeks (May 9 - June 7, 2024), and all SMB were euthanized to get a PIT tag recovery sample and to see how the population responded to the cull the following year. In 2025, operations were conducted in two day intervals, for seven consecutive weeks (May 1 - June 13, 2025). For the first two weeks of the project all SMB were euthanized to reduce the spawning potential of the population, and for subsequent weeks 25% of all SMB were implanted with PIT tags and released. A subset of 44 SMB were also impl anted with acoustic transmitters to track movements within, and from Cultus Lake. A total of 3,654 biological samples (length, weight (Figure 2); subset of stomach contents (Figure 3), scales, otoliths) were collected from SMB between 2023-2025. Of these samples, 268 stomach samples, 2,069 scale samples, and 20 otoliths samples were collected. Age analysis and acoustic tracking results are pending, and will be included in the final report (written by SFU).
-Between 2023 and 2025, a total of 6,650 SMB were captured by a combination of electrofishing and angling (942 in 2023, 1,616 in 2024, 4,092 in 2025; 95% by electrofishing, 5% by angling). A total of 1,469 PIT tags were deployed (897 in 2023, 572 in 2025), and 69 acoustic tags were surgically implanted in SMB (25 in 2023, 44 in 2025). Of the PIT tags deployed in 2023, 47 were recaptured in 2024 (4.8% recovery) and 12 were recaptured in 2025 (1.2% recovery), giving a rough population estimate of approximately 16,000 SMB in 2024. However, observations from staff at the Cultus Lake Laboratory, the Province of BC, and anglers have indicated a significant portion of the population occupy habitat at depths that preclude SMB from capture by electrofishing, thus, this estimate is likely biased low. The PIT tags deployed in 2025 have yet to be captured in 2026, therefore a current population estimate is unavailable at this time. It should be noted that in 2023, a total of two pumpkinseed were captured during the electrofishing program. In 2024 the number increased to 60, and in 2025 increased to 2,553. Further to this, the capture of pumpkinseed was incidental as there is some overlap in habitat with SMB, and if efforts were targeted for pumpkinseed (i.e. heavily vegetated near-shore habitat), those numbers would be higher. The rapid increase in pumpkinseed bycatch over the course of this work is alarming and should be investigated in future years.
-The subset of stomach samples taken, approximately 10% of samples contained juvenile salmonids (fry or smolt stage), and 2% contained sculpins. It is noted that many stomach samples were at an advanced stage of digestion therefore these estimates are biased low. Acoustic tracking of SMB is ongoing and will be discussed in the final report. However, between 2024 and 2025 a total of 17 SMB were captured at the DFO-operated smolt enumeration fence (run March - June annually), indicating some downstream movement of SMB in Sweltzer Creek to the Vedder River (tributary to the Fraser River). At this time there are no confirmed reports of SMB in the Vedder or Fraser rivers, however, as the population in Cultus Lake expands, downstream colonization is likely.
-The following results, in addition to acoustic tracking data, an evaluation of suppression methods (paired with feedback from the public and social survey results), and up-to-date SMB population estimates will be presented in the final report written by SFU, DFO and the Province of BC in 2027.</t>
   </si>
   <si>
     <t>This work has highlighted the Cultus Lake ecosystem is in peril with the introduction and expansion of not only SMB, but also pumpkinseed, threatening two endangered species (sockeye salmon and pygmy sculpin) and a variety of other native pacific salmonid populations (Chinook, coho, chum, pink, trout sp.). Cultus Lake is a unique ecosystem that is also one of the most popular recreational lakes in the lower Fraser watershed and concurrently faces other threats (e.g. eutrophication/water quality issues, invasive plant encroachment) that likely cumulatively impact native species within the lake, particularly those of conservation concern with severely depressed abundance. Further to this, the presence of SMB and pumpkinseed in Cultus Lake threatens the entire lower Fraser watershed as downstream movement from this source population has already been detected at the DFO juvenile enumeration fence for two consecutive years (2024 and 2025).
@@ -2899,12 +2893,6 @@
     <t>Thompson Rivers University (TRU): Dr Brian Heise, Selena Carl (MSc student), Torrie Bell (MSc student); Okanagan Nation Alliance (ONA): Elinor McGrath</t>
   </si>
   <si>
-    <t>*Habitat use and survival*
-Subyearling Chinook (n=547) raised in the kÅ‚ cpÌ“É™lkÌ“ stimÌ“ hatchery were implanted with ATS SS400 injectable acoustic transmitters. They were released in two groups, with group A (n=273) released in the Okanagan River below Vertical Drop Structure (VDS) 17 and above Vaseux Lake, and group B (n=274) released downstream of Vaseux lake below McIntyre Dam. A network of 15 ATS SR3001 autonomous receivers was deployed from Okanagan Falls to Osoyoos Lake between 21 May and 8 August, 2024). Receivers were clustered into 7 detection sites, placed to form acoustic "gates" at lake inlets and outlets, narrows and channel constrictions, and potential rearing/migration corridors. An ATS SR3017 mobile receiver with hydrophone was used to survey shallow side channels, deeper offshore areas beyond stationary coverage, and upstream and downstream of VDS structures. The proportion of fish detected decreased sharply for both release groups as fish migrated downstream, which translated to low survival in both release groups. Tag burden was not deemed a source of direct mortality, but could have increased susceptibility to predation.
-*Smallmouth bass diet and predation*
-Targeted angling was conducted in the Okanagan River, Vaseux Lake, Osoyoos Lake from May 3 to August 7, 2024. The dominant species captured were smallmouth bass, which comprised 76% of the total catch (n=196), followed by Northern Pikeminnow (16%, n=41) and Yellow Perch (4%, n=11). There was a spatial shift in the distribution of smallmouth bass caught during the study. In May, less than half (45%) of smallmouth bass were caught at Vertical Drop Structures (VDS), but the proportion of smallmouth bass captured at VDS structures increased to 100% and 80% in June and July, respectively. Bass were observed utilizing rocky substrate and rip rap below the VDS structures to ambush prey. Diet content visual analysis was performed on a subsample of 73 of the total 196 smallmouth bass. A total of 162 fish stomach samples were sent for DNA barcode sequencing. Chinook salmon was only detected once in the DNA samples, but direct evidence of bass predation on juvenile Chinook was obtained by recovery of an acoustic tag used in the juvenile migration and habitat use study. DNA metabarcoding identified a diverse assemblage of 146 unique prey taxa. Aquatic insects (Diptera, Ephemeroptera, Trichoptera), invasive fish (smallmouth bass, yellow perch, common carp), and native fish (prickly sculpin, mountain whitefish, sockeye/kokanee, Chinook) were the most common prey items in smallmouth bass stomach contents.</t>
-  </si>
-  <si>
     <t>Province of British Columbia; Simon Fraser University</t>
   </si>
   <si>
@@ -3207,6 +3195,18 @@
   <si>
     <t>Rosen, S., Bianucci, L., Jackson, J.M., Hare, A., Greengrove, C., Monks, R., Bartlett, M. and Dick, J., 2022. Seasonal near-surface hypoxia in a temperate fjord in Clayoquot Sound, British Columbia. Frontiers in Marine Science, 9, p.1000041.
 Foreman, M.G.G., Chandler, P.C., Bianucci, L., Wan, D., Krassovski, M.V., Thupaki, P., Cooper, G. and Lin, Y., 2024. A circulation model for inlets along the central West Coast of Vancouver Island. Atmosphere-Ocean, 62(1), pp.58-89.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Habitat use and survival
+Subyearling Chinook (n=547) raised in the kł cp̓əlk̓ stim̓ hatchery were implanted with ATS SS400 injectable acoustic transmitters. They were released in two groups, with group A (n=273) released in the Okanagan River below Vertical Drop Structure (VDS) 17 and above Vaseux Lake, and group B (n=274) released downstream of Vaseux lake below McIntyre Dam. A network of 15 ATS SR3001 autonomous receivers was deployed from Okanagan Falls to Osoyoos Lake between 21 May and 8 August, 2024). Receivers were clustered into 7 detection sites, placed to form acoustic “gates” at lake inlets and outlets, narrows and channel constrictions, and potential rearing/migration corridors. An ATS SR3017 mobile receiver with hydrophone was used to survey shallow side channels, deeper offshore areas beyond stationary coverage, and upstream and downstream of VDS structures. The proportion of fish detected decreased sharply for both release groups as fish migrated downstream, which translated to low survival in both release groups. Tag burden was not deemed a source of direct mortality, but could have increased susceptibility to predation. 
+Smallmouth bass diet and predation
+Targeted angling was conducted in the Okanagan River, Vaseux Lake, Osoyoos Lake from May 3 to August 7, 2024. The dominant species captured were smallmouth bass, which comprised 76% of the total catch (n=196), followed by Northern Pikeminnow (16%, n=41) and Yellow Perch (4%, n=11). There was a spatial shift in the distribution of smallmouth bass caught during the study. In May, less than half (45%) of smallmouth bass were caught at Vertical Drop Structures (VDS), but the proportion of smallmouth bass captured at VDS structures increased to 100% and 80% in June and July, respectively. Bass were observed utilizing rocky substrate and rip rap below the VDS structures to ambush prey. Diet content visual analysis was performed on a subsample of 73 of the total 196 smallmouth bass. A total of 162 fish stomach samples were sent for DNA barcode sequencing. Chinook salmon was only detected once in the DNA samples, but direct evidence of bass predation on juvenile Chinook was obtained by recovery of an acoustic tag used in the juvenile migration and habitat use study. DNA metabarcoding identified a diverse assemblage of 146 unique prey taxa. Aquatic insects (Diptera,  Ephemeroptera, Trichoptera), invasive fish (smallmouth bass, yellow perch, common carp), and native fish (prickly sculpin, mountain whitefish, sockeye/kokanee, Chinook) were the most common prey items in smallmouth bass stomach contents. </t>
+  </si>
+  <si>
+    <t>Electrofishing and angling was conducted in the spring to target SMB as they move to near-shore habitat to build nests and spawn. The perimeter of Cultus Lake was divided into quadrants (Figure 1) and swept with a boat electrofishing unit to target spawning SMB. In 2023, ten consecutive days of electrofishing were conducted (June 1-10, 2023), and all SMB captured (by electrofishing and angling) were implanted with a PIT tag and released to get an initial baseline of the population in 2024. A subset of SMB (n=25) were also implanted with acoustic transmitters to track movements within the lake, and downstream movement from the lake (acoustic receivers also deployed in 2023 in various locations). In 2024, two consecutive days (east side of lake day one; west side of lake day two) of electrofishing and angling were conducted for six consecutive weeks (May 9 - June 7, 2024), and all SMB were euthanized to get a PIT tag recovery sample and to see how the population responded to the cull the following year. In 2025, operations were conducted in two day intervals, for seven consecutive weeks (May 1 - June 13, 2025). For the first two weeks of the project all SMB were euthanized to reduce the spawning potential of the population, and for subsequent weeks 25% of all SMB were implanted with PIT tags and released. A subset of 44 SMB were also implanted with acoustic transmitters to track movements within, and from Cultus Lake. A total of 3,654 biological samples (length, weight (Figure 2); subset of stomach contents (Figure 3), scales, otoliths) were collected from SMB between 2023-2025. Of these samples, 268 stomach samples, 2,069 scale samples, and 20 otoliths samples were collected. Age analysis and acoustic tracking results are pending, and will be included in the final report (written by SFU).
+Between 2023 and 2025, a total of 6,650 SMB were captured by a combination of electrofishing and angling (942 in 2023, 1,616 in 2024, 4,092 in 2025; 95% by electrofishing, 5% by angling). A total of 1,469 PIT tags were deployed (897 in 2023, 572 in 2025), and 69 acoustic tags were surgically implanted in SMB (25 in 2023, 44 in 2025). Of the PIT tags deployed in 2023, 47 were recaptured in 2024 (4.8% recovery) and 12 were recaptured in 2025 (1.2% recovery), giving a rough population estimate of approximately 16,000 SMB in 2024. However, observations from staff at the Cultus Lake Laboratory, the Province of BC, and anglers have indicated a significant portion of the population occupy habitat at depths that preclude SMB from capture by electrofishing, thus, this estimate is likely biased low. The PIT tags deployed in 2025 have yet to be captured in 2026, therefore a current population estimate is unavailable at this time. It should be noted that in 2023, a total of two pumpkinseed were captured during the electrofishing program. In 2024 the number increased to 60, and in 2025 increased to 2,553. Further to this, the capture of pumpkinseed was incidental as there is some overlap in habitat with SMB, and if efforts were targeted for pumpkinseed (i.e. heavily vegetated near-shore habitat), those numbers would be higher. The rapid increase in pumpkinseed bycatch over the course of this work is alarming and should be investigated in future years.
+The subset of stomach samples taken, approximately 10% of samples contained juvenile salmonids (fry or smolt stage), and 2% contained sculpins. It is noted that many stomach samples were at an advanced stage of digestion therefore these estimates are biased low. Acoustic tracking of SMB is ongoing and will be discussed in the final report. However, between 2024 and 2025 a total of 17 SMB were captured at the DFO-operated smolt enumeration fence (run March - June annually), indicating some downstream movement of SMB in Sweltzer Creek to the Vedder River (tributary to the Fraser River). At this time there are no confirmed reports of SMB in the Vedder or Fraser rivers, however, as the population in Cultus Lake expands, downstream colonization is likely.
+The following results, in addition to acoustic tracking data, an evaluation of suppression methods (paired with feedback from the public and social survey results), and up-to-date SMB population estimates will be presented in the final report written by SFU, DFO and the Province of BC in 2027.</t>
   </si>
 </sst>
 </file>
@@ -4020,7 +4020,7 @@
     <col min="14" max="14" width="11.42578125" style="2"/>
     <col min="15" max="15" width="11.85546875" style="2" customWidth="1"/>
     <col min="16" max="16" width="13.42578125" style="2" customWidth="1"/>
-    <col min="17" max="17" width="19.140625" style="2" customWidth="1"/>
+    <col min="17" max="17" width="47.85546875" style="2" customWidth="1"/>
     <col min="18" max="18" width="11.42578125" style="2"/>
     <col min="19" max="19" width="12.85546875" style="2" customWidth="1"/>
     <col min="20" max="20" width="15.7109375" style="2" customWidth="1"/>
@@ -4104,7 +4104,7 @@
         <v>22</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>23</v>
@@ -4134,7 +4134,7 @@
         <v>31</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>32</v>
@@ -4184,7 +4184,7 @@
         <v>44</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>45</v>
@@ -4193,13 +4193,13 @@
         <v>46</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>47</v>
@@ -4234,13 +4234,13 @@
         <v>2400</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>56</v>
@@ -4249,7 +4249,7 @@
         <v>57</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>58</v>
@@ -4261,19 +4261,19 @@
         <v>59</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="P4" s="1" t="s">
         <v>60</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="R4" s="1" t="s">
         <v>61</v>
@@ -4282,10 +4282,10 @@
         <v>62</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -4299,16 +4299,16 @@
         <v>2401</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>65</v>
@@ -4340,7 +4340,7 @@
         <v>72</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -4381,7 +4381,7 @@
         <v>81</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>82</v>
@@ -4393,7 +4393,7 @@
         <v>84</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="R6" s="1" t="s">
         <v>85</v>
@@ -4419,7 +4419,7 @@
         <v>2403</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>90</v>
@@ -4440,7 +4440,7 @@
         <v>95</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="L7" s="4" t="s">
         <v>96</v>
@@ -4449,7 +4449,7 @@
         <v>96</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="O7" s="4" t="s">
         <v>97</v>
@@ -4458,19 +4458,19 @@
         <v>98</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="S7" s="5" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="8" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4490,31 +4490,31 @@
         <v>101</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>102</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>103</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>104</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="O8" s="4" t="s">
         <v>105</v>
@@ -4523,7 +4523,7 @@
         <v>106</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="R8" s="4" t="s">
         <v>107</v>
@@ -4532,10 +4532,10 @@
         <v>108</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="U8" s="5" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -4552,19 +4552,19 @@
         <v>110</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>111</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>65</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>112</v>
@@ -4573,13 +4573,13 @@
         <v>113</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>114</v>
@@ -4588,7 +4588,7 @@
         <v>115</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="R9" s="1" t="s">
         <v>116</v>
@@ -4600,7 +4600,7 @@
         <v>118</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -4620,40 +4620,40 @@
         <v>121</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>122</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>123</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>124</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>125</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="R10" s="1" t="s">
         <v>126</v>
@@ -4679,13 +4679,13 @@
         <v>2407</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>131</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>132</v>
@@ -4703,10 +4703,10 @@
         <v>56</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="N11" s="4" t="s">
         <v>136</v>
@@ -4727,10 +4727,10 @@
         <v>141</v>
       </c>
       <c r="T11" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="U11" s="4" t="s">
         <v>540</v>
-      </c>
-      <c r="U11" s="4" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -4744,13 +4744,13 @@
         <v>2408</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>56</v>
@@ -4777,7 +4777,7 @@
         <v>146</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>147</v>
@@ -4786,10 +4786,10 @@
         <v>148</v>
       </c>
       <c r="T12" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="U12" s="1" t="s">
         <v>544</v>
-      </c>
-      <c r="U12" s="1" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
@@ -4828,7 +4828,7 @@
         <v>156</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>157</v>
@@ -4849,10 +4849,10 @@
         <v>162</v>
       </c>
       <c r="T13" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="U13" s="1" t="s">
         <v>546</v>
-      </c>
-      <c r="U13" s="1" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -4872,10 +4872,10 @@
         <v>165</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>31</v>
@@ -4893,7 +4893,7 @@
         <v>31</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="N14" s="1" t="s">
         <v>31</v>
@@ -4917,7 +4917,7 @@
         <v>172</v>
       </c>
       <c r="U14" s="5" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
@@ -4931,7 +4931,7 @@
         <v>2412</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>174</v>
@@ -4943,34 +4943,34 @@
         <v>176</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>177</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>56</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="O15" s="1" t="s">
         <v>178</v>
       </c>
       <c r="P15" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="Q15" s="1" t="s">
         <v>549</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>550</v>
       </c>
       <c r="R15" s="1" t="s">
         <v>179</v>
@@ -4979,10 +4979,10 @@
         <v>180</v>
       </c>
       <c r="T15" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="U15" s="1" t="s">
         <v>551</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -4996,13 +4996,13 @@
         <v>2413</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>182</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>183</v>
@@ -5020,13 +5020,13 @@
         <v>186</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="O16" s="1" t="s">
         <v>187</v>
@@ -5044,7 +5044,7 @@
         <v>191</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="U16" s="1" t="s">
         <v>192</v>
@@ -5067,7 +5067,7 @@
         <v>195</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>196</v>
@@ -5091,10 +5091,10 @@
         <v>104</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="P17" s="1" t="s">
         <v>201</v>
@@ -5141,7 +5141,7 @@
         <v>212</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>213</v>
@@ -5153,10 +5153,10 @@
         <v>215</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="O18" s="1" t="s">
         <v>216</v>
@@ -5165,19 +5165,19 @@
         <v>217</v>
       </c>
       <c r="Q18" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="R18" s="1" t="s">
         <v>557</v>
-      </c>
-      <c r="R18" s="1" t="s">
-        <v>558</v>
       </c>
       <c r="S18" s="1" t="s">
         <v>218</v>
       </c>
       <c r="T18" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="U18" s="1" t="s">
         <v>559</v>
-      </c>
-      <c r="U18" s="1" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -5191,13 +5191,13 @@
         <v>2418</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>209</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>220</v>
@@ -5206,7 +5206,7 @@
         <v>221</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>222</v>
@@ -5218,31 +5218,31 @@
         <v>223</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="O19" s="1" t="s">
         <v>224</v>
       </c>
       <c r="P19" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="Q19" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="Q19" s="1" t="s">
+      <c r="R19" s="1" t="s">
         <v>563</v>
-      </c>
-      <c r="R19" s="1" t="s">
-        <v>564</v>
       </c>
       <c r="S19" s="1" t="s">
         <v>225</v>
       </c>
       <c r="T19" s="5" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -5256,22 +5256,22 @@
         <v>2421</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>227</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>197</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>228</v>
@@ -5280,13 +5280,13 @@
         <v>56</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>229</v>
@@ -5295,7 +5295,7 @@
         <v>230</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>231</v>
@@ -5304,10 +5304,10 @@
         <v>232</v>
       </c>
       <c r="T20" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="U20" s="1" t="s">
         <v>568</v>
-      </c>
-      <c r="U20" s="1" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
@@ -5327,13 +5327,13 @@
         <v>235</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>196</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>236</v>
@@ -5348,10 +5348,10 @@
         <v>238</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>239</v>
@@ -5372,7 +5372,7 @@
         <v>244</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -5392,10 +5392,10 @@
         <v>247</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>248</v>
@@ -5410,22 +5410,22 @@
         <v>251</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="O22" s="1" t="s">
         <v>252</v>
       </c>
       <c r="P22" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="Q22" s="1" t="s">
         <v>572</v>
-      </c>
-      <c r="Q22" s="1" t="s">
-        <v>573</v>
       </c>
       <c r="R22" s="1" t="s">
         <v>253</v>
@@ -5437,7 +5437,7 @@
         <v>255</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -5451,13 +5451,13 @@
         <v>2425</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>257</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>258</v>
@@ -5475,10 +5475,10 @@
         <v>261</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="N23" s="1" t="s">
         <v>262</v>
@@ -5499,10 +5499,10 @@
         <v>267</v>
       </c>
       <c r="T23" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="U23" s="1" t="s">
         <v>575</v>
-      </c>
-      <c r="U23" s="1" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
@@ -5516,13 +5516,13 @@
         <v>2426</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>269</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>270</v>
@@ -5552,10 +5552,10 @@
         <v>278</v>
       </c>
       <c r="P24" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="Q24" s="1" t="s">
         <v>577</v>
-      </c>
-      <c r="Q24" s="1" t="s">
-        <v>578</v>
       </c>
       <c r="R24" s="1" t="s">
         <v>279</v>
@@ -5567,7 +5567,7 @@
         <v>281</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -5587,13 +5587,13 @@
         <v>182</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>284</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>177</v>
@@ -5605,13 +5605,13 @@
         <v>286</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="O25" s="1" t="s">
         <v>287</v>
@@ -5620,7 +5620,7 @@
         <v>288</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="R25" s="1" t="s">
         <v>289</v>
@@ -5632,7 +5632,7 @@
         <v>291</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -5646,16 +5646,16 @@
         <v>2430</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>293</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>271</v>
@@ -5673,7 +5673,7 @@
         <v>297</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="N26" s="1" t="s">
         <v>298</v>
@@ -5682,22 +5682,22 @@
         <v>299</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="S26" s="1" t="s">
         <v>300</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="U26" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -5714,19 +5714,19 @@
         <v>302</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>303</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>250</v>
@@ -5735,13 +5735,13 @@
         <v>186</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="O27" s="1" t="s">
         <v>304</v>
@@ -5762,7 +5762,7 @@
         <v>309</v>
       </c>
       <c r="U27" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -5779,7 +5779,7 @@
         <v>311</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>312</v>
@@ -5788,28 +5788,28 @@
         <v>313</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>250</v>
       </c>
       <c r="K28" s="9" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="P28" s="1" t="s">
         <v>314</v>
@@ -5827,7 +5827,7 @@
         <v>318</v>
       </c>
       <c r="U28" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -5874,7 +5874,7 @@
         <v>328</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="P29" s="1" t="s">
         <v>329</v>
@@ -5906,7 +5906,7 @@
         <v>2435</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>336</v>
@@ -5957,7 +5957,7 @@
         <v>351</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -5977,7 +5977,7 @@
         <v>354</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>355</v>
@@ -5995,10 +5995,10 @@
         <v>359</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="N31" s="1" t="s">
         <v>360</v>
@@ -6022,7 +6022,7 @@
         <v>366</v>
       </c>
       <c r="U31" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -6042,7 +6042,7 @@
         <v>369</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>338</v>
@@ -6069,7 +6069,7 @@
         <v>376</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>377</v>
@@ -6101,13 +6101,13 @@
         <v>2439</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>384</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>385</v>
@@ -6116,28 +6116,28 @@
         <v>386</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="K33" s="1" t="s">
         <v>387</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="O33" s="1" t="s">
         <v>388</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="Q33" s="1" t="s">
         <v>389</v>
@@ -6152,7 +6152,7 @@
         <v>392</v>
       </c>
       <c r="U33" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -6172,7 +6172,7 @@
         <v>395</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>396</v>
@@ -6204,8 +6204,8 @@
       <c r="P34" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="Q34" s="1" t="s">
-        <v>594</v>
+      <c r="Q34" s="5" t="s">
+        <v>639</v>
       </c>
       <c r="R34" s="1" t="s">
         <v>403</v>
@@ -6217,7 +6217,7 @@
         <v>405</v>
       </c>
       <c r="U34" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -6237,7 +6237,7 @@
         <v>408</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>409</v>
@@ -6258,7 +6258,7 @@
         <v>410</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="N35" s="1" t="s">
         <v>412</v>
@@ -6269,25 +6269,25 @@
       <c r="P35" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="Q35" s="1" t="s">
+      <c r="Q35" s="5" t="s">
+        <v>640</v>
+      </c>
+      <c r="R35" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="R35" s="1" t="s">
+      <c r="S35" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="S35" s="1" t="s">
-        <v>417</v>
-      </c>
       <c r="T35" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="U35" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B36" s="7">
         <v>46083</v>
@@ -6296,25 +6296,25 @@
         <v>2447</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E36" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>420</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>78</v>
       </c>
       <c r="I36" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="J36" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>421</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>104</v>
@@ -6323,36 +6323,36 @@
         <v>104</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="N36" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="O36" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="O36" s="1" t="s">
+      <c r="P36" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="P36" s="1" t="s">
+      <c r="Q36" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="Q36" s="1" t="s">
+      <c r="R36" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="R36" s="1" t="s">
+      <c r="S36" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="S36" s="1" t="s">
+      <c r="T36" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="T36" s="1" t="s">
-        <v>428</v>
-      </c>
       <c r="U36" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B37" s="7">
         <v>46083</v>
@@ -6361,13 +6361,13 @@
         <v>2448</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="E37" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>431</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>56</v>
@@ -6376,48 +6376,48 @@
         <v>197</v>
       </c>
       <c r="I37" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="J37" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="J37" s="1" t="s">
+      <c r="K37" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="L37" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="M37" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="L37" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="M37" s="1" t="s">
+      <c r="N37" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="O37" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="N37" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="O37" s="1" t="s">
+      <c r="P37" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="P37" s="1" t="s">
+      <c r="Q37" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="Q37" s="1" t="s">
+      <c r="R37" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="S37" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="R37" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="S37" s="1" t="s">
+      <c r="T37" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="T37" s="1" t="s">
+      <c r="U37" s="1" t="s">
         <v>440</v>
-      </c>
-      <c r="U37" s="1" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B38" s="7">
         <v>46083</v>
@@ -6426,63 +6426,63 @@
         <v>2449</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E38" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="H38" s="1" t="s">
+      <c r="I38" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="J38" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="I38" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="J38" s="1" t="s">
+      <c r="K38" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="L38" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="L38" s="1" t="s">
+      <c r="M38" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="M38" s="1" t="s">
+      <c r="N38" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="N38" s="1" t="s">
+      <c r="O38" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="O38" s="1" t="s">
+      <c r="P38" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="P38" s="1" t="s">
+      <c r="Q38" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="Q38" s="1" t="s">
+      <c r="R38" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="R38" s="1" t="s">
+      <c r="S38" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="S38" s="1" t="s">
+      <c r="T38" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="T38" s="1" t="s">
+      <c r="U38" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="U38" s="1" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B39" s="7">
         <v>46083</v>
@@ -6491,13 +6491,13 @@
         <v>2451</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>369</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>338</v>
@@ -6506,7 +6506,7 @@
         <v>78</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J39" s="1" t="s">
         <v>325</v>
@@ -6515,39 +6515,39 @@
         <v>186</v>
       </c>
       <c r="L39" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="N39" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="M39" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="N39" s="1" t="s">
+      <c r="O39" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="O39" s="1" t="s">
+      <c r="P39" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="P39" s="1" t="s">
+      <c r="Q39" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="Q39" s="1" t="s">
+      <c r="R39" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="S39" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="R39" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="S39" s="1" t="s">
+      <c r="T39" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="T39" s="1" t="s">
-        <v>465</v>
-      </c>
       <c r="U39" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B40" s="7">
         <v>46083</v>
@@ -6556,7 +6556,7 @@
         <v>2452</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>369</v>
@@ -6571,48 +6571,48 @@
         <v>197</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="J40" s="1" t="s">
         <v>325</v>
       </c>
       <c r="K40" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="L40" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="L40" s="1" t="s">
+      <c r="M40" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="M40" s="1" t="s">
+      <c r="N40" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="N40" s="1" t="s">
+      <c r="O40" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="O40" s="1" t="s">
+      <c r="P40" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="P40" s="1" t="s">
+      <c r="Q40" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="R40" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="Q40" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="R40" s="1" t="s">
+      <c r="S40" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="S40" s="1" t="s">
+      <c r="T40" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="T40" s="1" t="s">
-        <v>477</v>
-      </c>
       <c r="U40" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B41" s="7">
         <v>46083</v>
@@ -6621,63 +6621,63 @@
         <v>2504</v>
       </c>
       <c r="D41" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="F41" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="G41" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="G41" s="1" t="s">
+      <c r="H41" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="I41" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="J41" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="J41" s="1" t="s">
+      <c r="K41" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="K41" s="1" t="s">
+      <c r="L41" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="L41" s="1" t="s">
+      <c r="M41" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="M41" s="1" t="s">
+      <c r="N41" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="O41" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="N41" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="O41" s="1" t="s">
+      <c r="P41" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="P41" s="1" t="s">
+      <c r="Q41" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="Q41" s="1" t="s">
+      <c r="R41" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="R41" s="1" t="s">
+      <c r="S41" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="S41" s="1" t="s">
+      <c r="T41" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="T41" s="1" t="s">
+      <c r="U41" s="1" t="s">
         <v>493</v>
-      </c>
-      <c r="U41" s="1" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B42" s="7">
         <v>46083</v>
@@ -6686,16 +6686,16 @@
         <v>2513</v>
       </c>
       <c r="D42" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>496</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>605</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>497</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>197</v>
@@ -6710,39 +6710,39 @@
         <v>104</v>
       </c>
       <c r="L42" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="O42" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="M42" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="N42" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="O42" s="1" t="s">
+      <c r="P42" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="P42" s="1" t="s">
+      <c r="Q42" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="R42" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="S42" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="Q42" s="1" t="s">
+      <c r="T42" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="U42" s="1" t="s">
         <v>606</v>
-      </c>
-      <c r="R42" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="S42" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="T42" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="U42" s="1" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B43" s="7">
         <v>46083</v>
@@ -6751,22 +6751,22 @@
         <v>2545</v>
       </c>
       <c r="D43" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="F43" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="G43" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="H43" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="I43" s="1" t="s">
         <v>508</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>509</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>31</v>
@@ -6784,30 +6784,30 @@
         <v>31</v>
       </c>
       <c r="O43" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="P43" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="P43" s="1" t="s">
+      <c r="Q43" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="Q43" s="1" t="s">
+      <c r="R43" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="R43" s="1" t="s">
+      <c r="S43" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="S43" s="1" t="s">
+      <c r="T43" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="T43" s="1" t="s">
-        <v>515</v>
-      </c>
       <c r="U43" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B44" s="7">
         <v>46083</v>
@@ -6816,13 +6816,13 @@
         <v>3682</v>
       </c>
       <c r="D44" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="F44" s="1" t="s">
         <v>518</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>519</v>
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
@@ -6835,25 +6835,25 @@
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
       <c r="O44" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="P44" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="P44" s="1" t="s">
+      <c r="Q44" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="Q44" s="1" t="s">
+      <c r="R44" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="R44" s="1" t="s">
+      <c r="S44" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="S44" s="1" t="s">
+      <c r="T44" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="T44" s="1" t="s">
-        <v>525</v>
-      </c>
       <c r="U44" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/pssi_form_data_altered.xlsx
+++ b/data/processed/pssi_form_data_altered.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ennsj\Documents\PSSI-final-tech-report\data\processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FF8C8F2-6170-4789-9100-586184E57A0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CCD6B92-F2B7-4073-96DE-24623086BF1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="639">
   <si>
     <t>source_file</t>
   </si>
@@ -1042,9 +1042,6 @@
     <t>All freshwater phases</t>
   </si>
   <si>
-    <t>Fraser</t>
-  </si>
-  <si>
     <t>CK-03, CK-04, CK-05, CK-06, CK-07, CK-08, CK-09, CK-10, CK-11, CK-12, CK-14, CK-16, CK-17, CK-18, CK-19, CO-05, CO-07, CO-08, CO-09, CO-48, SEL-03-02, SEL-03-03, SEL-03-04, SEL-04-01, SEL-05-02, SEL-06-07, SEL-06-10, SEL-06-11, SEL-06-13, SEL-06-14, SEL-06-16, SEL-07-01, SEL-09-xx, SEL-10-01, SEL-10-03, SER-02, CK-13, CK-15, CK-82, CM-02, CO-04, CO-47, PKE-9005, PKO-01, SEL-03-01, SEL-03-05, SEL-06-01, SEL-06-02,
 SEL-06-20, SEL-09-02, SEL-09-03, SER-03</t>
   </si>
@@ -1066,10 +1063,6 @@
   <si>
     <t>This project is the first to provide spatially extensive estimates of human activity and climate change threats that are directly linked to salmon, SAR, and their habitats at the stream reach scale. The approaches used to estimate each of the indicators provide an initial broad-scale standardized framework that can be applied to characterize threats throughout the Pacific Region. Within the FRB, we observed the highest threats in the Lower Fraser and interior plateau, and specifically, within the Nicola River, Guichon Creek, and San Jose River. Overall, roads were the greatest contributor to human activity-based threats, disturbing in-stream habitats, riparian areas, and contributing to sediment and nutrient loading. These results improve our understanding of the spatial distribution and relative magnitude of threats across the FRB, providing a foundation for predicting population-level impacts from cumulative effects and life-cycle modelling.
 A major source of uncertainty is the spatial accuracy of the BC Freshwater Atlas. Known issues to the FWA include overestimates of headwater streams in interior regions, misaligned stream delineations and large river catchment areas. Each of the individual threat scores have their own uncertainties and limitations, as detailed in Table 2 of Iacarella et al. (2025). In general, the input data are subject to limitations arising from potentially misclassified land cover or land use, features included in datasets but not present on the landscape, and unmapped activities or features, which introduce uncertainty into individual threat scores and the cumulative score. An additional source of uncertainty is the unresolved habitat use and distribution of salmon and SAR within the FRB. The approach used to combine individual threats into a cumulative threat score (e.g., addition, multiplication, etc.) is another source of uncertainty that can be evaluated in future work by modelling population responses to individual and cumulative threats.</t>
-  </si>
-  <si>
-    <t>Although our threat estimates represent the mechanisms by which salmon and freshwater SAR are affected, the magnitude at which these threats influence salmon population dynamics remains unknown. To address this gap, we are continuing to refine existing threat estimates and developing new threats that are explicitly linked to stressor-response functions for cumulative effects and life-cycle modelling. For example, we have developed additional riparian disturbance metrics that better capture the impacts to riparian function (e.g., large-woody debris recruitment, disturbance to stream-shading, riparian filtering), which were not included in the original report. Moreover, we are developing a stage-structured population model for Interior Fraser Coho (IFC) to estimate how stressors (estimated threats) are influencing the population across their freshwater life stages. For this work, we are utilising the Cumulative Effects Model for Prioritizing Recovery Actions (CEMPRA), which applies stressor-response functions to account for the impact of stressors on vital rates and the overall population overtime and under different climate change and mitigation scenarios (Bayly et al*.* 2024).
-Additional next steps for this work include expanding the cumulative threats model to other watersheds in the Pacific Region. To date, the model has also been applied to the Upper Bulkley Watershed to aid in salmon habitat restoration planning. Validation is an important step of most modelling exercises, though is often not a standard component of cumulative effect assessments (Halpern and Fujita 2013). Validating these threats through field verification and in situ data would be beneficial for threats that involve applied relationships and estimations, such as the flow accumulated loadings (i.e., nutrients, pollution, sedimentation). Future work could re-run the model at regular intervals to evaluate change in threats over time. Finally, additional analyses could quantify uncertainty in modelled threats and evaluate underlying assumptions through sensitivity tests.</t>
   </si>
   <si>
     <t>2426 PSSI Science Project Reporting Template Oct2025_Sakinaw Sockeye_KP-KF.docx</t>
@@ -1570,9 +1563,6 @@
   </si>
   <si>
     <t>Okanagan</t>
-  </si>
-  <si>
-    <t>Canadian Okanagan</t>
   </si>
   <si>
     <t>CK-01</t>
@@ -1604,11 +1594,6 @@
 - using predator-detecting acoustic tags to determine juvenile mortality from predation and finer-scale movement data to elucidate habitat use throughout the migration corridor;
 - estimating the smallmouth bass population size in the Okanagan River and Lake system to quantify the predation pressure on juvenile Chinook; and
 - understanding the role of predation from other native and invasive piscivorous fish and avian predators on juvenile Chinook survival.</t>
-  </si>
-  <si>
-    <t>Figure 1. Proportion of acoustic tagged juvenile Chinook detected at downstream detections sites and resulting survival curves for release Group A (n= 273 upstream of Vaseux Lake) and B (n=274 downstream of McIntyre Dam). In both release groups, there is a sharp decline in the proportion of fish detected and survival is low during the downstream migration.
-Figure 2. DNA metabarcoding stomach content analysis of n=162 smallmouth bass (*Micropterus dolomieu*) captured at various locations in the Okanagan River and Lake system. Aquatic insects (Diptera, Ephemeroptera, Trichoptera), invasive fish (smallmouth bass, yellow perch, common carp), and native fish (prickly sculpin, mountain whitefish, Sockeye/kokanee, Chinook) were the most common prey items identified.
-Table 1. Total length (TL) and weight of the 196 smallmouth bass (*Micropterus dolomieu*) captured in the juvenile Chinook predation study. Bass were captured by angling in the Okanagan River and Lake system and were sacrificed upon capture for stomach content analysis.</t>
   </si>
   <si>
     <t>2443 PSSI Science Project Reporting Template_Project ID.docx</t>
@@ -2757,33 +2742,6 @@
     <t>Chinook Salmon *OncorhynchusÂ tshawytscha*</t>
   </si>
   <si>
-    <t>Low flows during summer months can be an important bottleneck for stream-rearing rearing salmon. Determining how much water fish need is therefore a critical management question, especially given rising human water use and climate warming. Elevated water temperature is another threat facing stream-rearing salmon that is often linked to low flows. However, conventional modelling tools for determining instream flow needs have generally not explicitly considered temperature. This is a gap for management as it is unclear if current instream flow assessments will apply in a warmer future.
-This project developed an analytical framework to integrate water temperature into habitat simulation models, a widely used tool for determining instream flow needs. We used a bioenergetics framework that relates channel hydraulics (e.g., depth and velocity) and temperature to the daily energy balance of juvenile salmonids. We then applied the approach to 17 coho-rearing streams across the North Thompson watershed, interior BC. This work was collaborative with SecwÃ©pemc Fisheries Commission and Simpcw First Nation and will inform instream flow management through the lens of climate change.</t>
-  </si>
-  <si>
-    <t>We used a habitat simulation model framework that links streamflow to channel hydraulics, then channel hydraulics to fish using bioenergetics. The end result is a matrix of relative habitat availability across combinations of flow and water temperature. This can be used as a tool to support real-time flow and temperature monitoring or be linked to flow and temperature projections under contrasting climate change scenarios. Initial model outputs have been shared with SecwÃ©pemc Fisheries Commission to support drought monitoring in several priority systems.
-Flow-habitat relationships were variable across the different streams, suggesting that generic thresholds of flow (e.g., 20% of mean annual discharge) may not always apply. The combined effect of flow and temperature was also variable, reflecting the complex nonlinear pathways that temperature influences fish.
-While the specific model outputs generated to date are applicable to the North Thompson, the general approach is broadly applicable to other systems where the combined impacts of flow and temperature change are of interest.</t>
-  </si>
-  <si>
-    <t>Railsback, S.F., 2016. Why it is time to put PHABSIM out to pasture.Â *Fisheries*,Â *41*(12), pp.720-725.
-Naman, S.M., Rosenfeld, J.S., Neuswanger, J.R., Enders, E.C., Hayes, J.W., Goodwin, E.O., Jowett, I.G. and Eaton, B.C., 2020. Bioenergetic Habitat Suitability Curves for Instream Flow Modeling: Introducing Userâ€Friendly Software and its Potential Applications.Â *Fisheries*,Â *45*(11), pp.605-613.</t>
-  </si>
-  <si>
-    <t>Figure 1. (a) Human activity and landscape disturbance based additive cumulative threat score, and (b) Climate change additive cumulative threat score for 2040-2060 under RCP 4.5. Blue indicates low threat levels and red indicates high threat levels.
-Figure 2. Tukey's box-whiskers plots of the cumulative threat scores from human activity and landscape disturbance based threats and climate change based threats for all streams in the FRB, (a &amp; b) accessible streams within salmon CUs, and (c &amp; d) delineated stream habitats of fish SAR. Salmon CUs identified as Special Concern, Threatened, or Endangered by COSEWIC were distinguished from those not at risk.
-Figure 3. Median cumulative threat composite scores for watershed groups in the Thompson-Nicola EDU based on the multiplicative value of human activity and landscape disturbance based cumulative threats and modeled environmental favourability for spawning (row a) Chinook, (b) Coho, (c) Pink, and (d) Sockeye Salmon. Modeled environmental favourability probabilities used in the composite score were based on projected (column a) current and (b) future conditions for all stream reaches (â‰¥ 4th order) including inaccessible streams from dams and natural barriers. Watershed groups that are largely inaccessible are identified by hatched lines, and salmon CU boundaries in black outlines. Colour scale indicates increasing need for localized investigation and potential restoration.</t>
-  </si>
-  <si>
-    <t>Bayly, M., Tekatch, A., Rosenfeld, J., Jarvis, L. &amp; Enders, E. 2024. Cumulative Effects Model for Prioritizing Recovery Actions (CEMPRA): User Guide. Documentation prepared by ESSA Technologies Ltd. for the BC Water, Land and Resource S. Available from: https://essatech.github.io/CEMPRA/ [accessed 29 December 2025].
-DFO. 2022. Geospatial mapping tools, indicators, and metrics for fish habitat in the Pacific Region. DFO Can. Sci. Advis. Sec. Sci. Resp. 2022/047.
-Halpern, B.S., and Fujita, R. 2013. Assumptions, challenges, and future directions in cumulative impact analysis. Ecosphere. 4: art131. doi:10.1890/ES13-00181.1
-Halpern, B.S., McLeod, K.L., Rosenberg, A.A., and Crowder, L.B. 2008a. Managing for cumulative impacts in ecosystem-based management through ocean zoning. Ocean Coast. Manage. 51: 203-211. doi:10.1016/j.ocecoaman.2007.08.002
-Iacarella, J.C. and Weller, J.D., 2023. Predicting favourable streams for anadromous salmon spawning and natal rearing under climate change.Â Can. J. Fish. Aquat. Sci.,Â 81(1), pp.1-13. doi:10.1139/cjfas-2023-0096
-Iacarella, J.C., Paterson, K., Potapova, A., and Weller, J.D. 2025. Geospatial Indicators and Metrics for Threats to Fish Habitat in the Fraser River Basin with Thompson-Nicola as a Case Study. DFO Can. Sci. Advis. Sec. Res. Doc. 2025/013. xiii + 126 p.
-Rosenfeld, J., Gonzalez-Espinosa, P., Jarvis, L., Enders, E., Bayly, M., Paul, A., MacPherson, L., Moore, J., Sullivan, M., Ulaski, M., and Wilson, K. 2022. Stressor-response functions as a generalizable model for context dependence. Trends Ecol. Evolut. 37: 1032-1035. doi:10.1016/j.tree.2022.09.010</t>
-  </si>
-  <si>
     <t>Sakinaw sockeye have been listed as endangered with COSEWIC since 2003, and a *Species at Risk Act* Recovery Potential Assessment (RPA) was completed in 2017 (Ramshaw et al. 2019). The RPA cited low marine survival as the greatest limiting factor in recovery, with predator abundance and assumed predation on smolts and adults ranked as high risk, with a critical level of impact. Perpetually low marine survivals are preventing recovery such that the persistence of the population is entirely dependent on a captive brood program.
 Sakinaw sockeye smolts out-migrate from Sakinaw Lake each spring into the Malaspina Strait and Strait of Georgia. Localized marine predation is considered a major limiting factor for the survival of this stock. On water surveys (since 2019) of pinnipeds from the estuary to the seal haul-outs on Hodgson Islands (approximately 2km from the estuary, Figure 1) have observed approximately 100-350 harbour seals in the area during the spring out-migration.
 This project was started as a pilot (2022) in collaboration with shÃ­shÃ¡lh Nation to test the hypothesis that the Hodgson Island harbour seal population is negatively affecting smolt survival, and subsequently adult returns. The goal of the project is to transport and release smolts past the seal haul-out and then compare marine survival rates between transported smolts and those out-migrating naturally. The pilot project began with a low number of smolts transported in small trial releases to test the effect of handling, Passive Integrated Transponders (PIT) tagging, and increased osmoregulation on fish.
@@ -3197,16 +3155,54 @@
 Foreman, M.G.G., Chandler, P.C., Bianucci, L., Wan, D., Krassovski, M.V., Thupaki, P., Cooper, G. and Lin, Y., 2024. A circulation model for inlets along the central West Coast of Vancouver Island. Atmosphere-Ocean, 62(1), pp.58-89.</t>
   </si>
   <si>
-    <t xml:space="preserve">Habitat use and survival
-Subyearling Chinook (n=547) raised in the kł cp̓əlk̓ stim̓ hatchery were implanted with ATS SS400 injectable acoustic transmitters. They were released in two groups, with group A (n=273) released in the Okanagan River below Vertical Drop Structure (VDS) 17 and above Vaseux Lake, and group B (n=274) released downstream of Vaseux lake below McIntyre Dam. A network of 15 ATS SR3001 autonomous receivers was deployed from Okanagan Falls to Osoyoos Lake between 21 May and 8 August, 2024). Receivers were clustered into 7 detection sites, placed to form acoustic “gates” at lake inlets and outlets, narrows and channel constrictions, and potential rearing/migration corridors. An ATS SR3017 mobile receiver with hydrophone was used to survey shallow side channels, deeper offshore areas beyond stationary coverage, and upstream and downstream of VDS structures. The proportion of fish detected decreased sharply for both release groups as fish migrated downstream, which translated to low survival in both release groups. Tag burden was not deemed a source of direct mortality, but could have increased susceptibility to predation. 
-Smallmouth bass diet and predation
-Targeted angling was conducted in the Okanagan River, Vaseux Lake, Osoyoos Lake from May 3 to August 7, 2024. The dominant species captured were smallmouth bass, which comprised 76% of the total catch (n=196), followed by Northern Pikeminnow (16%, n=41) and Yellow Perch (4%, n=11). There was a spatial shift in the distribution of smallmouth bass caught during the study. In May, less than half (45%) of smallmouth bass were caught at Vertical Drop Structures (VDS), but the proportion of smallmouth bass captured at VDS structures increased to 100% and 80% in June and July, respectively. Bass were observed utilizing rocky substrate and rip rap below the VDS structures to ambush prey. Diet content visual analysis was performed on a subsample of 73 of the total 196 smallmouth bass. A total of 162 fish stomach samples were sent for DNA barcode sequencing. Chinook salmon was only detected once in the DNA samples, but direct evidence of bass predation on juvenile Chinook was obtained by recovery of an acoustic tag used in the juvenile migration and habitat use study. DNA metabarcoding identified a diverse assemblage of 146 unique prey taxa. Aquatic insects (Diptera,  Ephemeroptera, Trichoptera), invasive fish (smallmouth bass, yellow perch, common carp), and native fish (prickly sculpin, mountain whitefish, sockeye/kokanee, Chinook) were the most common prey items in smallmouth bass stomach contents. </t>
-  </si>
-  <si>
     <t>Electrofishing and angling was conducted in the spring to target SMB as they move to near-shore habitat to build nests and spawn. The perimeter of Cultus Lake was divided into quadrants (Figure 1) and swept with a boat electrofishing unit to target spawning SMB. In 2023, ten consecutive days of electrofishing were conducted (June 1-10, 2023), and all SMB captured (by electrofishing and angling) were implanted with a PIT tag and released to get an initial baseline of the population in 2024. A subset of SMB (n=25) were also implanted with acoustic transmitters to track movements within the lake, and downstream movement from the lake (acoustic receivers also deployed in 2023 in various locations). In 2024, two consecutive days (east side of lake day one; west side of lake day two) of electrofishing and angling were conducted for six consecutive weeks (May 9 - June 7, 2024), and all SMB were euthanized to get a PIT tag recovery sample and to see how the population responded to the cull the following year. In 2025, operations were conducted in two day intervals, for seven consecutive weeks (May 1 - June 13, 2025). For the first two weeks of the project all SMB were euthanized to reduce the spawning potential of the population, and for subsequent weeks 25% of all SMB were implanted with PIT tags and released. A subset of 44 SMB were also implanted with acoustic transmitters to track movements within, and from Cultus Lake. A total of 3,654 biological samples (length, weight (Figure 2); subset of stomach contents (Figure 3), scales, otoliths) were collected from SMB between 2023-2025. Of these samples, 268 stomach samples, 2,069 scale samples, and 20 otoliths samples were collected. Age analysis and acoustic tracking results are pending, and will be included in the final report (written by SFU).
 Between 2023 and 2025, a total of 6,650 SMB were captured by a combination of electrofishing and angling (942 in 2023, 1,616 in 2024, 4,092 in 2025; 95% by electrofishing, 5% by angling). A total of 1,469 PIT tags were deployed (897 in 2023, 572 in 2025), and 69 acoustic tags were surgically implanted in SMB (25 in 2023, 44 in 2025). Of the PIT tags deployed in 2023, 47 were recaptured in 2024 (4.8% recovery) and 12 were recaptured in 2025 (1.2% recovery), giving a rough population estimate of approximately 16,000 SMB in 2024. However, observations from staff at the Cultus Lake Laboratory, the Province of BC, and anglers have indicated a significant portion of the population occupy habitat at depths that preclude SMB from capture by electrofishing, thus, this estimate is likely biased low. The PIT tags deployed in 2025 have yet to be captured in 2026, therefore a current population estimate is unavailable at this time. It should be noted that in 2023, a total of two pumpkinseed were captured during the electrofishing program. In 2024 the number increased to 60, and in 2025 increased to 2,553. Further to this, the capture of pumpkinseed was incidental as there is some overlap in habitat with SMB, and if efforts were targeted for pumpkinseed (i.e. heavily vegetated near-shore habitat), those numbers would be higher. The rapid increase in pumpkinseed bycatch over the course of this work is alarming and should be investigated in future years.
 The subset of stomach samples taken, approximately 10% of samples contained juvenile salmonids (fry or smolt stage), and 2% contained sculpins. It is noted that many stomach samples were at an advanced stage of digestion therefore these estimates are biased low. Acoustic tracking of SMB is ongoing and will be discussed in the final report. However, between 2024 and 2025 a total of 17 SMB were captured at the DFO-operated smolt enumeration fence (run March - June annually), indicating some downstream movement of SMB in Sweltzer Creek to the Vedder River (tributary to the Fraser River). At this time there are no confirmed reports of SMB in the Vedder or Fraser rivers, however, as the population in Cultus Lake expands, downstream colonization is likely.
 The following results, in addition to acoustic tracking data, an evaluation of suppression methods (paired with feedback from the public and social survey results), and up-to-date SMB population estimates will be presented in the final report written by SFU, DFO and the Province of BC in 2027.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*Habitat use and survival*
+Subyearling Chinook (n=547) raised in the kł cp̓əlk̓ stim̓ hatchery were implanted with ATS SS400 injectable acoustic transmitters. They were released in two groups, with group A (n=273) released in the Okanagan River below Vertical Drop Structure (VDS) 17 and above Vaseux Lake, and group B (n=274) released downstream of Vaseux lake below McIntyre Dam. A network of 15 ATS SR3001 autonomous receivers was deployed from Okanagan Falls to Osoyoos Lake between 21 May and 8 August, 2024). Receivers were clustered into 7 detection sites, placed to form acoustic “gates” at lake inlets and outlets, narrows and channel constrictions, and potential rearing/migration corridors. An ATS SR3017 mobile receiver with hydrophone was used to survey shallow side channels, deeper offshore areas beyond stationary coverage, and upstream and downstream of VDS structures. The proportion of fish detected decreased sharply for both release groups as fish migrated downstream, which translated to low survival in both release groups. Tag burden was not deemed a source of direct mortality, but could have increased susceptibility to predation. 
+*Smallmouth bass diet and predation*
+Targeted angling was conducted in the Okanagan River, Vaseux Lake, Osoyoos Lake from May 3 to August 7, 2024. The dominant species captured were smallmouth bass, which comprised 76% of the total catch (n=196), followed by Northern Pikeminnow (16%, n=41) and Yellow Perch (4%, n=11). There was a spatial shift in the distribution of smallmouth bass caught during the study. In May, less than half (45%) of smallmouth bass were caught at Vertical Drop Structures (VDS), but the proportion of smallmouth bass captured at VDS structures increased to 100% and 80% in June and July, respectively. Bass were observed utilizing rocky substrate and rip rap below the VDS structures to ambush prey. Diet content visual analysis was performed on a subsample of 73 of the total 196 smallmouth bass. A total of 162 fish stomach samples were sent for DNA barcode sequencing. Chinook salmon was only detected once in the DNA samples, but direct evidence of bass predation on juvenile Chinook was obtained by recovery of an acoustic tag used in the juvenile migration and habitat use study. DNA metabarcoding identified a diverse assemblage of 146 unique prey taxa. Aquatic insects (Diptera,  Ephemeroptera, Trichoptera), invasive fish (smallmouth bass, yellow perch, common carp), and native fish (prickly sculpin, mountain whitefish, sockeye/kokanee, Chinook) were the most common prey items in smallmouth bass stomach contents. </t>
+  </si>
+  <si>
+    <t>Low flows during summer months can be an important bottleneck for stream-rearing rearing salmon. Determining how much water fish need is therefore a critical management question, especially given rising human water use and climate warming. Elevated water temperature is another threat facing stream-rearing salmon that is often linked to low flows. However, conventional modelling tools for determining instream flow needs have generally not explicitly considered temperature. This is a gap for management as it is unclear if current instream flow assessments will apply in a warmer future. 
+This project developed an analytical framework to integrate water temperature into habitat simulation models, a widely used tool for determining instream flow needs. We used a bioenergetics framework that relates channel hydraulics (e.g., depth and velocity) and temperature to the daily energy balance of juvenile salmonids. We then applied the approach to 17 coho-rearing streams across the North Thompson watershed, interior BC. This work was collaborative with Secwépemc Fisheries Commission and Simpcw First Nation and will inform instream flow management through the lens of climate change.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We used a habitat simulation model framework that links streamflow to channel hydraulics, then channel hydraulics to fish using bioenergetics. The end result is a matrix of relative habitat availability across combinations of flow and water temperature. This can be used as a tool to support real-time flow and temperature monitoring or be linked to flow and temperature projections under contrasting climate change scenarios. Initial model outputs have been shared with Secwépemc Fisheries Commission to support drought monitoring in several priority systems. 
+Flow-habitat relationships were variable across the different streams, suggesting that generic thresholds of flow (e.g., 20% of mean annual discharge) may not always apply. The combined effect of flow and temperature was also variable, reflecting the complex nonlinear pathways that temperature influences fish. 
+While the specific model outputs generated to date are applicable to the North Thompson, the general approach is broadly applicable to other systems where the combined impacts of flow and temperature change are of interest. </t>
+  </si>
+  <si>
+    <t>Railsback, S.F., 2016. Why it is time to put PHABSIM out to pasture. Fisheries, 41(12), pp.720-725.
+Naman, S.M., Rosenfeld, J.S., Neuswanger, J.R., Enders, E.C., Hayes, J.W., Goodwin, E.O., Jowett, I.G. and Eaton, B.C., 2020. Bioenergetic Habitat Suitability Curves for Instream Flow Modeling: Introducing User‐Friendly Software and its Potential Applications. Fisheries, 45(11), pp.605-613.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figure 1. (a) Human activity and landscape disturbance based additive cumulative threat score, and (b) Climate change additive cumulative threat score for 2040-2060 under RCP 4.5. Blue indicates low threat levels and red indicates high threat levels.
+Figure 2. Tukey’s box-whiskers plots of the cumulative threat scores from human activity and landscape disturbance based threats and climate change based threats for all streams in the FRB, (a &amp; b) accessible streams within salmon CUs, and (c &amp; d) delineated stream habitats of fish SAR. Salmon CUs identified as Special Concern, Threatened, or Endangered by COSEWIC were distinguished from those not at risk. 
+Figure 3. Median cumulative threat composite scores for watershed groups in the Thompson-Nicola EDU based on the multiplicative value of human activity and landscape disturbance based cumulative threats and modeled environmental favourability for spawning (row a) Chinook, (b) Coho, (c) Pink, and (d) Sockeye Salmon. Modeled environmental favourability probabilities used in the composite score were based on projected (column a) current and (b) future conditions for all stream reaches (≥ 4th order) including inaccessible streams from dams and natural barriers. Watershed groups that are largely inaccessible are identified by hatched lines, and salmon CU boundaries in black outlines. Colour scale indicates increasing need for localized investigation and potential restoration. </t>
+  </si>
+  <si>
+    <t>Although our threat estimates represent the mechanisms by which salmon and freshwater SAR are affected, the magnitude at which these threats influence salmon population dynamics remains unknown. To address this gap, we are continuing to refine existing threat estimates and developing new threats that are explicitly linked to stressor-response functions for cumulative effects and life-cycle modelling. For example, we have developed additional riparian disturbance metrics that better capture the impacts to riparian function (e.g., large-woody debris recruitment, disturbance to stream-shading, riparian filtering), which were not included in the original report. Moreover, we are developing a stage-structured population model for Interior Fraser Coho (IFC) to estimate how stressors (estimated threats) are influencing the population across their freshwater life stages. For this work, we are utilizing the Cumulative Effects Model for Prioritizing Recovery Actions (CEMPRA), which applies stressor-response functions to account for the impact of stressors on vital rates and the overall population overtime and under different climate change and mitigation scenarios (Bayly et al. 2024).
+Additional next steps for this work include expanding the cumulative threats model to other watersheds in the Pacific Region. To date, the model has also been applied to the Upper Bulkley Watershed to aid in salmon habitat restoration planning. Validation is an important step of most modelling exercises, though is often not a standard component of cumulative effect assessments (Halpern and Fujita 2013). Validating these threats through field verification and in situ data would be beneficial for threats that involve applied relationships and estimations, such as the flow accumulated loadings (i.e., nutrients, pollution, sedimentation). Future work could re-run the model at regular intervals to evaluate change in threats over time. Finally, additional analyses could quantify uncertainty in modelled threats and evaluate underlying assumptions through sensitivity tests.</t>
+  </si>
+  <si>
+    <t>Bayly, M., Tekatch, A., Rosenfeld, J., Jarvis, L. &amp; Enders, E. 2024. Cumulative Effects Model for Prioritizing Recovery Actions (CEMPRA): User Guide. Documentation prepared by ESSA Technologies Ltd. for the BC Water, Land and Resource S. Available from: https://essatech.github.io/CEMPRA/ [accessed 29 December 2025].
+DFO. 2022. Geospatial mapping tools, indicators, and metrics for fish habitat in the Pacific Region. DFO Can. Sci. Advis. Sec. Sci. Resp. 2022/047. 
+Halpern, B.S., and Fujita, R. 2013. Assumptions, challenges, and future directions in cumulative impact analysis. Ecosphere. 4: art131. doi:10.1890/ES13-00181.1
+Halpern, B.S., McLeod, K.L., Rosenberg, A.A., and Crowder, L.B. 2008a. Managing for cumulative impacts in ecosystem-based management through ocean zoning. Ocean Coast. Manage. 51: 203–211. doi:10.1016/j.ocecoaman.2007.08.002		 
+Iacarella, J.C. and Weller, J.D., 2023. Predicting favourable streams for anadromous salmon spawning and natal rearing under climate change. Can. J. Fish. Aquat. Sci., 81(1), pp.1-13. doi:10.1139/cjfas-2023-0096
+Iacarella, J.C., Paterson, K., Potapova, A., and Weller, J.D. 2025. Geospatial Indicators and Metrics for Threats to Fish Habitat in the Fraser River Basin with Thompson-Nicola as a Case Study. DFO Can. Sci. Advis. Sec. Res. Doc. 2025/013. xiii + 126 p.
+Rosenfeld, J., Gonzalez-Espinosa, P., Jarvis, L., Enders, E., Bayly, M., Paul, A., MacPherson, L., Moore, J., Sullivan, M., Ulaski, M., and Wilson, K. 2022. Stressor-response functions as a generalizable model  for context dependence. Trends Ecol. Evolut. 37: 1032–1035.   doi:10.1016/j.tree.2022.09.010
+Iacarella, J.C., Paterson, K., Potapova, A., and Weller, J.D. 2025. Geospatial Indicators and Metrics for Threats to Fish Habitat in the Fraser River Basin with Thompson-Nicola as a Case Study. DFO Can. Sci. Advis. Sec. Res. Doc. 2025/013. xiii + 126 p.
+Rosenfeld, J., Gonzalez-Espinosa, P., Jarvis, L., Enders, E., Bayly, M., Paul, A., MacPherson, L., Moore, J., Sullivan, M., Ulaski, M., and Wilson, K. 2022. Stressor-response functions as a generalizable model for context dependence. Trends Ecol. Evolut. 37: 1032-1035. doi:10.1016/j.tree.2022.09.010</t>
+  </si>
+  <si>
+    <t>Figure 1. Proportion of acoustic tagged juvenile Chinook detected at downstream detections sites and resulting survival curves for release Group A (n= 273 upstream of Vaseux Lake) and B (n=274 downstream of McIntyre Dam). In both release groups, there is a sharp decline in the proportion of fish detected and survival is low during the downstream migration.
+Figure 2. DNA metabarcoding stomach content analysis of n=162 smallmouth bass (*Micropterus dolomieu*) captured at various locations in the Okanagan River and Lake system. Aquatic insects (Diptera, Ephemeroptera, Trichoptera), invasive fish (smallmouth bass, yellow perch, common carp), and native fish (prickly sculpin, mountain whitefish, sockeye/kokanee, Chinook) were the most common prey items identified.
+Table 1. Total length (TL) and weight of the 196 smallmouth bass (*Micropterus dolomieu*) captured in the juvenile Chinook predation study. Bass were captured by angling in the Okanagan River and Lake system and were sacrificed upon capture for stomach content analysis.</t>
   </si>
 </sst>
 </file>
@@ -4104,7 +4100,7 @@
         <v>22</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>23</v>
@@ -4134,7 +4130,7 @@
         <v>31</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>32</v>
@@ -4184,7 +4180,7 @@
         <v>44</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>45</v>
@@ -4193,13 +4189,13 @@
         <v>46</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>47</v>
@@ -4234,13 +4230,13 @@
         <v>2400</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>56</v>
@@ -4249,7 +4245,7 @@
         <v>57</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>58</v>
@@ -4261,19 +4257,19 @@
         <v>59</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="P4" s="1" t="s">
         <v>60</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="R4" s="1" t="s">
         <v>61</v>
@@ -4282,10 +4278,10 @@
         <v>62</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -4299,16 +4295,16 @@
         <v>2401</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>65</v>
@@ -4340,7 +4336,7 @@
         <v>72</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -4381,7 +4377,7 @@
         <v>81</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>82</v>
@@ -4393,7 +4389,7 @@
         <v>84</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="R6" s="1" t="s">
         <v>85</v>
@@ -4419,7 +4415,7 @@
         <v>2403</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>90</v>
@@ -4440,7 +4436,7 @@
         <v>95</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="L7" s="4" t="s">
         <v>96</v>
@@ -4449,7 +4445,7 @@
         <v>96</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="O7" s="4" t="s">
         <v>97</v>
@@ -4458,19 +4454,19 @@
         <v>98</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="S7" s="5" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
     </row>
     <row r="8" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4490,31 +4486,31 @@
         <v>101</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>102</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>103</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>104</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="O8" s="4" t="s">
         <v>105</v>
@@ -4523,7 +4519,7 @@
         <v>106</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="R8" s="4" t="s">
         <v>107</v>
@@ -4532,10 +4528,10 @@
         <v>108</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="U8" s="5" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -4552,19 +4548,19 @@
         <v>110</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>111</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>65</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>112</v>
@@ -4573,13 +4569,13 @@
         <v>113</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>114</v>
@@ -4588,7 +4584,7 @@
         <v>115</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="R9" s="1" t="s">
         <v>116</v>
@@ -4600,7 +4596,7 @@
         <v>118</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -4620,40 +4616,40 @@
         <v>121</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>122</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>123</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>124</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>125</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="R10" s="1" t="s">
         <v>126</v>
@@ -4679,13 +4675,13 @@
         <v>2407</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>131</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>132</v>
@@ -4703,10 +4699,10 @@
         <v>56</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="N11" s="4" t="s">
         <v>136</v>
@@ -4727,10 +4723,10 @@
         <v>141</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="U11" s="4" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -4744,13 +4740,13 @@
         <v>2408</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>56</v>
@@ -4777,7 +4773,7 @@
         <v>146</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>147</v>
@@ -4786,10 +4782,10 @@
         <v>148</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
@@ -4828,7 +4824,7 @@
         <v>156</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>157</v>
@@ -4849,10 +4845,10 @@
         <v>162</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -4872,31 +4868,31 @@
         <v>165</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>31</v>
+        <v>522</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>522</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>31</v>
+      <c r="J14" s="9" t="s">
+        <v>522</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="L14" s="1" t="s">
-        <v>31</v>
+      <c r="L14" s="9" t="s">
+        <v>522</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>31</v>
+        <v>522</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>522</v>
       </c>
       <c r="O14" s="1" t="s">
         <v>167</v>
@@ -4917,7 +4913,7 @@
         <v>172</v>
       </c>
       <c r="U14" s="5" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
@@ -4931,7 +4927,7 @@
         <v>2412</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>174</v>
@@ -4943,34 +4939,34 @@
         <v>176</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>177</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>56</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="O15" s="1" t="s">
         <v>178</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="R15" s="1" t="s">
         <v>179</v>
@@ -4979,10 +4975,10 @@
         <v>180</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -4996,13 +4992,13 @@
         <v>2413</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>182</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>183</v>
@@ -5020,13 +5016,13 @@
         <v>186</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="O16" s="1" t="s">
         <v>187</v>
@@ -5044,7 +5040,7 @@
         <v>191</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="U16" s="1" t="s">
         <v>192</v>
@@ -5067,7 +5063,7 @@
         <v>195</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>196</v>
@@ -5091,10 +5087,10 @@
         <v>104</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="P17" s="1" t="s">
         <v>201</v>
@@ -5141,7 +5137,7 @@
         <v>212</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>213</v>
@@ -5153,10 +5149,10 @@
         <v>215</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="O18" s="1" t="s">
         <v>216</v>
@@ -5165,19 +5161,19 @@
         <v>217</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="S18" s="1" t="s">
         <v>218</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -5191,13 +5187,13 @@
         <v>2418</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>209</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>220</v>
@@ -5206,7 +5202,7 @@
         <v>221</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>222</v>
@@ -5218,31 +5214,31 @@
         <v>223</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="O19" s="1" t="s">
         <v>224</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="S19" s="1" t="s">
         <v>225</v>
       </c>
       <c r="T19" s="5" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -5256,22 +5252,22 @@
         <v>2421</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>227</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>197</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>228</v>
@@ -5280,13 +5276,13 @@
         <v>56</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>229</v>
@@ -5295,7 +5291,7 @@
         <v>230</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>231</v>
@@ -5304,10 +5300,10 @@
         <v>232</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
@@ -5327,13 +5323,13 @@
         <v>235</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>196</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>236</v>
@@ -5348,10 +5344,10 @@
         <v>238</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>239</v>
@@ -5372,7 +5368,7 @@
         <v>244</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -5392,10 +5388,10 @@
         <v>247</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>248</v>
@@ -5410,22 +5406,22 @@
         <v>251</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="O22" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="P22" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="Q22" s="1" t="s">
-        <v>572</v>
+      <c r="P22" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="Q22" s="5" t="s">
+        <v>633</v>
       </c>
       <c r="R22" s="1" t="s">
         <v>253</v>
@@ -5436,8 +5432,8 @@
       <c r="T22" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="U22" s="1" t="s">
-        <v>573</v>
+      <c r="U22" s="5" t="s">
+        <v>634</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -5451,13 +5447,13 @@
         <v>2425</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>257</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>258</v>
@@ -5471,43 +5467,43 @@
       <c r="J23" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="K23" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="N23" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="L23" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="N23" s="1" t="s">
+      <c r="O23" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="O23" s="1" t="s">
+      <c r="P23" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="P23" s="1" t="s">
+      <c r="Q23" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="Q23" s="1" t="s">
+      <c r="R23" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="R23" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="S23" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="T23" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="U23" s="1" t="s">
-        <v>575</v>
+      <c r="S23" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="T23" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="U23" s="5" t="s">
+        <v>637</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B24" s="7">
         <v>46083</v>
@@ -5516,63 +5512,63 @@
         <v>2426</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="E24" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>607</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="F24" s="9" t="s">
-        <v>616</v>
-      </c>
-      <c r="G24" s="1" t="s">
+      <c r="I24" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="J24" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="K24" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="L24" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="M24" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="L24" s="1" t="s">
+      <c r="N24" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="M24" s="1" t="s">
+      <c r="O24" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="N24" s="1" t="s">
+      <c r="P24" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="R24" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="O24" s="1" t="s">
+      <c r="S24" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="P24" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="Q24" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="R24" s="1" t="s">
+      <c r="T24" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="S24" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="T24" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="U24" s="1" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B25" s="7">
         <v>46083</v>
@@ -5581,63 +5577,63 @@
         <v>2427</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>182</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>177</v>
       </c>
       <c r="J25" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="O25" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="P25" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="L25" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="O25" s="1" t="s">
+      <c r="Q25" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="R25" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="P25" s="1" t="s">
+      <c r="S25" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="Q25" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="R25" s="1" t="s">
+      <c r="T25" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="S25" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="T25" s="1" t="s">
-        <v>291</v>
-      </c>
       <c r="U25" s="1" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B26" s="7">
         <v>46083</v>
@@ -5646,63 +5642,63 @@
         <v>2430</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="J26" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="I26" s="1" t="s">
+      <c r="K26" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="L26" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="M26" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="N26" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="L26" s="1" t="s">
+      <c r="O26" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="M26" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="N26" s="1" t="s">
+      <c r="P26" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="S26" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="O26" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="P26" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="Q26" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="R26" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="S26" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="T26" s="1" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="U26" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B27" s="7">
         <v>46083</v>
@@ -5711,22 +5707,22 @@
         <v>2432</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>250</v>
@@ -5735,39 +5731,39 @@
         <v>186</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="O27" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q27" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="P27" s="1" t="s">
+      <c r="R27" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="Q27" s="1" t="s">
+      <c r="S27" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="R27" s="1" t="s">
+      <c r="T27" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="S27" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="T27" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="U27" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B28" s="7">
         <v>46083</v>
@@ -5776,63 +5772,63 @@
         <v>2433</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>613</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="E28" s="9" t="s">
-        <v>622</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="H28" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>250</v>
       </c>
       <c r="K28" s="9" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="P28" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="R28" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="Q28" s="1" t="s">
+      <c r="S28" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="R28" s="1" t="s">
+      <c r="T28" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="S28" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="T28" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="U28" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B29" s="7">
         <v>46083</v>
@@ -5841,63 +5837,63 @@
         <v>2434</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="G29" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>323</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>197</v>
       </c>
       <c r="I29" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="L29" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="M29" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="K29" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="L29" s="1" t="s">
+      <c r="N29" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="M29" s="1" t="s">
+      <c r="O29" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="P29" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="N29" s="1" t="s">
+      <c r="Q29" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="O29" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="P29" s="1" t="s">
+      <c r="R29" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="Q29" s="1" t="s">
+      <c r="S29" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="R29" s="1" t="s">
+      <c r="T29" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="S29" s="1" t="s">
+      <c r="U29" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="T29" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="U29" s="1" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B30" s="7">
         <v>46083</v>
@@ -5906,63 +5902,63 @@
         <v>2435</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="E30" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="H30" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="I30" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="J30" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="K30" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="L30" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="M30" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="L30" s="1" t="s">
+      <c r="N30" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="M30" s="1" t="s">
+      <c r="O30" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="N30" s="1" t="s">
+      <c r="P30" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="O30" s="1" t="s">
+      <c r="Q30" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="P30" s="1" t="s">
+      <c r="R30" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="Q30" s="1" t="s">
+      <c r="S30" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="R30" s="1" t="s">
+      <c r="T30" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="S30" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="T30" s="1" t="s">
-        <v>351</v>
-      </c>
       <c r="U30" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B31" s="7">
         <v>46083</v>
@@ -5971,63 +5967,63 @@
         <v>2436</v>
       </c>
       <c r="D31" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="H31" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="G31" s="1" t="s">
+      <c r="I31" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="J31" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="K31" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="L31" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="N31" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="O31" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="L31" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="N31" s="1" t="s">
+      <c r="P31" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="O31" s="1" t="s">
+      <c r="Q31" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="P31" s="1" t="s">
+      <c r="R31" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="Q31" s="1" t="s">
+      <c r="S31" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="R31" s="1" t="s">
+      <c r="T31" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="S31" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="T31" s="1" t="s">
-        <v>366</v>
-      </c>
       <c r="U31" s="1" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B32" s="7">
         <v>46083</v>
@@ -6036,63 +6032,63 @@
         <v>2437</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="H32" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="I32" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="H32" s="1" t="s">
+      <c r="J32" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="K32" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="L32" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="M32" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="L32" s="1" t="s">
+      <c r="N32" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="M32" s="1" t="s">
+      <c r="O32" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="P32" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="N32" s="1" t="s">
+      <c r="Q32" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="O32" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="P32" s="1" t="s">
+      <c r="R32" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="Q32" s="1" t="s">
+      <c r="S32" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="R32" s="1" t="s">
+      <c r="T32" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="S32" s="1" t="s">
+      <c r="U32" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="T32" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="U32" s="1" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B33" s="7">
         <v>46083</v>
@@ -6101,128 +6097,128 @@
         <v>2439</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="E33" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="H33" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="F33" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="G33" s="1" t="s">
+      <c r="I33" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="K33" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="L33" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="O33" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="I33" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="K33" s="1" t="s">
+      <c r="P33" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="Q33" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="L33" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="M33" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="O33" s="1" t="s">
+      <c r="R33" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="P33" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="Q33" s="1" t="s">
+      <c r="S33" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="R33" s="1" t="s">
+      <c r="T33" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="S33" s="1" t="s">
+      <c r="U33" s="1" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="T33" s="1" t="s">
+      <c r="B34" s="8">
+        <v>46083</v>
+      </c>
+      <c r="C34" s="4">
+        <v>2442</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="U33" s="1" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+      <c r="E34" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="B34" s="7">
-        <v>46083</v>
-      </c>
-      <c r="C34" s="1">
-        <v>2442</v>
-      </c>
-      <c r="D34" s="1" t="s">
+      <c r="F34" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="I34" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="J34" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="F34" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="G34" s="1" t="s">
+      <c r="K34" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="H34" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="J34" s="1" t="s">
+      <c r="L34" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="M34" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="N34" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="K34" s="1" t="s">
+      <c r="O34" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="L34" s="1" t="s">
+      <c r="P34" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="M34" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="N34" s="1" t="s">
+      <c r="Q34" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="R34" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="O34" s="1" t="s">
+      <c r="S34" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="P34" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="Q34" s="5" t="s">
-        <v>639</v>
-      </c>
-      <c r="R34" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="S34" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="T34" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="U34" s="1" t="s">
-        <v>526</v>
+      <c r="T34" s="5" t="s">
+        <v>638</v>
+      </c>
+      <c r="U34" s="4" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B35" s="7">
         <v>46083</v>
@@ -6231,63 +6227,63 @@
         <v>2443</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>65</v>
       </c>
       <c r="I35" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="P35" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="J35" s="1" t="s">
+      <c r="Q35" s="5" t="s">
+        <v>630</v>
+      </c>
+      <c r="R35" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="K35" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="M35" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="N35" s="1" t="s">
+      <c r="S35" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="O35" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="P35" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="Q35" s="5" t="s">
-        <v>640</v>
-      </c>
-      <c r="R35" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="S35" s="1" t="s">
-        <v>416</v>
-      </c>
       <c r="T35" s="1" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="U35" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="B36" s="7">
         <v>46083</v>
@@ -6296,25 +6292,25 @@
         <v>2447</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>633</v>
+        <v>624</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>78</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>104</v>
@@ -6323,36 +6319,36 @@
         <v>104</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="N36" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R36" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="O36" s="1" t="s">
+      <c r="S36" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="P36" s="1" t="s">
+      <c r="T36" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="Q36" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="R36" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="S36" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="T36" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="U36" s="1" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="B37" s="7">
         <v>46083</v>
@@ -6361,13 +6357,13 @@
         <v>2448</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>56</v>
@@ -6376,48 +6372,48 @@
         <v>197</v>
       </c>
       <c r="I37" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="O37" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="J37" s="1" t="s">
+      <c r="P37" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="Q37" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="L37" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="M37" s="1" t="s">
+      <c r="R37" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="S37" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="N37" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="O37" s="1" t="s">
+      <c r="T37" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="P37" s="1" t="s">
+      <c r="U37" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="Q37" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="R37" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="S37" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="T37" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="U37" s="1" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="B38" s="7">
         <v>46083</v>
@@ -6426,63 +6422,63 @@
         <v>2449</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="E38" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="L38" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="H38" s="1" t="s">
+      <c r="M38" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="I38" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="J38" s="1" t="s">
+      <c r="N38" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="O38" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="L38" s="1" t="s">
+      <c r="P38" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="M38" s="1" t="s">
+      <c r="Q38" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="N38" s="1" t="s">
+      <c r="R38" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="O38" s="1" t="s">
+      <c r="S38" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="P38" s="1" t="s">
+      <c r="T38" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="Q38" s="1" t="s">
+      <c r="U38" s="1" t="s">
         <v>451</v>
-      </c>
-      <c r="R38" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="S38" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="T38" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="U38" s="1" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="B39" s="7">
         <v>46083</v>
@@ -6491,63 +6487,63 @@
         <v>2451</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>78</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="K39" s="1" t="s">
         <v>186</v>
       </c>
       <c r="L39" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="P39" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="Q39" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="M39" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="N39" s="1" t="s">
+      <c r="R39" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="S39" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="O39" s="1" t="s">
+      <c r="T39" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="P39" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="Q39" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="R39" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="S39" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="T39" s="1" t="s">
-        <v>464</v>
-      </c>
       <c r="U39" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B40" s="7">
         <v>46083</v>
@@ -6556,63 +6552,63 @@
         <v>2452</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>197</v>
       </c>
       <c r="I40" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="N40" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="J40" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="K40" s="1" t="s">
+      <c r="O40" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="L40" s="1" t="s">
+      <c r="P40" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="M40" s="1" t="s">
+      <c r="Q40" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="R40" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="N40" s="1" t="s">
+      <c r="S40" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="O40" s="1" t="s">
+      <c r="T40" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="P40" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="Q40" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="R40" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="S40" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="T40" s="1" t="s">
-        <v>476</v>
-      </c>
       <c r="U40" s="1" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B41" s="7">
         <v>46083</v>
@@ -6621,63 +6617,63 @@
         <v>2504</v>
       </c>
       <c r="D41" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="I41" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="J41" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="G41" s="1" t="s">
+      <c r="K41" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="L41" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="M41" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="J41" s="1" t="s">
+      <c r="N41" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="O41" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="K41" s="1" t="s">
+      <c r="P41" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="L41" s="1" t="s">
+      <c r="Q41" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="M41" s="1" t="s">
+      <c r="R41" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="N41" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="O41" s="1" t="s">
+      <c r="S41" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="P41" s="1" t="s">
+      <c r="T41" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="Q41" s="1" t="s">
+      <c r="U41" s="1" t="s">
         <v>489</v>
-      </c>
-      <c r="R41" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="S41" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="T41" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="U41" s="1" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="B42" s="7">
         <v>46083</v>
@@ -6686,16 +6682,16 @@
         <v>2513</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>197</v>
@@ -6710,39 +6706,39 @@
         <v>104</v>
       </c>
       <c r="L42" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="P42" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="Q42" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="R42" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="S42" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="T42" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="M42" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="N42" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="O42" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="P42" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="Q42" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="R42" s="1" t="s">
-        <v>605</v>
-      </c>
-      <c r="S42" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="T42" s="1" t="s">
-        <v>501</v>
-      </c>
       <c r="U42" s="1" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="B43" s="7">
         <v>46083</v>
@@ -6751,22 +6747,22 @@
         <v>2545</v>
       </c>
       <c r="D43" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="H43" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="I43" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>508</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>31</v>
@@ -6784,30 +6780,30 @@
         <v>31</v>
       </c>
       <c r="O43" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="P43" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="Q43" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="R43" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="S43" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="P43" s="1" t="s">
+      <c r="T43" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="Q43" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="R43" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="S43" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="T43" s="1" t="s">
-        <v>514</v>
-      </c>
       <c r="U43" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="B44" s="7">
         <v>46083</v>
@@ -6816,13 +6812,13 @@
         <v>3682</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
@@ -6835,25 +6831,25 @@
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
       <c r="O44" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="P44" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="Q44" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="R44" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="S44" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="P44" s="1" t="s">
+      <c r="T44" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="Q44" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="R44" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="S44" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="T44" s="1" t="s">
-        <v>524</v>
-      </c>
       <c r="U44" s="1" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/pssi_form_data_altered.xlsx
+++ b/data/processed/pssi_form_data_altered.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ennsj\Documents\PSSI-final-tech-report\data\processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CCD6B92-F2B7-4073-96DE-24623086BF1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72209C9B-6B2A-454B-AB74-0C9975FB44EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="636">
   <si>
     <t>source_file</t>
   </si>
@@ -1287,25 +1287,10 @@
     <t>Adult</t>
   </si>
   <si>
-    <t>Puntledge River Summer</t>
-  </si>
-  <si>
-    <t>Puntledge River Summer Chinook</t>
-  </si>
-  <si>
     <t>CK-83</t>
   </si>
   <si>
-    <t>GREB1L is a gene that explains a large amount of the variation in run timing for Chinook Salmon. Specific SNPs in the GREB1L gene are currently used as diagnostic genetic markers to retroactively distinguish between summer and fall runs of Chinook in the Puntledge River Hatchery. These markers have two alleles one of which is primarily carried by early returning Chinook Salmon and the other by late returning salmon. Current management of enhancement at the Puntledge River Hatchery uses a date threshold to ensure most "summer run" fish carry the early-run allele to preserve the genetic integrity of this population segment. Rapid in-season genotyping results would allow more accurate and expanded use of available broodstock for the Puntledge summer run. SHERLOCK assays are field deployable genotyping assays that can generate a result in under an hour and may provide this capacity to enhancement efforts in the Puntledge River. The technology has previously been demonstrated for rapid genotyping purposes including GREB1L markers in California populations of Chinook Salmon.</t>
-  </si>
-  <si>
-    <t>We used existing qPCR assays and data generated by the DFO GSI program for routine broodstock screening for Puntledge Chinook Salmon as the ground truth for underlying greb1l genotypes. We then tested a published SHERLOCK assay (Baerwald et al. 2025) to validate its efficacy for genotyping greb1l in Puntledge Chinook. Lab samples assayed with SHERLOCK were successfully genotyped (Figure 1) and had a high concordance with SNP genotyping results (99%, Table 1) indicating that the tool can accurately genotype samples and is consistent with existing SNP genotypes in Puntledge River Chinook. A test field deployment of the tool using lateral flow strips for genotype detection (Figure 2) resulted in only an 80% concordance rate (4/5), but had a majority of assays fail (19). These results suggest that the tool has promise, but that further optimization and simplification of the methodology is required before the tool could be adopted to improve management.</t>
-  </si>
-  <si>
     <t>The project has demonstrated that SHERLOCK assays could accurately genotype Chinook Salmon in the Puntledge River, but that reliability of the tool must be improved before it can be adopted.</t>
-  </si>
-  <si>
-    <t>Future studies could continue to optimize and stabilize the reagents for field delivery, but alternative techniques to rapidly genotype greb1l should be explored and considered. There remains a clear use-case and a real benefit to increase the number of Summer run fish for broodstock that such tools could enable.</t>
   </si>
   <si>
     <t>Figure 1. SHERLOCK genotyping of greb1l early (green) and late (orange) alleles in individuals known to be homozygous for the early allele (301-EE), heterozygous (320-EL), and homozygous for the late allele (824-LL). Accumulation of fluorescence (RFU) over time indicates the presence of the allele in the DNA sample tested.
@@ -1338,13 +1323,6 @@
   </si>
   <si>
     <t>Haida Gwaii, Central Coast, East Coast Vancouver Island, West Coast Vancouver Island, Howe Sound, Fraser Valley, Mid Fraser River, Thompson River</t>
-  </si>
-  <si>
-    <t>Chinook: Atnarko River, Cheakamus River, Chilliwack River Fall, Chilliwack River Summer, Nanaimo River Summer, Nicola River, Salmon River, Sarita River, Wannock River, Yakoun River
-Coho: Chehalis River, Conuma River, Quinsam River
----
-Chinook: Atnarko River, Cheakamus River, Chilliwack River Fall, Chilliwack River Summer, Nanaimo River Summer, Nicola River, Salmon River, Sarita River, Wannock River, Yakoun River
-Coho: Chehalis River, Conuma River, Quinsam River</t>
   </si>
   <si>
     <t>Chinook: Atnarko River, Cheakamus River, Chilliwack River Fall, Chilliwack River Summer, Nanaimo River Summer, Nicola River, Salmon River, Sarita River, Wannock River, Yakoun River
@@ -2143,11 +2121,6 @@
   </si>
   <si>
     <t>Province of British Columbia</t>
-  </si>
-  <si>
-    <t>Main Idea: The LAPSE framework is a systematic process and open-source tool that bridges regulatory language with standardized threat classifications (IUCN - CMP) to facilitate evidence-based stewardship planning for Pacific salmon in British Columbia.
-Key Findings: Analysis of 196 federal and provincial statutes revealed that pollution-related provisions are most prevalent across both jurisdictions. Salmon harvest regulation is mostly managed federally, while salmon habitat factors including water use and watercourse modifications are governed provincially, which reflects a structural disconnect between fish stock stewardship and habitat protection.
-Implications: The LAPSE framework demonstrates the ability to identify regulatory pathways relevant to specific human activity threats by linking IUCN-CMP threat classifications to legislation, enabling salmon stewardship practitioners to navigate the complex legal landscape and develop coordinated, inter-jurisdictional recovery strategies.</t>
   </si>
   <si>
     <t>Pacific salmon populations across British Columbia are experiencing widespread declines driven by multiple anthropogenic stressors including habitat degradation, climate change, and overharvest. The governance landscape for Pacific salmon is highly fragmented, with federal jurisdiction over harvest intersecting with provincial authority over freshwater habitat, creating regulatory complexity that impedes effective stewardship. This decentralized, multi-sector array of constitutional authority stems from Canada's adaptation of British Common Law and creates overlapping responsibilities where jurisdictional authority is rarely the responsibility of one level of government. The patchwork is particularly prominent in Pacific salmon management due to their anadromous life cycles spanning international boundaries, as well as, freshwater and marine ecosystems. While salmon populations and fisheries are regulated federally, water use and watercourse alterations affecting aquatic habitat are managed provincially, with both governments having authority to designate protected areas. British Columbia is even more decentralized than other provinces, with species at risk provisions spread over the greatest number of statutes and regulations.
@@ -2808,11 +2781,6 @@
 - Deeper mooring in The central Strait of Gorgia revealed that Pacific hake (predators) were present almost year-round.</t>
   </si>
   <si>
-    <t>- The objective of This project was to test The use of SHERLOCK lateral flow-type assays to assess their suitability for rapid, field-deployable genetic assays for use in SEP management applications.
-- We found excellent performance of The tool under ideal laboratory conditions, but inconclusive and inconsistent results when attempting field deployment of The tool.
-- Further optimization and simplification of The procedure will be required for This tool to improve management practices.</t>
-  </si>
-  <si>
     <t>McKinney, G., McPhee, M.V., Pascal, C., Seeb, J.E. and Seeb, L.W., 2020. Network analysis of linkage disequilibrium reveals genome architecture in chum salmon.Â *G3: Genes, Genomes, Genetics*,Â *10*(5), pp.1553-1561.
 McKinney, G.J., Barry, P.D., Pascal, C., Seeb, J.E., Seeb, L.W. and McPhee, M.V., 2022. A new genotypingâ€inâ€thousandsâ€byâ€sequencing single nucleotide polymorphism panel for mixedâ€stock analysis of chum salmon from coastal Western Alaska.Â *North American Journal of Fisheries Management*,Â *42*(5), pp.1134-1143.
 Small,Â M.,Â WarheitÂ K.,Â PascalÂ C.,Â SeebÂ L.,Â RuffÂ C.,Â ZischkeÂ J.,Â et al., Chum Salmon Southern Area Genetic Baseline Enhancement Part 1 and Part 2: Amplicon Development, Expanded Baseline Collections, and Genotyping. PSC report S14-I17 &amp; S15-I09
@@ -3203,6 +3171,28 @@
     <t>Figure 1. Proportion of acoustic tagged juvenile Chinook detected at downstream detections sites and resulting survival curves for release Group A (n= 273 upstream of Vaseux Lake) and B (n=274 downstream of McIntyre Dam). In both release groups, there is a sharp decline in the proportion of fish detected and survival is low during the downstream migration.
 Figure 2. DNA metabarcoding stomach content analysis of n=162 smallmouth bass (*Micropterus dolomieu*) captured at various locations in the Okanagan River and Lake system. Aquatic insects (Diptera, Ephemeroptera, Trichoptera), invasive fish (smallmouth bass, yellow perch, common carp), and native fish (prickly sculpin, mountain whitefish, sockeye/kokanee, Chinook) were the most common prey items identified.
 Table 1. Total length (TL) and weight of the 196 smallmouth bass (*Micropterus dolomieu*) captured in the juvenile Chinook predation study. Bass were captured by angling in the Okanagan River and Lake system and were sacrificed upon capture for stomach content analysis.</t>
+  </si>
+  <si>
+    <t>- The objective of This project was to test The use of SHERLOCK lateral flow-type assays to assess their suitability for rapid, field-deployable genetic assays for use in SEP management applications.
+- We found excellent performance of The tool under ideal laboratory conditions, but inconclusive and inconsistent results when attempting field deployment of the tool.
+- Further optimization and simplification of The procedure will be required for This tool to improve management practices.</t>
+  </si>
+  <si>
+    <t>GREB1L is a gene that explains a large amount of the variation in run timing for Chinook Salmon. Specific SNPs in the GREB1L gene are currently used as diagnostic genetic markers to retroactively distinguish between summer and fall runs of Chinook in the Puntledge River Hatchery. These markers have two alleles one of which is primarily carried by early returning Chinook salmon and the other by late returning salmon. Current management of enhancement at the Puntledge River Hatchery uses a date threshold to ensure most "summer run" fish carry the early-run allele to preserve the genetic integrity of this population segment. Rapid in-season genotyping results would allow more accurate and expanded use of available broodstock for the Puntledge summer run. SHERLOCK assays are field deployable genotyping assays that can generate a result in under an hour and may provide this capacity to enhancement efforts in the Puntledge River. The technology has previously been demonstrated for rapid genotyping purposes including GREB1L markers in California populations of Chinook salmon.</t>
+  </si>
+  <si>
+    <t>We used existing qPCR assays and data generated by the DFO GSI program for routine broodstock screening for Puntledge Chinook salmon as the ground truth for underlying greb1l genotypes. We then tested a published SHERLOCK assay (Baerwald et al. 2025) to validate its efficacy for genotyping greb1l in Puntledge Chinook. Lab samples assayed with SHERLOCK were successfully genotyped (Figure 1) and had a high concordance with SNP genotyping results (99%, Table 1) indicating that the tool can accurately genotype samples and is consistent with existing SNP genotypes in Puntledge River Chinook. A test field deployment of the tool using lateral flow strips for genotype detection (Figure 2) resulted in only an 80% concordance rate (4/5), but had a majority of assays fail (19). These results suggest that the tool has promise, but that further optimization and simplification of the methodology is required before the tool could be adopted to improve management.</t>
+  </si>
+  <si>
+    <t>Future studies could continue to optimize and stabilize the reagents for field delivery, but alternative techniques to rapidly genotype GREB1L should be explored and considered. There remains a clear use-case and a real benefit to increase the number of Summer run fish for broodstock that such tools could enable.</t>
+  </si>
+  <si>
+    <t>*Main Idea*
+The LAPSE framework is a systematic process and open-source tool that bridges regulatory language with standardized threat classifications (IUCN - CMP) to facilitate evidence-based stewardship planning for Pacific salmon in British Columbia.
+*Key Findings*
+Analysis of 196 federal and provincial statutes revealed that pollution-related provisions are most prevalent across both jurisdictions. Salmon harvest regulation is mostly managed federally, while salmon habitat factors including water use and watercourse modifications are governed provincially, which reflects a structural disconnect between fish stock stewardship and habitat protection.
+*Implications*
+The LAPSE framework demonstrates the ability to identify regulatory pathways relevant to specific human activity threats by linking IUCN-CMP threat classifications to legislation, enabling salmon stewardship practitioners to navigate the complex legal landscape and develop coordinated, inter-jurisdictional recovery strategies.</t>
   </si>
 </sst>
 </file>
@@ -3259,20 +3249,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3295,6 +3278,11 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3313,6 +3301,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3331,6 +3320,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3349,6 +3339,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3367,6 +3358,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3385,6 +3377,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3403,6 +3396,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3421,6 +3415,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3439,6 +3434,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3457,6 +3453,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3475,6 +3472,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3493,6 +3491,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3511,6 +3510,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3529,6 +3529,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3547,6 +3548,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3565,6 +3567,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3583,6 +3586,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3601,6 +3605,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3619,6 +3624,26 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3637,6 +3662,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3655,27 +3681,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3691,30 +3697,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C1235FC-468F-46C3-9676-E136DE729105}" name="Table1" displayName="Table1" ref="A1:U44" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C1235FC-468F-46C3-9676-E136DE729105}" name="Table1" displayName="Table1" ref="A1:U44" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
   <autoFilter ref="A1:U44" xr:uid="{9C1235FC-468F-46C3-9676-E136DE729105}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{21F25E78-D457-418F-9F78-7DE13AE8CD93}" name="source_file" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{B8BCB027-8A7D-4FCE-803F-A296662A280E}" name="extraction_date" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{683393A0-8045-467F-9A16-95D1CB0C532F}" name="project_id" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{5331C13B-A3FC-484A-95E7-7EAD3A2BB00D}" name="project_title" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{65143B71-B457-4DF3-96FB-A320AE4152BD}" name="project_leads" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{0B1052C0-47F1-41AA-B13F-BE70DF38178E}" name="collaborations" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{1204734C-F170-44F7-B4B4-5C53DC28A923}" name="location" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{DB4F19D6-FCB3-4A48-B206-A993711C4060}" name="species" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{3B9CC560-9650-4F10-B6EB-A8BB6D19FD2B}" name="waterbodies" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{3B74A0C4-6035-471F-BA59-5E5296130A6C}" name="life_history" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{83EB77D8-FF38-4BA7-8B8A-C5EB6609BA41}" name="region" dataDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{B5F0F367-295F-4C21-8EF2-8D796262B584}" name="stock" dataDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{592AD976-80C9-41A3-904D-28E27F957093}" name="population" dataDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{0841A155-6170-4816-B52F-62D315F16BB4}" name="cu" dataDxfId="7"/>
-    <tableColumn id="15" xr3:uid="{6A19023B-7495-49F1-A1EC-B098C5E333CF}" name="highlights" dataDxfId="6"/>
-    <tableColumn id="16" xr3:uid="{E075E454-2C61-4348-A20B-0C745E2EC565}" name="background" dataDxfId="5"/>
-    <tableColumn id="17" xr3:uid="{F232593A-A943-4A2F-A957-77EB6182BDA8}" name="methods_findings" dataDxfId="4"/>
-    <tableColumn id="18" xr3:uid="{2F87C396-47EA-4A13-9083-A6C4F71287B3}" name="insights" dataDxfId="3"/>
-    <tableColumn id="19" xr3:uid="{E3203637-205F-4D67-8A5B-15606B06B96D}" name="next_steps" dataDxfId="2"/>
-    <tableColumn id="20" xr3:uid="{71B5C06F-A10D-4B50-AAD8-E218E0D666CD}" name="tables_figures" dataDxfId="1"/>
-    <tableColumn id="21" xr3:uid="{671D065B-E9D7-4645-BF8D-C6523418AA9F}" name="references" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{21F25E78-D457-418F-9F78-7DE13AE8CD93}" name="source_file" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{B8BCB027-8A7D-4FCE-803F-A296662A280E}" name="extraction_date" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{683393A0-8045-467F-9A16-95D1CB0C532F}" name="project_id" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{5331C13B-A3FC-484A-95E7-7EAD3A2BB00D}" name="project_title" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{65143B71-B457-4DF3-96FB-A320AE4152BD}" name="project_leads" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{0B1052C0-47F1-41AA-B13F-BE70DF38178E}" name="collaborations" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{1204734C-F170-44F7-B4B4-5C53DC28A923}" name="location" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{DB4F19D6-FCB3-4A48-B206-A993711C4060}" name="species" dataDxfId="15"/>
+    <tableColumn id="9" xr3:uid="{3B9CC560-9650-4F10-B6EB-A8BB6D19FD2B}" name="waterbodies" dataDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{3B74A0C4-6035-471F-BA59-5E5296130A6C}" name="life_history" dataDxfId="13"/>
+    <tableColumn id="11" xr3:uid="{83EB77D8-FF38-4BA7-8B8A-C5EB6609BA41}" name="region" dataDxfId="12"/>
+    <tableColumn id="12" xr3:uid="{B5F0F367-295F-4C21-8EF2-8D796262B584}" name="stock" dataDxfId="11"/>
+    <tableColumn id="13" xr3:uid="{592AD976-80C9-41A3-904D-28E27F957093}" name="population" dataDxfId="10"/>
+    <tableColumn id="14" xr3:uid="{0841A155-6170-4816-B52F-62D315F16BB4}" name="cu" dataDxfId="9"/>
+    <tableColumn id="15" xr3:uid="{6A19023B-7495-49F1-A1EC-B098C5E333CF}" name="highlights" dataDxfId="8"/>
+    <tableColumn id="16" xr3:uid="{E075E454-2C61-4348-A20B-0C745E2EC565}" name="background" dataDxfId="7"/>
+    <tableColumn id="17" xr3:uid="{F232593A-A943-4A2F-A957-77EB6182BDA8}" name="methods_findings" dataDxfId="6"/>
+    <tableColumn id="18" xr3:uid="{2F87C396-47EA-4A13-9083-A6C4F71287B3}" name="insights" dataDxfId="5"/>
+    <tableColumn id="19" xr3:uid="{E3203637-205F-4D67-8A5B-15606B06B96D}" name="next_steps" dataDxfId="4"/>
+    <tableColumn id="20" xr3:uid="{71B5C06F-A10D-4B50-AAD8-E218E0D666CD}" name="tables_figures" dataDxfId="3"/>
+    <tableColumn id="21" xr3:uid="{671D065B-E9D7-4645-BF8D-C6523418AA9F}" name="references" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4002,2854 +4008,2866 @@
   <dimension ref="A1:U44"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13" style="2" customWidth="1"/>
-    <col min="2" max="2" width="17.140625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="96.140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" style="2" customWidth="1"/>
-    <col min="7" max="8" width="11.42578125" style="2"/>
-    <col min="9" max="9" width="14.28515625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="13.28515625" style="2" customWidth="1"/>
-    <col min="11" max="12" width="11.42578125" style="2"/>
-    <col min="13" max="13" width="12.85546875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" style="2"/>
-    <col min="15" max="15" width="11.85546875" style="2" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="2" customWidth="1"/>
-    <col min="17" max="17" width="47.85546875" style="2" customWidth="1"/>
-    <col min="18" max="18" width="11.42578125" style="2"/>
-    <col min="19" max="19" width="12.85546875" style="2" customWidth="1"/>
-    <col min="20" max="20" width="15.7109375" style="2" customWidth="1"/>
-    <col min="21" max="21" width="126.85546875" style="10" customWidth="1"/>
-    <col min="22" max="16384" width="11.42578125" style="2"/>
+    <col min="1" max="1" width="13" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="96.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="8" width="11.42578125" style="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" style="1" customWidth="1"/>
+    <col min="11" max="12" width="11.42578125" style="1"/>
+    <col min="13" max="13" width="12.85546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" style="1"/>
+    <col min="15" max="15" width="11.85546875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="47.85546875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="11.42578125" style="1"/>
+    <col min="19" max="19" width="12.85546875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="15.7109375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="126.85546875" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="10" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="4">
         <v>46083</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>616</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="D2" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="O2" s="1" t="s">
+      <c r="N2" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="T2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="U2" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="4">
         <v>46083</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="2">
         <v>2394</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="J3" s="1" t="s">
+      <c r="I3" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="O3" s="1" t="s">
+      <c r="L3" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="P3" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="Q3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="R3" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="S3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="T3" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="U3" s="2" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="4">
         <v>46083</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="2">
         <v>2400</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>626</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="D4" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="G4" s="1" t="s">
+      <c r="F4" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="J4" s="1" t="s">
+      <c r="I4" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="L4" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="M4" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="P4" s="1" t="s">
+      <c r="M4" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="P4" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Q4" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="R4" s="1" t="s">
+      <c r="Q4" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="R4" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="S4" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="T4" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>522</v>
+      <c r="T4" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="4">
         <v>46083</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="2">
         <v>2401</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>617</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="D5" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="H5" s="1" t="s">
+      <c r="F5" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1" t="s">
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="P5" s="1" t="s">
+      <c r="P5" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="Q5" s="1" t="s">
+      <c r="Q5" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="R5" s="1" t="s">
+      <c r="R5" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="S5" s="1" t="s">
+      <c r="S5" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="T5" s="1" t="s">
+      <c r="T5" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="U5" s="1" t="s">
-        <v>522</v>
+      <c r="U5" s="2" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="4">
         <v>46083</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="2">
         <v>2402</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="K6" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="L6" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="M6" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="4">
+        <v>46083</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2403</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="S7" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" s="4">
+        <v>46083</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2404</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="N6" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B7" s="8">
-        <v>46083</v>
-      </c>
-      <c r="C7" s="4">
-        <v>2403</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>618</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>522</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>604</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q7" s="4" t="s">
-        <v>522</v>
-      </c>
-      <c r="R7" s="4" t="s">
-        <v>522</v>
-      </c>
-      <c r="S7" s="5" t="s">
-        <v>605</v>
-      </c>
-      <c r="T7" s="4" t="s">
-        <v>522</v>
-      </c>
-      <c r="U7" s="4" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B8" s="8">
-        <v>46083</v>
-      </c>
-      <c r="C8" s="4">
-        <v>2404</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>522</v>
-      </c>
-      <c r="I8" s="4" t="s">
+      <c r="H8" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="J8" s="4" t="s">
-        <v>522</v>
-      </c>
-      <c r="K8" s="4" t="s">
+      <c r="J8" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="L8" s="4" t="s">
-        <v>522</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>522</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>522</v>
-      </c>
-      <c r="O8" s="4" t="s">
+      <c r="L8" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="O8" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="P8" s="4" t="s">
+      <c r="P8" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="Q8" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="R8" s="4" t="s">
+      <c r="Q8" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="R8" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="S8" s="4" t="s">
+      <c r="S8" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="T8" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="U8" s="5" t="s">
-        <v>629</v>
+      <c r="T8" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="4">
         <v>46083</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="2">
         <v>2405</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>612</v>
-      </c>
-      <c r="F9" s="1" t="s">
+      <c r="E9" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="H9" s="1" t="s">
+      <c r="G9" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="J9" s="1" t="s">
+      <c r="I9" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="K9" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="L9" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="O9" s="1" t="s">
+      <c r="L9" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="O9" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="P9" s="1" t="s">
+      <c r="P9" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="Q9" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="R9" s="1" t="s">
+      <c r="Q9" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="R9" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="S9" s="1" t="s">
+      <c r="S9" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="T9" s="1" t="s">
+      <c r="T9" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="U9" s="1" t="s">
-        <v>533</v>
+      <c r="U9" s="2" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="4">
         <v>46083</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="2">
         <v>2406</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="G10" s="1" t="s">
+      <c r="F10" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="I10" s="1" t="s">
+      <c r="H10" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="K10" s="1" t="s">
+      <c r="J10" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="K10" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="L10" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="P10" s="1" t="s">
+      <c r="L10" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="P10" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="Q10" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="R10" s="1" t="s">
+      <c r="Q10" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="R10" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="S10" s="1" t="s">
+      <c r="S10" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="T10" s="1" t="s">
+      <c r="T10" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="U10" s="1" t="s">
+      <c r="U10" s="2" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="11" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="4">
         <v>46083</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="2">
         <v>2407</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>627</v>
-      </c>
-      <c r="E11" s="4" t="s">
+      <c r="D11" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>614</v>
-      </c>
-      <c r="G11" s="4" t="s">
+      <c r="F11" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="J11" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="L11" s="4" t="s">
-        <v>522</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>522</v>
-      </c>
-      <c r="N11" s="4" t="s">
+      <c r="L11" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="N11" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="O11" s="4" t="s">
+      <c r="O11" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="P11" s="4" t="s">
+      <c r="P11" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="Q11" s="4" t="s">
+      <c r="Q11" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="R11" s="4" t="s">
+      <c r="R11" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="S11" s="4" t="s">
+      <c r="S11" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="T11" s="4" t="s">
-        <v>535</v>
-      </c>
-      <c r="U11" s="4" t="s">
-        <v>536</v>
+      <c r="T11" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>529</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="4">
         <v>46083</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="2">
         <v>2408</v>
       </c>
-      <c r="D12" s="9" t="s">
-        <v>619</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="D12" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="G12" s="1" t="s">
+      <c r="F12" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1" t="s">
+      <c r="I12" s="2"/>
+      <c r="J12" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="K12" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="L12" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1" t="s">
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="P12" s="1" t="s">
+      <c r="P12" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="Q12" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="R12" s="1" t="s">
+      <c r="Q12" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="R12" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="S12" s="1" t="s">
+      <c r="S12" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="T12" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="U12" s="1" t="s">
-        <v>540</v>
+      <c r="T12" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="4">
         <v>46083</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="2">
         <v>2409</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1" t="s">
+      <c r="G13" s="2"/>
+      <c r="H13" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="I13" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="J13" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="K13" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="L13" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="M13" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="N13" s="1" t="s">
+      <c r="M13" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="N13" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="O13" s="1" t="s">
+      <c r="O13" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="P13" s="1" t="s">
+      <c r="P13" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="Q13" s="1" t="s">
+      <c r="Q13" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="R13" s="1" t="s">
+      <c r="R13" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="S13" s="1" t="s">
+      <c r="S13" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="T13" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="U13" s="1" t="s">
-        <v>542</v>
+      <c r="T13" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="U13" s="2" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="4">
         <v>46083</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="2">
         <v>2410</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>522</v>
-      </c>
-      <c r="I14" s="1" t="s">
+      <c r="F14" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="J14" s="9" t="s">
-        <v>522</v>
-      </c>
-      <c r="K14" s="1" t="s">
+      <c r="J14" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="K14" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="L14" s="9" t="s">
-        <v>522</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="N14" s="9" t="s">
-        <v>522</v>
-      </c>
-      <c r="O14" s="1" t="s">
+      <c r="L14" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="O14" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="P14" s="1" t="s">
+      <c r="P14" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Q14" s="1" t="s">
+      <c r="Q14" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="R14" s="1" t="s">
+      <c r="R14" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="S14" s="1" t="s">
+      <c r="S14" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="T14" s="1" t="s">
+      <c r="T14" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="U14" s="5" t="s">
-        <v>628</v>
+      <c r="U14" s="3" t="s">
+        <v>620</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="4">
         <v>46083</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="2">
         <v>2412</v>
       </c>
-      <c r="D15" s="9" t="s">
-        <v>609</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="D15" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="I15" s="1" t="s">
+      <c r="H15" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="K15" s="1" t="s">
+      <c r="J15" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="K15" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="L15" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="O15" s="1" t="s">
+      <c r="L15" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="O15" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="P15" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="R15" s="1" t="s">
+      <c r="P15" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="R15" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="S15" s="1" t="s">
+      <c r="S15" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="T15" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>547</v>
+      <c r="T15" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="4">
         <v>46083</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="2">
         <v>2413</v>
       </c>
-      <c r="D16" s="9" t="s">
-        <v>620</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="D16" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="G16" s="1" t="s">
+      <c r="F16" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I16" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="J16" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="K16" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="L16" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="O16" s="1" t="s">
+      <c r="L16" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="O16" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="P16" s="1" t="s">
+      <c r="P16" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="Q16" s="1" t="s">
+      <c r="Q16" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="R16" s="1" t="s">
+      <c r="R16" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="S16" s="1" t="s">
+      <c r="S16" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="T16" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="U16" s="1" t="s">
+      <c r="T16" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="U16" s="2" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="4">
         <v>46083</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="2">
         <v>2416</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="G17" s="1" t="s">
+      <c r="F17" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="H17" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="I17" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="J17" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="K17" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="L17" s="1" t="s">
+      <c r="L17" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="M17" s="1" t="s">
+      <c r="M17" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="N17" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="O17" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="P17" s="1" t="s">
+      <c r="N17" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="P17" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="Q17" s="1" t="s">
+      <c r="Q17" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="R17" s="1" t="s">
+      <c r="R17" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="S17" s="1" t="s">
+      <c r="S17" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="T17" s="1" t="s">
+      <c r="T17" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="U17" s="1" t="s">
+      <c r="U17" s="2" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="4">
         <v>46083</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="2">
         <v>2417</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="H18" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="I18" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="J18" s="1" t="s">
+      <c r="I18" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="J18" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="K18" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="L18" s="1" t="s">
+      <c r="L18" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="M18" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="O18" s="1" t="s">
+      <c r="M18" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="O18" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="P18" s="1" t="s">
+      <c r="P18" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="Q18" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="R18" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="S18" s="1" t="s">
+      <c r="Q18" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="S18" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="T18" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="U18" s="1" t="s">
-        <v>555</v>
+      <c r="T18" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="U18" s="2" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="4">
         <v>46083</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" s="2">
         <v>2418</v>
       </c>
-      <c r="D19" s="9" t="s">
-        <v>621</v>
-      </c>
-      <c r="E19" s="1" t="s">
+      <c r="D19" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="G19" s="1" t="s">
+      <c r="F19" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="H19" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="I19" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="J19" s="1" t="s">
+      <c r="I19" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="J19" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="K19" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="L19" s="1" t="s">
+      <c r="L19" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="M19" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="O19" s="1" t="s">
+      <c r="M19" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="O19" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="P19" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="Q19" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="R19" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="S19" s="1" t="s">
+      <c r="P19" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="S19" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="T19" s="5" t="s">
-        <v>606</v>
-      </c>
-      <c r="U19" s="1" t="s">
-        <v>560</v>
+      <c r="T19" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="U19" s="2" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="4">
         <v>46083</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="2">
         <v>2421</v>
       </c>
-      <c r="D20" s="9" t="s">
-        <v>622</v>
-      </c>
-      <c r="E20" s="1" t="s">
+      <c r="D20" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="H20" s="1" t="s">
+      <c r="F20" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="I20" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="J20" s="1" t="s">
+      <c r="I20" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="J20" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="K20" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="L20" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="O20" s="1" t="s">
+      <c r="L20" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="O20" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="P20" s="1" t="s">
+      <c r="P20" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="Q20" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="R20" s="1" t="s">
+      <c r="Q20" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="R20" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="S20" s="1" t="s">
+      <c r="S20" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="T20" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="U20" s="1" t="s">
-        <v>564</v>
+      <c r="T20" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="U20" s="2" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="4">
         <v>46083</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" s="2">
         <v>2422</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="G21" s="1" t="s">
+      <c r="F21" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="I21" s="1" t="s">
+      <c r="H21" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="J21" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="K21" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="L21" s="1" t="s">
+      <c r="L21" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="M21" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="O21" s="1" t="s">
+      <c r="M21" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="O21" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="P21" s="1" t="s">
+      <c r="P21" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="Q21" s="1" t="s">
+      <c r="Q21" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="R21" s="1" t="s">
+      <c r="R21" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="S21" s="1" t="s">
+      <c r="S21" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="T21" s="1" t="s">
+      <c r="T21" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="U21" s="1" t="s">
-        <v>522</v>
+      <c r="U21" s="2" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="4">
         <v>46083</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="2">
         <v>2424</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="F22" s="9" t="s">
-        <v>615</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="H22" s="1" t="s">
+      <c r="F22" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="I22" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="J22" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="K22" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="L22" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="O22" s="1" t="s">
+      <c r="L22" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="O22" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="P22" s="5" t="s">
-        <v>632</v>
-      </c>
-      <c r="Q22" s="5" t="s">
-        <v>633</v>
-      </c>
-      <c r="R22" s="1" t="s">
+      <c r="P22" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="R22" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="S22" s="1" t="s">
+      <c r="S22" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="T22" s="1" t="s">
+      <c r="T22" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="U22" s="5" t="s">
-        <v>634</v>
+      <c r="U22" s="3" t="s">
+        <v>626</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="4">
         <v>46083</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" s="2">
         <v>2425</v>
       </c>
-      <c r="D23" s="9" t="s">
-        <v>603</v>
-      </c>
-      <c r="E23" s="1" t="s">
+      <c r="D23" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="F23" s="9" t="s">
-        <v>522</v>
-      </c>
-      <c r="G23" s="1" t="s">
+      <c r="F23" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="I23" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="J23" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="K23" s="9" t="s">
-        <v>522</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="N23" s="1" t="s">
+      <c r="K23" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="N23" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="O23" s="1" t="s">
+      <c r="O23" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="P23" s="1" t="s">
+      <c r="P23" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="Q23" s="1" t="s">
+      <c r="Q23" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="R23" s="1" t="s">
+      <c r="R23" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="S23" s="5" t="s">
-        <v>636</v>
-      </c>
-      <c r="T23" s="5" t="s">
-        <v>635</v>
-      </c>
-      <c r="U23" s="5" t="s">
-        <v>637</v>
+      <c r="S23" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="U23" s="3" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="4">
         <v>46083</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" s="2">
         <v>2426</v>
       </c>
-      <c r="D24" s="9" t="s">
-        <v>608</v>
-      </c>
-      <c r="E24" s="1" t="s">
+      <c r="D24" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="F24" s="9" t="s">
-        <v>607</v>
-      </c>
-      <c r="G24" s="1" t="s">
+      <c r="F24" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="I24" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="J24" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="K24" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="L24" s="1" t="s">
+      <c r="L24" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="M24" s="1" t="s">
+      <c r="M24" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="N24" s="1" t="s">
+      <c r="N24" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="O24" s="1" t="s">
+      <c r="O24" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="P24" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="Q24" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="R24" s="1" t="s">
+      <c r="P24" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="R24" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="S24" s="1" t="s">
+      <c r="S24" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="T24" s="1" t="s">
+      <c r="T24" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="U24" s="1" t="s">
-        <v>569</v>
+      <c r="U24" s="2" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="4">
         <v>46083</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" s="2">
         <v>2427</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="G25" s="1" t="s">
+      <c r="F25" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="H25" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="I25" s="1" t="s">
+      <c r="H25" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="J25" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="K25" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="L25" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="O25" s="1" t="s">
+      <c r="L25" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="O25" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="P25" s="1" t="s">
+      <c r="P25" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="Q25" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="R25" s="1" t="s">
+      <c r="Q25" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="R25" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="S25" s="1" t="s">
+      <c r="S25" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="T25" s="1" t="s">
+      <c r="T25" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="U25" s="1" t="s">
-        <v>571</v>
+      <c r="U25" s="2" t="s">
+        <v>564</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="4">
         <v>46083</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26" s="2">
         <v>2430</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="E26" s="1" t="s">
+      <c r="D26" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="H26" s="1" t="s">
+      <c r="F26" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="I26" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="J26" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="K26" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="L26" s="1" t="s">
+      <c r="L26" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="M26" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="N26" s="1" t="s">
+      <c r="M26" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="N26" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="O26" s="1" t="s">
+      <c r="O26" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="P26" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="Q26" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="R26" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="S26" s="1" t="s">
+      <c r="P26" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="S26" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="T26" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="U26" s="1" t="s">
-        <v>522</v>
+      <c r="T26" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="U26" s="2" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="4">
         <v>46083</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C27" s="2">
         <v>2432</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="E27" s="9" t="s">
-        <v>613</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="G27" s="1" t="s">
+      <c r="E27" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="H27" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="J27" s="1" t="s">
+      <c r="H27" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="J27" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="K27" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="L27" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="O27" s="1" t="s">
+      <c r="L27" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="O27" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="P27" s="1" t="s">
+      <c r="P27" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="Q27" s="1" t="s">
+      <c r="Q27" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="R27" s="1" t="s">
+      <c r="R27" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="S27" s="1" t="s">
+      <c r="S27" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="T27" s="1" t="s">
+      <c r="T27" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="U27" s="1" t="s">
-        <v>522</v>
+      <c r="U27" s="2" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="4">
         <v>46083</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28" s="2">
         <v>2433</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="E28" s="9" t="s">
-        <v>613</v>
-      </c>
-      <c r="F28" s="1" t="s">
+      <c r="E28" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="H28" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="J28" s="1" t="s">
+      <c r="H28" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="J28" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="K28" s="9" t="s">
-        <v>522</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="M28" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="O28" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="P28" s="1" t="s">
+      <c r="K28" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="P28" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="Q28" s="1" t="s">
+      <c r="Q28" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="R28" s="1" t="s">
+      <c r="R28" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="S28" s="1" t="s">
+      <c r="S28" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="T28" s="1" t="s">
+      <c r="T28" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="U28" s="1" t="s">
-        <v>522</v>
+      <c r="U28" s="2" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="4">
         <v>46083</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C29" s="2">
         <v>2434</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="H29" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="I29" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="J29" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="K29" s="1" t="s">
+      <c r="K29" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="L29" s="1" t="s">
+      <c r="L29" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="N29" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="M29" s="1" t="s">
+      <c r="O29" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="R29" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="N29" s="1" t="s">
+      <c r="S29" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="T29" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="O29" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="P29" s="1" t="s">
+      <c r="U29" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="Q29" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="R29" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="T29" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="U29" s="1" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B30" s="4">
+        <v>46083</v>
+      </c>
+      <c r="C30" s="2">
+        <v>2435</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="B30" s="7">
-        <v>46083</v>
-      </c>
-      <c r="C30" s="1">
-        <v>2435</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>610</v>
-      </c>
-      <c r="E30" s="1" t="s">
+      <c r="J30" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="K30" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="L30" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="M30" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="N30" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="O30" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="P30" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="Q30" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="L30" s="1" t="s">
+      <c r="R30" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="M30" s="1" t="s">
+      <c r="S30" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="N30" s="1" t="s">
+      <c r="T30" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="O30" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="P30" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="Q30" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="R30" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="T30" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="U30" s="1" t="s">
-        <v>522</v>
+      <c r="U30" s="2" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B31" s="4">
+        <v>46083</v>
+      </c>
+      <c r="C31" s="2">
+        <v>2436</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="J31" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="B31" s="7">
-        <v>46083</v>
-      </c>
-      <c r="C31" s="1">
-        <v>2436</v>
-      </c>
-      <c r="D31" s="1" t="s">
+      <c r="K31" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="L31" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="N31" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="G31" s="1" t="s">
+      <c r="O31" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="P31" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="Q31" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="R31" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="S31" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="L31" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="N31" s="1" t="s">
+      <c r="T31" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="O31" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="P31" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="Q31" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="R31" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="S31" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="T31" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="U31" s="1" t="s">
-        <v>577</v>
+      <c r="U31" s="2" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B32" s="4">
+        <v>46083</v>
+      </c>
+      <c r="C32" s="2">
+        <v>2437</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="K32" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="B32" s="7">
-        <v>46083</v>
-      </c>
-      <c r="C32" s="1">
-        <v>2437</v>
-      </c>
-      <c r="D32" s="1" t="s">
+      <c r="L32" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="M32" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="H32" s="1" t="s">
+      <c r="N32" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="O32" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="P32" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="Q32" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="R32" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="L32" s="1" t="s">
+      <c r="S32" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="M32" s="1" t="s">
+      <c r="T32" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="N32" s="1" t="s">
+      <c r="U32" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="O32" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="P32" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="Q32" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="R32" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="S32" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="T32" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="U32" s="1" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B33" s="4">
+        <v>46083</v>
+      </c>
+      <c r="C33" s="2">
+        <v>2439</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="Q33" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B33" s="7">
+      <c r="R33" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="S33" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="T33" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="U33" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B34" s="4">
         <v>46083</v>
       </c>
-      <c r="C33" s="1">
-        <v>2439</v>
-      </c>
-      <c r="D33" s="9" t="s">
+      <c r="C34" s="2">
+        <v>2442</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="Q34" s="3" t="s">
         <v>623</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="M33" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="P33" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="Q33" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="R33" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="S33" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="T33" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="U33" s="1" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="B34" s="8">
-        <v>46083</v>
-      </c>
-      <c r="C34" s="4">
-        <v>2442</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>392</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>393</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>583</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>522</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="I34" s="4" t="s">
+      <c r="R34" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="J34" s="4" t="s">
+      <c r="S34" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="K34" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="L34" s="5" t="s">
-        <v>522</v>
-      </c>
-      <c r="M34" s="5" t="s">
-        <v>522</v>
-      </c>
-      <c r="N34" s="4" t="s">
-        <v>397</v>
-      </c>
-      <c r="O34" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="P34" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="Q34" s="5" t="s">
-        <v>631</v>
-      </c>
-      <c r="R34" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="S34" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="T34" s="5" t="s">
-        <v>638</v>
-      </c>
-      <c r="U34" s="4" t="s">
-        <v>522</v>
+      <c r="T34" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="U34" s="2" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B35" s="4">
+        <v>46083</v>
+      </c>
+      <c r="C35" s="2">
+        <v>2443</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="N35" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B35" s="7">
-        <v>46083</v>
-      </c>
-      <c r="C35" s="1">
-        <v>2443</v>
-      </c>
-      <c r="D35" s="9" t="s">
+      <c r="O35" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="P35" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="F35" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="G35" s="1" t="s">
+      <c r="Q35" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="R35" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="H35" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I35" s="1" t="s">
+      <c r="S35" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="J35" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="M35" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="O35" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="P35" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="Q35" s="5" t="s">
-        <v>630</v>
-      </c>
-      <c r="R35" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="S35" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="T35" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="U35" s="1" t="s">
-        <v>522</v>
+      <c r="T35" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="U35" s="2" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B36" s="4">
+        <v>46083</v>
+      </c>
+      <c r="C36" s="2">
+        <v>2447</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="P36" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="B36" s="7">
-        <v>46083</v>
-      </c>
-      <c r="C36" s="1">
-        <v>2447</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>624</v>
-      </c>
-      <c r="E36" s="1" t="s">
+      <c r="Q36" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="F36" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="G36" s="1" t="s">
+      <c r="R36" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="H36" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="J36" s="1" t="s">
+      <c r="S36" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="K36" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M36" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="N36" s="1" t="s">
+      <c r="T36" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="O36" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="P36" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="Q36" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="R36" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="S36" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="T36" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="U36" s="1" t="s">
-        <v>587</v>
+      <c r="U36" s="2" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="B37" s="4">
+        <v>46083</v>
+      </c>
+      <c r="C37" s="2">
+        <v>2448</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="M37" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="B37" s="7">
-        <v>46083</v>
-      </c>
-      <c r="C37" s="1">
-        <v>2448</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>625</v>
-      </c>
-      <c r="E37" s="1" t="s">
+      <c r="N37" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="O37" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="P37" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="G37" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="I37" s="1" t="s">
+      <c r="Q37" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="J37" s="1" t="s">
+      <c r="R37" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="S37" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="T37" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="L37" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="M37" s="1" t="s">
+      <c r="U37" s="2" t="s">
         <v>430</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="O37" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="P37" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="Q37" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="R37" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="S37" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="T37" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="U37" s="1" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B38" s="4">
+        <v>46083</v>
+      </c>
+      <c r="C38" s="2">
+        <v>2449</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="M38" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="B38" s="7">
-        <v>46083</v>
-      </c>
-      <c r="C38" s="1">
-        <v>2449</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>611</v>
-      </c>
-      <c r="E38" s="1" t="s">
+      <c r="N38" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="H38" s="1" t="s">
+      <c r="O38" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="I38" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="J38" s="1" t="s">
+      <c r="P38" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="Q38" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="L38" s="1" t="s">
+      <c r="R38" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="M38" s="1" t="s">
+      <c r="S38" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="N38" s="1" t="s">
+      <c r="T38" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="O38" s="1" t="s">
+      <c r="U38" s="2" t="s">
         <v>445</v>
-      </c>
-      <c r="P38" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="Q38" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="R38" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="S38" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="T38" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="U38" s="1" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B39" s="4">
+        <v>46083</v>
+      </c>
+      <c r="C39" s="2">
+        <v>2451</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="Q39" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="B39" s="7">
-        <v>46083</v>
-      </c>
-      <c r="C39" s="1">
-        <v>2451</v>
-      </c>
-      <c r="D39" s="1" t="s">
+      <c r="R39" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="S39" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="I39" s="1" t="s">
+      <c r="T39" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="J39" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="M39" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="N39" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="O39" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="P39" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="Q39" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="R39" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="S39" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="T39" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="U39" s="1" t="s">
-        <v>522</v>
+      <c r="U39" s="2" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="B40" s="4">
+        <v>46083</v>
+      </c>
+      <c r="C40" s="2">
+        <v>2452</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="N40" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="B40" s="7">
-        <v>46083</v>
-      </c>
-      <c r="C40" s="1">
-        <v>2452</v>
-      </c>
-      <c r="D40" s="1" t="s">
+      <c r="O40" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="I40" s="1" t="s">
+      <c r="P40" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="J40" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="K40" s="1" t="s">
+      <c r="Q40" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="R40" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="L40" s="1" t="s">
+      <c r="S40" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="M40" s="1" t="s">
+      <c r="T40" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="N40" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="O40" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="P40" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="Q40" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="R40" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="S40" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="T40" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="U40" s="1" t="s">
-        <v>592</v>
+      <c r="U40" s="2" t="s">
+        <v>584</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="B41" s="4">
+        <v>46083</v>
+      </c>
+      <c r="C41" s="2">
+        <v>2504</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="J41" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="B41" s="7">
-        <v>46083</v>
-      </c>
-      <c r="C41" s="1">
-        <v>2504</v>
-      </c>
-      <c r="D41" s="1" t="s">
+      <c r="K41" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="L41" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="G41" s="1" t="s">
+      <c r="M41" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="N41" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="O41" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="P41" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="J41" s="1" t="s">
+      <c r="Q41" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="K41" s="1" t="s">
+      <c r="R41" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="L41" s="1" t="s">
+      <c r="S41" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="M41" s="1" t="s">
+      <c r="T41" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="N41" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="O41" s="1" t="s">
+      <c r="U41" s="2" t="s">
         <v>483</v>
-      </c>
-      <c r="P41" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="Q41" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="R41" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="S41" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="T41" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="U41" s="1" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="B42" s="4">
+        <v>46083</v>
+      </c>
+      <c r="C42" s="2">
+        <v>2513</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q42" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="R42" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="S42" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="B42" s="7">
-        <v>46083</v>
-      </c>
-      <c r="C42" s="1">
-        <v>2513</v>
-      </c>
-      <c r="D42" s="1" t="s">
+      <c r="T42" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="E42" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="L42" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="M42" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="N42" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="O42" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="P42" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q42" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="R42" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="S42" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="T42" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="U42" s="1" t="s">
-        <v>597</v>
+      <c r="U42" s="2" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B43" s="4">
+        <v>46083</v>
+      </c>
+      <c r="C43" s="2">
+        <v>2545</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="I43" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="B43" s="7">
-        <v>46083</v>
-      </c>
-      <c r="C43" s="1">
-        <v>2545</v>
-      </c>
-      <c r="D43" s="1" t="s">
+      <c r="J43" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="O43" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="P43" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="Q43" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="R43" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="S43" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="I43" s="1" t="s">
+      <c r="T43" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="J43" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L43" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M43" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="O43" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="P43" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="Q43" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="R43" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="S43" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="T43" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="U43" s="1" t="s">
-        <v>522</v>
+      <c r="U43" s="2" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
+      <c r="A44" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B44" s="4">
+        <v>46083</v>
+      </c>
+      <c r="C44" s="2">
+        <v>3682</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="P44" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="Q44" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="R44" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="B44" s="7">
-        <v>46083</v>
-      </c>
-      <c r="C44" s="1">
-        <v>3682</v>
-      </c>
-      <c r="D44" s="1" t="s">
+      <c r="S44" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="T44" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="F44" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="P44" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="Q44" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="R44" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="S44" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="T44" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="U44" s="1" t="s">
-        <v>598</v>
+      <c r="U44" s="2" t="s">
+        <v>590</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/pssi_form_data_altered.xlsx
+++ b/data/processed/pssi_form_data_altered.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ennsj\Documents\PSSI-final-tech-report\data\processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72209C9B-6B2A-454B-AB74-0C9975FB44EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F7D77F9-9F23-45BC-AFCB-7DF6E7C4C337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1485" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="636">
   <si>
     <t>source_file</t>
   </si>
@@ -227,32 +227,12 @@
     <t>Pacific</t>
   </si>
   <si>
-    <t>Chinook salmon (Fall, Spring, and Summer)
-Coho salmon (Fall)</t>
-  </si>
-  <si>
     <t>Juveniles, broodstock</t>
   </si>
   <si>
     <t>Puntledge, Nitinat, Coldwater River, Spius Creek, Nicola River, Chilcotin River, Chilko Ricer, Salmon River, Eagle River</t>
   </si>
   <si>
-    <t>*Renibacterium salmoninarum*, the causative agent of bacterial kidney disease (BKD), is endemic to the Pacific Northwest. Infection with this bacterial pathogen can result in significant morbidity and mortality in cultured juvenile Pacific salmon. Current BKD management relies on screening brood stock using an enzyme-linked immunosorbent assay (ELISA) and excluding eggs from females exceeding the defined optical density (OD) threshold. This approach has significantly reduced the incidence of disease in both hatchery-reared juveniles and returning adult fish. The Salmonid Enhancement Program (SEP) maintains an extensive dataset that includes 16 years of ELISA broodstock screening results for many Vancouver Island and mainland Coho and Chinook stocks.
-These datasets have not been previously subjected to a comprehensive epidemiological analysis to identify potential explanatory variables for BKD prevalence in stocks of concern. This project sought to address that knowledge gap by integrating ELISA data and linking broodstock ELISA values to Parental Based Tagging (PBT) information enabling stock-specific analyses. The work was conducted through a collaborative partnership among the Science Branch, SEP, and Aquaculture Management.</t>
-  </si>
-  <si>
-    <t>This project contributes significant clarity to the understanding of BKD transmission by identifying that environmental and population-level factors often overshadow direct parent-to-offspring transmission in wild and enhanced stocks. By demonstrating that BKD levels in returning adults are more closely associated with watershed characteristics and thermal regimes than with the status of their progenitors, this research shifts the focus toward environmental stressors as primary drivers of disease expression. These findings highlight a critical pathway of effect where colder water temperatures facilitate higher pathogen loads, a relationship that is further intensified by the cumulative impact of high disease prevalence within the population. This identification of thermal and density-dependent "modulating effects" provides a more nuanced understanding of how multiple stressors interact to influence the health of salmon cohorts.
-From a management and policy perspective, these insights inform risk assessment and hatchery planning by emphasizing that individual-level screening of broodstock may be insufficient without considering broader ecological context. The study provides a framework for evidence-based decisions regarding stock transfers and watershed-specific management, suggesting that biologically significant thresholds for disease may vary depending on local environmental conditions. By accounting for these spatial and temporal variables, managers can better navigate the trade-offs between enhancement goals and the risks of disease outbreaks.
-A primary source of uncertainty in this analysis, however, stems from the operational protocols used to manage BKD in hatcheries. The standard practice of utilizing OD thresholds to cull high-risk eggs creates a filtered data set, as the most heavily infected vertical transmission paths are often removed from the population before they can be assessed in returning adults. Furthermore, when conservation concerns for at-risk populations supersede these culling protocols, it introduces additional variability into the transmission pathway. This management-induced selection bias limits our ability to fully quantify the role of vertical transmission, as the observed returning population primarily represents individuals that either passed through a selective screening process or were spared due to conservation priorities.
----
-The findings reveal key knowledge gaps in understanding BKD dynamics, suggesting the need for further research to build a fuller picture of the factors influencing disease transmission and prevalence. The low goodness-of-fit of the current model indicates that additional variables, such as hatchery practices, genetic diversity, or other environmental and anthropogenic stressors, may play significant roles in shaping BKD dynamics. A promising avenue for research includes the use of simulation models to assess the impact of altering management practices, such as raising or lowering the positive-negative culling threshold OD value. This approach could help predict how adjustments to culling thresholds might influence disease prevalence and population outcomes under varying environmental conditions. Research should also focus on understanding potential thresholds or tipping points where environmental conditions, such as temperature extremes, significantly influence disease prevalence and outcomes.
-The study's findings can inform proactive strategies for salmon conservation and management, particularly concerning how environmental conditions affect BKD prevalence. Managers could prioritize monitoring in watersheds where conditions, including temperature and BKD prevalence, elevate disease transmission risks. Additionally, the insights from simulations examining the effect of changing the positive-negative culling threshold OD value could guide policy and operational decisions to strike a balance between limiting disease spread and optimizing population sustainability.</t>
-  </si>
-  <si>
-    <t>The findings reveal key knowledge gaps in understanding BKD dynamics, suggesting the need for further research to build a fuller picture of the factors influencing disease transmission and prevalence. The low goodness-of-fit of the current model indicates that additional variables, such as hatchery practices, genetic diversity, or other environmental and anthropogenic stressors, may play significant roles in shaping BKD dynamics. A promising avenue for research includes the use of simulation models to assess the impact of altering management practices, such as raising or lowering the positive-negative culling threshold OD value. This approach could help predict how adjustments to culling thresholds might influence disease prevalence and population outcomes under varying environmental conditions. Research should also focus on understanding potential thresholds or tipping points where environmental conditions, such as temperature extremes, significantly influence disease prevalence and outcomes.
-The study's findings can inform proactive strategies for salmon conservation and management, particularly concerning how environmental conditions affect BKD prevalence. Managers could prioritize monitoring in watersheds where conditions, including temperature and BKD prevalence, elevate disease transmission risks. Additionally, the insights from simulations examining the effect of changing the positive-negative culling threshold OD value could guide policy and operational decisions to strike a balance between limiting disease spread and optimizing population sustainability.</t>
-  </si>
-  <si>
     <t>2401 PSSI final report-Garver.docx</t>
   </si>
   <si>
@@ -263,35 +243,6 @@
   </si>
   <si>
     <t>Weaver Creek, Nadina River, Fulton River, Pinkut Creek</t>
-  </si>
-  <si>
-    <t>This study examined IHNV prevalence across different watersheds, Sockeye stocks, and environmental conditions to identify those factors responsible for driving IHNV prevalence and/or influencing disease within Sockeye salmon populations.</t>
-  </si>
-  <si>
-    <t>Infectious hematopoietic necrosis virus (IHNV) is a deadly virus of Sockeye salmon, causing catastrophic losses during the early lifestages. Long-term monitoring of IHNV infections across multiple stocks of Sockeye salmon has revealed the prevalence of IHNV infections can vary annually within and between stocks; however, the factor(s) responsible for such fluctuations in IHNV prevalence in sockeye salmon stocks in British Columbia remain unresolved. Understanding the drivers behind the occurrence and perpetuation of IHNV in Sockeye salmon is instrumental in managing and mitigating the risk of this endemic pathogen. Utilizing epidemiological analytical approaches to study the patterns of IHNV in Sockeye salmon we'll identify the factors which influence the prevalence of the virus in BC Sockeye salmon stocks.</t>
-  </si>
-  <si>
-    <t>METHODS:
-Adult and fry Sockeye salmon were each collected annually from 1987 to 2018, from each of four spawning channel populations, representing two stocks within the Fraser River watershed and two within the Skeena River watershed (Figure 1). Samples were screened for the presence of infectious hematopoiectic necrosis virus (IHNV) using cell culture methodologies. Characteristic cytopathic effects (CPE) observed in cells indicated the presence of viable replicating IHNV. Prevalence of IHNV was calculated by dividing the number of samples with CPE by the total number of samples screened.
-We used statistical methods to understand how IHNV prevalence in adult fish relate to infection levels in fry, and how infection in fry affects infection in adults that return 3-4 years later.
-To compare how infection levels changed over time, we looked at timeseries data for each project site (Fulton, Pinkut, Nadina, Weaver) and for each life stage (fry, adult males, adult females). We used a clustering method that can line up patterns even when the timing doesn't match perfectly (a technique called dynamic time warping) to measure how similar the trends were.
-To study how infection in returning adults affects IHNV prevalence in fry, we used a mixedeffects binomial model for proportions that accounted for differences between spawning years and project sites.
-To study how fry infection affects infection in adults 3-4 years later, we used a similar model along with escapement data to calculate a weighted average of fry infection that matched the makeup of the returning adult population. Because the relationship wasn't linear, we also added a quadratic term to better capture the pattern.
-RESULTS:
-From 1987 to 2018, a total of 56,692 Sockeye salmon were screened for IHNV. Over this 32 year timeframe, the prevalence of IHNV infections varied annually within and between the four stocks sampled (Figure 2). Across the entire dataset, there was a positive correlation between the detection of IHNV in male and female samples; with the prevalence being generally higher in females than in males (Figure 3). Nonetheless, this prevalence in spawned females was not demonstrative of what was observed in fry, as there were numerous years where IHNV was not detected in the fry despite high prevalence in the broodstock. However, it appears as though the IHNV prevalence in fry is a strong predictor of the population's IHNV status upon returning adults 4 years later. For instance, fry with 50% IHNV prevalence are predicted to return as adults with a prevalence of 30 to 80% (Figure 4).</t>
-  </si>
-  <si>
-    <t>This work provides the first long-term dataset of infectious hematopoietic necrosis virus (IHNV) prevalence among various Sockeye salmon stocks in British Columbia and reveals a highly dynamic nature of this deadly virus. From this data, it was learned that when surveying adult fish, it is best to sample females as they have the highest prevalence. In naturally spawning populations of Sockeye salmon, it was found that the IHNV prevalence in broodstock offers little insight into the infection status of fry, as true parent to progeny transmission is unlikely. In many instances, high IHNV prevalence in adults did not result in the occurrence of virus in fry. However, unexpectedly it was discovered that IHNV prevalence in fry is significantly correlated to the prevalence of returning adults, suggesting IHNV in adults is partially explained by their status as fry and supports the role of a lifelong IHNV carrier state in perpetuating IHNV in Sockeye salmon populations.</t>
-  </si>
-  <si>
-    <t>This work illustrates the importance of long-term datasets in differentiating genuine trends from short term fluctuations and to uncover complex ecological dynamics. Analysis of IHNV prevalence across the four stocks over the 32 year timeframe revealed that prevalence across stocks is most similar within a river system, suggesting watershed or regional specific factors may influence level of IHNV in the system (Figure 5). Nonetheless, a shared prolonged reduction of IHNV observed across both Fraser and Skeena watersheds, suggests broader oceanic factor(s) are contributing to the occurrence of IHNV in Sockeye salmon (Figure 2). Given these trends, we are presently gathering environmental, management and other data to determine if there are correlates that are explanatory for these trends. In particularly, we are employing Pacea, an R package of ecosystem information, to link biological data with environmental variable to generate models and visualizations.</t>
-  </si>
-  <si>
-    <t>Figure 1. Map showing the locations of the Sockeye Salmon spawning channels (red circles) within the Skeena and Fraser River watersheds, revealed by blue and olive shading; respectively.
-Figure 2. Annual prevalence of IHNV in adults (grey) and fry (black) Sockeye salmon collected over 32 years from spawning channels located at Fulton River, Pinkut Creek, Nadina River and Weaver Creek. Blue shading highlights years where IHNV prevalence was generally lower across all four collection sites.
-Figure 3. Plot illustrating a positive relationship between IHNV prevalence in males (y-axis) and females (x-axis)
-Figure 4. Plot illustrating the predicted IHNV prevalence in returning adult Sockeye salmon to Fulton River Spawning Channel based on IHNV prevalence in fry. Grey shading represents 95% confidence intervals.
-Figure 5. Cluster diagram illustrating similarities in IHNV prevalence of adult female Sockeye salmon across spawning channels over a 32 year time period.</t>
   </si>
   <si>
     <t>2402 PSSI Science Project Yukon Telemetry.docx</t>
@@ -376,16 +327,8 @@
     <t>Fry to smolt</t>
   </si>
   <si>
-    <t>San Juan Chinook</t>
-  </si>
-  <si>
     <t>- San Juan Chinook are a unique population part of the WCVI Fall Chinook CU that has recently received a rebuilding plan. Risk assessments have noted knowledge gaps related to juvenile life stages in the freshwater, estuary and early marine stages. This project aims to fill some of these data gaps.
 - The results from this project will inform a revised risk assessment process for WCVI Chinook in 2026, as well as provide Pacheedaht First Nation with data upon which to base their rebuilding plan for San Juan Chinook and to inform restoration efforts in the watershed.</t>
-  </si>
-  <si>
-    <t>These activities will all inform the San Juan Chinook Rebuilding Plan in development by PFN, which will be linked to the broader WCVI Chinook Rebuilding Plan recently developed by DFO (required under the Fish Stock Provisions Act for naturally-produced WCVI Chinook) (DFO 2025). This project will also inform a risk assessment re-scoring expected to happen in 2026, where new information from PSSI projects will be used to re-evaluate the most prominent bottlenecks to WCVI Chinook survival and recovery. The first round WCVI Chinook risk assessment process identified several knowledge gaps, mostly related to early freshwater and marine life cycle stages. For San Juan Chinook specifically, juvenile data from these life stages (and interactions between hatchery and wild juveniles) are sparse, and biological data on natural spawners (e.g., age, origin) are limited.
-These reasons made the San Juan River a good candidate to develop an integrated life history monitoring program in alignment with the larger Follow The Fish program. We focused on activities complemented Pacheedaht First Nation's established juvenile monitoring programs. First, we operated a rotary screw trap program to enumerate and sample naturally-produced out-migrating juveniles (all species, but focused on juvenile Chinook migration timing) in the freshwater environment, allowing us to compare natural migration timing to hatchery release timing, gather baseline biological traits relative to hatchery releases (e.g., size, condition), and estimate fry outmigration abundance. Otolith and stomach samples are also collected from a sub-sample of individuals to assess size-specific survival and diet contents. Second, we collected samples from Pacheedaht's estuary beach seine program to continue examining diet differences and estuary residency (via otolith microchemistry) between hatchery and natural-origin Chinook. Finally, we conducted biweekly purse seining in Port San Juan (PFMA 20-2) through the late spring, summer and fall months (~May-October) to collect mixed-stock information, including hatchery/natural-origin of juvenile Chinook, stock ID, biological traits, relative abundance, and information on other species schooling with Chinook (e.g., Coho, Pacific Herring). As with the RST and beach seine, we also collected otoliths and stomach contents from a sub-sample of Chinook encountered. Finally, we developed a biosampling plan to assess age and stock composition of naturally-spawning adult Chinook (a deadpitch program). Current information on the Proportion of Natural Influence (PNI) is limited only to broodstock sampling, but it is unknown whether these samples are biased and whether they are representative of the river spawning component of the population. It is critical to have an accurate representation of PNI and age and composition-at-return to assess productivity trends and hatchery release strategies for rebuilding San Juan Chinook.
-All work was done in collaboration with Pacheedaht First Nation. Their Fisheries Team lead the majority of the field work and sample collection, as well as advised on sampling designs and salmon dynamics to improve the study design of the project.</t>
   </si>
   <si>
     <t>2404 PSSI Science Project Reporting_Bianucci.docx</t>
@@ -624,20 +567,6 @@
   </si>
   <si>
     <t>Fraser River sockeye salmon productivity has been poor since the early 1990s (Peterman and Dorner 2012). Although the mechanism remains unclear and is likely multifaceted (Cohen 2012), bottom-up processes that reduce juvenile marine survival have been identified as a</t>
-  </si>
-  <si>
-    <t>We used multiple methods to evaluate SSL foraging ecology, quantify sockeye salmon mortality rates, and ultimately draw inference on the likely impact of SSLs on migrating Fraser River sockeye salmon. The following activities occurred during the 2024 and 2025 field seasons (Figure 1).
-*Sockeye Salmon Methods*
-Sockeye salmon were captured aboard a charter purse seine vessel from sites near Rennell Sound (west coast Haida Gwaii; 2024 and 2025) and Queen Charlotte Strait (2025 only). Sockeye salmon were landed and transferred to a flow through seawater trough where biological data, including genetic stock identification (GSI) samples, were collected. Individuals in good physical condition were tagged with either an acoustic or satellite tag before being immediately released. We deployed acoustic transmitters on sockeye salmon (n=625) which allowed individuals to be detected on moored receiver arrays near Haida Gwaii, Triangle Island, Queen Charlotte Strait, throughout the Salish Sea, and the lower Fraser River. The acoustic receiver network included approximately 40 receivers deployed by DFO throughout coastal British Columbia, as well as infrastructure maintained by NOAA, the Ocean Tracking Network, Kintama, and the University of British Columbia. Detections data will be used to parameterize mark-recapture models to estimate survival rates along the migration corridor and identify hotspots of mortality. We also deployed popup archival satellite tags (PSATs) on a smaller number of sockeye salmon (n=35). After releasing from the animal these tags transmit light, temperature, and pressure sensor data that can be used to identify predator taxa (Seitz et al. 2019).
-*Sockeye Salmon Findings*
-GSI results are currently only available for the 2024 field season; however, the majority (&gt;98%) of tagged sockeye salmon were identified as belonging to Fraser River populations with Chilko Lake being the dominant conservation unit (~55% of all samples). Only a subset of detections data are currently available for 2025; however preliminary results in both years (Figure 2) indicate overall survival from Haida Gwaii to the Fraser River was poor (&lt;8%). ~50% of individuals tagged at northern sites were detected on Haida Gwaii arrays; however, mark-recapture models that account for imperfect detection probability on these arrays are required for robust estimates of survival. Survival to the Fraser River of tags deployed in Queen Charlotte Strait was markedly higher (~40%). 2% of tags were detected in the study area after deployments were completed, suggesting short-term mortality due to tagging or handling was minimal. Only two tags were detected at Triangle Island (both in 2025), however 46 tags were detected in 2025 at sea lion haul outs throughout Queen Charlotte Strait. Importantly, additional analysis is required to determine how many of these fish were likely consumed by pinnipeds based on subsequent detections. No fish were reported as intercepted by fisheries in 2024, but 5% of tagged fish were recaptured by marine and in-river fisheries and reported in 2025.
-We deployed 18 PSATs at Haida Gwaii sites in 2024 and 17 in 2025 (ten in Haida Gwaii and seven in Queen Charlotte Strait). Six of the 2024 PSATs failed to report due to engineering issues. All of the remaining 12 reported before their programmed release data, suggesting the fish were predated. Of the confirmed mortalities, three could not be classified because the tag was not ingested, one was consumed by a benthic ectotherm, and eight were consumed by salmon sharks (Figure 3). In 2025, all PSATs reported and five survived to release, all from the Queen Charlotte Strait study area. Of the ten Haida Gwaii tags, four were consumed by blue sharks, three by a benthic ectotherm, and three by salmon sharks. Neither of the two Queen Charlotte Strait mortalities could be classified (Figure 3).
-*SSL Methods*
-We deployed satellite tags (paired head-mounted splash and flipper-mounted spot tags) on adult male (n=7) and female (n=14) SSLs on Triangle Island. Animals were sedated via darting gun and tagged with the assistance of staff from the Vancouver Aquarium. Females were captured near the end of July following pupping; males were captured at the beginning of June as animals staked out territories for the breeding period. Head mounted tags were epoxied to the fur and were shed by fall during the annual moult while the flipper mounted tags should stay affixed for multiple years although tag programming and battery life will ultimately determine transmission duration. The high resolution, yet shorter deployment splash tags will allow for an understanding of foraging behaviour (location and dive profiles) and sex-specific habitat use revealing explicit spatial-temporal overlap with sockeye salmon during their migration through Queen Charlotte Sound. This distribution data is critical in evaluating the relative proportion of the SSL population that has the opportunity to predate sockeye salmon. The longer-term flipper tags (8-16 months; multi-year) will allow for multi-season information on coarse foraging patterns.
-We also collected SSL diet information via biochemical tracers and scats from sites on Triangle Island, as well as key haul outs in Queen Charlotte Strait, southwest coast of Vancouver Island, and the southern Strait of Georgia. The two biochemical tracers we have focused on, fatty acid profiles and stable isotopes, provide estimates of diet composition integrated over weeks to month. The fatty acid analysis (FAA; Budget et al. 2006) will provide more discrete diet estimation (prey-specific proportions) while the stable isotope analysis (SIA; Layman et al. 2012) will be useful to discriminate feeding source (pelagic vs demersal, nearshore vs shelf vs shelf break) such that we can broadly characterize foraging behaviour beyond the satellite tagged individuals. Diets estimated from scats provide a short-term (~ 1 day) estimate requiring far more extensive, repeated sampling to capture temporal variation in diet-particularly if the objective is to capture a potential pulse of a relatively rapidly migrating prey. While we collected scats (n=1,200), there was insufficient funding provided to analyze these, let alone undertake a full-fledged sampling design for scats. These are therefore archived for potential future work and analysis focused on the integrated tracer samples. In total, ~400 sea lion biopsy samples were obtained directly from satellite tagged animals or randomly via a crossbow system. To estimate diet, over 1500 potential fish and invertebrate prey samples were obtained from various DFO research cruises.
-*SSL Findings*
-During the 5 - 6-week deployments prior to moult, female foraging was concentrated on the continental shelf (Figure 4a). In the initial weeks, animals used Triangle Island as a central place for short foraging forays. As pups inevitably grew and became more independent, there was a gradual expansion and dispersal away from Triangle east to Cook Bank and Queen Charlotte Strait and south-east to Quatsino Sound with females ultimately moving to sites both east and south of Triangle Island. During the 14 - 16-week deployments prior to moult, males demonstrated very limited foraging activity during the breeding period (Figure 4b). Subsequently by mid-July there was rapid and directed dispersal immediately post-breeding with individuals ranging as far north as southeast Alaska and south to the Washington border. Triangle was not used as major haul out outside of the breeding period for either females or males. More in-depth analysis of distribution and dive behaviour is underway to explicitly parameterize sea lion foraging effort in a spatial context and provide support for interpreting diet results.
-Stable isotope and fatty acid datasets for potential prey and sea lions have been completed for 2023-2024 samples; 2025 samples are currently being processed and analyzed. Preliminary analysis of 2023-2024 SI values for known age class and sex animals suggests that males and females are exploiting different prey/habitats diverging further with age (Figure 5).</t>
   </si>
   <si>
     <t>Although analyses are underway, there are several key preliminary results. We found that sockeye salmon mortality rates during adult marine migrations may be considerably higher than previously assumed (e.g. Cohen 2012). At the same time, it is clear that the predator community varies along the migratory corridor--while we found some evidence of pinniped predation in Queen Charlotte Strait that warrants additional investigation, we found no evidence of pinniped predation near Haida Gwaii where mortality rates were high and apparently driven by shark predation. Similarly, we found evidence that predation impacts likely vary among and within sea lion haul outs. Despite the large size of the Triangle Island rookery, we found a very small number of tags at this location, particularly relative to Queen Charlotte Strait haul outs.
@@ -892,18 +821,7 @@
     <t>Pacific Science Enterprise Centre</t>
   </si>
   <si>
-    <t>Chinook, coho, sockeye, and pink salmon</t>
-  </si>
-  <si>
-    <t>Egg stage; adult</t>
-  </si>
-  <si>
     <t>Capilano early and mid Coho, Chilliwack Fall Chinook, Cheakamus Chinook, Harrison Sockeye, Chilko Sockeye, Weaver Creek Sockeye, Chehalis Pink</t>
-  </si>
-  <si>
-    <t>- Thiamine deficiency complex (TDC) is an emerging concern in Pacific salmon, potentially contributing to en route and prespawn adult mortality and elevated fry mortality, yet little is known about the prevalence of TDC in Canadian Pacific salmon populations.
-- This project established thiamine analysis capability for fish tissues (e.g. eggs, plasma, muscle, liver) by the Nutrition lab at the DFO Pacific Science Enterprise Centre (PSEC).
-- Preliminary data discovered that total thiamine levels in eggs of both coho and Chinook salmon in BC generally ranged from 6 - 13 nmol/g, most pink Salmon contained 4 - 8 nmol/g, but most sockeye salmon eggs only contained 2 - 6 nmol/g, which suggests that some Pacific salmon populations in BC may exhibit TDC and warrant further monitoring.</t>
   </si>
   <si>
     <t>With the thiamine analysis capacity established at PSEC, DFO can now further expand research relevant to thiamine and fish in Canada. First of all, more research is urgently needed to determine the status of TDC across stocks of all 5 species of Pacific salmon in BC and the Yukon, across the life cycle (especially adults and eggs). Second, we need to establish how thiamine levels vary across tissue types (e.g. muscle, ventricle, liver, plasma, eggs) and identify whether plasma thiamine levels could be used as a non-lethal indicator of adult salmon thiamine status. Third, we need to establish the thiamine and thiaminase status of the primary prey species in both ocean and freshwater habitats and how these may be changing over time. As such, a next step for the Nutrition lab at PSEC is to establish a protocol for thiaminase activity and begin collaborating with other groups to collect and assess prey. Fourth, we need to determine TDC thresholds for impairment for all 5 species of Pacific salmon species, in both eggs and migrating adults. Finally, we need carefully controlled experiments to assess the effectiveness and necessity of thiamine treatment (both bathing eggs and injecting broodstock) for hatcheries in BC.</t>
@@ -1053,12 +971,6 @@
   <si>
     <t>Understanding where and how fish and fish habitat are impacted by human activities and climate change is critical information for targeting effective conservation and management actions to help preserve populations. Geospatial cumulative effects assessments offer a powerful approach for evaluating simultaneous threats across large spatial scales, improving upon traditional field-based assessments (Halpern et al. 2008a; Halpern and Fujita 2013). However, many existing assessments rely on simple proxies of human activity (e.g., road density) rather than mechanistic metrics that directly link stressors to ecological responses relevant to fish and fish habitat (e.g., sediment loading or flow alteration) to provide more meaningful applications (e.g., stressor-response curves; Rosenfeld et al. 2022). To address this gap, this project advanced existing geospatial tools, indicators, and threat metrics for the Pacific Region (DFO 2022) by incorporating a mechanistic approach to better quantify anthropogenic and climate change impacts and inform management actions for salmon and Species at Risk (SAR) in the Fraser River Basin (FRB).
 The Thompson-Shuswap and Nicola River watersheds were identified as pilot areas to deliver Integrated Planning for Salmon Ecosystems (IPSE) under the Pacific Salmon Strategy Initiative (PSSI). Within the scope of this project, we conducted a case-study on the Thompson-Nicola Ecological Drainage Unit (EDU) by developing examples of how individual and cumulative threat scores can be applied to help inform restoration prioritization and management actions. The Thompson-Nicola spatial analysis was used to inform IPSE collaborative planning processes in the Thompson-Nicola watersheds.</t>
-  </si>
-  <si>
-    <t>We developed a geospatial tool to summarize anthropogenic and climate change related cumulative threats to freshwater species and habitats using open-source input data and software that can be reproduced for different time periods and freshwater species and their habitats. All threats were estimated for each stream reach within the BC Freshwater Atlas (FWA). We derived nine individual human-activity and landscape disturbance threats: aquatic invasive species, riparian disturbance, in-stream habitat destruction, flow alteration, latitudinal fragmentation, sedimentation, pollutant loading, and nutrient loading. The input data was processed and combined to produce an individual threat score that characterizes the mechanism of disturbance to freshwater species for each score. For climate change threats, we compiled model outputs of projected stream flow and temperature to estimate threats of flood-risk, low and high stream flow, and high summer stream temperature from 2040-2060 under Representative Concentration Pathway (RCP) 4.5 and 8.5 scenarios. The individual threat scores were standardized across the study area, weighted equally, and added together to calculate a human activity and landscape disturbance cumulative threat score and a climate change based cumulative threat score (see Iacarella et al. 2025 for detailed methods). Finally, both cumulative threat scores were paired with salmon and SAR distributions (i.e., CU boundaries and delineated stream habitats, respectively) and evaluated to identify where threats were greatest and which species and CUs were exposed to the highest threat levels.
-For the Thompson-Nicola EDU case study, we focused on human activity threats that may reasonably be mitigated, including riparian disturbance, water withdrawal, and longitudinal fragmentation from dams. We identified overlap between these threats and two approaches used to identify areas important to salmon: (1) CU delineations and (2) modelled environmentally favourable spawning habitats. The modelled environmentally favourability predictions were derived from large-scale environmental niche models to predict shifts in habitat favourability from current to future climate conditions (Iacarella and Weller 2023). We multiplicatively combined threat scores with environmental favourability for salmon spawning to create composite scores that reflect a gradient of potential management implications (see Fig. 20 in Iacarella et al. 2025). A high threat score combined with a high favourable habitat probability identifies an area that warrants localized investigation and potential restoration or mitigation actions. Conversely, a low threat score combined with a low favourable habitat probability identifies an area that is less likely to need management attention based on salmon values (i.e., predicted spawning habitat) and low level of anthropogenic impact.
-Our results indicated the highest cumulative threat scores around the lower Fraser River and within the interior plateau of the FRB for both human activity and landscape disturbance based threats and climate change based threats (Figure 1). Watershed groups with the highest median cumulative threats were the Nicola River, Guichon Creek, and San Jose River. These heightened scores were predominately driven by riparian disturbance, nutrients, and sedimentation for the human activity based threats and high stream temperatures for the climate change based threats. Roads were the most frequent input that influenced human activity based threats across the FRB, and contributed consistently to in-stream habitat destruction, riparian disturbance, nutrients, and sedimentation. Other important inputs to these threats were forest fires, forest pest defoliation, rangeland, and forestry. We found that SAR with limited ranges (i.e., Coastrange Sculpin, Green Sturgeon, Nooksack Dace, and Salish Sucker) had higher median human activity cumulative threat scores relative to all streams in the FRB, corresponding to their at risk status (Figure 2). Median human activity threat scores tended to be more similar among salmon CUs and relative to all streams, though a few of the Threatened and Endangered Sockeye salmon CUs had notably higher median threat scores (Figure 2).
-Within the Thompson-Nicola EDU, median cumulative threat composite scores within watershed groups based on the multiplicative value of human activity cumulative threats and favourable spawning habitat under current and future conditions were highest for Sockeye (Figure 3). The greatest shifts in median composite scores from current to future climate conditions (i.e., based on changes in predicted spawning favourability), were increases in Upper North Thompson River for Chinook (median score change = 0.14), Bonaparte River for Pink (0.06), and Deadman River for Sockeye (0.11), and a decrease in Thompson River for Coho (-0.06). Overall, the Deadman and Adams River watershed groups were identified as having the highest cumulative composite scores under current and future climate conditions across salmon species in the EDU.</t>
   </si>
   <si>
     <t>This project is the first to provide spatially extensive estimates of human activity and climate change threats that are directly linked to salmon, SAR, and their habitats at the stream reach scale. The approaches used to estimate each of the indicators provide an initial broad-scale standardized framework that can be applied to characterize threats throughout the Pacific Region. Within the FRB, we observed the highest threats in the Lower Fraser and interior plateau, and specifically, within the Nicola River, Guichon Creek, and San Jose River. Overall, roads were the greatest contributor to human activity-based threats, disturbing in-stream habitats, riparian areas, and contributing to sediment and nutrient loading. These results improve our understanding of the spatial distribution and relative magnitude of threats across the FRB, providing a foundation for predicting population-level impacts from cumulative effects and life-cycle modelling.
@@ -1189,11 +1101,6 @@
     <t>CU 3 (Chilko-ES); CU 4 (Chilko-S)</t>
   </si>
   <si>
-    <t>- The main goal of the project was to test the use of SONAR technology to enumerate Sockeye salmon smolt outmigration, while concurrently running a counting fence to evaluate its performance over a four year period.
-- Over the course of three years (2025 results are pending), the total number of Sockeye smolts estimated with SONAR when compared to estimates generated at the enumeration fence, ranged from 5-33% (5% in 2024, 8% in 2023, 33% in 2022).
-- This method has been shown to be effective at enumerating Sockeye smolts, which is an important and often lacking piece of information in salmon stock assessments (e.g. estimating early freshwater survival, generating stock-recruit relationships). However, using SONAR in this configuration is highly dependent on site selection, stream morphology, flow conditions, and the ability to adequately sample smolts for size measurements used in the analysis.</t>
-  </si>
-  <si>
     <t>This work describes how split-beam SONAR systems can be deployed and configured to enumerate outmigrating salmon smolts, which can provide crucial information on egg to smolt survival, stock recruitment, and freshwater habitat conditions and quality. This additional information can then be used to inform management strategies or mitigations for stocks below conservation benchmarks, or inform enhancement work conducted by the DFO Salmonid Enhancement program where no metrics exist other than adult escapements to evaluate performance (e.g. Bowron, Pitt, Taseko rivers).</t>
   </si>
   <si>
@@ -1330,41 +1237,6 @@
   </si>
   <si>
     <t>CK-03, CK-14, CK-17, CK-20, CK-31, CK-39, CK-43, CO-13, CO-17, CO-47</t>
-  </si>
-  <si>
-    <t>- Hatchery and natural habitats favour different traits in Pacific salmon, and consistent with this, performance differences between hatchery- and natural-origin salmon are often observed in nature with natural-origin fish tending to outperform their hatchery counterparts.
-- Despite this, when hatchery programs are integrated with the natural component of the population, detection of genetic differences between hatchery- and natural-origin fish is rare.
-- In contrast, epigenetic differences, such as the addition or removal of methyl groups from DNA (i.e., DNA methylation), between hatchery- and natural-origin salmonids have recently been characterized in several species and populations.
-- These epigenetic differences may underlie hatchery effects on performance in Pacific salmon, and have the potential to be inherited across generations, which would pose a long-term fitness risk to enhanced populations.
-- These projects represent the most comprehensive study of variation in DNA methylation across hatcheries in Pacific salmon to date, assessing (1) the consistency of differences in DNA methylation across hatcheries, (2) the extent to which these differences are inherited by the offspring of hatchery-origin fish, and (3) the potential for development of epigenetic biomarkers for the management of hatchery effects in enhanced populations.
-- Differences in DNA methylation between hatchery- and natural-origin Chinook or Coho Salmon were observed in every population examined, but essentially all patterns with population- or hatchery-specific.
-- In outmigrating smolts, hatchery rearing strategies impacted DNA methylation patterns with juveniles reared with slower growth rates and released at smaller sizes showing patterns less divergent from natural epigenetic signatures than those observed in traditional hatchery releases.
-- As expected, tissue-type had substantial effects on DNA methylation even between different fins, and although fin tissue captured some of the differences in methylation detected in other tissues, the majority of patterns were tissue-specific.
-- Consistent with potential long-term effects of hatchery-mediated epigenetic variation, there was evidence of inheritance of DNA methylation patterns from hatchery parents to their offspring in controlled crosses, but the mode of inheritance varied depending on the region of the genome assessed.
-- Taken together, these projects clearly confirm that epigenetic effects of hatchery rearing are likely mechanisms underlying hatchery effects on performance in Pacific salmon, although these patterns are generally population-specific such that development of widely applicable epigenetic biomarkers for hatchery-origin is unlikely to be possible.
-- Instead the findings of these projects suggest that understanding how hatchery practices modify epigenetic variation in Chinook and Coho Salmon may guide modifications to reduce hatchery impacts in the future, and that population-specific biomarkers are likely to have utility when desired.</t>
-  </si>
-  <si>
-    <t>Enhancement of Pacific salmon through hatchery production is a key component of supporting salmon populations. Objectives of hatchery enhancement span conserving at-risk stocks, rebuilding lower abundance stocks, providing harvest opportunities and increasing public awareness through outreach and education. However, there are also risks associated with hatchery enhancement; differences between a hatchery and a natural habitat affect both the genetic and environmental factors that shape the performance and fitness of salmon. Consequently, hatchery-origin salmon may be less suited to wild habitats than their natural-origin counterparts, and the presence of hatchery-origin fish on a natural spawning ground may reduce the fitness of a population overall. Despite the known risks and consequences of hatchery enhancement, major genetic differences between hatchery- and natural-origin salmonids as a result of hatchery-mediated selection or relaxed selection have generally not been observed in integrated populations. In contrast, substantial epigenetic differences have been detected between hatchery- and natural-origin Pacific salmonids.
-Epigenetic variants are structural changes to DNA without a change in the DNA sequence itself. For example, DNA methylation is a commonly studied epigenetic mechanism in which a methyl group (-CH3) is covalently added to a cytosine residue. These modifications to DNA can alter the function of the genome, particularly through the regulation of gene expression. Given the extent of previously observed variation in epigenetic signatures between hatchery- and natural-origin salmon, the functional effects of epigenetic variants are excellent candidates to underlie the fitness consequences associated with hatchery enhancement. Additionally, it is possible for hatchery epigenetic variants to be inherited by the offspring of hatchery-origin fish, which aligns with the potential for long-term reductions in population fitness as hatchery-origin fish spawn in natural habitats. The study of epigenetic variation in Pacific salmonids is relatively in its infancy, but epigenetic biomarkers are a promising tool to facilitate managing hatchery enhancement specifically and salmon fisheries generally. Critical knowledge gaps in the generation of these tools are that epigenetic differences between hatchery- and natural-origin Chinook Salmon have not been well-characterized and the extent to which these patterns are inherited in Pacific salmon is unknown. These projects address both of these gaps using data for Chinook and Coho Salmon populations enhanced by the DFO Salmonid Enhancement Program (SEP).</t>
-  </si>
-  <si>
-    <t>Samples for these projects were obtained from fin tissues submitted to the Molecular Genetics Section as part of the parentage-based tagging (PBT) program in the SEP, or from additional sampling efforts for the Chehalis, Chilliwack and Sarita Rivers. DNA was isolated from all samples using standard laboratory protocols, and for a relatively small number of Chilliwack River Chinook tissues RNA was also isolated with standard protocols. All isolations were quantified and quality controlled prior to use in data generation. For whole-genome data, DNA or RNA was sent to Genome Quebec for enzymatic methylation sequencing or RNA sequencing, respectively. For screening of methylation patterns in candidate genome regions, high-resolution melt analyses were conducted following quantitative polymerase chain reactions (qPCR).
-Sequencing reads were trimmed, aligned to the corresponding species genome sequence, and filtered for alignment quality and duplicated sequences. Final alignments were used to call variation in DNA methylation at CpG sequences using MethylDackel v0.6.1. Differences in methylation were then assessed by multidimensional scaling analyses and differential methylation tests with DSS v2.50.1 using custom analysis scripts established for the projects.
-The final analyses and manuscripts for these projects are in progress. The sequencing reads, methylation results and all other datasets will be submitted to public repositories on publication of the corresponding manuscripts. Similarly, all bioinformatic pipelines and scripts files will be publicly available through GitHub.
-Methylation patterns demonstrated substantial variation among different populations, and were also highly dependent on the tissue from which DNA was isolated even between adipose and caudal fins (see Figure 1 for example for Chinook Salmon). In all populations and tissues, approximately 50-500 regions of the genome displayed differences in methylation between hatchery- and natural-origin fish (see Figure 2 for example for Atnarko River Chinook Salmon), but these differences were essentially all population-specific. Within the Chilliwack River Fall Chinook population, differences in methylation between origins showed some consistency across two brood years, and although many differences in methylation were tissue-specific, a subset of patterns observed in fin tissues were detected in other tissues as well. Inheritance of parental methylation patterns was examined in Chehalis River Coho Salmon by assessing candidate regions with known differences between hatchery- and natural-origin parents. Inheritance of parental patterns was observed with some regions showing offspring methylation consistent with additive inheritance (intermediate between the parents) and other regions showing methylation patterns consistent with paternal dominance (methylation inherited from the father) (Figure 3).</t>
-  </si>
-  <si>
-    <t>These two projects provide several novel insights into epigenetic variation in Pacific salmon. The Chinook Salmon datasets summarized above represent the most comprehensive efforts to date to characterize differences in DNA methylation between hatchery- and natural-origin fish in this species and have clearly established that common effects of hatchery rearing across facilities are rare. The Coho Salmon study is the first, to our knowledge, to assess inheritance of epigenetic variation in Pacific salmon, confirming the potential for persistence of hatchery-mediated epigenetic effects across generations in enhanced populations. These results highlight the key need to develop understanding of the relationships between hatchery practices and different methylation patterns, the functional consequences of differences in methylation, and the potential adjustments in hatcheries that could mitigate these effects.
-There are four main sources of uncertainty for the findings of these projects. First, although the results above are suggestive that epigenetic differences are an important consequence of hatchery rearing and differences in performance between hatchery- and natural-origin salmon, the functional effects of the methylation differences summarized above remain to be established. Second, the extent to which methylation patterns in fin tissue capture those that may underlie differences in performance also remain to be established. Third, the inheritance of DNA methylation patterns demonstrated above requires testing and validation under hatchery and natural conditions; this validation is a key aspect of linking hatchery-mediated epigenetic changes to potential long-term fitness impacts. Fourth, the utility of epigenetic biomarkers for tracking hatchery origin or age in Chinook and Coho Salmon remains to be tested, as the high degree of population-specific patterns detected in these projects delayed biomarker development.</t>
-  </si>
-  <si>
-    <t>Future studies should address the uncertainties described above by performing physiological tests of the impacts of DNA methylation on performance in Chinook and Coho Salmon, and by using parentage-based tagging to assess parent-offspring methylation patterns outside of laboratory settings. Additionally, a proof of concept study for epigenetic biomarkers of hatchery origin and age in a key population would further improve the utility of the results summarized here. Operationalization of these findings will require not only proof of concept efforts, but also manipulative experiments to assess alternative rearing strategies and their impacts on DNA methylation, which will then inform scientific best practices that mitigate the fitness risks associated with enhancement in Pacific salmon.</t>
-  </si>
-  <si>
-    <t>Figure 1. Multidimensional scaling plot of variation in genome-wide DNA methylation among integrated populations of Chinook Salmon. Points represent individual fish, and colours indicate populations. Ellipses show the 95% confidence limits for the distributions. DNA was isolated from adipose or caudal fins (adipose - Atnarko, Cheakamus, Salmon, Yakoun; caudal - Chilliwack Fall, Chilliwack Summer, Nicola, Sarita).
-Figure 2. Heatmap of differentially methylated regions between hatchery- (yellow) and natural-origin (blue) fish. Columns correspond to individuals and rows correspond to genomic regions. Methylation levels are shown by the white to steel blue colour scale. Females (grey) and males (black) are indicated by the top bar.
-Figure 3. Box plots for high-resolution melt analyses of offspring methylation patterns compared to parental methylation for two genomic regions. Offspring cross-types are shown as female x male parent with hatchery-origin x hatchery-origin (yellow), hatchery-origin x natural-origin (pale blue), natural-origin x hatchery-origin (pale yellow), and natural-origin x natural-origin (blue). Panel a displays a region showing a pattern similar to additive inheritance, whereas panel b displays a region demonstrating paternal dominance.</t>
   </si>
   <si>
     <t>2436 PSSI Science Project Reporting chum gsi sogfra_final.docx</t>
@@ -2164,28 +2036,12 @@
 The findings reveal key knowledge gaps in understanding BKD dynamics, suggesting the need for further research to build a fuller picture of the factors influencing disease transmission and prevalence.</t>
   </si>
   <si>
-    <t>The study explored the relationship between parental BKD levels on individual salmon results while controlling for the impact of environmental factors such as thermal regimes by incorporating various temperature metrics, such as average temperature, minimum and maximum temperatures, degree days, and the number of days within specific temperature thresholds (6Â°C to 10Â°C). While Nitinat's temperature data was based on monthly or daily mean temperatures (depending on the year), Puntledge and Spius provided daily mean, maximum, and minimum temperatures. For each stock year, temperature data were filtered to include dates that a stock occupied the hatchery, e.g.Â the day of first broodstock captured to the day of last juvenile release. Juveniles of Chinook stocks were released less than a year of holding at the hatchery at Puntledge and after two years at Spius, while Coho stocks were released after 1 year and 2 year but temperature measurements were calculated based on the 2 year release for Coho stocks.
-Data used in the analysis was from 2014 through 2023, and was dependent on data available in E-PRO and temperature data (Table 1). Only individuals with BKD value and maturity class information were included. Incomplete data points were filtrated out in each analysis. Dam's BKD optical density (OD) value and BKD level were attached to E-PRO records for progenies by matching progenies' dam DNA code to the dam's data in the report. This step was only possible for progenies with dam's DNA code and BKD OD value.
-To guide the modelling of the vertical transmission path, we collaborated with an expert panel to develop a causal diagram (Figure 1). This exercise facilitated the identification and characterization of relationships across multiple scales, including the watershed, hatchery, and individual fish levels, while specifically assessing variables for their potential to confound the results. We evaluated these factors using a mixed-effects generalized linear model framework, designating the OD from the BKD ELISA as the outcome of interest and the OD of the progenitor (the dam) as the primary predictor. Temporal variation was integrated as a random effect to account for annual fluctuations. The final model incorporated several confounding factors, most notably the specific watershed of origin. We also included terms for interactions between mean temperature--which was scaled and centered by creek--and BKD prevalence at the stock level. For the purposes of this analysis, a stock was defined as a cohort of brood fish of the same species returning to the same creek during the same season, such as Nitinat Spring Coho. While species and season were initially tested, they were excluded from the final model as they were not statistically significant and did not meet the criteria for confounders; their observed effects were largely captured by spatial and temporal variables.
-Research Findings
-The primary analysis indicates that BKD levels in returning adults do not demonstrate a significant association with the OD levels of their progenitors. Instead, the relationship appears to be confounded by environmental and population-level factors, including water temperature, specific watershed characteristics, and the overall BKD prevalence within the returning population. For instance, while the watershed variable was not statistically significant in isolation, its inclusion in the model resulted in a measurable change in the coefficient of the primary predictor, suggesting a latent environmental influence. A more notable finding was the negative association between BKD levels and scaled temperature, which suggests that OD levels generally decrease as temperatures increase. However, a significant interaction between temperature and BKD prevalence indicates a modulating effect on this relationship (Figure 2). While lower temperatures appear to provide a more suitable environment for the transmission of BKD, a higher proportion of infected individuals within a population further intensifies this effect.
-It is important to note, however, that the statistical model demonstrated a relatively low goodness-of-fit, indicating that a substantial portion of the variance in BKD levels remains unexplained by the variables currently under study. This suggests that the dynamics of BKD in these ecosystems are influenced by a complex array of factors--potentially including individual host immunity, varying hatchery practices, or additional environmental stressors--that were not fully captured in the present framework. Consequently, while the identified trends regarding temperature and prevalence offer valuable directional insights, they should be interpreted with caution and viewed as preliminary findings within a highly variable biological system.</t>
-  </si>
-  <si>
-    <t>Table 1. Stocks and cohorts used in this analysis as well as the years of available data for BKD screening, progenitor DNA, and temperature.
-Figure 1. Directed Acyclic Graph (DAG) of the causal web explaining OD results for BKD. Arrows represent plausible unidirectional associations between factors considered for the epidemiological model as identified and characterized by the experts panel.
-Figure 2. Interaction between the effects of Scaled Temperature and BKD Prevalence. Predicted values are derived from ourÂ linear mixed-effects modelÂ accounting for year to year variation. The scaled temperature is plotted on the x-axis against the OD for BKD (y-axis), with separate lines representing 20% (red) and 80% (blue) BKD prevalence in the returning population.Â Shaded regionsÂ of corresponding colours representÂ 95% confidence intervals.</t>
-  </si>
-  <si>
     <t>This project complimented tagging, telemetry tracking, and statistical models to estimate spawning migration mortality, alongside assessment of stock abundance and Conservation Unit (CU) status. Details of the latter are described in Connors et al. 2025 and here we briefly describe the tagging components of the work.
 Adult Yukon River Chinook salmon were tagged in the lower Alaskan portion of the Yukon River in 2023 and 2024. Migration rates and fate of tagged fish were monitored using a network of remote tracking stations (RTS) deployed throughout Alaska and the Yukon Territory, supplemented by aerial telemetry surveys. Tissue samples were collected from each tagged fish and analyzed by the DFO Molecular Genetics Lab to assign individuals to Canadian Yukon River CUs. These genetic assignments identified the CU each fish was expected to reach. Tagged fish were also aged by the Alaska Department of Fish and Game ageing lab via scale samples. Sex of individual fish was determined by combined visual and genetic methods.
 Remote tracking of Chinook salmon in the Canadian portion of the Yukon River was conducted using ATS R4500 receivers deployed at RTS sites. Beginning in 2023, DFO deployed four RTS: three along the mainstem Yukon River and one on the Porcupine River near Old Crow. During 2024, monitoring expanded substantially through a coordinated effort between DFO and the Yukon First Nations Salmon Stewardship Alliance (YFNSSA), undertaken with guidance from Yukon First Nations. This collaboration resulted in the deployment of 20 RTS towers across the basin (Figure 3). The RTS were strategically positioned throughout the Canadian drainage to monitor fish passage at key assessment locations. Stations at Dawson City and Rampart House detected Chinook salmon entering the Yukon Chinook Stock Management unit (SMU) and the Porcupine Chinook SMUs, respectively. Each RTS consisted of a 20 ft tall aluminum mast with antennas mounted at the top to maximize detection range and was installed on elevated riverbanks. Solar powered systems enabled continuous, autonomous operation throughout the migration period. The RTS network provided high-resolution data on movement patterns, timing, and fate of tagged Chinook salmon.
 Aerial telemetry surveys were conducted using a Maule M-7 fixed wing plane flying at 300-600 m altitude and approximately 160 km hr â»Â¹. An ATS R4520 receiver was operated onboard with dualH antennas mounted to the wings. Flights followed the Yukon River mainstem and its major tributaries to detect tagged fish. Aerial surveys expanded spatial coverage and provided finer-scale movement information, including identification of migration dropouts and verification of spawning locations, thereby enhancing the spatial resolution and completeness of the telemetry dataset.
 A hierarchical Bayesian mark-recapture model is in development to estimate survival by river segment and CU. This framework explicitly accounts for imperfect detections, small sample sizes, and uncertainty in genetic assignments. It will be used to derive annual and multi-year estimates of migration mortality by CU in relation to environmental conditions experienced during spawning migrations.
 Preliminary analysis of the tagging data suggest Yukon Chinook migrate at an average of 51 km d-1 (range 38-63 km d-1 ), and the furthest distance travelled was over 3200 kms. In 2024, an estimated 85% of tagged Chinook likely reached their assigned CU spawning grounds. This compares to an estimate of 84% survival of migrating Chinook in the Alaskan portion of the river (as estimated by sonar projects at the river mouth and Yukon/Alaska border) in 2024 which is remarkably similar. If this relationship persists in subsequent years, in-season estimates of migration mortality derived in Alaska may help inform expected migration mortality in Canada and support development of precautionary buffers for bilateral border passage goals under the Yukon River Agreement.</t>
-  </si>
-  <si>
-    <t>Fisheries and Oceans Canada (DFO). 2025. Rebuilding plan: West Coast of Vancouver Island Chinook Salmon, Oncorhynchus tshawytscha, Suuhaa | SÈ¾Oá¸°I | sat'sam. Rebuilding Plan. 50 p. https://publications.gc.ca/collections/collection_2025/mpo-dfo/Fs144-87-2025-eng.pdf</t>
   </si>
   <si>
     <t>Ahousaht First Nation, Hesquiaht First Nation, Tla-o-qui-aht First Nation, Nuu-cha-nulth Tribal Council, Nature Trust of BC, Maaqutusiis Hahoulthee Stewardship Society</t>
@@ -2446,34 +2302,6 @@
 Richmond, Z., &amp; Plant, K. 2021. Quantitative PCR (RT-qPCR) for Detection of *R.sal* using AgPath-ID One-Step RT-qPCR kit in Multiorgan tissue of Finfish Species. BC Centre For Aquatic Health Sciences, SOP 83-v5.1.</t>
   </si>
   <si>
-    <t>Figure 1. Map of study area showing approximate Fraser River sockeye salmon migration corridor, sockeye salmon and Steller sea lion tagging sites, and diet sampling locations.
-Figure 2. Proportion of tagged sockeye salmon detected along migration corridor by release cohort (HG is Haida Gwaii, QCS is Queen Charlotte Strait). Detections provide an approximate estimate of survival but do not account for imperfect detection probability. Final results require parameterization of mark-recapture model.
-Figure 3. Fates of popup satellite tags stratified by release location. Survival to release represents tags that uploaded data at their release date. All other tags transmitted early indicating they were no longer attached to the tagged animal. Ingested tags could be assigned to a predator guild based on temperature and pressure data while unknown mortalities represent deployments where the tag was removed from the prey, but not ingested by a predator.
-Figure 4. Tracks of individual a) female and b) male Steller sea lions satellite tagged on Triangle Island in 2024 or 2025.
-Figure 5. Posterior mean isotopic (Î´13C and Î´15N) space for Steller sea lions by age class and sex. Points represent draws from the posterior distribution of population-level mean isotope values from Bayesian hierarchical models. Ellipses denote 95% Bayesian credible regions of uncertainty in mean isotopic values for each group.</t>
-  </si>
-  <si>
-    <t>Budge, S.M., Iverson, S.J. and Koopman, H.N., 2006. Studying trophic ecology in marine ecosystems using fatty acids: a primer on analysis and interpretation. Marine Mammal Science, 22(4).
-Chasco, B., Kaplan, I., Thomas, A., Acevedo-GutiÃ©rrez, A., Noren, D., Ford, M., Hanson, M., Scordino, J., Jeffries, S., Marshall, K., Shelton, A., Matkin, C., Burke, B. &amp; Ward, E. 2017a. Competing tradeoffs between increasing marine mammal predation and fisheries harvest of Chinook salmon. Scientific Reports, 7.
-Chasco, B., Kaplan, I., Thomas, A., Acevedo-GutiÃ©rrez, A., Noren, D., Ford, M., Hanson, M., Scordino, J., Jeffries, S., Pearson, S., Marshall, K. &amp; Ward, E. 2017b. Estimates of Chinook salmon consumption in Washington State inland waters by four marine mammal predators from 1970 to 2015. Canadian Journal of Fisheries and Aquatic Sciences 74: 1173-1194.
-Cohen, B. 2012. The Uncertain Future of Fraser River Sockeye Salmon Volume 2: Causes of the Decline. 212 p.
-Crossin, G.T., Hinch, S.G., Cooke, S.J., Welch, D.W., Batten, S.D., Patterson, D.A., Van Der Kraak, G., Shrimpton, J.M., and Farrell, A.P. 2007. Behaviour and physiology of sockeye salmon homing through coastal waters to a natal river. Mar. Biol. 152: 905-918.
-Crossin, G.T., Hinch, S.G., Cooke, S.J., Cooperman, M.S., Patterson, D.A., Welch, D.W., Hanson, K.C., Olsson, I., English, K.K., and Farrell, A.P. 2009. Mechanisms influencing the timing and success of reproductive migration in a capital breeding semelparous fish species, the sockeye salmon. Phys. Biochem. Zool. 82: 635-652.
-Freshwater, C., Burke, B.J., Scheuerell, M.D., Grant, S.C.H., Trudel, M., and Juanes, F. 2018. Coherent population dynamic associated with sockeye salmon juvenile life history strategies. Can. J. Fish. Aquat. Sci. 75: 1346-1356.
-Layman, C.A., Araujo, M.S., Boucek, R., Hammerschlagâ€Peyer, C.M., Harrison, E., Jud, Z.R., Matich, P.,
-Rosenblatt, A.E., Vaudo, J.J., Yeager, L.A. and Post, D.M., 2012. Applying stable isotopes to examine foodweb structure: an overview of analytical tools. Biological reviews, 87(3), pp.545-562.
-McKinnell, S., Curchitser, E., Groot, K., Kaeriyama, M., and Trudel, M. 2014. Oceanic and atmospheric extremes motivate a new hypothesis for variable marine survival of Fraser River sockeye salmon. Fish. Ocean. 23: 322-341.
-Nelson, B., Pearson, S., Anderson, J., Jeffries, S., Thomas, A., Walker, W., Acevedo-GutiÃ©rrez, A., Kemp, I., Lance, M., Louden, A. &amp; Voelker, M. 2021. Variation in predator diet and prey size affects perceived impacts to salmon species of high conservation concern. Canadian Journal of Fisheries and Aquatic Sciences 78: 1661-1676.
-Nelson, B.W., McAllister, M.K., Trites, A.W., Thomas, A.C. and Walters, C.J. 2024. Quantifying impacts of harbor seal *Phoca vitulina* predation on juvenile Coho Salmon in the Strait of Georgia, British Columbia. Marine and Coastal Fisheries 16(1), p.e210271.
-Peterman, R.M. and Dorner, B.D. 2012. A widespread decrease in productivity of sockeye salmon (*Oncorhynchus nerka*) populations in western North America. Can. J. Fish. Aquat. Sci. 69: 1255-1260.
-Proudfoot, B., Thompson, P.L, Vaidyanathan, T., Robb, C.K. 2024. Spatial estimate of blue shark, salmon shark, Pacific sleeper shark, and bluntnose sixgill shark presence in British Columbia. Can. Tech. Rep. Fish. Aquat. Sci. 3600: 27 p.
-Rechisky, E.L., Porter, A.D., Clark, T.D., Furey, N.B., Gale, M.K., Hinch, S.G., and Welch, D.W. 2019. Quantifying survival of age-2 Chilko Lake sockeye salmon during the first 50 days of migration. Can. J. Fish. Aquat. Sci. 76: 136-152.
-Seitz, A.C., Courtney, M.B., Evans, M.D., and Manishin, K. 2019. Pop-up satellite archival tags reveal evidence of intense predation on large immature Chinook salmon (*Oncorhynchus tshawytscha*) in the North Pacific Ocean. Can. J. Fish. Aquat. Sci. 76: 1608-1615.
-Walters, C.J., McAllister, M.K., and Christensen, V. 2020. Has Steller sea lion predation impacted survival of Fraser River sockeye salmon? Fish. 45: 597-604.
-Wells, B.W., Huff, D.D., Quinn, T.P., Santora, J.A., Gomes D.G.E. et al. 2025. When, where, and why salmon become vulnerable to predation. ICES J. Mar. Sci. 82: fsaf162.
-Williams, R., Okey, T.A., Wallace, S.S., Gallucci, V.F. 2010. Shark aggregation in coastal waters of British Columbia. Mar. Ecol. Prog. Ser. 414: 249-265.</t>
-  </si>
-  <si>
     <t>Province of British Columbia, Pacific Salmon Commission</t>
   </si>
   <si>
@@ -2598,61 +2426,6 @@
     <t>Salmon Enhancement Program Hatcheries, University of British Columbia (Dr Brian Hunt), DFO environmental Watch (EWATCH)</t>
   </si>
   <si>
-    <t>Thiamine (Vitamin B1) is an essential water soluble vitamin for fish, supporting physiological functions such as metabolism, immune, neuron and cardiac functions (BÃ¢ 2008; Manzetti et al. 2014; Roman-Campos and Cruz 2014; Whitfield et al. 2018), normal development (Carvalho et al. 2009), growth (Reed et al. 2023; Lee et al. 2026) and reproductive success (Fitzsimons et al. 2005; Honeyfield et al. 2005; Mantua et al. 2025). In aquatic systems, thiamine is synthesized by bacteria and phytoplankton at the base of the food web (Croft et al. 2007; Tang et al. 2010; Paerl et al. 2015; Hylander et al. 2024; Suffridge et al. 2024), and fish obtain thiamine exclusively through their diet (Fridolfsson et al. 2018; Harder et al. 2018; Ejsmond et al. 2019; Hylander et al. 2024). Thiamine deficiency complex (TDC) is a syndrome that is caused by a chronic deficiency in thiamine, impacting salmon across the life cycle. In adult salmon, reduced swimming and migratory ability, and increased pre-spawn mortality have been linked to TDC (Brown et al. 2005a; Fitzsimons et al. 2005). For early-stage salmon fry hatched from thiamine-deficient eggs, symptoms include loss of equilibrium (Fitzsimons et al. 2005), abnormal swimming behaviour (i.e. swimming in a corkscrew pattern) (Mantua et al. 2025), impaired vision and foraging ability (Carvalho et al. 2009), and high mortality (Koski et al. 1999; Mantua et al. 2025). TDC is caused by low availability of thiamine in the diet and/or ingestion of prey high in thiaminase (enzyme that degrades thiamine, Fisher et al. 1998; Brown et al. 2005a; Honeyfield et al. 2005; Houde et al. 2015; Mantua et al. 2025). Both extrinsic (e.g. changing environmental conditions, variation in the migration experience) and intrinsic factors (e.g. species, size, sex, disease state) could further modulate fish thiamine levels.
-TDC has been linked to salmonid population declines globally, including Atlantic salmon *Salmo salar* in the Baltic Sea (Amcoff et al. 1999), lake trout *Salvelinus namaycush* in the Great Lakes (Ladago et al. 2020), and Chinook salmon in Alaska (Strasburger et al. 2023) and California (Mantua et al. 2025). However, there is little published information about the status of TDC in Pacific salmon, especially in British Columbia (BC), Canada (but see Welch et al. 2018). More research is thus urgently needed to investigate how thiamine status has been impacting Pacific salmon in BC, Canada. The objectives of this project were to: (1) establish thiamine analysis capacity at DFO to support studies and programs investigating the thiamine status of salmonids in Canada. Until this project, there were no Canadian labs providing thiamine analysis services, thus Canadian projects must rely on a few labs in the USA, creating a bottleneck (costly, delayed, sample loss risk) in thiamine analysis. (2) determine preliminary thiamine status in eggs collected from both wild and hatchery-derived stocks of Chinook salmon, coho salmon, pink salmon and sockeye salmon in BC. And (3) assess the effectiveness of thiamine treatment practices being tested at some DFO hatcheries. This research was conducted in collaboration with the Pelagic Ecosystem Lab at University of British Columbia (UBC), DFO Salmon Enhancement Program (SEP) and DFO Environmental Watch Program (EWATCH).</t>
-  </si>
-  <si>
-    <t>Thiamine analysis capacity was established by researchers in the Nutrition lab at the DFO Pacific Science Enterprise Centre (PSEC), based on the methodology of Brown et al. (1998) with expert advice from Dr. Jacques Rinchard from SUNY Brockport and Dr. Cody Pinger from National Oceanic and Atmospheric Administration (NOAA). To confirm the reliability of our analysis protocol, we analyzed 27 Chinook salmon egg samples collected in 2023 by Pelagic Ecosystem Lab at UBC and compared our results with those provided to UBC by the lab at SUNY Brockport. There was a strong and significant linear relationship (Fig 1; y = 0.8183 x - 0.4131) between SUNY Brockport and PSEC's results on total mean thiamine levels (p &lt; 0.001) providing confidence that the methodology employed by PSEC is reliable and accurate. Overall, PSEC reported consistently lower total mean thiamine levels, especially lower TPP levels, compared to SUNY Brockport. This is not surprising given that PSEC conducted the analysis in 2025, almost 2 years later than SUNY Brockport. Given the sensitivity of thiamine (temperature, light, pH; Brown et al. 1998; Wright et al. 2005; Edwards et al. 2017; Rocchi et al. 2022), thiamine degradation in tissues is expected to occur over time with prolonged storage and multiple sample handing events.
-Additional salmon samples from both hatcheries and the wild were collected to obtain baseline, preliminary data on the thiamine status of salmon in BC. Sample collection included: Chilliwack River hatchery coho salmon (N=10 females; eggs, plasma), Chilliwack River hatchery Chinook salmon (N=10 females; eggs, plasma), Capilano hatchery mid coho salmon (N=10 females; eggs), Harrison River sockeye salmon (N=10 females; eggs, ventricles, plasma), Chilko River sockeye salmon (N=10 females; eggs, ventricles, plasma), Weaver Creek sockeye salmon (N = 9, eggs, ventricles, plasma), Chehalis pink salmon (N = 11 females; eggs ). Tissues were immediately frozen (dry shipper or dry ice) and stored at -80oC until analysis. Ventricle and plasma analysis is ongoing, only egg data are presented here. Total thiamine levels were very similar in the Chinook and coho eggs assessed here (Figure 2), mostly ranging between 6 - 13 nmol/g. However, sockeye salmon eggs had much lower total thiamine levels of mostly 2 - 6 nmol/g, while total thiamine in pink salmon eggs mostly ranged from 4 - 8 nmol/g. Using the thiamine thresholds as established by Mantua et al. (2025), 20 - 40% of each coho and Chinook salmon population are considered as being likely impacted by thiamine deficiency to some degree (&lt; 7.7 nmol/g; Figure 3). However, all sockeye salmon samples are below 7.7 nmol/g, with over 50 - 100% of eggs considered having low (2.7 -5.9 nmol/g) or critically low thiamine (&lt; 2.7 nmol/g) levels. For the Chehalis pink salmon population, 72% of samples are considered to be likely thiamine deficient (&lt; 7.7 nmol/g), with 45% of eggs in the low category (2.7 - 5.9 nmol/g; Figure 3).
-To counteract the effects of TDC, thiamine supplementation is seen as an effective strategy to improve salmon reproduction success in hatcheries (Harder et al. 2025) and is currently implemented at a few DFO hatcheries. Current practices include injecting thiamine (500 mg thiamine hydrochloride) into broodfish ~12-25 days prior to spawning (Shuswap River hatchery) or immersing fertilized eggs in a static bath made of 1000 ppm thiamine mononitrate for 1 hour (Tenderfoot Creek hatchery, Capilano hatchery). We sampled thiamine-injection-treated eggs from Middle Shuswap Chinook salmon at Shuswap River hatchery (N=6, no control fish were available).We sampled both untreated (control) and thiamine-bath-treated eggs (immediately after the 1 h bath) from Cheakamus Chinook salmon at Tenderfoot Creek hatchery (N=4 females), early coho (N=20 females) , mid coho salmon (N=20 females) and late coho salmon (N=20 females) from Capilano hatchery. In addition, thiamine-bath treated eggs were sampled ~1 month post-fertilization in coho salmon from Capilano hatchery (N= 400 eggs each for early, mid and late Coho; eggs from different females were mixed; no control fish were available).
-Thiamine injection-treatment (Middle Shuswap Chinook salmon at Shuswap River hatchery) produced eggs with total thiamine levels ranging between 16-27 nmol/g (Table 1). While there are no control fish for comparison, these levels are above egg thiamine levels in untreated eggs from other locations (Tenderfoot and Chilliwack hatchery Chinook salmon, Figure 2). This suggests that the thiamine injection treatment likely was effective at increasing total thiamine levels in the eggs. Unfortunately, the effectiveness of the thiamine bath treatment (Tenderfoot Creek hatchery and Capilano hatchery) could not be resolved here. Sampling eggs immediately following the 1 h thiamine bath treatment resulted in extremely elevated and highly variable total thiamine levels (range = 256.8 - 327.0 nmol/g). In fact, we were unable to determine accurate total thiamine levels for the bath-treated samples from Capilano, as the results were contradictory (i.e. varying from 0.95 - 291.20 nmol/g). While we reported consistently high total thiamine from bath-treated eggs from Tenderfoot Creek Hatchery, these levels are not biologically reasonable and were likely produced by excess thiamine associated with the bath. Given this, we sampled some eggs ~1 month post bath treatment from Capilano Hatchery and found levels to vary among batches (early coho batch#1: 0.90 Â± 0.06, batch #2: 2.49 Â± 0.60; mid coho batch#1: 3.86 Â± 1.18; N=5 tests, unit = nmol/g). However, without control, un-treated eggs at the same life stage, we are unable to assess whether the thiamine bath treatment was successful at increasing thiamine levels in these eggs.</t>
-  </si>
-  <si>
-    <t>This project successfully established thiamine analysis capability at PSEC, which is currently the only known laboratory in Canada conducting these analyses. A detailed protocol outlining the equipment, consumables and procedural steps is available for distribution to other research groups at DFO to set up the same analysis capacity. Our lab at PSEC is currently welcoming thiamine analysis requests and collaborative projects to support research programs monitoring the thiamine status of Pacific salmon and their prey in Canada.
-The thiamine levels in coho and Chinook salmon eggs were within the expected range, consistent with previous work on Chinook salmon in Alaska (Honeyfield et al. 2016; Larson and Howard 2019) and California (Mantua et al. 2025), and preliminary data available for BC (Lerner and McLaskey 2024). Notably, the relatively wide range of thiamine levels suggests considerable variation among individuals within each population. Future studies should consider increasing the sample size from each population (i.e. &gt;10 fish per population) to have a more precise estimate of salmon thiamine status. In contrast, the total thiamine amounts in sockeye salmon eggs from Weaver Creek, Harrison and Chilko River were less variable, but also had lower levels (mostly within 2 - 6 nmol/g). While the Harrison River samples were considered not fully ripe, the thiamine levels in these eggs were similar to those of fully ripe fish in Chilko River. Notably, a previous study found much higher total thiamine levels in eggs of sockeye salmon from Harrison River, and pink salmon from Seton River in 2015 (Sockeye: 10.9 Â± 1.2 nmol/g, n = 5; pink: 19.5 Â± 2.3 nmol/g, n=20; Welch et al., 2018). The cause of these differences in thiamine levels between studies of the same population conducted ~10 years apart is unknown, but may be related to changes in prey (and thus dietary thiamine/thiaminase levels), changing ocean or migration conditions or other factors not identified.
-Based on the thiamine thresholds by Mantua et al. (2025), 20 - 40 % of the eggs analyzed from each coho and Chinook salmon population in this study, are considered to be likely impacted by thiamine deficiency (Figure 3). However, the total thiamine in all eggs from sockeye salmon from both Harrison and Chilko River are well below this threshold, and only 27% of Chehalis pink salmon eggs were above it. It must also be noted that the threshold from Mantua et al. (2025) is set based on Chinook salmon, but the susceptibility to TDC, or thiamine threshold, is likely species-specific (Brown et al. 2005b; Fitzsimons et al. 2007; Honeyfield et al. 2008; Harder et al. 2018). To our knowledge, there are no published data on thiamine status of sockeye and pink salmon other than Welch et al. (2018). Future research should track thiamine status of Pacific salmon in BC, especially sockeye salmon.
-The broodfish-thiamine-injection method appeared to effectively improve the total thiamine levels, mostly in form of TH, in Chinook salmon eggs. Although there were no untreated, control eggs available as a comparison at Shuswap River Hatchery, the injection-treated eggs (20.5 Â± 4.8 nmol/g, range from 16 - 27 nmol/g) contained up to 2 - 3 times the usual thiamine amount in untreated eggs of other Chinook salmon stocks (Figure 2 and 3, 6 - 13 nmol/g). The total thiamine levels in eggs from these injection-treated fish are within the range reported for similar studies on coho salmon (21.925 Â±1.694 nmol/g, Fitzsimons et al., 2005) and steelhead trout *Oncorhynchus mykiss* (total thiamine 20.4 Â± 11.3 nmol/g; Futia et al 2017; mean total thiamine: 33.5 nmol/g, range: 15.4 - 51.1 nmol/g; Reed et al 2023). Unfortunately, our study could not resolve the effectiveness of thiamine bath-treated eggs because of supra-biological and varying levels measured in eggs sampled immediately after the 1 h treatment bath (e.g. 302.5 Â± 31.2 nmol/g in Chinook salmon at Tenderfoot Creek hatchery; 0.95 - 291.20 nmol/g in mid Coho salmon eggs at Capilano Hatchery). Thus, it was unknown how much of the thiamine was actually retained and biologically available to the eggs over time. Future work should resolve the effectiveness and necessity of these thiamine treatments, as these methods could prove highly valuable in both minimizing the potential negative impacts of TDC on early fry and optimizing hatchery salmon production (Futia et al. 2017; Reed et al. 2023; Harder et al. 2025).</t>
-  </si>
-  <si>
-    <t>Amcoff, P., BÃ¶rjeson, H., Landergren, P., Vallin, L., and Norrgren, L. 1999. Thiamine (vitamin B1) concentrations in salmon (*Salmo salar*), brown trout (Salmo trutta) and cod (Gadus morhua) from the Baltic Sea. Ambio 28(1): 48-54.
-BÃ¢, A. 2008. Metabolic and structural role of thiamine in nervous tissues. Cell. Mol. Neurobiol. 28(7): 923-931. doi:10.1007/s10571-008-9297-7.
-Brown, S.B., Fitzsimons, J.D., Honeyfield, D.C., and Tillitt, D.E. 2005a. Implications of thiamine deficiency in Great Lakes salmonines. J. Aquat. Anim. Health 17(1): 113-124. doi:10.1577/H04-015.1.
-Brown, S.B., Honeyfield, D.C., Hnath, J.G., Wolgamood, M., Marcquenski, S. V., Fitzsimons, J.D., and Tillitt, D.E. 2005b. Thiamine status in adult salmonines in the Great Lakes. J. Aquat. Anim. Health 17(1): 59-64. doi:10.1577/H04-059.1.
-Brown, S.B., Honeyfield, D.C., and Vandenbyllaardt, L. 1998. Thiamine analysis in fish tissues. Am. Fish. Soc. Sumpos. 21(January 1998): 73-81.
-Carvalho, P.S.M., Tillitt, D.E., Zajicek, J.L., Claunch, R.A., Honeyfield, D.C., Fitzsimons, J.D., and Brown, S.B. 2009. Thiamine deficiency effects on the vision and foraging ability of lake trout fry. J. Aquat. Anim. Health 21(4): 315-325. doi:10.1577/H08-025.1.
-Croft, M.T., Moulin, M., Webb, M.E., and Smith, A.G. 2007. Thiamine biosynthesis in algae is regulated by riboswitches. Proc. Natl. Acad. Sci. U. S. A. 104(52): 20770-20775. doi:10.1073/pnas.0705786105.
-Edwards, K.A., Tu-Maung, N., Cheng, K., Wang, B., Baeumner, A.J., and Kraft, C.E. 2017. Thiamine Assays--Advances, Challenges, and Caveats. ChemistryOpen 6(2): 178-191. doi:10.1002/open.201600160.
-Ejsmond, M.J., Blackburn, N., Fridolfsson, E., Haecky, P., Andersson, A., Casini, M., Belgrano, A., and Hylander, S. 2019. Modeling vitamin B1 transfer to consumers in the aquatic food web. Sci. Rep. 9(1): 1-11. Springer US. doi:10.1038/s41598-019-46422-2.
-Fisher, J.P., Brown, S.B., Wooster, G.W., and Bowser, P.R. 1998. Maternal blood, egg and larval thiamin levels correlate with larval survival in landlocked Atlantic salmon (*Salmo salar*). J. Nutr. 128(12): 2456-2466. American Society for Nutrition. doi:10.1093/jn/128.12.2456.
-Fitzsimons, J.D., Williston, B., Amcoff, P., Balk, L., Pecor, C., Ketola, H.G., Hinterkopf, J.P., and Honeyfield, D.C. 2005. The effect of thiamine injection on upstream migration, survival, and thiamine status of putative thiamine-deficient coho salmon. J. Aquat. Anim. Health 17(1): 48-58. doi:10.1577/H04-003.1.
-Fitzsimons, J.D., Williston, B., Williston, G., Brown, L., El-Shaarawi, A., Vandenbyllaardt, L., Honeyfeld, D., Tillitt, D., Wolgamood, M., and Brown, S.B. 2007. Egg thiamine status of Lake Ontario salmonines 1995-2004 with emphasis on lake trout. J. Great Lakes Res. 33(1): 93-103. Elsevier. doi:10.3394/0380-1330(2007)33[93:ETSOLO]2.0.CO;2.
-Fridolfsson, E., Lindehoff, E., Legrand, C., and Hylander, S. 2018. Thiamin (vitamin B1) content in phytoplankton and zooplankton in the presence of filamentous cyanobacteria. Limnol. Oceanogr. 63(6): 2423-2435. doi:10.1002/lno.10949.
-Futia, M.H., Hallenbeck, S., Noyes, A.D., Honeyfield, D.C., Eckerlin, G.E., and Rinchard, J. 2017. Thiamine deficiency and the effectiveness of thiamine treatments through broodstock injections and egg immersion on Lake Ontario steelhead trout. J. Great Lakes Res. 43(2): 352-358. doi:10.1016/j.jglr.2017.01.001.
-Harder, A.M., Ardren, W.R., Evans, A.N., Futia, M.H., Kraft, C.E., Marsden, J.E., Richter, C.A., Rinchard, J., Tillitt, D.E., and Christie, M.R. 2018. Thiamine deficiency in fishes: causes, consequences, and potential solutions. Rev. Fish Biol. Fish. 28(4): 865-886. Springer International Publishing. doi:10.1007/s11160-018-9538-x.
-Harder, A.M., Reed, A.N., and Rowland, F.E. 2025. Evolutionary perspectives on thiamine supplementation of managed Pacific salmonid populations. Can. J. Fish. Aquat. Sci. 82(Bettendorff 2013): 1-10. doi:10.1139/cjfas-2024-0109.
-Honeyfield, D.C., Hinterkopf, J.P., Fitzsimons, J.D., Tillitt, D.E., Zajicek, J.L., and Brown, S.B. 2005. Development of thiamine deficiencies and early mortality syndrome in lake trout by feeding experimental and feral fish diets containing thiaminase. J. Aquat. Anim. Health 17(1): 4-12. doi:10.1577/H03-078.1.
-Honeyfield, D.C., Murphy, J.M., Howard, K.G., Strasburger, W.W., and Matz, A.C. 2016. An Exploratory Assessment of Thiamine Status in Western Alaska Chinook Salmon (*Oncorhynchus tshawytscha*). North Pacific Anadromous Fish Comm. Bull. (6): 21-31.
-Honeyfield, D.C., Peters, A.K., and Jones, M.L. 2008. Thiamine and fatty acid content of Lake Michigan Chinook salmon. J. Great Lakes Res. 34(4): 581-589. Elsevier. doi:10.1016/s0380-1330(08)71603-4.
-Houde, A.L.S., Saez, P.J., Wilson, C.C., Bureau, D.P., and Neff, B.D. 2015. Effects of feeding high dietary thiaminase to sub-adult Atlantic salmon from three populations. J. Great Lakes Res. 41(3): 898-906. International Association for Great Lakes Research. doi:10.1016/j.jglr.2015.06.009.
-Hylander, S., Farnelid, H., Fridolfsson, E., Hauber, M.M., Todisco, V., Ejsmond, M.J., and Lindehoff, E. 2024. Thiamin (vitamin B1, thiamine) transfer in the aquatic food web from lower to higher trophic levels. *In* PLoS ONE. doi:10.1371/journal.pone.0308844.
-Koski, P., Pakarinen, M., Nakari, T., Soivio, A., and Hartikainen, K. 1999. Treatment with thiamine hydrochloride and astaxanthine for the prevention of yolk-sac mortality in Baltic salmon fry (M74 syndrome). Dis. Aquat. Organ. 37(3): 209-220. doi:10.3354/dao037209.
-Ladago, B.J., Futia, M.H., Ardren, W.R., Honeyfield, D.C., Kelsey, K.P., Kozel, C.L., Riley, S.C., Rinchard, J., Tillitt, D.E., Zajicek, J.L., and Marsden, J.E. 2020. Thiamine concentrations in lake trout and Atlantic salmon eggs during 14 years following the invasion of alewife in Lake Champlain. J. Great Lakes Res. 46(5): 1340-1348. International Association for Great Lakes Research. doi:10.1016/j.jglr.2020.06.018.
-Larson, S., and Howard, K. 2019. Exploration of AYK Chinook Salmon egg thiamine levels as a potential mechanism contributing to recent low productivity patterns, 2014 and 2015.
-Lee, Y., Kim, S., Hasanthi, M., Song, S., Kim, S., and Lee, K.J. 2026. Dietary thiamine supplementation enhances the growth performance, digestive enzyme activity, intestine development, immunity and anti-inflammatory gene expression of juvenile olive flounder (*Paralichthys olivaceus*). Comp. Biochem. Physiol. Part - B Biochem. Mol. Biol. 281(September 2025): 111162. Elsevier Inc. doi:10.1016/j.cbpb.2025.111162.
-Mantua, N.J., Bell, H., Todgham, A.E., Daniels, M.E., Rinchard, J., Ludwig, J.M., Field, J.C., Lindley, S.T., Rowland, F.E., Richter, C.A., Walters, D., Finney, B., Distajo, H.A.R., Tillitt, D., and Honeyfield, D.C. 2025. Widespread thiamine deficiency in California salmon linked to an anchovy- dominated marine prey base. Proc. Natl. Acad. Sci. 122(26): e2426011122. doi:10.1073/pnas.
-Manzetti, S., Zhang, J., and Van Der Spoel, D. 2014. Thiamin function, metabolism, uptake, and transport. Biochemistry 53(5): 821-835. doi:10.1021/bi401618y.
-Paerl, R.W., Bertrand, E.M., Allen, A.E., Palenik, B., and Azam, F. 2015. Vitamin B1 ecophysiology of marine picoeukaryotic algae: Strain-specific differences and a new role for bacteria in vitamin cycling. Limnol. Oceanogr. 60(1): 215-228. doi:10.1002/lno.10009.
-Reed, A.N., Rowland, F.E., Krajcik, J.A., and Tillitt, D.E. 2023. Thiamine Supplementation Improves Survival and Body Condition of Hatchery-Reared Steelhead (*Oncorhynchus mykiss*) in Oregon. Vet. Sci. 10(2): 1-11. doi:10.3390/vetsci10020156.
-Rocchi, R., van Kekem, K., Heijnis, W.H., and Smid, E.J. 2022. A simple, sensitive, and specific method for the extraction and determination of thiamine and thiamine phosphate esters in fresh yeast biomass. J. Microbiol. Methods 201(August): 106561. Elsevier B.V. doi:10.1016/j.mimet.2022.106561.
-Roman-Campos, D., and Cruz, J.S. 2014. Current aspects of thiamine deficiency on heart function. Life Sci. 98(1): 1-5. Elsevier Inc. doi:10.1016/j.lfs.2013.12.029.
-Strasburger, W.W., Honeyfield, D.C., Murphy, J.M., and Pinger, C. 2023. A Review of the Thiamine Status of Alaskan Chinook Stocks and the U . S . West Coast. Available from https://meetings.pices.int/Publications/Presentations/2022-SPF/S1-Strasburger.pdf.
-Suffridge, C.P., Shannon, K.C., Matthews, H., Johnson, R.C., Jeffres, C., Mantua, N., Ward, A.E., Holmes, E., Kindopp, J., Aidoo, M., and Colwell, F.S. 2024. Connecting thiamine availability to the microbial community composition in Chinook salmon spawning habitats of the Sacramento River basin. Appl. Environ. Microbiol. 90(1). American Society for Microbiology. doi:10.1128/aem.01760-23.
-Tang, Y.Z., Koch, F., and Gobler, C.J. 2010. Most harmful algal bloom species are vitamin B1 and B 12 auxotrophs. Proc. Natl. Acad. Sci. U. S. A. 107(48): 20756-20761. doi:10.1073/pnas.1009566107.
-Welch, D.W., Futia, M.H., Rinchard, J., Teffer, A.K., Miller, K.M., Hinch, S.G., and Honeyfield, D.C. 2018. Thiamine Levels in Muscle and Eggs of Adult Pacific Salmon from the Fraser River, British Columbia. J. Aquat. Anim. Health 30(3): 191-200. doi:10.1002/aah.10024.
-Whitfield, K.C., Bourassa, M.W., Adamolekun, B., Bergeron, G., Bettendorff, L., Brown, K.H., Cox, L., Fattal-Valevski, A., Fischer, P.R., Frank, E.L., Hiffler, L., Hlaing, L.M., Jefferds, M.E., Kapner, H., Kounnavong, S., Mousavi, M.P.S., Roth, D.E., Tsaloglou, M.N., Wieringa, F., and Combs, G.F. 2018. Thiamine deficiency disorders: diagnosis, prevalence, and a roadmap for global control programs. Ann. N. Y. Acad. Sci. 1430(1): 3-43. doi:10.1111/nyas.13919.
-Wright, G.M., Brown, S.B., Brown, L.R., Moore, K., Villella, M., Zajicek, J.L., Tillitt, D.E., Fitzsimons, J.D., and Honeyfield, D.C. 2005. Effect of sample handling on thiamine and thiaminolytic activity in alewife. J. Aquat. Anim. Health 17(1): 77-81. doi:10.1577/H03-074.1.</t>
-  </si>
-  <si>
     <t>Mr. Reid Williams, MSc student; Dr. Nicholas Bernier, University of Guelph; Dr. Fredrick Laberge, University of Guelph</t>
   </si>
   <si>
@@ -2761,15 +2534,6 @@
 Venello, T.A. 2021. Linking zooplankton community composition to ecosystem functioning off the west coast of Vancouver Island and in the northeast subarctic Pacific. PhD Thesis, University of Victoria. https://dspace.library.uvic.ca/items/e81d1081-e7d4-48b5-ab78-f970896d0502/full
 Ware, D.M., and Thomson, R.E. 2005. Bottom-Up ecosystem trophic dynamics determine fish production in the Northeast Pacific. *Science.* 308: 1280-1284. DOI:10.1126/science.1109049
 Young, K., Galbraith, M., Sastri, A., and Perry, R.I. Zooplankton status and trends in the central and northern Strait of Georgia, 2022. *In* Boldt, J.L., Joyce, E., Tucker, S., and Gauthier, S. (Eds.). 2023. State of the physical, biological and selected fishery resources of Pacific Canadian marine ecosystems in 2022. Can. Tech.Rep. Fish. Aquat. Sci. 3542: viii + 312 p.</t>
-  </si>
-  <si>
-    <t>Aquacoustics Inc., TÅilhqot'in National Government (TNG)</t>
-  </si>
-  <si>
-    <t>Acoustic data were collected with two Simrad WBT Mini SONAR systems deployed approximately 2 km downstream of the Chilko River smolt enumeration fence. Each SONAR system operated with a 7Â° circular 120 kHz split-beam transducer. For the up-looking system, the transducer was mounted on the river bottom, in the thalweg, aimed straight up towards the water surface. For the side-looking system, the transducer was mounted nearshore on the left bank of the river, with its center approximately 15 cm below the surface, aimed across the river with a transducer tilt angle of approximately 3Â° down from horizontal. Data were recorded with a ping rate of 20 pings per second on the up-looking (maximum range 4 m), 12 pings per s on the side-looking system (maximum range 12 m). Both systems were set to 50 W power output. For all four years of the study, SONAR data were collected from mid-April to late-May during the entire Chilko Sockeye smolt outmigration period.
-SONAR data was manually reviewed and edited using Echoview software to remove noise, and echo integrated in 1 hour x 1 m range cells (side-looking) or 1 hour x 0.2 m range cells (up-looking). The results were exported as csv files, and all echo integration csv files belonging to the same transducer and site were concatenated for further analysis in Microsoft Excel. Excel was then used to convert the echo integration results to smolt passage estimates, which were then compared to the estimates generated at the Chilko River smolt enumeration fence.
-In 2023 and 2024 (2025 results pending), daily estimates of smolt passage showed close correspondence (5% in 2023, 9% in 2024) between fence counts and independent acoustic estimates both in time and magnitude. In the first year of the study (2022), daily SONAR estimates were in good agreement with the fence counts over the first 9 days of the study, but consistently higher over the last 9 days (May 3rd and thereafter). At present, the source of this divergence is unclear.
-This project is one of few that have used split-beam SONARs configured in this manner to enumerate outmigrating salmon smolts. While further testing needs to be conducted in both the Chilko River where the study was conducted, and in other candidate systems, the preliminary results of this study are promising. These methods could be modified and applied to a variety of salmon stock assessment programs to gain crucial information on survival in the early freshwater life stages (egg to smolt survival), however, considerable planning and care needs to be taken when selecting a suitable site.</t>
   </si>
   <si>
     <t>Follow The fish team</t>
@@ -2974,24 +2738,11 @@
     <t>Feasibility of estimating Chilko River smolt abundance using upward- and side-Looking SONAR methods</t>
   </si>
   <si>
-    <t>Chilko Sockeye salmon represent the only wild Sockeye indicator stock in the Fraser watershed. The annual Chilko Lake Sockeye smolt assessment (1951-present) comprises the only long-term time series data available to assess juvenile recruitment, and freshwater and marine productivity for wild Fraser River Sockeye salmon. Since program inception, Sockeye smolts have been enumerated during their out-migration from Chilko Lake using a traditional fish counting weir and photographic sampling/counting techniques. During the first six decades of the program (1951-2012), interruptions in weir operation were relatively rare: in only three years (1979, 1993, 2006) did early freshets necessitate removal of the weir before the vast majority of smolts had migrated from Chilko Lake.
-Recently, unusually early freshets have been experienced in the Chilko watershed that have translated into high and variable water conditions much earlier in the season. As such, DFO Stock Assessment crews were not able to operate the weir in 2015 due to high water flows, and have had to remove the weir structure prior to the completion of smolt migration on numerous other recent years (e.g., 2019). The observed increase in the frequency of early freshets in the Chilko watershed is consistent with predicted hydrographic changes for interior BC streams as a whole in response to climate variability, with the average timing of the spring freshet expected to continue shifting earlier as air temperatures rise. The future of operating the Chilko Sockeye smolt weir is in jeopardy given the current trend related to the timing, frequency, and strength of the spring freshets. If proven effective, the SONAR method would provide an alternate assessment method for the Chilko watershed that could be quickly employed in years when high flows either prevent the installation of the weir at the beginning of the migration, or necessitate the removal of the weir before the smolt migration is largely complete.
-The objective of this work was to:
-- test the feasibility of using upward-looking SONAR technology to assess daily abundances of Chilko Lake sockeye smolts as they migrate downstream through the Chilko River, and
-- evaluate the reliability of using daily SONAR-derived abundance indices predict the daily migration totals observed at the counting weir that is deployed annually on the Chilko River.
-This work was conducted in collaboration with the TÅilhqot'in National Government (TNG).</t>
-  </si>
-  <si>
     <t>This project has shown sockeye salmon at the smolt life stage can be effectively enumerated using SONAR, and is an easily-deployed and operated alternative to installing large enumeration fences which are typically labor-intensive and may disturb stream substrates. Many salmon stocks are solely assessed through adult escapements, which does not capture survival during the early freshwater life stages, and creates additional challenges when investigating individual stock recruitment and forecasting returns that are used in fisheries management and planning.
 Using SONAR to enumerate salmon at the smolt stage enables researchers to investigate survival metrics during the early freshwater period in which there is often little or no data at the population or Conservation Unit (CU) level. In systems where there is ongoing juvenile enumeration work (e.g. with counting fences, rotary screw traps (RST), incline plane traps (IPT), etc.), this method may provide a suitable, and less invasive alternative to conventional methods. Further to this, the observed increase in frequency of early freshets and hydrographic changes in response to climate variability may preclude the operation of some juvenile assessment methods, leading to the need for other means of collecting juvenile salmon data.
 Sources of uncertainty raised from this project include discrepancies in SONAR counts when compared to fence counts (particularly in the 2022 study year), which at this time are unresolved. Additionally, there in uncertainty how the system deployed would operate under heavy flow conditions, in systems with different stream characteristics, and in systems with multiple species of Pacific salmon with overlapping outmigration timing.</t>
   </si>
   <si>
-    <t>Figure 1. 2024 daily estimates of Chilko River Sockeye smolt passage: side-looking SONAR estimates versus fence counts.
-Figure 2. 2023 daily estimates of Chilko River Sockeye smolt passage: side-looking SONAR estimates versus fence counts.
-Figure 3. 2022 daily estimates of Chilko River Sockeye smolt passage: side-looking SONAR estimates versus fence counts.</t>
-  </si>
-  <si>
     <t>Geospatial indicators and metrics for threats to fish habitat in the Fraser River Basin with Thompson-Nicola as a case study</t>
   </si>
   <si>
@@ -3000,12 +2751,6 @@
   <si>
     <t>The key finding of this project will be the specific differences in dynamics between hatchery and natural-origin San Juan Chinook, and using this information to both improve the survival and health of natural-origin juveniles while producing hatchery fish that complement, rather than compete with, the natural population. These findings may be applicable to other systems, although collecting stock-specific information is critical to ensure that any future "indicator" populations are in fact indicative of dynamics in other systems.
 Future studies should further examine specific indicators of early mortality in juvenile salmon, primarily in the freshwater and estuarine stages which are largely unmonitored by DFO. In addition, consideration should be given as to how hatchery release strategies change the life history dynamics of juvenile salmon.</t>
-  </si>
-  <si>
-    <t>Table 1. Results of total thiamine levels detected in chinook salmon eggs treated or untreated with thiamine. The results shown were the mean of duplicates. Each test represented results of eggs collected from an individual fish of each population. Note that for Cheakamus chinook salmon, each pair of control and treated eggs (same row) was collected from the same fish. All Middle Shuswap chinook salmon were treated with injection prior to spawning, and thus untreated eggs were not available for sampling. The bath-treated eggs were all fertilized, while the untreated eggs, and the injection-treated eggs were not fertilized. 
-Figure 1. Results of linear regression analysis on the total mean thiamine level results reported by SUNY Brockport and PSEC on the same set of chinook salmon eggs. Each dot represents an individual sample. 
-Figure 2. Results of the total thiamine levels in untreated and unfertilized eggs collected from Capilano mid coho (Cap-mid-Coho, n=5), Chilliwack mid coho (Cwk-mid-Coho, n=10), Tenderfoot Cheakamus Chinook (Tdf-Chinook, n=4), Chilliwack fall Chinook (Cwk-Chinook, n=10), Harrison sockeye (Har-Sockeye, n=10), Chilko sockeye (Cko-Sockeye, n=10), Weaver sockeye (Wvr-Sockeye, n=9) and Chehalis pink (Chs-Pink, n=11). Note that the Harrison sockeye eggs were considered not ripe during sample collection; Tenderfoot Cheakamus Chinook data came from results of untreated eggs reported in Table 1. The dash lines represent thiamine level thresholds established by Mantua et al. (2025) to illustrate the likelihood of being impacted by thiamine deficiency: high - unlikely impacted (&gt; 7.7 nmol/g), intermediate - likely impacted (5.9-7.7 nmol/g), low - impacted (2.7-5.9 nmol/g) and critically low - severely impacted (&lt; 2.7 nmol/g). The cross symbol (Ã—) in the box plot indicates mean values within each group.
-Figure 3. Proportion of salmon eggs from different populations measured by the thiamine level thresholds established by Mantua et al. (2025). Different category of total thiamine level represents different likelihood of being impacted by thiamine deficiency: high - unlikely impacted (&gt; 7.7 nmol/g), intermediate - likely impacted (5.9-7.7 nmol/g), low - impacted (2.7-5.9 nmol/g) and critically low - severely impacted (&lt; 2.7 nmol/g). Eggs were collected from different salmon species and population: Capilano mid coho (n=5), Chilliwack mid coho (n=10), Tenderfoot Cheakamus Chinook (n=4), Chilliwack fall Chinook (n=10), Harrison sockeye (n=10), Chilko sockeye (n=10), Weaver sockeye (n=9) and Chehalis pink (n=11).</t>
   </si>
   <si>
     <t>shíshálh Nation</t>
@@ -3148,11 +2893,6 @@
 Naman, S.M., Rosenfeld, J.S., Neuswanger, J.R., Enders, E.C., Hayes, J.W., Goodwin, E.O., Jowett, I.G. and Eaton, B.C., 2020. Bioenergetic Habitat Suitability Curves for Instream Flow Modeling: Introducing User‐Friendly Software and its Potential Applications. Fisheries, 45(11), pp.605-613.</t>
   </si>
   <si>
-    <t xml:space="preserve">Figure 1. (a) Human activity and landscape disturbance based additive cumulative threat score, and (b) Climate change additive cumulative threat score for 2040-2060 under RCP 4.5. Blue indicates low threat levels and red indicates high threat levels.
-Figure 2. Tukey’s box-whiskers plots of the cumulative threat scores from human activity and landscape disturbance based threats and climate change based threats for all streams in the FRB, (a &amp; b) accessible streams within salmon CUs, and (c &amp; d) delineated stream habitats of fish SAR. Salmon CUs identified as Special Concern, Threatened, or Endangered by COSEWIC were distinguished from those not at risk. 
-Figure 3. Median cumulative threat composite scores for watershed groups in the Thompson-Nicola EDU based on the multiplicative value of human activity and landscape disturbance based cumulative threats and modeled environmental favourability for spawning (row a) Chinook, (b) Coho, (c) Pink, and (d) Sockeye Salmon. Modeled environmental favourability probabilities used in the composite score were based on projected (column a) current and (b) future conditions for all stream reaches (≥ 4th order) including inaccessible streams from dams and natural barriers. Watershed groups that are largely inaccessible are identified by hatched lines, and salmon CU boundaries in black outlines. Colour scale indicates increasing need for localized investigation and potential restoration. </t>
-  </si>
-  <si>
     <t>Although our threat estimates represent the mechanisms by which salmon and freshwater SAR are affected, the magnitude at which these threats influence salmon population dynamics remains unknown. To address this gap, we are continuing to refine existing threat estimates and developing new threats that are explicitly linked to stressor-response functions for cumulative effects and life-cycle modelling. For example, we have developed additional riparian disturbance metrics that better capture the impacts to riparian function (e.g., large-woody debris recruitment, disturbance to stream-shading, riparian filtering), which were not included in the original report. Moreover, we are developing a stage-structured population model for Interior Fraser Coho (IFC) to estimate how stressors (estimated threats) are influencing the population across their freshwater life stages. For this work, we are utilizing the Cumulative Effects Model for Prioritizing Recovery Actions (CEMPRA), which applies stressor-response functions to account for the impact of stressors on vital rates and the overall population overtime and under different climate change and mitigation scenarios (Bayly et al. 2024).
 Additional next steps for this work include expanding the cumulative threats model to other watersheds in the Pacific Region. To date, the model has also been applied to the Upper Bulkley Watershed to aid in salmon habitat restoration planning. Validation is an important step of most modelling exercises, though is often not a standard component of cumulative effect assessments (Halpern and Fujita 2013). Validating these threats through field verification and in situ data would be beneficial for threats that involve applied relationships and estimations, such as the flow accumulated loadings (i.e., nutrients, pollution, sedimentation). Future work could re-run the model at regular intervals to evaluate change in threats over time. Finally, additional analyses could quantify uncertainty in modelled threats and evaluate underlying assumptions through sensitivity tests.</t>
   </si>
@@ -3193,6 +2933,262 @@
 Analysis of 196 federal and provincial statutes revealed that pollution-related provisions are most prevalent across both jurisdictions. Salmon harvest regulation is mostly managed federally, while salmon habitat factors including water use and watercourse modifications are governed provincially, which reflects a structural disconnect between fish stock stewardship and habitat protection.
 *Implications*
 The LAPSE framework demonstrates the ability to identify regulatory pathways relevant to specific human activity threats by linking IUCN-CMP threat classifications to legislation, enabling salmon stewardship practitioners to navigate the complex legal landscape and develop coordinated, inter-jurisdictional recovery strategies.</t>
+  </si>
+  <si>
+    <t>We developed a geospatial tool to summarize anthropogenic and climate change related cumulative threats to freshwater species and habitats using open-source input data and software that can be reproduced for different time periods and freshwater species and their habitats. All threats were estimated for each stream reach within the BC Freshwater Atlas (FWA). We derived nine individual human-activity and landscape disturbance threats: aquatic invasive species, riparian disturbance, in-stream habitat destruction, flow alteration, latitudinal fragmentation, sedimentation, pollutant loading, and nutrient loading. The input data was processed and combined to produce an individual threat score that characterizes the mechanism of disturbance to freshwater species for each score. For climate change threats, we compiled model outputs of projected stream flow and temperature to estimate threats of flood-risk, low and high stream flow, and high summer stream temperature from 2040-2060 under Representative Concentration Pathway (RCP) 4.5 and 8.5 scenarios. The individual threat scores were standardized across the study area, weighted equally, and added together to calculate a human activity and landscape disturbance cumulative threat score and a climate change based cumulative threat score (see Iacarella et al. 2025 for detailed methods). Finally, both cumulative threat scores were paired with salmon and SAR distributions (i.e., CU boundaries and delineated stream habitats, respectively) and evaluated to identify where threats were greatest and which species and CUs were exposed to the highest threat levels.
+For the Thompson-Nicola EDU case study, we focused on human activity threats that may reasonably be mitigated, including riparian disturbance, water withdrawal, and longitudinal fragmentation from dams. We identified overlap between these threats and two approaches used to identify areas important to salmon: (1) CU delineations and (2) modelled environmentally favourable spawning habitats. The modelled environmentally favourability predictions were derived from large-scale environmental niche models to predict shifts in habitat favourability from current to future climate conditions (Iacarella and Weller 2023). We multiplicatively combined threat scores with environmental favourability for salmon spawning to create composite scores that reflect a gradient of potential management implications (see Fig. 20 in Iacarella et al. 2025). A high threat score combined with a high favourable habitat probability identifies an area that warrants localized investigation and potential restoration or mitigation actions. Conversely, a low threat score combined with a low favourable habitat probability identifies an area that is less likely to need management attention based on salmon values (i.e., predicted spawning habitat) and low level of anthropogenic impact.
+Our results indicated the highest cumulative threat scores around the lower Fraser River and within the interior plateau of the FRB for both human activity and landscape disturbance based threats and climate change based threats (Figure 1). Watershed groups with the highest median cumulative threats were the Nicola River, Guichon Creek, and San Jose River. These heightened scores were predominately driven by riparian disturbance, nutrients, and sedimentation for the human activity based threats and high stream temperatures for the climate change based threats. Roads were the most frequent input that influenced human activity based threats across the FRB, and contributed consistently to in-stream habitat destruction, riparian disturbance, nutrients, and sedimentation. Other important inputs to these threats were forest fires, forest pest defoliation, rangeland, and forestry. We found that SAR with limited ranges (i.e., coastrange sculpin, green sturgeon, Nooksack dace, and Salish sucker) had higher median human activity cumulative threat scores relative to all streams in the FRB, corresponding to their at risk status (Figure 2). Median human activity threat scores tended to be more similar among salmon CUs and relative to all streams, though a few of the Threatened and Endangered sockeye salmon CUs had notably higher median threat scores (Figure 2).
+Within the Thompson-Nicola EDU, median cumulative threat composite scores within watershed groups based on the multiplicative value of human activity cumulative threats and favourable spawning habitat under current and future conditions were highest for sockeye (Figure 3). The greatest shifts in median composite scores from current to future climate conditions (i.e., based on changes in predicted spawning favourability), were increases in Upper North Thompson River for Chinook (median score change = 0.14), Bonaparte River for pink (0.06), and Deadman River for sockeye (0.11), and a decrease in Thompson River for coho (-0.06). Overall, the Deadman and Adams River watershed groups were identified as having the highest cumulative composite scores under current and future climate conditions across salmon species in the EDU.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figure 1. (a) Human activity and landscape disturbance based additive cumulative threat score, and (b) Climate change additive cumulative threat score for 2040-2060 under RCP 4.5. Blue indicates low threat levels and red indicates high threat levels.
+Figure 2. Tukey’s box-whiskers plots of the cumulative threat scores from human activity and landscape disturbance based threats and climate change based threats for all streams in the FRB, (a &amp; b) accessible streams within salmon CUs, and (c &amp; d) delineated stream habitats of fish SAR. Salmon CUs identified as Special Concern, Threatened, or Endangered by COSEWIC were distinguished from those not at risk. 
+Figure 3. Median cumulative threat composite scores for watershed groups in the Thompson-Nicola EDU based on the multiplicative value of human activity and landscape disturbance based cumulative threats and modeled environmental favourability for spawning (row a) Chinook, (b) coho, (c) pink, and (d) sockeye salmon. Modeled environmental favourability probabilities used in the composite score were based on projected (column a) current and (b) future conditions for all stream reaches (≥ 4th order) including inaccessible streams from dams and natural barriers. Watershed groups that are largely inaccessible are identified by hatched lines, and salmon CU boundaries in black outlines. Colour scale indicates increasing need for localized investigation and potential restoration. </t>
+  </si>
+  <si>
+    <t>We used multiple methods to evaluate SSL foraging ecology, quantify sockeye salmon mortality rates, and ultimately draw inference on the likely impact of SSLs on migrating Fraser River sockeye salmon. The following activities occurred during the 2024 and 2025 field seasons (Figure 1).
+*Sockeye salmon methods*
+Sockeye salmon were captured aboard a charter purse seine vessel from sites near Rennell Sound (west coast Haida Gwaii; 2024 and 2025) and Queen Charlotte Strait (2025 only). Sockeye salmon were landed and transferred to a flow through seawater trough where biological data, including genetic stock identification (GSI) samples, were collected. Individuals in good physical condition were tagged with either an acoustic or satellite tag before being immediately released. We deployed acoustic transmitters on sockeye salmon (n=625) which allowed individuals to be detected on moored receiver arrays near Haida Gwaii, Triangle Island, Queen Charlotte Strait, throughout the Salish Sea, and the lower Fraser River. The acoustic receiver network included approximately 40 receivers deployed by DFO throughout coastal British Columbia, as well as infrastructure maintained by NOAA, the Ocean Tracking Network, Kintama, and the University of British Columbia. Detections data will be used to parameterize mark-recapture models to estimate survival rates along the migration corridor and identify hotspots of mortality. We also deployed popup archival satellite tags (PSATs) on a smaller number of sockeye salmon (n=35). After releasing from the animal these tags transmit light, temperature, and pressure sensor data that can be used to identify predator taxa (Seitz et al. 2019).
+*Sockeye salmon findings*
+GSI results are currently only available for the 2024 field season; however, the majority (&gt;98%) of tagged sockeye salmon were identified as belonging to Fraser River populations with Chilko Lake being the dominant conservation unit (~55% of all samples). Only a subset of detections data are currently available for 2025; however preliminary results in both years (Figure 2) indicate overall survival from Haida Gwaii to the Fraser River was poor (&lt;8%). ~50% of individuals tagged at northern sites were detected on Haida Gwaii arrays; however, mark-recapture models that account for imperfect detection probability on these arrays are required for robust estimates of survival. Survival to the Fraser River of tags deployed in Queen Charlotte Strait was markedly higher (~40%). 2% of tags were detected in the study area after deployments were completed, suggesting short-term mortality due to tagging or handling was minimal. Only two tags were detected at Triangle Island (both in 2025), however 46 tags were detected in 2025 at sea lion haul outs throughout Queen Charlotte Strait. Importantly, additional analysis is required to determine how many of these fish were likely consumed by pinnipeds based on subsequent detections. No fish were reported as intercepted by fisheries in 2024, but 5% of tagged fish were recaptured by marine and in-river fisheries and reported in 2025.
+We deployed 18 PSATs at Haida Gwaii sites in 2024 and 17 in 2025 (ten in Haida Gwaii and seven in Queen Charlotte Strait). Six of the 2024 PSATs failed to report due to engineering issues. All of the remaining 12 reported before their programmed release data, suggesting the fish were predated. Of the confirmed mortalities, three could not be classified because the tag was not ingested, one was consumed by a benthic ectotherm, and eight were consumed by salmon sharks (Figure 3). In 2025, all PSATs reported and five survived to release, all from the Queen Charlotte Strait study area. Of the ten Haida Gwaii tags, four were consumed by blue sharks, three by a benthic ectotherm, and three by salmon sharks. Neither of the two Queen Charlotte Strait mortalities could be classified (Figure 3).
+*SSL methods*
+We deployed satellite tags (paired head-mounted splash and flipper-mounted spot tags) on adult male (n=7) and female (n=14) SSLs on Triangle Island. Animals were sedated via darting gun and tagged with the assistance of staff from the Vancouver Aquarium. Females were captured near the end of July following pupping; males were captured at the beginning of June as animals staked out territories for the breeding period. Head mounted tags were epoxied to the fur and were shed by fall during the annual moult while the flipper mounted tags should stay affixed for multiple years although tag programming and battery life will ultimately determine transmission duration. The high resolution, yet shorter deployment splash tags will allow for an understanding of foraging behaviour (location and dive profiles) and sex-specific habitat use revealing explicit spatial-temporal overlap with sockeye salmon during their migration through Queen Charlotte Sound. This distribution data is critical in evaluating the relative proportion of the SSL population that has the opportunity to predate sockeye salmon. The longer-term flipper tags (8-16 months; multi-year) will allow for multi-season information on coarse foraging patterns.
+We also collected SSL diet information via biochemical tracers and scats from sites on Triangle Island, as well as key haul outs in Queen Charlotte Strait, southwest coast of Vancouver Island, and the southern Strait of Georgia. The two biochemical tracers we have focused on, fatty acid profiles and stable isotopes, provide estimates of diet composition integrated over weeks to month. The fatty acid analysis (FAA; Budget et al. 2006) will provide more discrete diet estimation (prey-specific proportions) while the stable isotope analysis (SIA; Layman et al. 2012) will be useful to discriminate feeding source (pelagic vs demersal, nearshore vs shelf vs shelf break) such that we can broadly characterize foraging behaviour beyond the satellite tagged individuals. Diets estimated from scats provide a short-term (~ 1 day) estimate requiring far more extensive, repeated sampling to capture temporal variation in diet-particularly if the objective is to capture a potential pulse of a relatively rapidly migrating prey. While we collected scats (n=1,200), there was insufficient funding provided to analyze these, let alone undertake a full-fledged sampling design for scats. These are therefore archived for potential future work and analysis focused on the integrated tracer samples. In total, ~400 sea lion biopsy samples were obtained directly from satellite tagged animals or randomly via a crossbow system. To estimate diet, over 1500 potential fish and invertebrate prey samples were obtained from various DFO research cruises.
+*SSL Findings*
+During the 5 - 6-week deployments prior to moult, female foraging was concentrated on the continental shelf (Figure 4a). In the initial weeks, animals used Triangle Island as a central place for short foraging forays. As pups inevitably grew and became more independent, there was a gradual expansion and dispersal away from Triangle east to Cook Bank and Queen Charlotte Strait and south-east to Quatsino Sound with females ultimately moving to sites both east and south of Triangle Island. During the 14 - 16-week deployments prior to moult, males demonstrated very limited foraging activity during the breeding period (Figure 4b). Subsequently by mid-July there was rapid and directed dispersal immediately post-breeding with individuals ranging as far north as southeast Alaska and south to the Washington border. Triangle was not used as major haul out outside of the breeding period for either females or males. More in-depth analysis of distribution and dive behaviour is underway to explicitly parameterize sea lion foraging effort in a spatial context and provide support for interpreting diet results.
+Stable isotope and fatty acid datasets for potential prey and sea lions have been completed for 2023-2024 samples; 2025 samples are currently being processed and analyzed. Preliminary analysis of 2023-2024 SI values for known age class and sex animals suggests that males and females are exploiting different prey/habitats diverging further with age (Figure 5).</t>
+  </si>
+  <si>
+    <t>Budge, S.M., Iverson, S.J. and Koopman, H.N., 2006. Studying trophic ecology in marine ecosystems using fatty acids: a primer on analysis and interpretation. Marine Mammal Science, 22(4).
+Chasco, B., Kaplan, I., Thomas, A., Acevedo-Gutiérrez, A., Noren, D., Ford, M., Hanson, M., Scordino, J., Jeffries, S., Marshall, K., Shelton, A., Matkin, C., Burke, B. &amp; Ward, E. 2017a. Competing tradeoffs between increasing marine mammal predation and fisheries harvest of Chinook salmon. Scientific Reports, 7. 
+Chasco, B., Kaplan, I., Thomas, A., Acevedo-Gutiérrez, A., Noren, D., Ford, M., Hanson, M., Scordino, J., Jeffries, S., Pearson, S., Marshall, K. &amp; Ward, E. 2017b. Estimates of Chinook salmon consumption in Washington State inland waters by four marine mammal predators from 1970 to 2015. Canadian Journal of Fisheries and Aquatic Sciences 74: 1173-1194. 
+Cohen, B. 2012. The Uncertain Future of Fraser River Sockeye Salmon Volume 2: Causes of the Decline. 212 p. 
+Crossin, G.T., Hinch, S.G., Cooke, S.J., Welch, D.W., Batten, S.D., Patterson, D.A., Van Der Kraak, G., Shrimpton, J.M., and Farrell, A.P. 2007. Behaviour and physiology of sockeye salmon homing through coastal waters to a natal river. Mar. Biol. 152: 905-918.
+Crossin, G.T., Hinch, S.G., Cooke, S.J., Cooperman, M.S., Patterson, D.A., Welch, D.W., Hanson, K.C., Olsson, I., English, K.K., and Farrell, A.P. 2009. Mechanisms influencing the timing and success of reproductive migration in a capital breeding semelparous fish species, the sockeye salmon. Phys. Biochem. Zool. 82: 635-652.
+Freshwater, C., Burke, B.J., Scheuerell, M.D., Grant, S.C.H., Trudel, M., and Juanes, F. 2018. Coherent population dynamic associated with sockeye salmon juvenile life history strategies. Can. J. Fish. Aquat. Sci. 75: 1346-1356. 
+Layman, C.A., Araujo, M.S., Boucek, R., Hammerschlag‐Peyer, C.M., Harrison, E., Jud, Z.R., Matich, P., 
+Rosenblatt, A.E., Vaudo, J.J., Yeager, L.A. and Post, D.M., 2012. Applying stable isotopes to examine foodweb structure: an overview of analytical tools. Biological reviews, 87(3), pp.545-562.
+McKinnell, S., Curchitser, E., Groot, K., Kaeriyama, M., and Trudel, M. 2014. Oceanic and atmospheric extremes motivate a new hypothesis for variable marine survival of Fraser River sockeye salmon. Fish. Ocean. 23: 322-341.
+Nelson, B., Pearson, S., Anderson, J., Jeffries, S., Thomas, A., Walker, W., Acevedo-Gutiérrez, A., Kemp, I., Lance, M., Louden, A. &amp; Voelker, M. 2021. Variation in predator diet and prey size affects perceived impacts to salmon species of high conservation concern. Canadian Journal of Fisheries and Aquatic Sciences 78: 1661-1676. 
+Nelson, B.W., McAllister, M.K., Trites, A.W., Thomas, A.C. and Walters, C.J. 2024. Quantifying impacts of harbor seal Phoca vitulina predation on juvenile Coho Salmon in the Strait of Georgia, British Columbia. Marine and Coastal Fisheries 16(1), p.e210271. 
+Peterman, R.M. and Dorner, B.D. 2012. A widespread decrease in productivity of sockeye salmon (Oncorhynchus nerka) populations in western North America. Can. J. Fish. Aquat. Sci. 69: 1255-1260.
+Proudfoot, B., Thompson, P.L, Vaidyanathan, T., Robb, C.K. 2024. Spatial estimate of blue shark, salmon shark, Pacific sleeper shark, and bluntnose sixgill shark presence in British Columbia. Can. Tech. Rep. Fish. Aquat. Sci. 3600: 27 p.
+Rechisky, E.L., Porter, A.D., Clark, T.D., Furey, N.B., Gale, M.K., Hinch, S.G., and Welch, D.W. 2019. Quantifying survival of age-2 Chilko Lake sockeye salmon during the first 50 days of migration. Can. J. Fish. Aquat. Sci. 76: 136-152. 
+Seitz, A.C., Courtney, M.B., Evans, M.D., and Manishin, K. 2019. Pop-up satellite archival tags reveal evidence of intense predation on large immature Chinook salmon (Oncorhynchus tshawytscha) in the North Pacific Ocean. Can. J. Fish. Aquat. Sci. 76: 1608-1615.
+Walters, C.J., McAllister, M.K., and Christensen, V. 2020. Has Steller sea lion predation impacted survival of Fraser River sockeye salmon? Fish. 45: 597-604.
+Wells, B.W., Huff, D.D., Quinn, T.P., Santora, J.A., Gomes D.G.E. et al. 2025. When, where, and why salmon become vulnerable to predation. ICES J. Mar. Sci. 82: fsaf162.
+Williams, R., Okey, T.A., Wallace, S.S., Gallucci, V.F. 2010. Shark aggregation in coastal waters of British Columbia. Mar. Ecol. Prog. Ser. 414: 249-265.</t>
+  </si>
+  <si>
+    <t>Figure 1. Map of study area showing approximate Fraser River sockeye salmon migration corridor, sockeye salmon and Steller sea lion tagging sites, and diet sampling locations.
+Figure 2. Proportion of tagged sockeye salmon detected along migration corridor by release cohort (HG is Haida Gwaii, QCS is Queen Charlotte Strait). Detections provide an approximate estimate of survival but do not account for imperfect detection probability. Final results require parameterization of mark-recapture model.
+Figure 3. Fates of popup satellite tags stratified by release location. Survival to release represents tags that uploaded data at their release date. All other tags transmitted early indicating they were no longer attached to the tagged animal. Ingested tags could be assigned to a predator guild based on temperature and pressure data while unknown mortalities represent deployments where the tag was removed from the prey, but not ingested by a predator.
+Figure 4. Tracks of individual a) female and b) male Steller sea lions satellite tagged on Triangle Island in 2024 or 2025. 
+Figure 5. Posterior mean isotopic (δ13C and δ15N) space for Steller sea lions by age class and sex. Points represent draws from the posterior distribution of population-level mean isotope values from Bayesian hierarchical models. Ellipses denote 95% Bayesian credible regions of uncertainty in mean isotopic values for each group.</t>
+  </si>
+  <si>
+    <t>- The main goal of the project was to test the use of SONAR technology to enumerate sockeye salmon smolt outmigration, while concurrently running a counting fence to evaluate its performance over a four year period.
+- Over the course of three years (2025 results are pending), the total number of sockeye smolts estimated with SONAR when compared to estimates generated at the enumeration fence, ranged from 5-33% (5% in 2024, 8% in 2023, 33% in 2022).
+- This method has been shown to be effective at enumerating sockeye smolts, which is an important and often lacking piece of information in salmon stock assessments (e.g. estimating early freshwater survival, generating stock-recruit relationships). However, using SONAR in this configuration is highly dependent on site selection, stream morphology, flow conditions, and the ability to adequately sample smolts for size measurements used in the analysis.</t>
+  </si>
+  <si>
+    <t>Aquacoustics Inc., Tŝilhqot'in National Government (TNG)</t>
+  </si>
+  <si>
+    <t>Chilko sockeye salmon represent the only wild sockeye indicator stock in the Fraser watershed. The annual Chilko Lake sockeye smolt assessment (1951-present) comprises the only long-term time series data available to assess juvenile recruitment, and freshwater and marine productivity for wild Fraser River sockeye salmon. Since program inception, sockeye smolts have been enumerated during their out-migration from Chilko Lake using a traditional fish counting weir and photographic sampling/counting techniques. During the first six decades of the program (1951-2012), interruptions in weir operation were relatively rare: in only three years (1979, 1993, 2006) did early freshets necessitate removal of the weir before the vast majority of smolts had migrated from Chilko Lake.
+Recently, unusually early freshets have been experienced in the Chilko watershed that have translated into high and variable water conditions much earlier in the season. As such, DFO Stock Assessment crews were not able to operate the weir in 2015 due to high water flows, and have had to remove the weir structure prior to the completion of smolt migration on numerous other recent years (e.g., 2019). The observed increase in the frequency of early freshets in the Chilko watershed is consistent with predicted hydrographic changes for interior BC streams as a whole in response to climate variability, with the average timing of the spring freshet expected to continue shifting earlier as air temperatures rise. The future of operating the Chilko sockeye smolt weir is in jeopardy given the current trend related to the timing, frequency, and strength of the spring freshets. If proven effective, the SONAR method would provide an alternate assessment method for the Chilko watershed that could be quickly employed in years when high flows either prevent the installation of the weir at the beginning of the migration, or necessitate the removal of the weir before the smolt migration is largely complete.
+The objective of this work was to:
+- test the feasibility of using upward-looking SONAR technology to assess daily abundances of Chilko Lake sockeye smolts as they migrate downstream through the Chilko River, and
+- evaluate the reliability of using daily SONAR-derived abundance indices predict the daily migration totals observed at the counting weir that is deployed annually on the Chilko River.
+This work was conducted in collaboration with the Tŝilhqot'in National Government (TNG).</t>
+  </si>
+  <si>
+    <t>Acoustic data were collected with two Simrad WBT Mini SONAR systems deployed approximately 2 km downstream of the Chilko River smolt enumeration fence. Each SONAR system operated with a 7° circular 120 kHz split-beam transducer. For the up-looking system, the transducer was mounted on the river bottom, in the thalweg, aimed straight up towards the water surface. For the side-looking system, the transducer was mounted nearshore on the left bank of the river, with its center approximately 15 cm below the surface, aimed across the river with a transducer tilt angle of approximately 3° down from horizontal. Data were recorded with a ping rate of 20 pings per second on the up-looking (maximum range 4 m), 12 pings per s on the side-looking system (maximum range 12 m). Both systems were set to 50 W power output. For all four years of the study, SONAR data were collected from mid-April to late-May during the entire Chilko sockeye smolt outmigration period. 
+SONAR data was manually reviewed and edited using Echoview software to remove noise, and echo integrated in 1 hour x 1 m range cells (side-looking) or 1 hour x 0.2 m range cells (up-looking). The results were exported as csv files, and all echo integration csv files belonging to the same transducer and site were concatenated for further analysis in Microsoft Excel. Excel was then used to convert the echo integration results to smolt passage estimates, which were then compared to the estimates generated at the Chilko River smolt enumeration fence. 
+In 2023 and 2024 (2025 results pending), daily estimates of smolt passage showed close correspondence (5% in 2023, 9% in 2024) between fence counts and independent acoustic estimates both in time and magnitude. In the first year of the study (2022), daily SONAR estimates were in good agreement with the fence counts over the first 9 days of the study, but consistently higher over the last 9 days (May 3rd and thereafter). At present, the source of this divergence is unclear.
+This project is one of few that have used split-beam SONARs configured in this manner to enumerate outmigrating salmon smolts. While further testing needs to be conducted in both the Chilko River where the study was conducted, and in other candidate systems, the preliminary results of this study are promising. These methods could be modified and applied to a variety of salmon stock assessment programs to gain crucial information on survival in the early freshwater life stages (egg to smolt survival), however, considerable planning and care needs to be taken when selecting a suitable site.</t>
+  </si>
+  <si>
+    <t>Figure 1. 2024 daily estimates of Chilko River sockeye smolt passage: side-looking SONAR estimates versus fence counts.
+Figure 2. 2023 daily estimates of Chilko River sockeye smolt passage: side-looking SONAR estimates versus fence counts.
+Figure 3. 2022 daily estimates of Chilko River sockeye smolt passage: side-looking SONAR estimates versus fence counts.</t>
+  </si>
+  <si>
+    <t>This study examined IHNV prevalence across different watersheds, sockeye stocks, and environmental conditions to identify those factors responsible for driving IHNV prevalence and/or influencing disease within sockeye salmon populations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*Methods*
+Adult and fry sockeye salmon were each collected annually from 1987 to 2018, from each of four spawning channel populations,  representing two stocks within the Fraser River watershed and two within the Skeena River watershed (Figure 1).  Samples were screened for the presence of infectious hematopoiectic necrosis virus (IHNV) using cell culture methodologies.  Characteristic cytopathic effects (CPE) observed in cells indicated the presence of  viable replicating IHNV. Prevalence of IHNV was calculated by dividing the number of samples with CPE by the total number of samples screened.
+We used statistical methods to understand how IHNV prevalence in adult fish relate to infection levels in fry, and how infection in fry affects infection in adults that return 3–4 years later.
+To compare how infection levels changed over time, we looked at time series data for each project site (Fulton, Pinkut, Nadina, Weaver) and for each life stage (fry, adult males, adult females). We used a clustering method that can line up patterns even when the timing doesn’t match perfectly (a technique called dynamic time warping) to measure how similar the trends were.
+To study how infection in returning adults affects IHNV prevalence in fry, we used a mixed effects binomial model for proportions that accounted for differences between spawning years and project sites.
+To study how fry infection affects infection in adults 3–4 years later, we used a similar model along with escapement data to calculate a weighted average of fry infection that matched the makeup of the returning adult population. Because the relationship wasn’t linear, we also added a quadratic term to better capture the pattern.
+*Results* 
+From 1987 to 2018, a total of 56,692 sockeye salmon were screened for IHNV. Over this 32 year timeframe, the prevalence of IHNV infections varied annually within and between the four stocks sampled (Figure 2). Across the entire dataset, there was a positive correlation between the detection of IHNV in male and female samples; with the prevalence being generally higher in females than in males (Figure 3).  Nonetheless, this prevalence in spawned females was not demonstrative of what was observed in fry, as there were numerous years where IHNV was not detected in the fry despite high prevalence in the broodstock.  However, it appears as though the IHNV prevalence in fry is a strong predictor of the population’s IHNV status upon returning adults 4 years later.  For instance, fry with 50% IHNV prevalence are predicted to return as adults with a prevalence of 30 to 80% (Figure 4).  </t>
+  </si>
+  <si>
+    <t>This work provides the first long-term dataset of infectious hematopoietic necrosis virus (IHNV) prevalence among various sockeye salmon stocks in British Columbia and reveals a highly dynamic nature of this deadly virus.  From this data, it was learned that when surveying adult fish, it is best to sample females as they have the highest prevalence. In naturally spawning populations of sockeye salmon, it was found that the IHNV prevalence in broodstock offers little insight into the infection status of fry, as true parent to progeny transmission is unlikely.  In many instances, high IHNV prevalence in adults did not result in the occurrence of virus in fry.  However, unexpectedly it was discovered that IHNV prevalence in fry is significantly correlated to the prevalence of returning adults, suggesting IHNV in adults is partially explained by their status as fry and supports the role of a lifelong IHNV carrier state in perpetuating IHNV in sockeye salmon populations.</t>
+  </si>
+  <si>
+    <t>This work illustrates the importance of long-term datasets in differentiating genuine trends from short term fluctuations and to uncover complex ecological dynamics. Analysis of IHNV prevalence across the four stocks over the 32 year timeframe revealed that prevalence across stocks is most similar within a river system, suggesting watershed or regional specific factors may influence level of IHNV in the system (Figure 5).  Nonetheless, a shared prolonged reduction of IHNV observed across both Fraser and Skeena watersheds, suggests broader oceanic factor(s) are contributing to the occurrence of IHNV in sockeye salmon (Figure 2).  Given these trends, we are presently gathering environmental, management and other data to determine if there are correlates that are explanatory for these trends.  In particularly, we are employing Pacea, an R package of ecosystem information, to  link biological data with environmental variable to generate models and visualizations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figure 1. Map showing the locations of the sockeye Salmon spawning channels (red circles) within the Skeena and Fraser River watersheds, revealed by blue and olive shading; respectively. 
+Figure 2. Annual prevalence of IHNV in adults (grey) and fry (black) sockeye salmon collected over 32 years from spawning channels located at Fulton River, Pinkut Creek, Nadina River and Weaver Creek.  Blue shading highlights years where IHNV prevalence was generally lower across all four collection sites.
+Figure 3.  Plot illustrating a positive relationship between IHNV prevalence in males (y-axis) and females (x-axis)
+Figure 4. Plot illustrating the predicted IHNV prevalence in returning adult sockeye salmon to Fulton River Spawning Channel based on IHNV prevalence in fry. Grey shading represents 95% confidence intervals.
+Figure 5. Cluster diagram illustrating similarities in IHNV prevalence of adult female sockeye salmon across spawning channels over a 32 year time period. </t>
+  </si>
+  <si>
+    <t>Infectious hematopoietic necrosis virus (IHNV) is a deadly virus of sockeye salmon, causing catastrophic losses during the early lifestages.  Long-term monitoring of IHNV infections across multiple stocks of sockeye salmon has revealed the prevalence of IHNV infections can vary annually within and between stocks; however, the factor(s) responsible for such fluctuations in IHNV prevalence in sockeye salmon stocks in British Columbia remain unresolved. Understanding the drivers behind the occurrence and perpetuation of IHNV in sockeye salmon is instrumental in managing and mitigating the risk of this endemic pathogen. Utilizing epidemiological analytical approaches to study the patterns of IHNV in sockeye salmon we’ll identify the factors which influence the prevalence of the virus in BC sockeye salmon stocks.</t>
+  </si>
+  <si>
+    <t>Table 1. Results of total thiamine levels detected in chinook salmon eggs treated or untreated with thiamine. 
+Figure 1. Results of linear regression analysis on the total mean thiamine level results reported by SUNY Brockport  and PSEC on the same set of chinook salmon eggs. Each dot represents an individual sample. 
+Figure 2. Results of the total thiamine levels in untreated and unfertilized eggs collected from Capilano mid coho (Cap-mid-Coho, n=5), Chilliwack mid coho (Cwk-mid-Coho, n=10), Tenderfoot Cheakamus Chinook (Tdf-Chinook, n=4), Chilliwack fall Chinook (Cwk-Chinook, n=10), Harrison sockeye (Har-Sockeye, n=10), Chilko sockeye (Cko-Sockeye, n=10), Weaver sockeye (Wvr-Sockeye, n=9) and Chehalis pink (Chs-Pink, n=11). Note that the Harrison sockeye eggs were considered not ripe during sample collection; Tenderfoot Cheakamus Chinook data came from results of untreated eggs reported in Table 1. The dash lines represent thiamine level thresholds established by Mantua et al. (2025) to illustrate the likelihood of being impacted by thiamine deficiency: high - unlikely impacted (&gt; 7.7 nmol/g), intermediate - likely impacted (5.9-7.7 nmol/g), low - impacted (2.7-5.9 nmol/g) and critically low - severely impacted (&lt; 2.7 nmol/g). The cross symbol (×) in the box plot indicates mean values within each group. 
+Figure 3. Proportion of salmon eggs from different populations measured by the thiamine level thresholds established by Mantua et al. (2025). Different category of total thiamine level represents different likelihood of being impacted by thiamine deficiency: high - unlikely impacted (&gt; 7.7 nmol/g), intermediate - likely impacted (5.9-7.7 nmol/g), low - impacted (2.7-5.9 nmol/g) and critically low - severely impacted (&lt; 2.7 nmol/g). Eggs were collected from different salmon species and population: Capilano mid coho (n=5), Chilliwack mid coho (n=10), Tenderfoot Cheakamus Chinook (n=4), Chilliwack fall Chinook (n=10), Harrison sockeye (n=10), Chilko sockeye (n=10), Weaver sockeye (n=9) and Chehalis pink (n=11).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">These activities will all inform the San Juan Chinook Rebuilding Plan in development by PFN, which will be linked to the broader WCVI Chinook Rebuilding Plan recently developed by DFO (required under the Fish Stock Provisions Act for naturally-produced WCVI Chinook) (DFO 2025). This project will also inform a risk assessment re-scoring expected to happen in 2026, where new information from PSSI projects will be used to re-evaluate the most prominent bottlenecks to WCVI Chinook survival and recovery. The first round WCVI Chinook risk assessment process identified several knowledge gaps, mostly related to early freshwater and marine life cycle stages. For San Juan Chinook specifically, juvenile data from these life stages (and interactions between hatchery and wild juveniles) are sparse, and biological data on natural spawners (e.g., age, origin) are limited.
+These reasons made the San Juan River a good candidate to develop an integrated life history monitoring program in alignment with the larger Follow The Fish program. We focused on activities complemented Pacheedaht First Nation’s established juvenile monitoring programs. First, we operated a rotary screw trap program to enumerate and sample naturally-produced out-migrating juveniles (all species, but focused on juvenile Chinook migration timing) in the freshwater environment, allowing us to compare natural migration timing to hatchery release timing, gather baseline biological traits relative to hatchery releases (e.g., size, condition), and estimate fry outmigration abundance. Otolith and stomach samples are also collected from a sub-sample of individuals to assess size-specific survival and diet contents. Second, we collected samples from Pacheedaht’s estuary beach seine program to continue examining diet differences and estuary residency (via otolith microchemistry) between hatchery and natural-origin Chinook. Finally, we conducted biweekly purse seining in Port San Juan (PFMA 20-2) through the late spring, summer and fall months (~May-October) to collect mixed-stock information, including hatchery/natural-origin of juvenile Chinook, stock ID, biological traits, relative abundance, and information on other species schooling with Chinook (e.g., coho, Pacific herring). As with the RST and beach seine, we also collected otoliths and stomach contents from a sub-sample of Chinook encountered. Finally, we developed a biosampling plan to assess age and stock composition of naturally-spawning adult Chinook (a deadpitch program). Current information on the Proportion of Natural Influence (PNI) is limited only to broodstock sampling, but it is unknown whether these samples are biased and whether they are representative of the river spawning component of the population. It is critical to have an accurate representation of PNI and age and composition-at-return to assess productivity trends and hatchery release strategies for rebuilding San Juan Chinook.
+All work was done in collaboration with Pacheedaht First Nation. Their Fisheries Team lead the majority of the field work and sample collection, as well as advised on sampling designs and salmon dynamics to improve the study design of the project. </t>
+  </si>
+  <si>
+    <t>Fisheries and Oceans Canada (DFO). 2025. Rebuilding plan: West Coast of Vancouver Island Chinook Salmon, *Oncorhynchus tshawytscha*, Suuhaa | SȾOKI | sat’sam. Rebuilding Plan. 50 p. https://publications.gc.ca/collections/collection_2025/mpo-dfo/Fs144-87-2025-eng.pdf</t>
+  </si>
+  <si>
+    <t>These two projects provide several novel insights into epigenetic variation in Pacific salmon. The Chinook salmon datasets summarized above represent the most comprehensive efforts to date to characterize differences in DNA methylation between hatchery- and natural-origin fish in this species and have clearly established that common effects of hatchery rearing across facilities are rare. The coho salmon study is the first, to our knowledge, to assess inheritance of epigenetic variation in Pacific salmon, confirming the potential for persistence of hatchery-mediated epigenetic effects across generations in enhanced populations. These results highlight the key need to develop understanding of the relationships between hatchery practices and different methylation patterns, the functional consequences of differences in methylation, and the potential adjustments in hatcheries that could mitigate these effects.
+There are four main sources of uncertainty for the findings of these projects. First, although the results above are suggestive that epigenetic differences are an important consequence of hatchery rearing and differences in performance between hatchery- and natural-origin salmon, the functional effects of the methylation differences summarized above remain to be established. Second, the extent to which methylation patterns in fin tissue capture those that may underlie differences in performance also remain to be established. Third, the inheritance of DNA methylation patterns demonstrated above requires testing and validation under hatchery and natural conditions; this validation is a key aspect of linking hatchery-mediated epigenetic changes to potential long-term fitness impacts. Fourth, the utility of epigenetic biomarkers for tracking hatchery origin or age in Chinook and coho salmon remains to be tested, as the high degree of population-specific patterns detected in these projects delayed biomarker development.</t>
+  </si>
+  <si>
+    <t>Future studies should address the uncertainties described above by performing physiological tests of the impacts of DNA methylation on performance in Chinook and coho salmon, and by using parentage-based tagging to assess parent-offspring methylation patterns outside of laboratory settings. Additionally, a proof of concept study for epigenetic biomarkers of hatchery origin and age in a key population would further improve the utility of the results summarized here. Operationalization of these findings will require not only proof of concept efforts, but also manipulative experiments to assess alternative rearing strategies and their impacts on DNA methylation, which will then inform scientific best practices that mitigate the fitness risks associated with enhancement in Pacific salmon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Hatchery and natural habitats favour different traits in Pacific salmon, and consistent with this, performance differences between hatchery- and natural-origin salmon are often observed in nature with natural-origin fish tending to outperform their hatchery counterparts.
+•	Despite this, when hatchery programs are integrated with the natural component of the population, detection of genetic differences between hatchery- and natural-origin fish is rare.
+•	In contrast, epigenetic differences, such as the addition or removal of methyl groups from DNA (i.e., DNA methylation), between hatchery- and natural-origin salmonids have recently been characterized in several species and populations.
+•	These epigenetic differences may underlie hatchery effects on performance in Pacific salmon, and have the potential to be inherited across generations, which would pose a long-term fitness risk to enhanced populations.
+•	These projects represent the most comprehensive study of variation in DNA methylation across hatcheries in Pacific salmon to date, assessing (1) the consistency of differences in DNA methylation across hatcheries, (2) the extent to which these differences are inherited by the offspring of hatchery-origin fish, and (3) the potential for development of epigenetic biomarkers for the management of hatchery effects in enhanced populations.
+•	Differences in DNA methylation between hatchery- and natural-origin Chinook or coho salmon were observed in every population examined, but essentially all patterns with population- or hatchery-specific.
+•	In outmigrating smolts, hatchery rearing strategies impacted DNA methylation patterns with juveniles reared with slower growth rates and released at smaller sizes showing patterns less divergent from natural epigenetic signatures than those observed in traditional hatchery releases.
+•	As expected, tissue-type had substantial effects on DNA methylation even between different fins, and although fin tissue captured some of the differences in methylation detected in other tissues, the majority of patterns were tissue-specific.
+•	Consistent with potential long-term effects of hatchery-mediated epigenetic variation, there was evidence of inheritance of DNA methylation patterns from hatchery parents to their offspring in controlled crosses, but the mode of inheritance varied depending on the region of the genome assessed.
+•	Taken together, these projects clearly confirm that epigenetic effects of hatchery rearing are likely mechanisms underlying hatchery effects on performance in Pacific salmon, although these patterns are generally population-specific such that development of widely applicable epigenetic biomarkers for hatchery-origin is unlikely to be possible.
+•	Instead the findings of these projects suggest that understanding how hatchery practices modify epigenetic variation in Chinook and coho salmon may guide modifications to reduce hatchery impacts in the future, and that population-specific biomarkers are likely to have utility when desired. </t>
+  </si>
+  <si>
+    <t>Enhancement of Pacific salmon through hatchery production is a key component of supporting salmon populations. Objectives of hatchery enhancement span conserving at-risk stocks, rebuilding lower abundance stocks, providing harvest opportunities and increasing public awareness through outreach and education. However, there are also risks associated with hatchery enhancement; differences between a hatchery and a natural habitat affect both the genetic and environmental factors that shape the performance and fitness of salmon. Consequently, hatchery-origin salmon may be less suited to wild habitats than their natural-origin counterparts, and the presence of hatchery-origin fish on a natural spawning ground may reduce the fitness of a population overall. Despite the known risks and consequences of hatchery enhancement, major genetic differences between hatchery- and natural-origin salmonids as a result of hatchery-mediated selection or relaxed selection have generally not been observed in integrated populations. In contrast, substantial epigenetic differences have been detected between hatchery- and natural-origin Pacific salmonids.
+Epigenetic variants are structural changes to DNA without a change in the DNA sequence itself. For example, DNA methylation is a commonly studied epigenetic mechanism in which a methyl group (-CH3) is covalently added to a cytosine residue. These modifications to DNA can alter the function of the genome, particularly through the regulation of gene expression. Given the extent of previously observed variation in epigenetic signatures between hatchery- and natural-origin salmon, the functional effects of epigenetic variants are excellent candidates to underlie the fitness consequences associated with hatchery enhancement. Additionally, it is possible for hatchery epigenetic variants to be inherited by the offspring of hatchery-origin fish, which aligns with the potential for long-term reductions in population fitness as hatchery-origin fish spawn in natural habitats. The study of epigenetic variation in Pacific salmonids is relatively in its infancy, but epigenetic biomarkers are a promising tool to facilitate managing hatchery enhancement specifically and salmon fisheries generally. Critical knowledge gaps in the generation of these tools are that epigenetic differences between hatchery- and natural-origin Chinook salmon have not been well-characterized and the extent to which these patterns are inherited in Pacific salmon is unknown. These projects address both of these gaps using data for Chinook and coho salmon populations enhanced by the DFO Salmonid Enhancement Program (SEP).</t>
+  </si>
+  <si>
+    <t>Samples for these projects were obtained from fin tissues submitted to the Molecular Genetics Section as part of the parentage-based tagging (PBT) program in the SEP, or from additional sampling efforts for the Chehalis, Chilliwack and Sarita Rivers. DNA was isolated from all samples using standard laboratory protocols, and for a relatively small number of Chilliwack River Chinook tissues RNA was also isolated with standard protocols. All isolations were quantified and quality controlled prior to use in data generation. For whole-genome data, DNA or RNA was sent to Genome Quebec for enzymatic methylation sequencing or RNA sequencing, respectively. For screening of methylation patterns in candidate genome regions, high-resolution melt analyses were conducted following quantitative polymerase chain reactions (qPCR).
+Sequencing reads were trimmed, aligned to the corresponding species genome sequence, and filtered for alignment quality and duplicated sequences. Final alignments were used to call variation in DNA methylation at CpG sequences using MethylDackel v0.6.1. Differences in methylation were then assessed by multidimensional scaling analyses and differential methylation tests with DSS v2.50.1 using custom analysis scripts established for the projects. 
+The final analyses and manuscripts for these projects are in progress. The sequencing reads, methylation results and all other datasets will be submitted to public repositories on publication of the corresponding manuscripts. Similarly, all bioinformatic pipelines and scripts files will be publicly available through GitHub.
+Methylation patterns demonstrated substantial variation among different populations, and were also highly dependent on the tissue from which DNA was isolated even between adipose and caudal fins (see Figure 1 for example for Chinook salmon). In all populations and tissues, approximately 50-500 regions of the genome displayed differences in methylation between hatchery- and natural-origin fish (see Figure 2 for example for Atnarko River Chinook salmon), but these differences were essentially all population-specific. Within the Chilliwack River Fall Chinook population, differences in methylation between origins showed some consistency across two brood years, and although many differences in methylation were tissue-specific, a subset of patterns observed in fin tissues were detected in other tissues as well. Inheritance of parental methylation patterns was examined in Chehalis River coho salmon by assessing candidate regions with known differences between hatchery- and natural-origin parents. Inheritance of parental patterns was observed with some regions showing offspring methylation consistent with additive inheritance (intermediate between the parents) and other regions showing methylation patterns consistent with paternal dominance (methylation inherited from the father) (Figure 3).</t>
+  </si>
+  <si>
+    <t>Figure 1. Multidimensional scaling plot of variation in genome-wide DNA methylation among integrated populations of Chinook salmon. Points represent individual fish, and colours indicate populations. Ellipses show the 95% confidence limits for the distributions. DNA was isolated from adipose or caudal fins (adipose – Atnarko, Cheakamus, Salmon, Yakoun; caudal – Chilliwack Fall, Chilliwack Summer, Nicola, Sarita).
+Figure 2. Heatmap of differentially methylated regions between hatchery- (yellow) and natural-origin (blue) fish. Columns correspond to individuals and rows correspond to genomic regions. Methylation levels are shown by the white to steel blue colour scale. Females (grey) and males (black) are indicated by the top bar.
+Figure 3. Box plots for high-resolution melt analyses of offspring methylation patterns compared to parental methylation for two genomic regions. Offspring cross-types are shown as female x male parent with hatchery-origin x hatchery-origin (yellow), hatchery-origin x natural-origin (pale blue), natural-origin x hatchery-origin (pale yellow), and natural-origin x natural-origin (blue). Panel a displays a region showing a pattern similar to additive inheritance, whereas panel b displays a region demonstrating paternal dominance.</t>
+  </si>
+  <si>
+    <t>Chinook (Fall, Spring, and Summer), Coho (Fall)</t>
+  </si>
+  <si>
+    <t>Renibacterium salmoninarum, the causative agent of bacterial kidney disease (BKD), is endemic to the Pacific Northwest. Infection with this bacterial pathogen can result in significant morbidity and mortality in cultured juvenile Pacific salmon. Current BKD management relies on screening brood stock using an enzyme-linked immunosorbent assay (ELISA) and excluding eggs from females exceeding the defined optical density (OD) threshold. This approach has significantly reduced the incidence of disease in both hatchery-reared juveniles and returning adult fish. The Salmonid Enhancement Program (SEP) maintains an extensive dataset that includes 16 years of ELISA broodstock screening results for many Vancouver Island and mainland coho and Chinook stocks. 
+These datasets have not been previously subjected to a comprehensive epidemiological analysis to identify potential explanatory variables for BKD prevalence in stocks of concern. This project sought to address that knowledge gap by integrating ELISA data and linking broodstock ELISA values to Parental Based Tagging (PBT) information enabling stock-specific analyses. The work was conducted through a collaborative partnership among the Science Branch, SEP, and Aquaculture Management.</t>
+  </si>
+  <si>
+    <t>The study explored the relationship between parental BKD levels on individual salmon results while controlling for the impact of environmental factors such as thermal regimes by incorporating various temperature metrics, such as average temperature, minimum and maximum temperatures, degree days, and the number of days within specific temperature thresholds (6°C to 10°C). While Nitinat's temperature data was based on monthly or daily mean temperatures (depending on the year), Puntledge and Spius provided daily mean, maximum, and minimum temperatures. For each stock year, temperature data were filtered to include dates that a stock occupied the hatchery, e.g. the day of first broodstock captured to the day of last juvenile release. Juveniles of Chinook stocks were released less than a year of holding at the hatchery at Puntledge and after two years at Spius, while coho stocks were released after 1 year and 2 year but temperature measurements were calculated based on the 2 year release for coho stocks. 
+Data used in the analysis was from 2014 through 2023, and was dependent on data available in E-PRO and temperature data (Table 1). Only individuals with BKD value and maturity class information were included. Incomplete data points were filtrated out in each analysis. Dam’s BKD optical density (OD) value and BKD level were attached to E-PRO records for progenies by matching progenies’ dam DNA code to the dam’s data in the report. This step was only possible for progenies with dam’s DNA code and BKD OD value. 
+To guide the modelling of the vertical transmission path, we collaborated with an expert panel to develop a causal diagram (Figure 1). This exercise facilitated the identification and characterization of relationships across multiple scales, including the watershed, hatchery, and individual fish levels, while specifically assessing variables for their potential to confound the results. We evaluated these factors using a mixed-effects generalized linear model framework, designating the OD from the BKD ELISA as the outcome of interest and the OD of the progenitor (the dam) as the primary predictor. Temporal variation was integrated as a random effect to account for annual fluctuations. The final model incorporated several confounding factors, most notably the specific watershed of origin. We also included terms for interactions between mean temperature—which was scaled and centered by creek—and BKD prevalence at the stock level. For the purposes of this analysis, a stock was defined as a cohort of brood fish of the same species returning to the same creek during the same season, such as Nitinat spring coho. While species and season were initially tested, they were excluded from the final model as they were not statistically significant and did not meet the criteria for confounders; their observed effects were largely captured by spatial and temporal variables.
+*Research Findings*
+The primary analysis indicates that BKD levels in returning adults do not demonstrate a significant association with the OD levels of their progenitors. Instead, the relationship appears to be confounded by environmental and population-level factors, including water temperature, specific watershed characteristics, and the overall BKD prevalence within the returning population. For instance, while the watershed variable was not statistically significant in isolation, its inclusion in the model resulted in a measurable change in the coefficient of the primary predictor, suggesting a latent environmental influence. A more notable finding was the negative association between BKD levels and scaled temperature, which suggests that OD levels generally decrease as temperatures increase. However, a significant interaction between temperature and BKD prevalence indicates a modulating effect on this relationship (Figure 2). While lower temperatures appear to provide a more suitable environment for the transmission of BKD, a higher proportion of infected individuals within a population further intensifies this effect.
+It is important to note, however, that the statistical model demonstrated a relatively low goodness-of-fit, indicating that a substantial portion of the variance in BKD levels remains unexplained by the variables currently under study. This suggests that the dynamics of BKD in these ecosystems are influenced by a complex array of factors—potentially including individual host immunity, varying hatchery practices, or additional environmental stressors—that were not fully captured in the present framework. Consequently, while the identified trends regarding temperature and prevalence offer valuable directional insights, they should be interpreted with caution and viewed as preliminary findings within a highly variable biological system.</t>
+  </si>
+  <si>
+    <t>Table 1. Stocks and cohorts used in this analysis as well as the years of available data for BKD screening, progenitor DNA, and temperature.
+Figure 1. Directed Acyclic Graph (DAG) of the causal web explaining OD results for BKD. Arrows represent plausible unidirectional associations between factors considered for the epidemiological model as identified and characterized by the experts panel.  
+Figure 2. Interaction between the effects of Scaled Temperature and BKD Prevalence. Predicted values are derived from our linear mixed-effects model accounting for year to year variation. The scaled temperature is plotted on the x-axis against the OD for BKD (y-axis), with separate lines representing 20% (red) and 80% (blue) BKD prevalence in the returning population. Shaded regions of corresponding colours represent 95% confidence intervals.</t>
+  </si>
+  <si>
+    <t>The findings reveal key knowledge gaps in understanding BKD dynamics, suggesting the need for further research to build a fuller picture of the factors influencing disease transmission and prevalence. The low goodness-of-fit of the current model indicates that additional variables, such as hatchery practices, genetic diversity, or other environmental and anthropogenic stressors, may play significant roles in shaping BKD dynamics. A promising avenue for research includes the use of simulation models to assess the impact of altering management practices, such as raising or lowering the positive-negative culling threshold OD value. This approach could help predict how adjustments to culling thresholds might influence disease prevalence and population outcomes under varying environmental conditions. Research should also focus on understanding potential thresholds or tipping points where environmental conditions, such as temperature extremes, significantly influence disease prevalence and outcomes.
+The study’s findings can inform proactive strategies for salmon conservation and management, particularly concerning how environmental conditions affect BKD prevalence. Managers could prioritize monitoring in watersheds where conditions, including temperature and BKD prevalence, elevate disease transmission risks. Additionally, the insights from simulations examining the effect of changing the positive-negative culling threshold OD value could guide policy and operational decisions to strike a balance between limiting disease spread and optimizing population sustainability.</t>
+  </si>
+  <si>
+    <t>This project contributes significant clarity to the understanding of BKD transmission by identifying that environmental and population-level factors often overshadow direct parent-to-offspring transmission in wild and enhanced stocks. By demonstrating that BKD levels in returning adults are more closely associated with watershed characteristics and thermal regimes than with the status of their progenitors, this research shifts the focus toward environmental stressors as primary drivers of disease expression. These findings highlight a critical pathway of effect where colder water temperatures facilitate higher pathogen loads, a relationship that is further intensified by the cumulative impact of high disease prevalence within the population. This identification of thermal and density-dependent "modulating effects" provides a more nuanced understanding of how multiple stressors interact to influence the health of salmon cohorts.
+From a management and policy perspective, these insights inform risk assessment and hatchery planning by emphasizing that individual-level screening of broodstock may be insufficient without considering broader ecological context. The study provides a framework for evidence-based decisions regarding stock transfers and watershed-specific management, suggesting that biologically significant thresholds for disease may vary depending on local environmental conditions. By accounting for these spatial and temporal variables, managers can better navigate the trade-offs between enhancement goals and the risks of disease outbreaks.
+A primary source of uncertainty in this analysis, however, stems from the operational protocols used to manage BKD in hatcheries. The standard practice of utilizing OD thresholds to cull high-risk eggs creates a filtered data set, as the most heavily infected vertical transmission paths are often removed from the population before they can be assessed in returning adults. Furthermore, when conservation concerns for at-risk populations supersede these culling protocols, it introduces additional variability into the transmission pathway. This management-induced selection bias limits our ability to fully quantify the role of vertical transmission, as the observed returning population primarily represents individuals that either passed through a selective screening process or were spared due to conservation priorities.</t>
+  </si>
+  <si>
+    <t>- Thiamine deficiency complex (TDC) is an emerging concern in Pacific salmon, potentially contributing to en route and prespawn adult mortality and elevated fry mortality, yet little is known about the prevalence of TDC in Canadian Pacific salmon populations.
+- This project established thiamine analysis capability for fish tissues (e.g. eggs, plasma, muscle, liver) by the Nutrition lab at the DFO Pacific Science Enterprise Centre (PSEC).
+- Preliminary data discovered that total thiamine levels in eggs of both coho and Chinook salmon in BC generally ranged from 6 – 13 nmol/g, most pink salmon contained 4 – 8 nmol/g, but most sockeye salmon eggs only contained 2 – 6 nmol/g, which suggests that some Pacific salmon populations in BC may exhibit TDC and warrant further monitoring.</t>
+  </si>
+  <si>
+    <t>Dr. Erika Eliason, Dr. Ian Forster, Greig Oldford</t>
+  </si>
+  <si>
+    <t>Chinook, Coho, Sockeye, Pink</t>
+  </si>
+  <si>
+    <t>Egg stage, adult</t>
+  </si>
+  <si>
+    <t>Thiamine (Vitamin B1) is an essential water soluble vitamin for fish, supporting physiological functions such as metabolism, immune, neuron and cardiac functions (Bâ 2008; Manzetti et al. 2014; Roman-Campos and Cruz 2014; Whitfield et al. 2018), normal development (Carvalho et al. 2009), growth (Reed et al. 2023; Lee et al. 2026) and reproductive success (Fitzsimons et al. 2005; Honeyfield et al. 2005; Mantua et al. 2025). In aquatic systems, thiamine is synthesized by bacteria and phytoplankton at the base of the food web (Croft et al. 2007; Tang et al. 2010; Paerl et al. 2015; Hylander et al. 2024; Suffridge et al. 2024), and fish obtain thiamine exclusively through their diet (Fridolfsson et al. 2018; Harder et al. 2018; Ejsmond et al. 2019; Hylander et al. 2024). Thiamine deficiency complex (TDC) is a syndrome that is caused by a chronic deficiency in thiamine, impacting salmon across the life cycle. In adult salmon, reduced swimming and migratory ability, and increased pre-spawn mortality have been linked to TDC (Brown et al. 2005a; Fitzsimons et al. 2005). For early-stage salmon fry hatched from thiamine-deficient eggs, symptoms include loss of equilibrium (Fitzsimons et al. 2005), abnormal swimming behaviour (i.e. swimming in a corkscrew pattern) (Mantua et al. 2025), impaired vision and foraging ability (Carvalho et al. 2009), and high mortality (Koski et al. 1999; Mantua et al. 2025). TDC is caused by low availability of thiamine in the diet and/or ingestion of prey high in thiaminase (enzyme that degrades thiamine, Fisher et al. 1998; Brown et al. 2005a; Honeyfield et al. 2005; Houde et al. 2015; Mantua et al. 2025). Both extrinsic (e.g. changing environmental conditions, variation in the migration experience) and intrinsic factors (e.g. species, size, sex, disease state) could further modulate fish thiamine levels.
+TDC has been linked to salmonid population declines globally, including Atlantic salmon Salmo salar in the Baltic Sea (Amcoff et al. 1999), lake trout Salvelinus namaycush in the Great Lakes (Ladago et al. 2020), and Chinook salmon in Alaska (Strasburger et al. 2023) and California (Mantua et al. 2025). However, there is little published information about the status of TDC in Pacific salmon, especially in British Columbia (BC), Canada (but see Welch et al. 2018). More research is thus urgently needed to investigate how thiamine status has been impacting Pacific salmon in BC, Canada. The objectives of this project were to: (1) establish thiamine analysis capacity at DFO to support studies and programs investigating the thiamine status of salmonids in Canada. Until this project, there were no Canadian labs providing thiamine analysis services, thus Canadian projects must rely on a few labs in the USA, creating a bottleneck (costly, delayed, sample loss risk) in thiamine analysis. (2) determine preliminary thiamine status in eggs collected from both wild and hatchery-derived stocks of Chinook salmon, coho salmon, pink salmon and sockeye salmon in BC. And (3) assess the effectiveness of thiamine treatment practices being tested at some DFO hatcheries. This research was conducted in collaboration with the Pelagic Ecosystem Lab at University of British Columbia (UBC), DFO Salmon Enhancement Program (SEP) and DFO Environmental Watch Program (EWATCH).</t>
+  </si>
+  <si>
+    <t>Thiamine analysis capacity was established by researchers in the Nutrition lab at the DFO Pacific Science Enterprise Centre (PSEC), based on the methodology of Brown et al. (1998) with expert advice from Dr. Jacques Rinchard from SUNY Brockport and Dr. Cody Pinger from National Oceanic and Atmospheric Administration (NOAA). To confirm the reliability of our analysis protocol, we analyzed 27 Chinook salmon egg samples collected in 2023 by Pelagic Ecosystem Lab at UBC and compared our results with those provided to UBC by the lab at SUNY Brockport. There was a strong and significant linear relationship (Fig 1; y = 0.8183 x – 0.4131) between SUNY Brockport and PSEC’s results on total mean thiamine levels (p &lt; 0.001) providing confidence that the methodology employed by PSEC is reliable and accurate. Overall, PSEC reported consistently lower total mean thiamine levels, especially lower TPP levels, compared to SUNY Brockport. This is not surprising given that PSEC conducted the analysis in 2025, almost 2 years later than SUNY Brockport. Given the sensitivity of thiamine (temperature, light, pH; Brown et al. 1998; Wright et al. 2005; Edwards et al. 2017; Rocchi et al. 2022), thiamine degradation in tissues is expected to occur over time with prolonged storage and multiple sample handing events. 
+Additional salmon samples from both hatcheries and the wild were collected to obtain baseline, preliminary data on the thiamine status of salmon in BC. Sample collection included: Chilliwack River hatchery coho salmon (N=10 females; eggs, plasma), Chilliwack River hatchery Chinook salmon (N=10 females; eggs, plasma), Capilano hatchery mid coho salmon (N=10 females; eggs), Harrison River sockeye salmon (N=10 females; eggs, ventricles, plasma), Chilko River sockeye salmon (N=10 females; eggs, ventricles, plasma), Weaver Creek sockeye salmon (N = 9, eggs, ventricles, plasma), Chehalis pink salmon (N = 11 females; eggs ). Tissues were immediately frozen (dry shipper or dry ice) and stored at -80oC until analysis. Ventricle and plasma analysis is ongoing, only egg data are presented here. Total thiamine levels were very similar in the Chinook and coho eggs assessed here (Figure 2), mostly ranging between 6 – 13 nmol/g. However, sockeye salmon eggs had much lower total thiamine levels of mostly 2 – 6 nmol/g, while total thiamine in pink salmon eggs mostly ranged from 4 – 8 nmol/g.  Using the thiamine thresholds as established by Mantua et al. (2025), 20 – 40% of each coho and Chinook salmon population are considered as being likely impacted by thiamine deficiency to some degree (&lt; 7.7 nmol/g; Figure 3). However, all sockeye salmon samples are below 7.7 nmol/g, with over 50 – 100% of eggs considered having low (2.7 -5.9 nmol/g) or critically low thiamine (&lt; 2.7 nmol/g) levels. For the Chehalis pink salmon population, 72% of samples are considered to be likely thiamine deficient (&lt; 7.7 nmol/g), with 45% of eggs in the low category (2.7 – 5.9 nmol/g; Figure 3).  
+To counteract the effects of TDC, thiamine supplementation is seen as an effective strategy to improve salmon reproduction success in hatcheries (Harder et al. 2025) and is currently implemented at a few DFO hatcheries. Current practices include injecting thiamine (500 mg thiamine hydrochloride) into broodfish ~12-25 days prior to spawning (Shuswap River hatchery) or immersing fertilized eggs in a static bath made of 1000 ppm thiamine mononitrate for 1 hour (Tenderfoot Creek hatchery, Capilano hatchery). We sampled thiamine-injection-treated eggs from Middle Shuswap Chinook salmon at Shuswap River hatchery (N=6, no control fish were available).We sampled both untreated (control) and thiamine-bath-treated eggs (immediately after the 1 h bath) from Cheakamus Chinook salmon at Tenderfoot Creek hatchery (N=4 females), early coho (N=20 females) , mid coho salmon (N=20 females) and late coho salmon (N=20 females) from Capilano hatchery. In addition, thiamine-bath treated eggs were sampled ~1 month post-fertilization in coho salmon from Capilano hatchery (N= 400 eggs each for early, mid and late coho; eggs from different females were mixed; no control fish were available).
+Thiamine injection-treatment (Middle Shuswap Chinook salmon at Shuswap River hatchery) produced eggs with total thiamine levels ranging between 16-27 nmol/g (Table 1). While there are no control fish for comparison, these levels are above egg thiamine levels in untreated eggs from other locations (Tenderfoot and Chilliwack hatchery Chinook salmon, Figure 2). This suggests that the thiamine injection treatment likely was effective at increasing total thiamine levels in the eggs. Unfortunately, the effectiveness of the thiamine bath treatment (Tenderfoot Creek hatchery and Capilano hatchery) could not be resolved here. Sampling eggs immediately following the 1 h thiamine bath treatment resulted in extremely elevated and highly variable total thiamine levels (range = 256.8 – 327.0 nmol/g). In fact, we were unable to determine accurate total thiamine levels for the bath-treated samples from Capilano, as the results were contradictory (i.e. varying from 0.95 – 291.20 nmol/g). While we reported consistently high total thiamine from bath-treated eggs from Tenderfoot Creek Hatchery, these levels are not biologically reasonable and were likely produced by excess thiamine associated with the bath. Given this, we sampled some eggs ~1 month post bath treatment from Capilano Hatchery and found levels to vary among batches (early coho batch#1: 0.90 ± 0.06, batch #2: 2.49 ± 0.60; mid coho batch#1: 3.86 ± 1.18; N=5 tests, unit = nmol/g). However, without control, un-treated eggs at the same life stage, we are unable to assess whether the thiamine bath treatment was successful at increasing thiamine levels in these eggs.</t>
+  </si>
+  <si>
+    <t>This project successfully established thiamine analysis capability at PSEC, which is currently the only known laboratory in Canada conducting these analyses. A detailed protocol outlining the equipment, consumables and procedural steps is available for distribution to other research groups at DFO to set up the same analysis capacity. Our lab at PSEC is currently welcoming thiamine analysis requests and collaborative projects to support research programs monitoring the thiamine status of Pacific salmon and their prey in Canada. 
+The thiamine levels in coho and Chinook salmon eggs were within the expected range, consistent with previous work on Chinook salmon in Alaska (Honeyfield et al. 2016; Larson and Howard 2019) and California (Mantua et al. 2025), and preliminary data available for BC (Lerner and McLaskey 2024). Notably, the relatively wide range of thiamine levels suggests considerable variation among individuals within each population. Future studies should consider increasing the sample size from each population (i.e. &gt;10 fish per population) to have a more precise estimate of salmon thiamine status. In contrast, the total thiamine amounts in sockeye salmon eggs from Weaver Creek, Harrison and Chilko River were less variable, but also had lower levels (mostly within 2 – 6 nmol/g). While the Harrison River samples were considered not fully ripe, the thiamine levels in these eggs were similar to those of fully ripe fish in Chilko River. Notably, a previous study found much higher total thiamine levels in eggs of sockeye salmon from Harrison River, and pink salmon from Seton River in 2015 (sockeye: 10.9 ± 1.2 nmol/g, n = 5; pink: 19.5 ± 2.3 nmol/g, n=20; Welch et al., 2018). The cause of these differences in thiamine levels between studies of the same population conducted ~10 years apart is unknown, but may be related to changes in prey (and thus dietary thiamine/thiaminase levels), changing ocean or migration conditions or other factors not identified. 
+Based on the thiamine thresholds by Mantua et al. (2025), 20 – 40 % of the eggs analyzed from each coho and Chinook salmon population in this study, are considered to be likely impacted by thiamine deficiency (Figure 3). However, the total thiamine in all eggs from sockeye salmon from both Harrison and Chilko River are well below this threshold, and only 27% of Chehalis pink salmon eggs were above it. It must also be noted that the threshold from Mantua et al. (2025) is set based on Chinook salmon, but the susceptibility to TDC, or thiamine threshold, is likely species-specific (Brown et al. 2005b; Fitzsimons et al. 2007; Honeyfield et al. 2008; Harder et al. 2018). To our knowledge, there are no published data on thiamine status of sockeye and pink salmon other than Welch et al. (2018). Future research should track thiamine status of Pacific salmon in BC, especially sockeye salmon. 
+The broodfish-thiamine-injection method appeared to effectively improve the total thiamine levels, mostly in form of TH, in Chinook salmon eggs. Although there were no untreated, control eggs available as a comparison at Shuswap River Hatchery, the injection-treated eggs (20.5 ± 4.8 nmol/g, range from 16 - 27 nmol/g) contained up to 2 – 3 times the usual thiamine amount in untreated eggs of other Chinook salmon stocks (Figure 2 and 3, 6 – 13 nmol/g). The total thiamine levels in eggs from these injection-treated fish are within the range reported for similar studies on coho salmon (21.925 ±1.694 nmol/g, Fitzsimons et al., 2005) and steelhead trout Oncorhynchus mykiss (total thiamine 20.4 ± 11.3 nmol/g; Futia et al 2017; mean total thiamine: 33.5 nmol/g, range: 15.4 – 51.1 nmol/g; Reed et al 2023). Unfortunately, our study could not resolve the effectiveness of thiamine bath-treated eggs because of supra-biological and varying levels measured in eggs sampled immediately after the 1 h treatment bath (e.g. 302.5 ± 31.2 nmol/g in Chinook salmon at Tenderfoot Creek hatchery; 0.95 – 291.20 nmol/g in mid coho salmon eggs at Capilano Hatchery). Thus, it was unknown how much of the thiamine was actually retained and biologically available to the eggs over time. Future work should resolve the effectiveness and necessity of these thiamine treatments, as these methods could prove highly valuable in both minimizing the potential negative impacts of TDC on early fry and optimizing hatchery salmon production (Futia et al. 2017; Reed et al. 2023; Harder et al. 2025).</t>
+  </si>
+  <si>
+    <t>Amcoff, P., Börjeson, H., Landergren, P., Vallin, L., and Norrgren, L. 1999. Thiamine (vitamin B1) concentrations in salmon (Salmo salar), brown trout (Salmo trutta) and cod (Gadus morhua) from the Baltic Sea. Ambio 28(1): 48–54.
+Bâ, A. 2008. Metabolic and structural role of thiamine in nervous tissues. Cell. Mol. Neurobiol. 28(7): 923–931. doi:10.1007/s10571-008-9297-7.
+Brown, S.B., Fitzsimons, J.D., Honeyfield, D.C., and Tillitt, D.E. 2005a. Implications of thiamine deficiency in Great Lakes salmonines. J. Aquat. Anim. Health 17(1): 113–124. doi:10.1577/H04-015.1.
+Brown, S.B., Honeyfield, D.C., Hnath, J.G., Wolgamood, M., Marcquenski, S. V., Fitzsimons, J.D., and Tillitt, D.E. 2005b. Thiamine status in adult salmonines in the Great Lakes. J. Aquat. Anim. Health 17(1): 59–64. doi:10.1577/H04-059.1.
+Brown, S.B., Honeyfield, D.C., and Vandenbyllaardt, L. 1998. Thiamine analysis in fish tissues. Am. Fish. Soc. Sumpos. 21(January 1998): 73–81.
+Carvalho, P.S.M., Tillitt, D.E., Zajicek, J.L., Claunch, R.A., Honeyfield, D.C., Fitzsimons, J.D., and Brown, S.B. 2009. Thiamine deficiency effects on the vision and foraging ability of lake trout fry. J. Aquat. Anim. Health 21(4): 315–325. doi:10.1577/H08-025.1.
+Croft, M.T., Moulin, M., Webb, M.E., and Smith, A.G. 2007. Thiamine biosynthesis in algae is regulated by riboswitches. Proc. Natl. Acad. Sci. U. S. A. 104(52): 20770–20775. doi:10.1073/pnas.0705786105.
+Edwards, K.A., Tu-Maung, N., Cheng, K., Wang, B., Baeumner, A.J., and Kraft, C.E. 2017. Thiamine Assays—Advances, Challenges, and Caveats. ChemistryOpen 6(2): 178–191. doi:10.1002/open.201600160.
+Ejsmond, M.J., Blackburn, N., Fridolfsson, E., Haecky, P., Andersson, A., Casini, M., Belgrano, A., and Hylander, S. 2019. Modeling vitamin B1 transfer to consumers in the aquatic food web. Sci. Rep. 9(1): 1–11. Springer US. doi:10.1038/s41598-019-46422-2.
+Fisher, J.P., Brown, S.B., Wooster, G.W., and Bowser, P.R. 1998. Maternal blood, egg and larval thiamin levels correlate with larval survival in landlocked Atlantic salmon (Salmo salar). J. Nutr. 128(12): 2456–2466. American Society for Nutrition. doi:10.1093/jn/128.12.2456.
+Fitzsimons, J.D., Williston, B., Amcoff, P., Balk, L., Pecor, C., Ketola, H.G., Hinterkopf, J.P., and Honeyfield, D.C. 2005. The effect of thiamine injection on upstream migration, survival, and thiamine status of putative thiamine-deficient coho salmon. J. Aquat. Anim. Health 17(1): 48–58. doi:10.1577/H04-003.1.
+Fitzsimons, J.D., Williston, B., Williston, G., Brown, L., El-Shaarawi, A., Vandenbyllaardt, L., Honeyfeld, D., Tillitt, D., Wolgamood, M., and Brown, S.B. 2007. Egg thiamine status of Lake Ontario salmonines 1995-2004 with emphasis on lake trout. J. Great Lakes Res. 33(1): 93–103. Elsevier. doi:10.3394/0380-1330(2007)33[93:ETSOLO]2.0.CO;2.
+Fridolfsson, E., Lindehoff, E., Legrand, C., and Hylander, S. 2018. Thiamin (vitamin B1) content in phytoplankton and zooplankton in the presence of filamentous cyanobacteria. Limnol. Oceanogr. 63(6): 2423–2435. doi:10.1002/lno.10949.
+Futia, M.H., Hallenbeck, S., Noyes, A.D., Honeyfield, D.C., Eckerlin, G.E., and Rinchard, J. 2017. Thiamine deficiency and the effectiveness of thiamine treatments through broodstock injections and egg immersion on Lake Ontario steelhead trout. J. Great Lakes Res. 43(2): 352–358. doi:10.1016/j.jglr.2017.01.001.
+Harder, A.M., Ardren, W.R., Evans, A.N., Futia, M.H., Kraft, C.E., Marsden, J.E., Richter, C.A., Rinchard, J., Tillitt, D.E., and Christie, M.R. 2018. Thiamine deficiency in fishes: causes, consequences, and potential solutions. Rev. Fish Biol. Fish. 28(4): 865–886. Springer International Publishing. doi:10.1007/s11160-018-9538-x.
+Harder, A.M., Reed, A.N., and Rowland, F.E. 2025. Evolutionary perspectives on thiamine supplementation of managed Pacific salmonid populations. Can. J. Fish. Aquat. Sci. 82(Bettendorff 2013): 1–10. doi:10.1139/cjfas-2024-0109.
+Honeyfield, D.C., Hinterkopf, J.P., Fitzsimons, J.D., Tillitt, D.E., Zajicek, J.L., and Brown, S.B. 2005. Development of thiamine deficiencies and early mortality syndrome in lake trout by feeding experimental and feral fish diets containing thiaminase. J. Aquat. Anim. Health 17(1): 4–12. doi:10.1577/H03-078.1.
+Honeyfield, D.C., Murphy, J.M., Howard, K.G., Strasburger, W.W., and Matz, A.C. 2016. An Exploratory Assessment of Thiamine Status in Western Alaska Chinook Salmon (Oncorhynchus tshawytscha). North Pacific Anadromous Fish Comm. Bull. (6): 21–31.
+Honeyfield, D.C., Peters, A.K., and Jones, M.L. 2008. Thiamine and fatty acid content of Lake Michigan Chinook salmon. J. Great Lakes Res. 34(4): 581–589. Elsevier. doi:10.1016/s0380-1330(08)71603-4.
+Houde, A.L.S., Saez, P.J., Wilson, C.C., Bureau, D.P., and Neff, B.D. 2015. Effects of feeding high dietary thiaminase to sub-adult Atlantic salmon from three populations. J. Great Lakes Res. 41(3): 898–906. International Association for Great Lakes Research. doi:10.1016/j.jglr.2015.06.009.
+Hylander, S., Farnelid, H., Fridolfsson, E., Hauber, M.M., Todisco, V., Ejsmond, M.J., and Lindehoff, E. 2024. Thiamin (vitamin B1, thiamine) transfer in the aquatic food web from lower to higher trophic levels. In PLoS ONE. doi:10.1371/journal.pone.0308844.
+Koski, P., Pakarinen, M., Nakari, T., Soivio, A., and Hartikainen, K. 1999. Treatment with thiamine hydrochloride and astaxanthine for the prevention of yolk-sac mortality in Baltic salmon fry (M74 syndrome). Dis. Aquat. Organ. 37(3): 209–220. doi:10.3354/dao037209.
+Ladago, B.J., Futia, M.H., Ardren, W.R., Honeyfield, D.C., Kelsey, K.P., Kozel, C.L., Riley, S.C., Rinchard, J., Tillitt, D.E., Zajicek, J.L., and Marsden, J.E. 2020. Thiamine concentrations in lake trout and Atlantic salmon eggs during 14 years following the invasion of alewife in Lake Champlain. J. Great Lakes Res. 46(5): 1340–1348. International Association for Great Lakes Research. doi:10.1016/j.jglr.2020.06.018.
+Larson, S., and Howard, K. 2019. Exploration of AYK Chinook Salmon egg thiamine levels as a potential mechanism contributing to recent low productivity patterns, 2014 and 2015.
+Lee, Y., Kim, S., Hasanthi, M., Song, S., Kim, S., and Lee, K.J. 2026. Dietary thiamine supplementation enhances the growth performance, digestive enzyme activity, intestine development, immunity and anti-inflammatory gene expression of juvenile olive flounder (Paralichthys olivaceus). Comp. Biochem. Physiol. Part - B Biochem. Mol. Biol. 281(September 2025): 111162. Elsevier Inc. doi:10.1016/j.cbpb.2025.111162.
+Mantua, N.J., Bell, H., Todgham, A.E., Daniels, M.E., Rinchard, J., Ludwig, J.M., Field, J.C., Lindley, S.T., Rowland, F.E., Richter, C.A., Walters, D., Finney, B., Distajo, H.A.R., Tillitt, D., and Honeyfield, D.C. 2025. Widespread thiamine deficiency in California salmon linked to an anchovy- dominated marine prey base. Proc. Natl. Acad. Sci. 122(26): e2426011122. doi:10.1073/pnas.
+Manzetti, S., Zhang, J., and Van Der Spoel, D. 2014. Thiamin function, metabolism, uptake, and transport. Biochemistry 53(5): 821–835. doi:10.1021/bi401618y.
+Paerl, R.W., Bertrand, E.M., Allen, A.E., Palenik, B., and Azam, F. 2015. Vitamin B1 ecophysiology of marine picoeukaryotic algae: Strain-specific differences and a new role for bacteria in vitamin cycling. Limnol. Oceanogr. 60(1): 215–228. doi:10.1002/lno.10009.
+Reed, A.N., Rowland, F.E., Krajcik, J.A., and Tillitt, D.E. 2023. Thiamine Supplementation Improves Survival and Body Condition of Hatchery-Reared Steelhead (Oncorhynchus mykiss) in Oregon. Vet. Sci. 10(2): 1–11. doi:10.3390/vetsci10020156.
+Rocchi, R., van Kekem, K., Heijnis, W.H., and Smid, E.J. 2022. A simple, sensitive, and specific method for the extraction and determination of thiamine and thiamine phosphate esters in fresh yeast biomass. J. Microbiol. Methods 201(August): 106561. Elsevier B.V. doi:10.1016/j.mimet.2022.106561.
+Roman-Campos, D., and Cruz, J.S. 2014. Current aspects of thiamine deficiency on heart function. Life Sci. 98(1): 1–5. Elsevier Inc. doi:10.1016/j.lfs.2013.12.029.
+Strasburger, W.W., Honeyfield, D.C., Murphy, J.M., and Pinger, C. 2023. A Review of the Thiamine Status of Alaskan Chinook Stocks and the U . S . West Coast. Available from https://meetings.pices.int/Publications/Presentations/2022-SPF/S1-Strasburger.pdf.
+Suffridge, C.P., Shannon, K.C., Matthews, H., Johnson, R.C., Jeffres, C., Mantua, N., Ward, A.E., Holmes, E., Kindopp, J., Aidoo, M., and Colwell, F.S. 2024. Connecting thiamine availability to the microbial community composition in Chinook salmon spawning habitats of the Sacramento River basin. Appl. Environ. Microbiol. 90(1). American Society for Microbiology. doi:10.1128/aem.01760-23.
+Tang, Y.Z., Koch, F., and Gobler, C.J. 2010. Most harmful algal bloom species are vitamin B1 and B 12 auxotrophs. Proc. Natl. Acad. Sci. U. S. A. 107(48): 20756–20761. doi:10.1073/pnas.1009566107.
+Welch, D.W., Futia, M.H., Rinchard, J., Teffer, A.K., Miller, K.M., Hinch, S.G., and Honeyfield, D.C. 2018. Thiamine Levels in Muscle and Eggs of Adult Pacific Salmon from the Fraser River, British Columbia. J. Aquat. Anim. Health 30(3): 191–200. doi:10.1002/aah.10024.
+Whitfield, K.C., Bourassa, M.W., Adamolekun, B., Bergeron, G., Bettendorff, L., Brown, K.H., Cox, L., Fattal-Valevski, A., Fischer, P.R., Frank, E.L., Hiffler, L., Hlaing, L.M., Jefferds, M.E., Kapner, H., Kounnavong, S., Mousavi, M.P.S., Roth, D.E., Tsaloglou, M.N., Wieringa, F., and Combs, G.F. 2018. Thiamine deficiency disorders: diagnosis, prevalence, and a roadmap for global control programs. Ann. N. Y. Acad. Sci. 1430(1): 3–43. doi:10.1111/nyas.13919.
+Wright, G.M., Brown, S.B., Brown, L.R., Moore, K., Villella, M., Zajicek, J.L., Tillitt, D.E., Fitzsimons, J.D., and Honeyfield, D.C. 2005. Effect of sample handling on thiamine and thiaminolytic activity in alewife. J. Aquat. Anim. Health 17(1): 77–81. doi:10.1577/H03-074.1.</t>
   </si>
 </sst>
 </file>
@@ -3261,29 +3257,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="23">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3683,6 +3656,29 @@
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3697,30 +3693,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C1235FC-468F-46C3-9676-E136DE729105}" name="Table1" displayName="Table1" ref="A1:U44" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C1235FC-468F-46C3-9676-E136DE729105}" name="Table1" displayName="Table1" ref="A1:U44" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
   <autoFilter ref="A1:U44" xr:uid="{9C1235FC-468F-46C3-9676-E136DE729105}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{21F25E78-D457-418F-9F78-7DE13AE8CD93}" name="source_file" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{B8BCB027-8A7D-4FCE-803F-A296662A280E}" name="extraction_date" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{683393A0-8045-467F-9A16-95D1CB0C532F}" name="project_id" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{5331C13B-A3FC-484A-95E7-7EAD3A2BB00D}" name="project_title" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{65143B71-B457-4DF3-96FB-A320AE4152BD}" name="project_leads" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{0B1052C0-47F1-41AA-B13F-BE70DF38178E}" name="collaborations" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{1204734C-F170-44F7-B4B4-5C53DC28A923}" name="location" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{DB4F19D6-FCB3-4A48-B206-A993711C4060}" name="species" dataDxfId="15"/>
-    <tableColumn id="9" xr3:uid="{3B9CC560-9650-4F10-B6EB-A8BB6D19FD2B}" name="waterbodies" dataDxfId="14"/>
-    <tableColumn id="10" xr3:uid="{3B74A0C4-6035-471F-BA59-5E5296130A6C}" name="life_history" dataDxfId="13"/>
-    <tableColumn id="11" xr3:uid="{83EB77D8-FF38-4BA7-8B8A-C5EB6609BA41}" name="region" dataDxfId="12"/>
-    <tableColumn id="12" xr3:uid="{B5F0F367-295F-4C21-8EF2-8D796262B584}" name="stock" dataDxfId="11"/>
-    <tableColumn id="13" xr3:uid="{592AD976-80C9-41A3-904D-28E27F957093}" name="population" dataDxfId="10"/>
-    <tableColumn id="14" xr3:uid="{0841A155-6170-4816-B52F-62D315F16BB4}" name="cu" dataDxfId="9"/>
-    <tableColumn id="15" xr3:uid="{6A19023B-7495-49F1-A1EC-B098C5E333CF}" name="highlights" dataDxfId="8"/>
-    <tableColumn id="16" xr3:uid="{E075E454-2C61-4348-A20B-0C745E2EC565}" name="background" dataDxfId="7"/>
-    <tableColumn id="17" xr3:uid="{F232593A-A943-4A2F-A957-77EB6182BDA8}" name="methods_findings" dataDxfId="6"/>
-    <tableColumn id="18" xr3:uid="{2F87C396-47EA-4A13-9083-A6C4F71287B3}" name="insights" dataDxfId="5"/>
-    <tableColumn id="19" xr3:uid="{E3203637-205F-4D67-8A5B-15606B06B96D}" name="next_steps" dataDxfId="4"/>
-    <tableColumn id="20" xr3:uid="{71B5C06F-A10D-4B50-AAD8-E218E0D666CD}" name="tables_figures" dataDxfId="3"/>
-    <tableColumn id="21" xr3:uid="{671D065B-E9D7-4645-BF8D-C6523418AA9F}" name="references" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{21F25E78-D457-418F-9F78-7DE13AE8CD93}" name="source_file" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{B8BCB027-8A7D-4FCE-803F-A296662A280E}" name="extraction_date" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{683393A0-8045-467F-9A16-95D1CB0C532F}" name="project_id" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{5331C13B-A3FC-484A-95E7-7EAD3A2BB00D}" name="project_title" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{65143B71-B457-4DF3-96FB-A320AE4152BD}" name="project_leads" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{0B1052C0-47F1-41AA-B13F-BE70DF38178E}" name="collaborations" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{1204734C-F170-44F7-B4B4-5C53DC28A923}" name="location" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{DB4F19D6-FCB3-4A48-B206-A993711C4060}" name="species" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{3B9CC560-9650-4F10-B6EB-A8BB6D19FD2B}" name="waterbodies" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{3B74A0C4-6035-471F-BA59-5E5296130A6C}" name="life_history" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{83EB77D8-FF38-4BA7-8B8A-C5EB6609BA41}" name="region" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{B5F0F367-295F-4C21-8EF2-8D796262B584}" name="stock" dataDxfId="9"/>
+    <tableColumn id="13" xr3:uid="{592AD976-80C9-41A3-904D-28E27F957093}" name="population" dataDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{0841A155-6170-4816-B52F-62D315F16BB4}" name="cu" dataDxfId="7"/>
+    <tableColumn id="15" xr3:uid="{6A19023B-7495-49F1-A1EC-B098C5E333CF}" name="highlights" dataDxfId="6"/>
+    <tableColumn id="16" xr3:uid="{E075E454-2C61-4348-A20B-0C745E2EC565}" name="background" dataDxfId="5"/>
+    <tableColumn id="17" xr3:uid="{F232593A-A943-4A2F-A957-77EB6182BDA8}" name="methods_findings" dataDxfId="4"/>
+    <tableColumn id="18" xr3:uid="{2F87C396-47EA-4A13-9083-A6C4F71287B3}" name="insights" dataDxfId="3"/>
+    <tableColumn id="19" xr3:uid="{E3203637-205F-4D67-8A5B-15606B06B96D}" name="next_steps" dataDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{71B5C06F-A10D-4B50-AAD8-E218E0D666CD}" name="tables_figures" dataDxfId="1"/>
+    <tableColumn id="21" xr3:uid="{671D065B-E9D7-4645-BF8D-C6523418AA9F}" name="references" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4006,31 +4002,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U44"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.140625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="96.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" style="1" customWidth="1"/>
-    <col min="7" max="8" width="11.42578125" style="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.28515625" style="1" customWidth="1"/>
-    <col min="11" max="12" width="11.42578125" style="1"/>
-    <col min="13" max="13" width="12.85546875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" style="1"/>
-    <col min="15" max="15" width="11.85546875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="47.85546875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="11.42578125" style="1"/>
-    <col min="19" max="19" width="12.85546875" style="1" customWidth="1"/>
-    <col min="20" max="20" width="15.7109375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="126.85546875" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.42578125" style="1"/>
+    <col min="2" max="2" width="17.1796875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="96.1796875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.1796875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.7265625" style="1" customWidth="1"/>
+    <col min="7" max="8" width="11.453125" style="1"/>
+    <col min="9" max="9" width="14.26953125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13.26953125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="11.453125" style="1"/>
+    <col min="13" max="13" width="12.81640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="11.453125" style="1"/>
+    <col min="15" max="15" width="11.81640625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13.453125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="47.81640625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="11.453125" style="1"/>
+    <col min="19" max="19" width="12.81640625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="15.7265625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="126.81640625" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="11.453125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4095,7 +4091,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>21</v>
       </c>
@@ -4106,7 +4102,7 @@
         <v>22</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>608</v>
+        <v>570</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>23</v>
@@ -4136,7 +4132,7 @@
         <v>31</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>32</v>
@@ -4160,7 +4156,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>39</v>
       </c>
@@ -4186,7 +4182,7 @@
         <v>44</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>45</v>
@@ -4195,13 +4191,13 @@
         <v>46</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>47</v>
@@ -4225,7 +4221,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>54</v>
       </c>
@@ -4236,63 +4232,63 @@
         <v>2400</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>618</v>
+        <v>580</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H4" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>56</v>
       </c>
       <c r="L4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="B5" s="4">
         <v>46083</v>
@@ -4301,53 +4297,63 @@
         <v>2401</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="R5" s="3" t="s">
         <v>609</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>72</v>
+      <c r="S5" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>611</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B6" s="4">
         <v>46083</v>
@@ -4356,63 +4362,63 @@
         <v>2402</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="P6" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="Q6" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="R6" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="S6" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="T6" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="U6" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="I6" s="2" t="s">
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="S6" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="U6" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="B7" s="4">
         <v>46083</v>
@@ -4421,63 +4427,63 @@
         <v>2403</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>610</v>
+        <v>572</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>96</v>
+        <v>491</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>491</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>596</v>
+        <v>559</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>98</v>
+        <v>86</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>614</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>597</v>
+        <v>560</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="U7" s="2" t="s">
-        <v>521</v>
+        <v>491</v>
+      </c>
+      <c r="U7" s="3" t="s">
+        <v>615</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="B8" s="4">
         <v>46083</v>
@@ -4486,63 +4492,63 @@
         <v>2404</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>522</v>
+        <v>495</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>523</v>
+        <v>496</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>524</v>
+        <v>497</v>
       </c>
       <c r="U8" s="3" t="s">
-        <v>621</v>
+        <v>583</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="B9" s="4">
         <v>46083</v>
@@ -4551,63 +4557,63 @@
         <v>2405</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>604</v>
+        <v>566</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>525</v>
+        <v>498</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>526</v>
+        <v>499</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="B10" s="4">
         <v>46083</v>
@@ -4616,63 +4622,63 @@
         <v>2406</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>514</v>
+        <v>490</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>527</v>
+        <v>500</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="B11" s="4">
         <v>46083</v>
@@ -4681,63 +4687,63 @@
         <v>2407</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>619</v>
+        <v>581</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>606</v>
+        <v>568</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>56</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>528</v>
+        <v>501</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>529</v>
+        <v>502</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="B12" s="4">
         <v>46083</v>
@@ -4746,57 +4752,57 @@
         <v>2408</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>611</v>
+        <v>573</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>530</v>
+        <v>503</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>56</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>56</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>531</v>
+        <v>504</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>532</v>
+        <v>505</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>533</v>
+        <v>506</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="B13" s="4">
         <v>46083</v>
@@ -4805,61 +4811,61 @@
         <v>2409</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="T13" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="U13" s="3" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="S13" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="T13" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="U13" s="2" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>163</v>
       </c>
       <c r="B14" s="4">
         <v>46083</v>
@@ -4868,63 +4874,63 @@
         <v>2410</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>536</v>
+        <v>507</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>43</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="U14" s="3" t="s">
-        <v>620</v>
+        <v>582</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="B15" s="4">
         <v>46083</v>
@@ -4933,63 +4939,63 @@
         <v>2412</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>601</v>
+        <v>563</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>56</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>537</v>
+        <v>508</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>538</v>
+        <v>509</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>539</v>
+        <v>510</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>540</v>
+        <v>511</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="B16" s="4">
         <v>46083</v>
@@ -4998,63 +5004,63 @@
         <v>2413</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>612</v>
+        <v>574</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>541</v>
+        <v>512</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>542</v>
+        <v>513</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="B17" s="4">
         <v>46083</v>
@@ -5063,63 +5069,63 @@
         <v>2416</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="T17" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="U17" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="S17" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="T17" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="U17" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="B18" s="4">
         <v>46083</v>
@@ -5128,63 +5134,63 @@
         <v>2417</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>545</v>
+        <v>516</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>546</v>
+        <v>517</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>547</v>
+        <v>518</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>548</v>
+        <v>519</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="B19" s="4">
         <v>46083</v>
@@ -5193,63 +5199,63 @@
         <v>2418</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="T19" s="3" t="s">
         <v>613</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="S19" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="T19" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="U19" s="2" t="s">
-        <v>553</v>
+      <c r="U19" s="3" t="s">
+        <v>635</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="B20" s="4">
         <v>46083</v>
@@ -5258,63 +5264,63 @@
         <v>2421</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>614</v>
+        <v>576</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>554</v>
+        <v>521</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>56</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>555</v>
+        <v>522</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>556</v>
+        <v>523</v>
       </c>
       <c r="U20" s="2" t="s">
-        <v>557</v>
+        <v>524</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="B21" s="4">
         <v>46083</v>
@@ -5323,63 +5329,63 @@
         <v>2422</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>559</v>
+        <v>526</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="B22" s="4">
         <v>46083</v>
@@ -5388,63 +5394,63 @@
         <v>2424</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>607</v>
+        <v>569</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>624</v>
+        <v>586</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>625</v>
+        <v>587</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="U22" s="3" t="s">
-        <v>626</v>
+        <v>588</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="B23" s="4">
         <v>46083</v>
@@ -5453,63 +5459,63 @@
         <v>2425</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>595</v>
+        <v>558</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>264</v>
+        <v>247</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>597</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>628</v>
+        <v>589</v>
       </c>
       <c r="T23" s="3" t="s">
-        <v>627</v>
+        <v>598</v>
       </c>
       <c r="U23" s="3" t="s">
-        <v>629</v>
+        <v>590</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="B24" s="4">
         <v>46083</v>
@@ -5518,63 +5524,63 @@
         <v>2426</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>600</v>
+        <v>562</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>599</v>
+        <v>561</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>560</v>
+        <v>527</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>561</v>
+        <v>528</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="U24" s="2" t="s">
-        <v>562</v>
+        <v>529</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="B25" s="4">
         <v>46083</v>
@@ -5583,63 +5589,63 @@
         <v>2427</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>563</v>
+        <v>530</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="U25" s="2" t="s">
-        <v>564</v>
+        <v>531</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="B26" s="4">
         <v>46083</v>
@@ -5648,63 +5654,63 @@
         <v>2430</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>565</v>
+        <v>274</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>603</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="O26" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="P26" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="Q26" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="R26" s="2" t="s">
-        <v>593</v>
+        <v>279</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>557</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="T26" s="2" t="s">
-        <v>594</v>
+        <v>280</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>606</v>
       </c>
       <c r="U26" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="B27" s="4">
         <v>46083</v>
@@ -5713,63 +5719,63 @@
         <v>2432</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>605</v>
+        <v>567</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>567</v>
+        <v>532</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="U27" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="B28" s="4">
         <v>46083</v>
@@ -5778,63 +5784,63 @@
         <v>2433</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>605</v>
+        <v>567</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>311</v>
+        <v>293</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>568</v>
+        <v>533</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>312</v>
+        <v>294</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="U28" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="B29" s="4">
         <v>46083</v>
@@ -5843,63 +5849,63 @@
         <v>2434</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>318</v>
+        <v>300</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>322</v>
+        <v>304</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>631</v>
+        <v>592</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>632</v>
+        <v>593</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>633</v>
+        <v>594</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>634</v>
+        <v>595</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="U29" s="2" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
       <c r="B30" s="4">
         <v>46083</v>
@@ -5908,63 +5914,63 @@
         <v>2435</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>602</v>
+        <v>564</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>330</v>
+        <v>312</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>333</v>
+        <v>315</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>334</v>
+        <v>316</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>335</v>
+        <v>317</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>336</v>
+        <v>491</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>336</v>
+        <v>318</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="O30" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="P30" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="Q30" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="R30" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="S30" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="T30" s="2" t="s">
-        <v>343</v>
+        <v>319</v>
+      </c>
+      <c r="O30" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="P30" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="Q30" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="R30" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="S30" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="T30" s="3" t="s">
+        <v>621</v>
       </c>
       <c r="U30" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>344</v>
+        <v>320</v>
       </c>
       <c r="B31" s="4">
         <v>46083</v>
@@ -5973,63 +5979,63 @@
         <v>2436</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>345</v>
+        <v>321</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>346</v>
+        <v>322</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>347</v>
+        <v>323</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>348</v>
+        <v>324</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>349</v>
+        <v>325</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>350</v>
+        <v>326</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>351</v>
+        <v>327</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>352</v>
+        <v>328</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>353</v>
+        <v>329</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>354</v>
+        <v>330</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>355</v>
+        <v>331</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>356</v>
+        <v>332</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>357</v>
+        <v>333</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>358</v>
+        <v>334</v>
       </c>
       <c r="U31" s="2" t="s">
-        <v>569</v>
+        <v>534</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>359</v>
+        <v>335</v>
       </c>
       <c r="B32" s="4">
         <v>46083</v>
@@ -6038,63 +6044,63 @@
         <v>2437</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>360</v>
+        <v>336</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>361</v>
+        <v>337</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>570</v>
+        <v>535</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>362</v>
+        <v>338</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>363</v>
+        <v>339</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>364</v>
+        <v>340</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>365</v>
+        <v>341</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>366</v>
+        <v>342</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>368</v>
+        <v>344</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>571</v>
+        <v>536</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>369</v>
+        <v>345</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>371</v>
+        <v>347</v>
       </c>
       <c r="S32" s="2" t="s">
-        <v>372</v>
+        <v>348</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
       <c r="U32" s="2" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
       <c r="B33" s="4">
         <v>46083</v>
@@ -6103,63 +6109,63 @@
         <v>2439</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>615</v>
+        <v>577</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>572</v>
+        <v>537</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>378</v>
+        <v>354</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>379</v>
+        <v>355</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>380</v>
+        <v>356</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>573</v>
+        <v>538</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>381</v>
+        <v>357</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>382</v>
+        <v>358</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>384</v>
+        <v>360</v>
       </c>
       <c r="U33" s="2" t="s">
-        <v>574</v>
+        <v>539</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="B34" s="4">
         <v>46083</v>
@@ -6168,63 +6174,63 @@
         <v>2442</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>386</v>
+        <v>362</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>387</v>
+        <v>363</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>575</v>
+        <v>540</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>388</v>
+        <v>364</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>389</v>
+        <v>365</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>390</v>
+        <v>366</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>391</v>
+        <v>367</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>392</v>
+        <v>368</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>393</v>
+        <v>369</v>
       </c>
       <c r="Q34" s="3" t="s">
-        <v>623</v>
+        <v>585</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>394</v>
+        <v>370</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>395</v>
+        <v>371</v>
       </c>
       <c r="T34" s="3" t="s">
-        <v>630</v>
+        <v>591</v>
       </c>
       <c r="U34" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>396</v>
+        <v>372</v>
       </c>
       <c r="B35" s="4">
         <v>46083</v>
@@ -6233,63 +6239,63 @@
         <v>2443</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>397</v>
+        <v>373</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>398</v>
+        <v>374</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>576</v>
+        <v>541</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>399</v>
+        <v>375</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>400</v>
+        <v>376</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>401</v>
+        <v>377</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>400</v>
+        <v>376</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>402</v>
+        <v>378</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>403</v>
+        <v>379</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>404</v>
+        <v>380</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>622</v>
+        <v>584</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>405</v>
+        <v>381</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>406</v>
+        <v>382</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>577</v>
+        <v>542</v>
       </c>
       <c r="U35" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>407</v>
+        <v>383</v>
       </c>
       <c r="B36" s="4">
         <v>46083</v>
@@ -6298,63 +6304,63 @@
         <v>2447</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>616</v>
+        <v>578</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>408</v>
+        <v>384</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>578</v>
+        <v>543</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>409</v>
+        <v>385</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>409</v>
+        <v>385</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>410</v>
+        <v>386</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>411</v>
+        <v>387</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>412</v>
+        <v>388</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>413</v>
+        <v>389</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>414</v>
+        <v>390</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>415</v>
+        <v>391</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>416</v>
+        <v>392</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>417</v>
+        <v>393</v>
       </c>
       <c r="U36" s="2" t="s">
-        <v>579</v>
+        <v>544</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>418</v>
+        <v>394</v>
       </c>
       <c r="B37" s="4">
         <v>46083</v>
@@ -6363,63 +6369,63 @@
         <v>2448</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>617</v>
+        <v>579</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>419</v>
+        <v>395</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>420</v>
+        <v>396</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>56</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>421</v>
+        <v>397</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>422</v>
+        <v>398</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>423</v>
+        <v>399</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>421</v>
+        <v>397</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>424</v>
+        <v>400</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>425</v>
+        <v>401</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>426</v>
+        <v>402</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>427</v>
+        <v>403</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>580</v>
+        <v>545</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>428</v>
+        <v>404</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>429</v>
+        <v>405</v>
       </c>
       <c r="U37" s="2" t="s">
-        <v>430</v>
+        <v>406</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>431</v>
+        <v>407</v>
       </c>
       <c r="B38" s="4">
         <v>46083</v>
@@ -6428,63 +6434,63 @@
         <v>2449</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>603</v>
+        <v>565</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>432</v>
+        <v>408</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>581</v>
+        <v>546</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>433</v>
+        <v>409</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>435</v>
+        <v>411</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>436</v>
+        <v>412</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>437</v>
+        <v>413</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>438</v>
+        <v>414</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>439</v>
+        <v>415</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>440</v>
+        <v>416</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>441</v>
+        <v>417</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>442</v>
+        <v>418</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>444</v>
+        <v>420</v>
       </c>
       <c r="U38" s="2" t="s">
-        <v>445</v>
+        <v>421</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>446</v>
+        <v>422</v>
       </c>
       <c r="B39" s="4">
         <v>46083</v>
@@ -6493,63 +6499,63 @@
         <v>2451</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>447</v>
+        <v>423</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>361</v>
+        <v>337</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>449</v>
+        <v>425</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>450</v>
+        <v>426</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>451</v>
+        <v>427</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>452</v>
+        <v>428</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>582</v>
+        <v>547</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>453</v>
+        <v>429</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>454</v>
+        <v>430</v>
       </c>
       <c r="U39" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>455</v>
+        <v>431</v>
       </c>
       <c r="B40" s="4">
         <v>46083</v>
@@ -6558,63 +6564,63 @@
         <v>2452</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>456</v>
+        <v>432</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>361</v>
+        <v>337</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>457</v>
+        <v>433</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>458</v>
+        <v>434</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>462</v>
+        <v>438</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>463</v>
+        <v>439</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>583</v>
+        <v>548</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>464</v>
+        <v>440</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>465</v>
+        <v>441</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>466</v>
+        <v>442</v>
       </c>
       <c r="U40" s="2" t="s">
-        <v>584</v>
+        <v>549</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>467</v>
+        <v>443</v>
       </c>
       <c r="B41" s="4">
         <v>46083</v>
@@ -6623,63 +6629,63 @@
         <v>2504</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>468</v>
+        <v>444</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>469</v>
+        <v>445</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>585</v>
+        <v>550</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>470</v>
+        <v>446</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>471</v>
+        <v>447</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>472</v>
+        <v>448</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>473</v>
+        <v>449</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>474</v>
+        <v>450</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>475</v>
+        <v>451</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>476</v>
+        <v>452</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>476</v>
+        <v>452</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>477</v>
+        <v>453</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>478</v>
+        <v>454</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>479</v>
+        <v>455</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>480</v>
+        <v>456</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>481</v>
+        <v>457</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>482</v>
+        <v>458</v>
       </c>
       <c r="U41" s="2" t="s">
-        <v>483</v>
+        <v>459</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>484</v>
+        <v>460</v>
       </c>
       <c r="B42" s="4">
         <v>46083</v>
@@ -6688,63 +6694,63 @@
         <v>2513</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>485</v>
+        <v>461</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>469</v>
+        <v>445</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>586</v>
+        <v>551</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>486</v>
+        <v>462</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>487</v>
+        <v>463</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>488</v>
+        <v>464</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>489</v>
+        <v>465</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>587</v>
+        <v>552</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>588</v>
+        <v>553</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>490</v>
+        <v>466</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>491</v>
+        <v>467</v>
       </c>
       <c r="U42" s="2" t="s">
-        <v>589</v>
+        <v>554</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>492</v>
+        <v>468</v>
       </c>
       <c r="B43" s="4">
         <v>46083</v>
@@ -6753,22 +6759,22 @@
         <v>2545</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>493</v>
+        <v>469</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>494</v>
+        <v>470</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>495</v>
+        <v>471</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>496</v>
+        <v>472</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>497</v>
+        <v>473</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>498</v>
+        <v>474</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>31</v>
@@ -6786,30 +6792,30 @@
         <v>31</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>499</v>
+        <v>475</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>500</v>
+        <v>476</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>501</v>
+        <v>477</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>502</v>
+        <v>478</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>503</v>
+        <v>479</v>
       </c>
       <c r="T43" s="2" t="s">
-        <v>504</v>
+        <v>480</v>
       </c>
       <c r="U43" s="2" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>505</v>
+        <v>481</v>
       </c>
       <c r="B44" s="4">
         <v>46083</v>
@@ -6818,56 +6824,56 @@
         <v>3682</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>506</v>
+        <v>482</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>507</v>
+        <v>483</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>508</v>
+        <v>484</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="3" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>56</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="N44" s="3" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>635</v>
+        <v>596</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>509</v>
+        <v>485</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>510</v>
+        <v>486</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>511</v>
+        <v>487</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>512</v>
+        <v>488</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>513</v>
+        <v>489</v>
       </c>
       <c r="U44" s="2" t="s">
-        <v>590</v>
+        <v>555</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/pssi_form_data_altered.xlsx
+++ b/data/processed/pssi_form_data_altered.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ennsj\Documents\PSSI-final-tech-report\data\processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F7D77F9-9F23-45BC-AFCB-7DF6E7C4C337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26259EBF-E6DC-48D2-9D16-B8C77A01F6B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1485" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/processed/pssi_form_data_altered.xlsx
+++ b/data/processed/pssi_form_data_altered.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ennsj\Documents\PSSI-final-tech-report\data\processed\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://086gc-my.sharepoint.com/personal/cory_lagasse_dfo-mpo_gc_ca/Documents/0.Workspace/PSSI-final-tech-report/data/processed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72209C9B-6B2A-454B-AB74-0C9975FB44EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="250" documentId="13_ncr:1_{72209C9B-6B2A-454B-AB74-0C9975FB44EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9656DA6-090A-4E89-876A-13E6B23390F7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="674">
   <si>
     <t>source_file</t>
   </si>
@@ -113,16 +113,7 @@
     <t>Southern BC</t>
   </si>
   <si>
-    <t>Chinook Salmon (Oncorhynchus tshawytscha)</t>
-  </si>
-  <si>
-    <t>Bute Inlet (PFMA 13), Toba Inlet (PFMA 15), Sechelt Inlet (PFMA 16), Gulf Islands/Saanich Inlet (PFMAs 17,18,19), Victoria &amp; Haro Straight (PFMA 19), Howe Sound (PFMA 28). See (Figure 1).</t>
-  </si>
-  <si>
     <t>Adult (Ocean Phase)</t>
-  </si>
-  <si>
-    <t>Southern British Columbia</t>
   </si>
   <si>
     <t>All Chinook Stocks Present</t>
@@ -180,9 +171,6 @@
     <t>Pacific Region</t>
   </si>
   <si>
-    <t>All Oncorhynchus spp.</t>
-  </si>
-  <si>
     <t>Marine</t>
   </si>
   <si>
@@ -225,10 +213,6 @@
   </si>
   <si>
     <t>Pacific</t>
-  </si>
-  <si>
-    <t>Chinook salmon (Fall, Spring, and Summer)
-Coho salmon (Fall)</t>
   </si>
   <si>
     <t>Juveniles, broodstock</t>
@@ -257,9 +241,6 @@
   </si>
   <si>
     <t>Kyle Garver</t>
-  </si>
-  <si>
-    <t>Sockeye salmon</t>
   </si>
   <si>
     <t>Weaver Creek, Nadina River, Fulton River, Pinkut Creek</t>
@@ -309,9 +290,6 @@
     <t>Yukon</t>
   </si>
   <si>
-    <t>Chinook salmon</t>
-  </si>
-  <si>
     <t>Yukon River basin</t>
   </si>
   <si>
@@ -367,9 +345,6 @@
     <t>Port Renfrew, BC</t>
   </si>
   <si>
-    <t>Chinook (focus), Coho, Chum</t>
-  </si>
-  <si>
     <t>San Juan River, Gordon River</t>
   </si>
   <si>
@@ -430,13 +405,7 @@
     <t>Biological models to support prioritizing salmon stocks under future climates</t>
   </si>
   <si>
-    <t>Amber Holdsworth and Angelica Pena (Ocean Sciences Division); Dan Selbie, Howard Stiff, Greig Oldford, and Josie Iacarella (Ecosystem Science Division)</t>
-  </si>
-  <si>
     <t>Lifecycle: Spawners, smolts, escapement</t>
-  </si>
-  <si>
-    <t>British Columbia and Washington</t>
   </si>
   <si>
     <t>- The goal of the project is to estimate how climate related environmental variables are influencing sockeye salmon productivity across different life stages and populations using quantitative models. These estimates will be combined with climate projections to estimate how future conditions may impact salmon populations in future decades.
@@ -526,9 +495,6 @@
     <t>West Coast of Vancouver Island, Stamp River, Sarita River, Nitinat River, Barkley Sound</t>
   </si>
   <si>
-    <t>Chinook Salmon</t>
-  </si>
-  <si>
     <t>Sooke Basin, Port San Juan, Nitinat Lake, Barkley Sound, Clayoquot Sound, Nootka Sound, Kyuquot Sound, Quatsino Sound</t>
   </si>
   <si>
@@ -564,14 +530,6 @@
     <t>2408 PSSI Science Project Reporting_Long_Project.docx</t>
   </si>
   <si>
-    <t>See Supplemental Table 1</t>
-  </si>
-  <si>
-    <t>See Supplemental Table 1
----
-See Supplemental Table 1</t>
-  </si>
-  <si>
     <t>- The project focused on developing, validating, and implementing quantitative PCR (qPCR) assays for seven endemic fish pathogens in British Columbia to improve disease detection and support salmon health management.
 - Targeted surveillance revealed differences in pathogen prevalence among salmon stocks and tissues, with *F. psychrophilum* more frequently detected in spleen samples than kidney, alongside observed genetic diversity in isolates. For *R. salmoninarum*, ELISA testing was more reliable than qPCR, with non-lethal sampling methods under ongoing evaluation.
 - Improved diagnostic tools enhance pathogen detection and understanding of disease prevalence, aiding targeted interventions in salmon hatcheries.</t>
@@ -594,16 +552,6 @@
   </si>
   <si>
     <t>Convergent tracks: a tagging study to quantify salmon predation by sea lions</t>
-  </si>
-  <si>
-    <t>Cameron Freshwater and Strahan Tucker</t>
-  </si>
-  <si>
-    <t>**Salmon**: Justin Fleming and Jackie King (DFO ESD), Erin Rechisky (DFO South Coast Stock Assessment), Andy Seitz and Michael Courtney (University of Alaska Fairbanks)
-**Sea lions**: Chad Nordstrom, Ali Bowker, Sheena Majewski, Kurt Trzcinski (DFO ESD), Marty Haulena (Vancouver Aquarium), Christine Rock (ECCC)</t>
-  </si>
-  <si>
-    <t>Continental shelf, Queen Charlotte Strait, Johnstone Strait, Strait of Georgia</t>
   </si>
   <si>
     <t>Adult marine</t>
@@ -658,9 +606,6 @@
     <t>Thomas Therriault</t>
   </si>
   <si>
-    <t>All; Freshwater Ecoregions of the World</t>
-  </si>
-  <si>
     <t>- This project has prioritized the risk of 515 Aquatic Invasive Species across multiple taxa (primarily fish, invertebrates and plants) for five freshwater ecoregions in the Pacific Region.
 - Several high-risk AIS were identified within each taxonomic group and ecoregion that could negatively impact salmon stocks throughout the Pacific Region.
 - Managers and other decision makers need to explicitly consider the many threats posed by AIS in management and recovery plans for all salmon stocks in Pacific Region, recognizing these threats will not be uniform.</t>
@@ -698,12 +643,6 @@
     <t>2412 PSSI Science Project Reporting_Pearce_Mackenzie_Forster_Neville.docx</t>
   </si>
   <si>
-    <t>Chris Pearce, Clara Mackenzie, Ian Forster (DFO, Nearshore Ecosystems Section)</t>
-  </si>
-  <si>
-    <t>Chrys Neville (DFO, Salmon Marine Interactions Program, Regional Ecosystem Effects on Fish &amp; Fisheries Section)</t>
-  </si>
-  <si>
     <t>Strait of Georgia (SOG); Pacific Biological Station (PBS), Nanaimo; Pacific Science Enterprise Center (PSEC), West Vancouver</t>
   </si>
   <si>
@@ -728,9 +667,6 @@
   </si>
   <si>
     <t>Barkley Sound, Clayoquot Sound</t>
-  </si>
-  <si>
-    <t>WCVI Chinook, Coho</t>
   </si>
   <si>
     <t>First marine year</t>
@@ -861,9 +797,6 @@
     <t>West Vancouver, BC</t>
   </si>
   <si>
-    <t>Chinook salmon (*Oncorhynchus tshawytscha*)</t>
-  </si>
-  <si>
     <t>First feeding to release</t>
   </si>
   <si>
@@ -890,9 +823,6 @@
   </si>
   <si>
     <t>Pacific Science Enterprise Centre</t>
-  </si>
-  <si>
-    <t>Chinook, coho, sockeye, and pink salmon</t>
   </si>
   <si>
     <t>Egg stage; adult</t>
@@ -1034,9 +964,6 @@
   </si>
   <si>
     <t>Fraser River Basin</t>
-  </si>
-  <si>
-    <t>Coho, Chinook, Sockeye, Pink, Chum</t>
   </si>
   <si>
     <t>All freshwater phases</t>
@@ -1373,9 +1300,6 @@
     <t>Chum whole genome sequencing for improved stock delineation</t>
   </si>
   <si>
-    <t>Anna Tigano, Eric Rondeau, Timothy Healy, Kyle Wellband,.</t>
-  </si>
-  <si>
     <t>PBS, Nanaimo, BC</t>
   </si>
   <si>
@@ -1433,16 +1357,7 @@
     <t>Timothy Healy, Eric Rondeau, Kyle Wellband</t>
   </si>
   <si>
-    <t>Chinook, Sockeye, Coho, Pink, Chum</t>
-  </si>
-  <si>
-    <t>The majority of major watersheds across the Canadian range for each of the species</t>
-  </si>
-  <si>
     <t>All (adult samples)</t>
-  </si>
-  <si>
-    <t>Across North American range (BC and Yukon in Canada)</t>
   </si>
   <si>
     <t>Many stocks across range</t>
@@ -1487,12 +1402,6 @@
   </si>
   <si>
     <t>Pacific Biological Station, Nanaimo, BC</t>
-  </si>
-  <si>
-    <t>Chum and Chinook</t>
-  </si>
-  <si>
-    <t>Pacific North West</t>
   </si>
   <si>
     <t>- The Alternative Age Estimation program (AAE) in the Sclerochronology lab (SCL) is conducting research in Convolutional Neural Network (CNN) and Deep Machine Learning (DML) predictive age modeling with a goal to deploy an AI-driven pipeline that augments traditional ageing techniques and transforms fish age estimation.
@@ -1529,9 +1438,6 @@
   </si>
   <si>
     <t>Habitat use and predation on juvenile Chinook salmon in the Canadian Okanagan River and Lake system</t>
-  </si>
-  <si>
-    <t>Lauren Weir (DFO), Tommy Pontbriand (DFO)</t>
   </si>
   <si>
     <t>Okanagan River and Lake system</t>
@@ -1792,9 +1698,6 @@
     <t>Carrie Holt, Catarina Wor and Brendan Connors</t>
   </si>
   <si>
-    <t>Applicable to all species; case study on Chinook salmon</t>
-  </si>
-  <si>
     <t>Complete life cycle</t>
   </si>
   <si>
@@ -1949,22 +1852,10 @@
     <t>Identifying and characterizing tire-related chemical (6PPD-quinone) toxic hotspots in salmon habitat</t>
   </si>
   <si>
-    <t>Lisa Loseto (prev. T. Brown)</t>
-  </si>
-  <si>
     <t>Metro Vancouver, Squamish, Vancouver Island</t>
   </si>
   <si>
-    <t>All Pacific salmonids.</t>
-  </si>
-  <si>
-    <t>Watersheds in Southwestern B.C.</t>
-  </si>
-  <si>
     <t>Juvenile, Adults</t>
-  </si>
-  <si>
-    <t>Southwestern B.C.</t>
   </si>
   <si>
     <t>Hundreds</t>
@@ -2071,16 +1962,7 @@
     <t>Eric Rondeau, Anna Tigano</t>
   </si>
   <si>
-    <t>Too many to list in full</t>
-  </si>
-  <si>
     <t>Nanaimo, BC</t>
-  </si>
-  <si>
-    <t>Chinook, Sockeye, Chum, Coho, Pink</t>
-  </si>
-  <si>
-    <t>Pacific Ocean, Freshwater systems throughout Pacific region</t>
   </si>
   <si>
     <t>Stabilized funding for core Genetic Stock Identification work enabled the genotyping of over 60,000 individuals as directed by regional stock assessment teams</t>
@@ -2154,9 +2036,6 @@
   </si>
   <si>
     <t>NA</t>
-  </si>
-  <si>
-    <t>Derek Price, DFO, Ian Keith, DFO, Cheryl Lynch, DFO</t>
   </si>
   <si>
     <t>The study explored the relationship between parental BKD levels on individual salmon results while controlling for the impact of environmental factors such as thermal regime using previously collected data including broodstock disease levels, environmental parameters, and progenitor disease status.
@@ -2653,9 +2532,6 @@
 Wright, G.M., Brown, S.B., Brown, L.R., Moore, K., Villella, M., Zajicek, J.L., Tillitt, D.E., Fitzsimons, J.D., and Honeyfield, D.C. 2005. Effect of sample handling on thiamine and thiaminolytic activity in alewife. J. Aquat. Anim. Health 17(1): 77-81. doi:10.1577/H03-074.1.</t>
   </si>
   <si>
-    <t>Mr. Reid Williams, MSc student; Dr. Nicholas Bernier, University of Guelph; Dr. Fredrick Laberge, University of Guelph</t>
-  </si>
-  <si>
     <t>*Laboratory Studies*
 Scale preparation and extraction of corticosteroids followed the methods described by Laberge et al., (2019) with a few small modifications. Preliminary studies were done to determine the number of scales required for analysis, as well as to examine whether scale cortisol concentrations varied across body regions.
 Using hatchery-reared juvenile Chinook salmon, three experiments were performed to assess the temporal profiles of cortisol accumulation and clearance in plasma and scales in response to stressors of varying intensity and duration: an acute stressor, three weeks of unpredictable chronic stress, and the transition from freshwater (FW) to seawater (SW) under elevated temperatures. Cortisone, the breakdown product of cortisol, was also quantified to determine whether whole animal and local cortisol metabolism contribute to scale cortisol levels and whether scale cortisol-cortisone ratios can be used for long-term stress monitoring.
@@ -2709,12 +2585,6 @@
 de Vrieze, E., Heijnen, L., Metz, J.R., and Flik, G. 2012. Evidence for a hydroxyapatite precursor in regenerating cyprinid scales. Journal of Applied Ichthyology 28(3): 388-392. doi:10.1111/j.1439-0426.2012.01989.x.</t>
   </si>
   <si>
-    <t>DFO Stock assessment, LGL Ltd, Huu-ay-aht First Nation</t>
-  </si>
-  <si>
-    <t>Chinook Salmon *OncorhynchusÂ tshawytscha*</t>
-  </si>
-  <si>
     <t>Sakinaw sockeye have been listed as endangered with COSEWIC since 2003, and a *Species at Risk Act* Recovery Potential Assessment (RPA) was completed in 2017 (Ramshaw et al. 2019). The RPA cited low marine survival as the greatest limiting factor in recovery, with predator abundance and assumed predation on smolts and adults ranked as high risk, with a critical level of impact. Perpetually low marine survivals are preventing recovery such that the persistence of the population is entirely dependent on a captive brood program.
 Sakinaw sockeye smolts out-migrate from Sakinaw Lake each spring into the Malaspina Strait and Strait of Georgia. Localized marine predation is considered a major limiting factor for the survival of this stock. On water surveys (since 2019) of pinnipeds from the estuary to the seal haul-outs on Hodgson Islands (approximately 2km from the estuary, Figure 1) have observed approximately 100-350 harbour seals in the area during the spring out-migration.
 This project was started as a pilot (2022) in collaboration with shÃ­shÃ¡lh Nation to test the hypothesis that the Hodgson Island harbour seal population is negatively affecting smolt survival, and subsequently adult returns. The goal of the project is to transport and release smolts past the seal haul-out and then compare marine survival rates between transported smolts and those out-migrating naturally. The pilot project began with a low number of smolts transported in small trial releases to test the effect of handling, Passive Integrated Transponders (PIT) tagging, and increased osmoregulation on fish.
@@ -2763,18 +2633,12 @@
 Young, K., Galbraith, M., Sastri, A., and Perry, R.I. Zooplankton status and trends in the central and northern Strait of Georgia, 2022. *In* Boldt, J.L., Joyce, E., Tucker, S., and Gauthier, S. (Eds.). 2023. State of the physical, biological and selected fishery resources of Pacific Canadian marine ecosystems in 2022. Can. Tech.Rep. Fish. Aquat. Sci. 3542: viii + 312 p.</t>
   </si>
   <si>
-    <t>Aquacoustics Inc., TÅilhqot'in National Government (TNG)</t>
-  </si>
-  <si>
     <t>Acoustic data were collected with two Simrad WBT Mini SONAR systems deployed approximately 2 km downstream of the Chilko River smolt enumeration fence. Each SONAR system operated with a 7Â° circular 120 kHz split-beam transducer. For the up-looking system, the transducer was mounted on the river bottom, in the thalweg, aimed straight up towards the water surface. For the side-looking system, the transducer was mounted nearshore on the left bank of the river, with its center approximately 15 cm below the surface, aimed across the river with a transducer tilt angle of approximately 3Â° down from horizontal. Data were recorded with a ping rate of 20 pings per second on the up-looking (maximum range 4 m), 12 pings per s on the side-looking system (maximum range 12 m). Both systems were set to 50 W power output. For all four years of the study, SONAR data were collected from mid-April to late-May during the entire Chilko Sockeye smolt outmigration period.
 SONAR data was manually reviewed and edited using Echoview software to remove noise, and echo integrated in 1 hour x 1 m range cells (side-looking) or 1 hour x 0.2 m range cells (up-looking). The results were exported as csv files, and all echo integration csv files belonging to the same transducer and site were concatenated for further analysis in Microsoft Excel. Excel was then used to convert the echo integration results to smolt passage estimates, which were then compared to the estimates generated at the Chilko River smolt enumeration fence.
 In 2023 and 2024 (2025 results pending), daily estimates of smolt passage showed close correspondence (5% in 2023, 9% in 2024) between fence counts and independent acoustic estimates both in time and magnitude. In the first year of the study (2022), daily SONAR estimates were in good agreement with the fence counts over the first 9 days of the study, but consistently higher over the last 9 days (May 3rd and thereafter). At present, the source of this divergence is unclear.
 This project is one of few that have used split-beam SONARs configured in this manner to enumerate outmigrating salmon smolts. While further testing needs to be conducted in both the Chilko River where the study was conducted, and in other candidate systems, the preliminary results of this study are promising. These methods could be modified and applied to a variety of salmon stock assessment programs to gain crucial information on survival in the early freshwater life stages (egg to smolt survival), however, considerable planning and care needs to be taken when selecting a suitable site.</t>
   </si>
   <si>
-    <t>Follow The fish team</t>
-  </si>
-  <si>
     <t>- Large scale acoustic surveys within The Salish sea indicate The presence of Pacific hake (a significant source of potential predation for juvenile salmon) throughout The Salish sea, with increasing biomass over The past years.
 - Fine temporal scale monitoring in nearshore coastal areas of The Strait indicate low abundance of juvenile salmon compare to juvenile Pacific herring, suggesting high levels of Competition for food.
 - The nearshore Moorings (including cameras) revealed a wide array of potential predators for juvenile salmon, but surface predation from birds and/or marine mammals were not as frequent as observed in nearshore coastal areas of Barkley Sound.
@@ -2785,9 +2649,6 @@
 McKinney, G.J., Barry, P.D., Pascal, C., Seeb, J.E., Seeb, L.W. and McPhee, M.V., 2022. A new genotypingâ€inâ€thousandsâ€byâ€sequencing single nucleotide polymorphism panel for mixedâ€stock analysis of chum salmon from coastal Western Alaska.Â *North American Journal of Fisheries Management*,Â *42*(5), pp.1134-1143.
 Small,Â M.,Â WarheitÂ K.,Â PascalÂ C.,Â SeebÂ L.,Â RuffÂ C.,Â ZischkeÂ J.,Â et al., Chum Salmon Southern Area Genetic Baseline Enhancement Part 1 and Part 2: Amplicon Development, Expanded Baseline Collections, and Genotyping. PSC report S14-I17 &amp; S15-I09
 Small, M.P., Rogers Olive, S.D., Seeb, L.W., Seeb, J.E., Pascal, C.E., Warheit, K.I. and Templin, W., 2015. Chum salmon genetic diversity in the northeastern Pacific Ocean assessed with single nucleotide polymorphisms (SNPs): Applications to fishery management.Â *North American Journal of Fisheries Management*,Â *35*(5), pp.974-987.</t>
-  </si>
-  <si>
-    <t>Sockeye salmon work collaboratively funded through the GRDI GenARCC program, Chum salmon work collaboratively completed with PSSI project 2436</t>
   </si>
   <si>
     <t>- Pacific salmon are found across a Large geographic range, which covers substantial variation in environmental conditions
@@ -2879,10 +2740,6 @@
   </si>
   <si>
     <t>Dr. T. Brown, SFU; Dr. Rachel Scholes, Dr. Tim Rodgers, UBC; Dr. Edward Kolodziej; Tsawwassen First Nation; Tsleil-Waututh Nation; Musqueam Nation; Cowichan Tribes; Redd fish Restoration; Vancouver Island University; BC conservation Foundation; World fisheries Trust; The Pacific Streamkeepers Federation; BC Ministry of Transportation; and Somenos Marsh Wildlife Society</t>
-  </si>
-  <si>
-    <t>Dr. T. Brown, SFU
-*Follow the Fish Program and associated partners and nations/organizations*: Huu-ay-aht First Nation; Toquaht Nation; Uchucklesaht Tribe; HupaÄasath First *Nation*; YuuÅ‚uÊ”iÅ‚Ê”atá¸¥ Government; Tseshaht First Nation</t>
   </si>
   <si>
     <t>*Field collections*:
@@ -3044,17 +2901,10 @@
     <t>A decision-support tool that considers harvest, hatchery, and habitat management levers to support implementation of the Fisheries Act for Pacific salmon</t>
   </si>
   <si>
-    <t>Jan Finke, Travis Tai, Brendan Connors, 
-Cameron Freshwater, Patrick Thompson</t>
-  </si>
-  <si>
     <t>Stéphane Gauthier</t>
   </si>
   <si>
     <t>Ahousaht First Nation; Coal Harbour Ltd.; British Columbia Conservation Foundation; Cedar Coast Field Station; Charter Tofino; Ditidaht First Nation; Ehattesaht/Chinehkint First Nation; Ha’oom Fisheries Society; Hesquiaht First Nation; Hupačasath First Nation; Huu-ay-aht First Nations; The Juanes Lab (University of Victoria); Ka:’yu:’k’t’h’/Che:k:tles7et’h’ First Nations; LGL Limited; Maaqutusiis Hahoulthee Stewardship Society; M.C. Wright and Associates Ltd.; Mowachaht-Muchalaht First Nations; Nootka Sound Watershed Society; Nuu-Chah-Nulth Tribal Council; Nuchatlaht Tribe; Pacheedaht First Nation; Pacific Salmon Foundation; Quatsino First Nation; Redd Fish Restoration Society; Thornton Creek Enhancement Society; Tla-o-qui-aht First Nation; Toquaht Nation; Tseshaht First Nation; T’Sou-ke Nation; Uchucklesaht Tribe; Yuułuʔiłʔatḥ Government</t>
-  </si>
-  <si>
-    <t>Doug Braun, Josephine Iacarella, Secwépemc Fisheries Commission</t>
   </si>
   <si>
     <t>Enhanced Mark Selective Fishery (MSF) monitoring (including a Chinook Reference Fishery)</t>
@@ -3194,6 +3044,265 @@
 *Implications*
 The LAPSE framework demonstrates the ability to identify regulatory pathways relevant to specific human activity threats by linking IUCN-CMP threat classifications to legislation, enabling salmon stewardship practitioners to navigate the complex legal landscape and develop coordinated, inter-jurisdictional recovery strategies.</t>
   </si>
+  <si>
+    <t>short_title</t>
+  </si>
+  <si>
+    <t>Enhanced MSF Monitoring and Chinook Reference Fishery</t>
+  </si>
+  <si>
+    <t>Enhanced Salmon Bycatch Monitoring in Trawl Fishery</t>
+  </si>
+  <si>
+    <t>Modeling Chinook and Coho Broodstock Disease Screening</t>
+  </si>
+  <si>
+    <t>IHNV Epidemiological Modeling in Sockeye Salmon</t>
+  </si>
+  <si>
+    <t>Yukon Chinook Migration Mortality</t>
+  </si>
+  <si>
+    <t>San Juan River Adult and Juvenile Salmon Assessment</t>
+  </si>
+  <si>
+    <t>Environmental Conditions and Hypoxia in Vancouver Island Fjords</t>
+  </si>
+  <si>
+    <t>Biological Models of Salmon Under Future Climates</t>
+  </si>
+  <si>
+    <t>Using Sediment Cores To Study Changing Coastal Productivity</t>
+  </si>
+  <si>
+    <t>Juvenile Chinook Distribution, Diet, and Health on WCVI</t>
+  </si>
+  <si>
+    <t>Modernizing Salmonid Health Diagnostic Services</t>
+  </si>
+  <si>
+    <t>Tagging Study of Sea Lion Predation on Salmon</t>
+  </si>
+  <si>
+    <t>Assessing AIS Threats to Freshwater Salmon Habitats</t>
+  </si>
+  <si>
+    <t>Krill Monitoring in Barkley and Clayoquot Sounds</t>
+  </si>
+  <si>
+    <t>Climate Stressors and Nutritional Quality of pteropods</t>
+  </si>
+  <si>
+    <t>Predicting Salmon Exposure to Harmful Algal Biotoxins</t>
+  </si>
+  <si>
+    <t>Optimizing Hatchery Feeds for Pacific Salmon Production</t>
+  </si>
+  <si>
+    <t>Thiamine-Based Prediction of Chinook Reproductive Success</t>
+  </si>
+  <si>
+    <t>Scale Hormones to Assess Chronic Stress</t>
+  </si>
+  <si>
+    <t>LA-ICP-MS for Estuary Entry Size and Habitat Use</t>
+  </si>
+  <si>
+    <t>Modelling Hydrology and Juvenile Salmon Productivity</t>
+  </si>
+  <si>
+    <t>Geospatial Threat Indicators in the Fraser River Basin</t>
+  </si>
+  <si>
+    <t>Sakinaw Sockeye Marine Survival Enhancement Research</t>
+  </si>
+  <si>
+    <t>Salish Sea Plankton and Oceanography Monitoring</t>
+  </si>
+  <si>
+    <t>Estimating Chilko Smolt Abundance with SONAR Methods</t>
+  </si>
+  <si>
+    <t>Acoustic Monitoring of Salmon and Prey in Barkley Sound</t>
+  </si>
+  <si>
+    <t>Integrated Salish Sea Acoustic Monitoring of Salmon</t>
+  </si>
+  <si>
+    <t>Rapid Genotyping Using SHERLOCK Assay</t>
+  </si>
+  <si>
+    <t>Epigenetic Variation in Hatchery and Wild Salmon</t>
+  </si>
+  <si>
+    <t>Chum Whole Genome Sequencing for Stock Delineation</t>
+  </si>
+  <si>
+    <t>Adaptive Genetic Variation and Salmon Climate Resilience</t>
+  </si>
+  <si>
+    <t>Modernizing Fish Age Estimation with FT-NIR and AI</t>
+  </si>
+  <si>
+    <t>Habitat Use and Predation on Okanagan Juvenile Chinook</t>
+  </si>
+  <si>
+    <t>Assessing Smallmouth Bass Control Impacts in Cultus Lake</t>
+  </si>
+  <si>
+    <t>Ecosystem Approaches Using Fit-Chips and eDNA</t>
+  </si>
+  <si>
+    <t>Holistic Salmon Health Management using Fit-Chips</t>
+  </si>
+  <si>
+    <t>SalmonMSE Decision-Support Tool</t>
+  </si>
+  <si>
+    <t>Relative Reproductive Success of Hatchery Vs Wild Salmon</t>
+  </si>
+  <si>
+    <t>Genetic Associations with Chinook Male Return Age</t>
+  </si>
+  <si>
+    <t>Identifying Toxic 6PPD‑Quinone Hotspots in Salmon Habitat</t>
+  </si>
+  <si>
+    <t>Monitoring Key Contaminants in WCVI Juvenile Salmon</t>
+  </si>
+  <si>
+    <t>Genetic Stock ID and Parentage-Based Tagging of Salmon</t>
+  </si>
+  <si>
+    <t>Legislation Applicable to Pacific Salmon and Ecosystems</t>
+  </si>
+  <si>
+    <t>Jan Finke, Travis Tai, Brendan Connors, Cameron Freshwater, Patrick Thompson</t>
+  </si>
+  <si>
+    <t>Cameron Freshwater, Strahan Tucker</t>
+  </si>
+  <si>
+    <t>Chris Pearce, Clara Mackenzie, Ian Forster</t>
+  </si>
+  <si>
+    <t>Anna Tigano, Eric Rondeau, Timothy Healy, Kyle Wellband</t>
+  </si>
+  <si>
+    <t>Lauren Weir, Tommy Pontbriand</t>
+  </si>
+  <si>
+    <t>Lisa Loseto</t>
+  </si>
+  <si>
+    <t>DFO: Derek Price, Ian Keith,  Cheryl Lynch</t>
+  </si>
+  <si>
+    <t>DFO: Amber Holdsworth and Angelica Pena; Dan Selbie, Howard Stiff, Greig Oldford, and Josie Iacarella</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DFO: Justin Fleming, Jackie King, Erin Rechisky, Andy Seitz Michael Courtney, Chad Nordstrom, Ali Bowker; University of Alaska Fairbanks: Sheena Majewski, Kurt Trzcinski; Vancouver Aquarium: Marty Haulena; ECCC: Christine Rock
+</t>
+  </si>
+  <si>
+    <t>DFO:Chrys Neville</t>
+  </si>
+  <si>
+    <t>University of Guelph: Reid Williams, Dr. Nicholas Bernier, Dr. Fredrick Laberge</t>
+  </si>
+  <si>
+    <t>LGL Ltd, Huu-ay-aht First Nation</t>
+  </si>
+  <si>
+    <t>DFO: Doug Braun, Josephine Iacarella; Secwépemc Fisheries Commission</t>
+  </si>
+  <si>
+    <t>Aquacoustics Inc., TÅilhqot'in National Government</t>
+  </si>
+  <si>
+    <t>Follow The Fish team</t>
+  </si>
+  <si>
+    <t>GRDI GenARCC program</t>
+  </si>
+  <si>
+    <t>Dr. T. Brown, SFU,  Huu-ay-aht First Nation; Toquaht Nation; Uchucklesaht Tribe; HupaÄasath First *Nation*; YuuÅ‚uÊ”iÅ‚Ê”atá¸¥ Government; Tseshaht First Nation</t>
+  </si>
+  <si>
+    <t>Multiple collaborators</t>
+  </si>
+  <si>
+    <t>Multiple stocks</t>
+  </si>
+  <si>
+    <t>Chinook, Coho, Chum</t>
+  </si>
+  <si>
+    <t>All Oncorhynchus spp</t>
+  </si>
+  <si>
+    <t>Chum, Chinook</t>
+  </si>
+  <si>
+    <t>Chinook, Coho, Sockeye</t>
+  </si>
+  <si>
+    <t>Northwest Pacific</t>
+  </si>
+  <si>
+    <t>Fraser Interior</t>
+  </si>
+  <si>
+    <t>Pacific Northwest</t>
+  </si>
+  <si>
+    <t>BC Coast</t>
+  </si>
+  <si>
+    <t>BC</t>
+  </si>
+  <si>
+    <t>BC &amp; Yukon</t>
+  </si>
+  <si>
+    <t>Fraser</t>
+  </si>
+  <si>
+    <t>Mainland Inlets</t>
+  </si>
+  <si>
+    <t>East Vancouver Island</t>
+  </si>
+  <si>
+    <t>WCVI Chinook</t>
+  </si>
+  <si>
+    <t>Chilko ES/S sockeye</t>
+  </si>
+  <si>
+    <t>Cultus Lake sockeye</t>
+  </si>
+  <si>
+    <t>Okanagan Chinook</t>
+  </si>
+  <si>
+    <t>Sarita River case study</t>
+  </si>
+  <si>
+    <t>ECVI Georgia Strait Summer Chinook</t>
+  </si>
+  <si>
+    <t>sub_region</t>
+  </si>
+  <si>
+    <t>focus_population</t>
+  </si>
+  <si>
+    <t>Bute Inlet, Toba Inlet, Sechelt Inlet, Gulf Islands/Saanich Inlet, Victoria &amp; Haro Straight, Howe Sound</t>
+  </si>
+  <si>
+    <t>Queen Charlotte Strait, Johnstone Strait, Strait of Georgia</t>
+  </si>
 </sst>
 </file>
 
@@ -3202,7 +3311,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -3228,6 +3337,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3249,18 +3364,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="26">
     <dxf>
       <font>
         <b val="0"/>
@@ -3277,10 +3398,6 @@
         <name val="Calibri"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -3431,6 +3548,45 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
@@ -3683,6 +3839,29 @@
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3697,13 +3876,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C1235FC-468F-46C3-9676-E136DE729105}" name="Table1" displayName="Table1" ref="A1:U44" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
-  <autoFilter ref="A1:U44" xr:uid="{9C1235FC-468F-46C3-9676-E136DE729105}"/>
-  <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{21F25E78-D457-418F-9F78-7DE13AE8CD93}" name="source_file" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{B8BCB027-8A7D-4FCE-803F-A296662A280E}" name="extraction_date" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{683393A0-8045-467F-9A16-95D1CB0C532F}" name="project_id" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{5331C13B-A3FC-484A-95E7-7EAD3A2BB00D}" name="project_title" dataDxfId="19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C1235FC-468F-46C3-9676-E136DE729105}" name="Table1" displayName="Table1" ref="A1:X44" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
+  <autoFilter ref="A1:X44" xr:uid="{9C1235FC-468F-46C3-9676-E136DE729105}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X44">
+    <sortCondition ref="C1:C44"/>
+  </sortState>
+  <tableColumns count="24">
+    <tableColumn id="1" xr3:uid="{21F25E78-D457-418F-9F78-7DE13AE8CD93}" name="source_file" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{B8BCB027-8A7D-4FCE-803F-A296662A280E}" name="extraction_date" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{683393A0-8045-467F-9A16-95D1CB0C532F}" name="project_id" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{5331C13B-A3FC-484A-95E7-7EAD3A2BB00D}" name="project_title" dataDxfId="20"/>
+    <tableColumn id="23" xr3:uid="{B20EF691-6E0B-4ECA-8201-9BC2B73BF9C0}" name="short_title" dataDxfId="19"/>
     <tableColumn id="5" xr3:uid="{65143B71-B457-4DF3-96FB-A320AE4152BD}" name="project_leads" dataDxfId="18"/>
     <tableColumn id="6" xr3:uid="{0B1052C0-47F1-41AA-B13F-BE70DF38178E}" name="collaborations" dataDxfId="17"/>
     <tableColumn id="7" xr3:uid="{1204734C-F170-44F7-B4B4-5C53DC28A923}" name="location" dataDxfId="16"/>
@@ -3711,16 +3894,18 @@
     <tableColumn id="9" xr3:uid="{3B9CC560-9650-4F10-B6EB-A8BB6D19FD2B}" name="waterbodies" dataDxfId="14"/>
     <tableColumn id="10" xr3:uid="{3B74A0C4-6035-471F-BA59-5E5296130A6C}" name="life_history" dataDxfId="13"/>
     <tableColumn id="11" xr3:uid="{83EB77D8-FF38-4BA7-8B8A-C5EB6609BA41}" name="region" dataDxfId="12"/>
-    <tableColumn id="12" xr3:uid="{B5F0F367-295F-4C21-8EF2-8D796262B584}" name="stock" dataDxfId="11"/>
-    <tableColumn id="13" xr3:uid="{592AD976-80C9-41A3-904D-28E27F957093}" name="population" dataDxfId="10"/>
-    <tableColumn id="14" xr3:uid="{0841A155-6170-4816-B52F-62D315F16BB4}" name="cu" dataDxfId="9"/>
-    <tableColumn id="15" xr3:uid="{6A19023B-7495-49F1-A1EC-B098C5E333CF}" name="highlights" dataDxfId="8"/>
-    <tableColumn id="16" xr3:uid="{E075E454-2C61-4348-A20B-0C745E2EC565}" name="background" dataDxfId="7"/>
-    <tableColumn id="17" xr3:uid="{F232593A-A943-4A2F-A957-77EB6182BDA8}" name="methods_findings" dataDxfId="6"/>
-    <tableColumn id="18" xr3:uid="{2F87C396-47EA-4A13-9083-A6C4F71287B3}" name="insights" dataDxfId="5"/>
-    <tableColumn id="19" xr3:uid="{E3203637-205F-4D67-8A5B-15606B06B96D}" name="next_steps" dataDxfId="4"/>
-    <tableColumn id="20" xr3:uid="{71B5C06F-A10D-4B50-AAD8-E218E0D666CD}" name="tables_figures" dataDxfId="3"/>
-    <tableColumn id="21" xr3:uid="{671D065B-E9D7-4645-BF8D-C6523418AA9F}" name="references" dataDxfId="2"/>
+    <tableColumn id="22" xr3:uid="{ED1DE9A2-87F7-4340-A8C7-0C03E532BFBC}" name="sub_region" dataDxfId="11"/>
+    <tableColumn id="24" xr3:uid="{EB63FD23-5CED-4E73-B0F8-2959D0D9A8B2}" name="focus_population" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{B5F0F367-295F-4C21-8EF2-8D796262B584}" name="stock" dataDxfId="9"/>
+    <tableColumn id="13" xr3:uid="{592AD976-80C9-41A3-904D-28E27F957093}" name="population" dataDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{0841A155-6170-4816-B52F-62D315F16BB4}" name="cu" dataDxfId="7"/>
+    <tableColumn id="15" xr3:uid="{6A19023B-7495-49F1-A1EC-B098C5E333CF}" name="highlights" dataDxfId="6"/>
+    <tableColumn id="16" xr3:uid="{E075E454-2C61-4348-A20B-0C745E2EC565}" name="background" dataDxfId="5"/>
+    <tableColumn id="17" xr3:uid="{F232593A-A943-4A2F-A957-77EB6182BDA8}" name="methods_findings" dataDxfId="4"/>
+    <tableColumn id="18" xr3:uid="{2F87C396-47EA-4A13-9083-A6C4F71287B3}" name="insights" dataDxfId="3"/>
+    <tableColumn id="19" xr3:uid="{E3203637-205F-4D67-8A5B-15606B06B96D}" name="next_steps" dataDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{71B5C06F-A10D-4B50-AAD8-E218E0D666CD}" name="tables_figures" dataDxfId="1"/>
+    <tableColumn id="21" xr3:uid="{671D065B-E9D7-4645-BF8D-C6523418AA9F}" name="references" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4005,32 +4190,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U44"/>
+  <dimension ref="A1:X44"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.140625" style="5" customWidth="1"/>
     <col min="3" max="3" width="12.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="96.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" style="1" customWidth="1"/>
-    <col min="7" max="8" width="11.42578125" style="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.28515625" style="1" customWidth="1"/>
-    <col min="11" max="12" width="11.42578125" style="1"/>
-    <col min="13" max="13" width="12.85546875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" style="1"/>
-    <col min="15" max="15" width="11.85546875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="47.85546875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="11.42578125" style="1"/>
-    <col min="19" max="19" width="12.85546875" style="1" customWidth="1"/>
-    <col min="20" max="20" width="15.7109375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="126.85546875" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.42578125" style="1"/>
+    <col min="4" max="4" width="96.140625" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="96.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="8" max="9" width="11.42578125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="48.42578125" style="1" customWidth="1"/>
+    <col min="12" max="14" width="44.7109375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="12.85546875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="11.42578125" style="1"/>
+    <col min="18" max="18" width="11.85546875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="47.85546875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="11.42578125" style="1"/>
+    <col min="22" max="22" width="12.85546875" style="1" customWidth="1"/>
+    <col min="23" max="23" width="15.7109375" style="1" customWidth="1"/>
+    <col min="24" max="24" width="126.85546875" style="1" customWidth="1"/>
+    <col min="25" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4044,58 +4231,67 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>21</v>
       </c>
@@ -4106,63 +4302,72 @@
         <v>22</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>608</v>
-      </c>
-      <c r="E2" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="L2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="R2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N2" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="O2" s="2" t="s">
+      <c r="U2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="V2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="W2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="X2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="S2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="B3" s="4">
         <v>46083</v>
@@ -4171,63 +4376,72 @@
         <v>2394</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="I3" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="M3" t="s">
+        <v>658</v>
+      </c>
+      <c r="N3" t="s">
+        <v>477</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="J3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="U3" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="O3" s="2" t="s">
+      <c r="V3" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="W3" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="X3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="R3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="B4" s="4">
         <v>46083</v>
@@ -4236,63 +4450,72 @@
         <v>2400</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>618</v>
-      </c>
-      <c r="E4" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="S4" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="T4" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="U4" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="V4" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="J4" s="2" t="s">
+      <c r="W4" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="X4" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="B5" s="4">
         <v>46083</v>
@@ -4301,53 +4524,60 @@
         <v>2401</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>609</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>64</v>
+        <v>561</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>592</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>515</v>
+        <v>59</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>515</v>
+        <v>477</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="J5" s="2"/>
+        <v>477</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2" t="s">
+      <c r="M5" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="N5" s="3"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="B6" s="4">
         <v>46083</v>
@@ -4356,63 +4586,72 @@
         <v>2402</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="N6" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="O6" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q6" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="R6" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="S6" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="T6" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="U6" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="V6" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="W6" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L6" s="2" t="s">
+      <c r="X6" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="M6" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="N6" s="2" t="s">
+    </row>
+    <row r="7" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="S6" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="U6" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="B7" s="4">
         <v>46083</v>
@@ -4421,63 +4660,72 @@
         <v>2403</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>610</v>
-      </c>
-      <c r="E7" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="S7" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="T7" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="V7" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="S7" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="U7" s="2" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="B8" s="4">
         <v>46083</v>
@@ -4486,63 +4734,70 @@
         <v>2404</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="N8" s="3"/>
+      <c r="O8" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="V8" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="W8" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="B9" s="4">
         <v>46083</v>
@@ -4551,63 +4806,70 @@
         <v>2405</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>515</v>
+        <v>102</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>639</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>515</v>
+        <v>477</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>246</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>112</v>
+        <v>477</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>515</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="N9" s="3"/>
       <c r="O9" s="2" t="s">
-        <v>114</v>
+        <v>477</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>115</v>
+        <v>477</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>525</v>
+        <v>477</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>118</v>
+        <v>486</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>526</v>
+        <v>106</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X9" s="2" t="s">
+        <v>487</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="B10" s="4">
         <v>46083</v>
@@ -4616,63 +4878,70 @@
         <v>2406</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="N10" s="3"/>
+      <c r="O10" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="W10" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="X10" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="U10" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="B11" s="4">
         <v>46083</v>
@@ -4681,63 +4950,72 @@
         <v>2407</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="E11" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="W11" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="X11" s="2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="U11" s="2" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="B12" s="4">
         <v>46083</v>
@@ -4746,57 +5024,66 @@
         <v>2408</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>611</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>55</v>
+        <v>563</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>599</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>530</v>
+        <v>51</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>56</v>
+        <v>491</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>477</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>531</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
       <c r="R12" s="2" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>532</v>
+        <v>492</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>533</v>
+        <v>134</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="W12" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="X12" s="2" t="s">
+        <v>494</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="B13" s="4">
         <v>46083</v>
@@ -4805,61 +5092,68 @@
         <v>2409</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>154</v>
+        <v>137</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>640</v>
+      </c>
+      <c r="H13" s="2"/>
+      <c r="I13" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>673</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>157</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="N13" s="3"/>
       <c r="O13" s="2" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>159</v>
+        <v>477</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>534</v>
+        <v>144</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>535</v>
+        <v>145</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="W13" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="X13" s="2" t="s">
+        <v>496</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="B14" s="4">
         <v>46083</v>
@@ -4868,63 +5162,70 @@
         <v>2410</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>165</v>
+        <v>148</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>601</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>536</v>
+        <v>149</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>166</v>
+        <v>497</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>477</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>167</v>
+        <v>477</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3" t="s">
+        <v>477</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>169</v>
+        <v>477</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>477</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>620</v>
+        <v>152</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="V14" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="W14" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>572</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="B15" s="4">
         <v>46083</v>
@@ -4933,63 +5234,70 @@
         <v>2412</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>176</v>
+        <v>555</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>641</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>515</v>
+        <v>157</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>515</v>
+        <v>477</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>477</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>56</v>
+        <v>477</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>515</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="N15" s="3"/>
       <c r="O15" s="2" t="s">
-        <v>178</v>
+        <v>477</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>537</v>
+        <v>477</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>538</v>
+        <v>477</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>180</v>
+        <v>498</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>539</v>
+        <v>499</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>540</v>
+        <v>160</v>
+      </c>
+      <c r="V15" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="W15" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="X15" s="2" t="s">
+        <v>501</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="B16" s="4">
         <v>46083</v>
@@ -4998,63 +5306,70 @@
         <v>2413</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>612</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>182</v>
+        <v>564</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>602</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>183</v>
+        <v>163</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>502</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>183</v>
+        <v>164</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>309</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>515</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="N16" s="3"/>
       <c r="O16" s="2" t="s">
-        <v>187</v>
+        <v>477</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>188</v>
+        <v>477</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>189</v>
+        <v>477</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>190</v>
+        <v>167</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>542</v>
+        <v>169</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>192</v>
+        <v>170</v>
+      </c>
+      <c r="V16" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="W16" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="X16" s="2" t="s">
+        <v>172</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="B17" s="4">
         <v>46083</v>
@@ -5063,63 +5378,72 @@
         <v>2416</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>195</v>
+        <v>174</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>604</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>543</v>
+        <v>175</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>196</v>
+        <v>504</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>104</v>
+        <v>96</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>166</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>515</v>
+        <v>180</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>544</v>
+        <v>180</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>201</v>
+        <v>96</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>202</v>
+        <v>477</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>203</v>
+        <v>505</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>205</v>
+        <v>182</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>206</v>
+        <v>183</v>
+      </c>
+      <c r="V17" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="W17" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="X17" s="2" t="s">
+        <v>186</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="B18" s="4">
         <v>46083</v>
@@ -5128,63 +5452,72 @@
         <v>2417</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>209</v>
+        <v>188</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>605</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>515</v>
+        <v>191</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>177</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>213</v>
+        <v>477</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>515</v>
+        <v>193</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>659</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>515</v>
+        <v>194</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>217</v>
+        <v>477</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>545</v>
+        <v>477</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>546</v>
+        <v>195</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>547</v>
+        <v>506</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>548</v>
+        <v>507</v>
+      </c>
+      <c r="V18" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="W18" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="X18" s="2" t="s">
+        <v>509</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="B19" s="4">
         <v>46083</v>
@@ -5193,63 +5526,72 @@
         <v>2418</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>209</v>
+        <v>565</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>606</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>549</v>
+        <v>189</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>220</v>
+        <v>510</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>515</v>
+        <v>199</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>652</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>222</v>
+        <v>477</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>515</v>
+        <v>193</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>659</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>515</v>
+        <v>201</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>550</v>
+        <v>477</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>551</v>
+        <v>477</v>
       </c>
       <c r="R19" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="T19" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="U19" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="V19" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="W19" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="S19" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="T19" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="U19" s="2" t="s">
-        <v>553</v>
+      <c r="X19" s="2" t="s">
+        <v>514</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="B20" s="4">
         <v>46083</v>
@@ -5258,63 +5600,70 @@
         <v>2421</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>614</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>227</v>
+        <v>566</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>607</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="G20" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="N20" s="3"/>
+      <c r="O20" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="T20" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="H20" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="R20" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="S20" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="T20" s="2" t="s">
-        <v>556</v>
-      </c>
       <c r="U20" s="2" t="s">
-        <v>557</v>
+        <v>209</v>
+      </c>
+      <c r="V20" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="W20" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="X20" s="2" t="s">
+        <v>517</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="B21" s="4">
         <v>46083</v>
@@ -5323,63 +5672,72 @@
         <v>2422</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>235</v>
+        <v>212</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>608</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>196</v>
+        <v>213</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>643</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>236</v>
+        <v>176</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>177</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>104</v>
+        <v>215</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>515</v>
+        <v>96</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>216</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>239</v>
+        <v>216</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>240</v>
+        <v>477</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>241</v>
+        <v>477</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>242</v>
+        <v>217</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>243</v>
+        <v>218</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>244</v>
+        <v>219</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>515</v>
+        <v>220</v>
+      </c>
+      <c r="V21" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="W21" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="X21" s="2" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="B22" s="4">
         <v>46083</v>
@@ -5388,63 +5746,70 @@
         <v>2424</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>607</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>515</v>
+        <v>224</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>644</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>248</v>
+        <v>477</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>250</v>
+        <v>227</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>515</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="N22" s="3"/>
       <c r="O22" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>624</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>625</v>
+        <v>477</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>477</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="S22" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="T22" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>626</v>
+        <v>230</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="U22" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="V22" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="W22" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>578</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="B23" s="4">
         <v>46083</v>
@@ -5453,63 +5818,70 @@
         <v>2425</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>258</v>
+        <v>549</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>477</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>156</v>
+        <v>236</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>652</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>261</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="N23" s="3"/>
       <c r="O23" s="2" t="s">
-        <v>262</v>
+        <v>477</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>263</v>
+        <v>477</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>628</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>627</v>
-      </c>
-      <c r="U23" s="3" t="s">
-        <v>629</v>
+        <v>239</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="U23" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="W23" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="X23" s="3" t="s">
+        <v>581</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="B24" s="4">
         <v>46083</v>
@@ -5518,63 +5890,72 @@
         <v>2426</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>599</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>268</v>
+        <v>554</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>553</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>269</v>
+        <v>245</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>271</v>
+        <v>247</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>272</v>
+        <v>248</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>274</v>
+        <v>249</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>662</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>275</v>
+        <v>252</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>276</v>
+        <v>250</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="Q24" s="2" t="s">
-        <v>561</v>
+        <v>251</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>252</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>277</v>
+        <v>253</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>278</v>
+        <v>518</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>279</v>
+        <v>519</v>
       </c>
       <c r="U24" s="2" t="s">
-        <v>562</v>
+        <v>254</v>
+      </c>
+      <c r="V24" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="W24" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="X24" s="2" t="s">
+        <v>520</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="B25" s="4">
         <v>46083</v>
@@ -5583,63 +5964,70 @@
         <v>2427</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>182</v>
+        <v>258</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>612</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>515</v>
+        <v>163</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>282</v>
+        <v>477</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>515</v>
+        <v>259</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>177</v>
+        <v>477</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>283</v>
+        <v>158</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>515</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="N25" s="3"/>
       <c r="O25" s="2" t="s">
-        <v>285</v>
+        <v>477</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>286</v>
+        <v>477</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>563</v>
+        <v>477</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>287</v>
+        <v>262</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>288</v>
+        <v>263</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>289</v>
+        <v>521</v>
       </c>
       <c r="U25" s="2" t="s">
-        <v>564</v>
+        <v>264</v>
+      </c>
+      <c r="V25" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="W25" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="X25" s="2" t="s">
+        <v>522</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>290</v>
+        <v>267</v>
       </c>
       <c r="B26" s="4">
         <v>46083</v>
@@ -5648,63 +6036,72 @@
         <v>2430</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>291</v>
+        <v>545</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>613</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>515</v>
+        <v>268</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>645</v>
       </c>
       <c r="H26" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="J26" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="I26" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>293</v>
-      </c>
       <c r="K26" s="2" t="s">
-        <v>294</v>
+        <v>270</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="N26" s="2" t="s">
-        <v>296</v>
+        <v>271</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>665</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>297</v>
+        <v>272</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>592</v>
+        <v>477</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>566</v>
+        <v>273</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>593</v>
+        <v>274</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>298</v>
+        <v>546</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>594</v>
+        <v>523</v>
       </c>
       <c r="U26" s="2" t="s">
-        <v>515</v>
+        <v>547</v>
+      </c>
+      <c r="V26" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="W26" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="X26" s="2" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="B27" s="4">
         <v>46083</v>
@@ -5713,63 +6110,70 @@
         <v>2432</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>301</v>
+        <v>277</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>614</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>646</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>515</v>
+        <v>278</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>515</v>
+        <v>477</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>250</v>
+        <v>477</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>186</v>
+        <v>228</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M27" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="N27" s="2" t="s">
-        <v>515</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="N27" s="3"/>
       <c r="O27" s="2" t="s">
-        <v>302</v>
+        <v>477</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>303</v>
+        <v>477</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>304</v>
+        <v>477</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>305</v>
+        <v>279</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>306</v>
+        <v>280</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>307</v>
+        <v>281</v>
       </c>
       <c r="U27" s="2" t="s">
-        <v>515</v>
+        <v>282</v>
+      </c>
+      <c r="V27" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="W27" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="X27" s="2" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="B28" s="4">
         <v>46083</v>
@@ -5778,63 +6182,70 @@
         <v>2433</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>310</v>
+        <v>286</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>558</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>311</v>
+        <v>287</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>515</v>
+        <v>288</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>515</v>
+        <v>477</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="N28" s="2" t="s">
-        <v>515</v>
-      </c>
+        <v>477</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="N28" s="3"/>
       <c r="O28" s="2" t="s">
-        <v>568</v>
+        <v>477</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>312</v>
+        <v>477</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>313</v>
+        <v>477</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>314</v>
+        <v>524</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>315</v>
+        <v>289</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>316</v>
+        <v>290</v>
       </c>
       <c r="U28" s="2" t="s">
-        <v>515</v>
+        <v>291</v>
+      </c>
+      <c r="V28" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="W28" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="X28" s="2" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="B29" s="4">
         <v>46083</v>
@@ -5843,63 +6254,72 @@
         <v>2434</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>319</v>
+        <v>295</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>616</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>321</v>
+        <v>297</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>197</v>
+        <v>298</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>322</v>
+        <v>177</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>323</v>
+        <v>299</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>515</v>
+        <v>300</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>261</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="N29" s="2" t="s">
-        <v>324</v>
+        <v>663</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>669</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>631</v>
+        <v>477</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>632</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>633</v>
-      </c>
-      <c r="R29" s="2" t="s">
-        <v>325</v>
+        <v>477</v>
+      </c>
+      <c r="Q29" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>583</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>634</v>
-      </c>
-      <c r="T29" s="2" t="s">
-        <v>326</v>
+        <v>584</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>585</v>
       </c>
       <c r="U29" s="2" t="s">
-        <v>327</v>
+        <v>302</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="W29" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="X29" s="2" t="s">
+        <v>304</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>328</v>
+        <v>305</v>
       </c>
       <c r="B30" s="4">
         <v>46083</v>
@@ -5908,63 +6328,70 @@
         <v>2435</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>602</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>329</v>
+        <v>556</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>617</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>330</v>
+        <v>306</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>331</v>
+        <v>307</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>332</v>
+        <v>308</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="M30" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="N30" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="O30" s="2" t="s">
-        <v>338</v>
+        <v>310</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="3" t="s">
+        <v>313</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>339</v>
+        <v>313</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>340</v>
+        <v>314</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>341</v>
+        <v>315</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>342</v>
+        <v>316</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>343</v>
+        <v>317</v>
       </c>
       <c r="U30" s="2" t="s">
-        <v>515</v>
+        <v>318</v>
+      </c>
+      <c r="V30" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="W30" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="X30" s="2" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>344</v>
+        <v>321</v>
       </c>
       <c r="B31" s="4">
         <v>46083</v>
@@ -5973,63 +6400,72 @@
         <v>2436</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>515</v>
+        <v>322</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>618</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>635</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>347</v>
+        <v>477</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>348</v>
+        <v>323</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>349</v>
+        <v>324</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>350</v>
+        <v>325</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>351</v>
+        <v>326</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>515</v>
+        <v>327</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>352</v>
+        <v>328</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>353</v>
+        <v>477</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>354</v>
+        <v>477</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>355</v>
+        <v>328</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>356</v>
+        <v>329</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>357</v>
+        <v>330</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>358</v>
+        <v>331</v>
       </c>
       <c r="U31" s="2" t="s">
-        <v>569</v>
+        <v>332</v>
+      </c>
+      <c r="V31" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="W31" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="X31" s="2" t="s">
+        <v>525</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>359</v>
+        <v>335</v>
       </c>
       <c r="B32" s="4">
         <v>46083</v>
@@ -6038,63 +6474,70 @@
         <v>2437</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>361</v>
+        <v>336</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>619</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>331</v>
+        <v>337</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>647</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>364</v>
+        <v>308</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>477</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="N32" s="2" t="s">
-        <v>368</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="N32" s="3"/>
       <c r="O32" s="2" t="s">
-        <v>571</v>
+        <v>339</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>369</v>
+        <v>340</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>370</v>
+        <v>341</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>371</v>
+        <v>526</v>
       </c>
       <c r="S32" s="2" t="s">
-        <v>372</v>
+        <v>342</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>373</v>
+        <v>343</v>
       </c>
       <c r="U32" s="2" t="s">
-        <v>374</v>
+        <v>344</v>
+      </c>
+      <c r="V32" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="W32" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="X32" s="2" t="s">
+        <v>347</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>375</v>
+        <v>348</v>
       </c>
       <c r="B33" s="4">
         <v>46083</v>
@@ -6103,63 +6546,68 @@
         <v>2439</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>376</v>
+        <v>567</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>620</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>377</v>
+        <v>349</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>527</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>515</v>
+        <v>350</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>653</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>515</v>
+        <v>477</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="N33" s="2" t="s">
-        <v>515</v>
-      </c>
+        <v>477</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
       <c r="O33" s="2" t="s">
-        <v>380</v>
+        <v>477</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>573</v>
+        <v>477</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>381</v>
+        <v>477</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>382</v>
+        <v>351</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>383</v>
+        <v>528</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>384</v>
+        <v>352</v>
       </c>
       <c r="U33" s="2" t="s">
-        <v>574</v>
+        <v>353</v>
+      </c>
+      <c r="V33" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="W33" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="X33" s="2" t="s">
+        <v>529</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>385</v>
+        <v>356</v>
       </c>
       <c r="B34" s="4">
         <v>46083</v>
@@ -6168,63 +6616,72 @@
         <v>2442</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="F34" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="P34" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q34" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="R34" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="S34" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="T34" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="N34" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="O34" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="P34" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="Q34" s="3" t="s">
-        <v>623</v>
-      </c>
-      <c r="R34" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="S34" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="T34" s="3" t="s">
-        <v>630</v>
-      </c>
       <c r="U34" s="2" t="s">
-        <v>515</v>
+        <v>364</v>
+      </c>
+      <c r="V34" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="W34" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="X34" s="2" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>396</v>
+        <v>366</v>
       </c>
       <c r="B35" s="4">
         <v>46083</v>
@@ -6233,63 +6690,72 @@
         <v>2443</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>398</v>
+        <v>367</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>622</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>576</v>
+        <v>368</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>399</v>
+        <v>531</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>400</v>
+        <v>369</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>246</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>401</v>
+        <v>370</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="N35" s="2" t="s">
-        <v>402</v>
+        <v>371</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>666</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>403</v>
+        <v>370</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>622</v>
+        <v>477</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>405</v>
+        <v>373</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="T35" s="2" t="s">
-        <v>577</v>
+        <v>374</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>574</v>
       </c>
       <c r="U35" s="2" t="s">
-        <v>515</v>
+        <v>375</v>
+      </c>
+      <c r="V35" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="W35" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="X35" s="2" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>407</v>
+        <v>377</v>
       </c>
       <c r="B36" s="4">
         <v>46083</v>
@@ -6298,63 +6764,72 @@
         <v>2447</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>408</v>
+        <v>568</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>623</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>578</v>
+        <v>378</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>409</v>
+        <v>533</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>409</v>
+        <v>379</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>177</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>410</v>
+        <v>379</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>104</v>
+        <v>380</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="N36" s="2" t="s">
-        <v>411</v>
+        <v>96</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>664</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>412</v>
+        <v>96</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>413</v>
+        <v>477</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>414</v>
+        <v>381</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>415</v>
+        <v>382</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>416</v>
+        <v>383</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>417</v>
+        <v>384</v>
       </c>
       <c r="U36" s="2" t="s">
-        <v>579</v>
+        <v>385</v>
+      </c>
+      <c r="V36" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="W36" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="X36" s="2" t="s">
+        <v>534</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="B37" s="4">
         <v>46083</v>
@@ -6363,63 +6838,72 @@
         <v>2448</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>617</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>419</v>
+        <v>569</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>624</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>56</v>
+        <v>389</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>390</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>197</v>
+        <v>52</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>421</v>
+        <v>177</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>422</v>
+        <v>391</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>423</v>
+        <v>392</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="M37" s="2" t="s">
-        <v>424</v>
+        <v>393</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>515</v>
+        <v>391</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>425</v>
+        <v>391</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>426</v>
+        <v>394</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>427</v>
+        <v>477</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>580</v>
+        <v>395</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>428</v>
+        <v>396</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>429</v>
+        <v>397</v>
       </c>
       <c r="U37" s="2" t="s">
-        <v>430</v>
+        <v>535</v>
+      </c>
+      <c r="V37" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="W37" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="X37" s="2" t="s">
+        <v>400</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>431</v>
+        <v>401</v>
       </c>
       <c r="B38" s="4">
         <v>46083</v>
@@ -6428,63 +6912,72 @@
         <v>2449</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>432</v>
+        <v>557</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>625</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>581</v>
+        <v>402</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>515</v>
+        <v>536</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>515</v>
+        <v>477</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>652</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>434</v>
+        <v>477</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>435</v>
+        <v>403</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>438</v>
+        <v>404</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>668</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>439</v>
+        <v>405</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>440</v>
+        <v>406</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>441</v>
+        <v>407</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>442</v>
+        <v>408</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>443</v>
+        <v>409</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="U38" s="2" t="s">
-        <v>445</v>
+        <v>411</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="W38" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="X38" s="2" t="s">
+        <v>414</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>446</v>
+        <v>415</v>
       </c>
       <c r="B39" s="4">
         <v>46083</v>
@@ -6493,63 +6986,72 @@
         <v>2451</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>361</v>
+        <v>416</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>626</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>515</v>
+        <v>337</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>331</v>
+        <v>477</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>448</v>
+        <v>308</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>177</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>323</v>
+        <v>417</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>186</v>
+        <v>300</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="M39" s="2" t="s">
-        <v>448</v>
+        <v>166</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>166</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>449</v>
+        <v>417</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>450</v>
+        <v>417</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>451</v>
+        <v>417</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>452</v>
+        <v>418</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>582</v>
+        <v>419</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>453</v>
+        <v>420</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>454</v>
+        <v>421</v>
       </c>
       <c r="U39" s="2" t="s">
-        <v>515</v>
+        <v>537</v>
+      </c>
+      <c r="V39" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="W39" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="X39" s="2" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B40" s="4">
         <v>46083</v>
@@ -6558,63 +7060,72 @@
         <v>2452</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>361</v>
+        <v>425</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>627</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>331</v>
+        <v>297</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>197</v>
+        <v>308</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>457</v>
+        <v>177</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>323</v>
+        <v>426</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>458</v>
+        <v>300</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="M40" s="2" t="s">
-        <v>460</v>
+        <v>427</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>659</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>461</v>
+        <v>429</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>462</v>
+        <v>428</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>463</v>
+        <v>429</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>583</v>
+        <v>430</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>464</v>
+        <v>431</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>465</v>
+        <v>432</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>466</v>
+        <v>538</v>
       </c>
       <c r="U40" s="2" t="s">
-        <v>584</v>
+        <v>433</v>
+      </c>
+      <c r="V40" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="W40" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="X40" s="2" t="s">
+        <v>539</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>467</v>
+        <v>436</v>
       </c>
       <c r="B41" s="4">
         <v>46083</v>
@@ -6623,63 +7134,70 @@
         <v>2504</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>585</v>
+        <v>437</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>637</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>470</v>
+        <v>540</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>473</v>
+        <v>438</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>477</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="M41" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="N41" s="2" t="s">
-        <v>476</v>
-      </c>
+        <v>439</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N41" s="3"/>
       <c r="O41" s="2" t="s">
-        <v>477</v>
+        <v>440</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>478</v>
+        <v>441</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>479</v>
+        <v>441</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>480</v>
+        <v>442</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>481</v>
+        <v>443</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>482</v>
+        <v>444</v>
       </c>
       <c r="U41" s="2" t="s">
-        <v>483</v>
+        <v>445</v>
+      </c>
+      <c r="V41" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="W41" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="X41" s="2" t="s">
+        <v>448</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>484</v>
+        <v>449</v>
       </c>
       <c r="B42" s="4">
         <v>46083</v>
@@ -6688,63 +7206,72 @@
         <v>2513</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>486</v>
+        <v>450</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>629</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>648</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>197</v>
+        <v>451</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>250</v>
+        <v>164</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>104</v>
+        <v>228</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="M42" s="2" t="s">
-        <v>515</v>
+        <v>96</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>166</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>515</v>
+        <v>452</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>488</v>
+        <v>452</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>587</v>
+        <v>477</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>588</v>
+        <v>453</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>490</v>
+        <v>454</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>491</v>
+        <v>541</v>
       </c>
       <c r="U42" s="2" t="s">
-        <v>589</v>
+        <v>542</v>
+      </c>
+      <c r="V42" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="W42" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="X42" s="2" t="s">
+        <v>543</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>492</v>
+        <v>457</v>
       </c>
       <c r="B43" s="4">
         <v>46083</v>
@@ -6753,63 +7280,70 @@
         <v>2545</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>494</v>
+        <v>458</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>630</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>496</v>
+        <v>459</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>649</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>31</v>
+        <v>460</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>477</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M43" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N43" s="2" t="s">
-        <v>31</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="N43" s="3"/>
       <c r="O43" s="2" t="s">
-        <v>499</v>
+        <v>28</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>501</v>
+        <v>28</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>502</v>
+        <v>461</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>503</v>
+        <v>462</v>
       </c>
       <c r="T43" s="2" t="s">
-        <v>504</v>
+        <v>463</v>
       </c>
       <c r="U43" s="2" t="s">
-        <v>515</v>
+        <v>464</v>
+      </c>
+      <c r="V43" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="W43" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="X43" s="2" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>505</v>
+        <v>467</v>
       </c>
       <c r="B44" s="4">
         <v>46083</v>
@@ -6818,56 +7352,63 @@
         <v>3682</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>507</v>
+        <v>468</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>631</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="G44" s="2"/>
-      <c r="H44" s="3" t="s">
-        <v>515</v>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="H44" s="2"/>
       <c r="I44" s="3" t="s">
-        <v>515</v>
+        <v>652</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>515</v>
+        <v>477</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>515</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="N44" s="3"/>
       <c r="O44" s="3" t="s">
-        <v>635</v>
-      </c>
-      <c r="P44" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="Q44" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="R44" s="2" t="s">
-        <v>511</v>
+        <v>477</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>587</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>512</v>
+        <v>471</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>513</v>
+        <v>472</v>
       </c>
       <c r="U44" s="2" t="s">
-        <v>590</v>
+        <v>473</v>
+      </c>
+      <c r="V44" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="W44" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="X44" s="2" t="s">
+        <v>544</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/pssi_form_data_altered.xlsx
+++ b/data/processed/pssi_form_data_altered.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ennsj\Documents\PSSI-final-tech-report\data\processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26259EBF-E6DC-48D2-9D16-B8C77A01F6B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987695FB-23C7-41D9-8D88-06E31FD7BDBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1485" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="632">
   <si>
     <t>source_file</t>
   </si>
@@ -507,14 +507,6 @@
     <t>2408 PSSI Science Project Reporting_Long_Project.docx</t>
   </si>
   <si>
-    <t>See Supplemental Table 1</t>
-  </si>
-  <si>
-    <t>See Supplemental Table 1
----
-See Supplemental Table 1</t>
-  </si>
-  <si>
     <t>- The project focused on developing, validating, and implementing quantitative PCR (qPCR) assays for seven endemic fish pathogens in British Columbia to improve disease detection and support salmon health management.
 - Targeted surveillance revealed differences in pathogen prevalence among salmon stocks and tissues, with *F. psychrophilum* more frequently detected in spleen samples than kidney, alongside observed genetic diversity in isolates. For *R. salmoninarum*, ELISA testing was more reliable than qPCR, with non-lethal sampling methods under ongoing evaluation.
 - Improved diagnostic tools enhance pathogen detection and understanding of disease prevalence, aiding targeted interventions in salmon hatcheries.</t>
@@ -625,9 +617,6 @@
   </si>
   <si>
     <t>2412 PSSI Science Project Reporting_Pearce_Mackenzie_Forster_Neville.docx</t>
-  </si>
-  <si>
-    <t>Chris Pearce, Clara Mackenzie, Ian Forster (DFO, Nearshore Ecosystems Section)</t>
   </si>
   <si>
     <t>Chrys Neville (DFO, Salmon Marine Interactions Program, Regional Ecosystem Effects on Fish &amp; Fisheries Section)</t>
@@ -1489,9 +1478,6 @@
   </si>
   <si>
     <t>2447 PSSI Reporting - Fit-Chips and eDNA Project .docx</t>
-  </si>
-  <si>
-    <t>Kristi Saunders (retired), Christoph Deeg, Arthur Bass, Carl Llewellyn</t>
   </si>
   <si>
     <t>WCVI sounds</t>
@@ -1585,9 +1571,6 @@
     <t>2448 PSSI_Science_Project_Reporting.docx</t>
   </si>
   <si>
-    <t>Christoph Deeg, Kristi Miller-Saunders (retired), Karia Kaukinen, Arthur Bass</t>
-  </si>
-  <si>
     <t>**SEP Hatcheries**: Nitinat River Hatchery, Robertson Creek Hatchery, Chehalis River Hatchery, Tenderfoot Hatchery, and Puntledge Creek Hatchery.</t>
   </si>
   <si>
@@ -1770,15 +1753,7 @@
     <t>Genetic associations with age of return in male Canadian Chinook salmon</t>
   </si>
   <si>
-    <t>Atnarko River, Chilliwack River, Big Qualicum River, Puntledge River</t>
-  </si>
-  <si>
     <t>Central coast, Fraser Valley, East Coast Vancouver Island</t>
-  </si>
-  <si>
-    <t>Atnarko River, Chilliwack River Fall, Big Qualicum River, Puntledge River Fall
----
-Atnarko River, Chilliwack River Fall, Big Qualicum River, Puntledge River Fall</t>
   </si>
   <si>
     <t>Atnarko River, Chilliwack River Fall, Big Qualicum River, Puntledge River Fall</t>
@@ -1911,13 +1886,6 @@
     <t>Robertson</t>
   </si>
   <si>
-    <t>- The goal of the project was to better characterize contaminant levels and evaluate their potential impacts on the health of juvenile Chinook from the West Coast of Vancouver Island.
-- 12 contaminant classes were analyzed in two composite samples collected in 2022 from Barkley Sound (completed) and polychlorinated biphenyls (PCBs), polycyclic aromatic hydrocarbons (PAHs) and metals were analysed in individual fish collected in 2023 and 2024 in Clayoquot Sound and Barkley Sound (in progress).
-- Metals, PAHs, and PCBs were the top three contaminant classes detected with the highest concentrations in the two composite samples from Barkley Sound.
-- Comparing our results to established effects thresholds, juvenile Chinook salmon from Barkley Sound may be at low risk of exposure to contaminants, specifically PCBs, PBDEs, Dichlorodiphenyltrichloroethane (DDT), PAHs and mercury.
-- Concentrations of contaminant classes measured in WCVI juvenile Chinook Salmon range from 3 to 100x lower than levels of contaminant classes documented in juvenile Chinook in the Fraser River. As such contaminant levels in WCVI juvenile provide a benchmark of 'lower' levels reflecting lower urban and industrial associated sources.</t>
-  </si>
-  <si>
     <t>The marine environment is under significant anthropogenic pressures including overfishing, habitat degradation shipping, climate change and contaminants (Quinn, 2018). Although declines in Chinook salmon abundance are thought to be linked to freshwater, estuarine and marine environmental conditions, contaminants may also play a role, especially exposure to contaminants during their early life stage. For example, exposure to contaminants in freshwater and/or estuaries have been shown to impact growth and survival of juvenile Chinook salmon (Lundin et al., 2019, 2023; Zabel et al., 2004; Meador et al., 2014).
 A variety of contaminants have been detected in adult Chinook salmon collected from the West Coast of Vancouver Island (WCVI) (Holbert et al., 2024). Some of the highest concentrations (on a lipid weight basis) of alkylphenols (APs), total hexachlorocyclohexane (HCH), short chain chlorinated paraffins (SCCPs) and medium-chain chlorinated paraffins (MCCPs) have also been measured in WCVI adult Chinook relative to other stocks (Brown and Holbert, unpublished data). Juvenile salmon are exposed to a variety of contaminants during their seaward migration depending on the characteristics and anthropogenic activities of the watershed. In their study of hatchery-reared Chinook salmon, Meador et al. (2014) found that individuals transiting through contaminated estuaries had a survival rate that was 45% lower than for those transiting through uncontaminated estuaries. To better characterize contaminant levels and evaluate their potential impacts on the health of juvenile Chinook, we collected juvenile Chinook salmon throughout Barkley Sound on the WCVI in July 2022 to evaluate the levels of over 700 compounds from 12 different contaminant classes. In addition, PCBs, PAHs and metals were analysed in individual fish collected in 2023 and 2024 in Clayoquot Sound and Barkley Sound. This project was conducted in partnership with the Follow the Fish program.</t>
   </si>
@@ -2045,20 +2013,6 @@
   </si>
   <si>
     <t>Ahousaht First Nation, Hesquiaht First Nation, Tla-o-qui-aht First Nation, Nuu-cha-nulth Tribal Council, Nature Trust of BC, Maaqutusiis Hahoulthee Stewardship Society</t>
-  </si>
-  <si>
-    <t>Our observational methods are traditionally used in oceanographic research, e.g. sampling temperature, salinity and oxygen profiles with a CTD instrument as well as deploying moorings and weather stations. However, the innovative aspect is the collaboration with local communities. These collaborations allowed for sampling at a much higher frequency (~monthly) than anything achievable by DFO alone, but still maintaining DFO's high-quality data standards (thanks to training and data post-processing and quality control by DFO). As a reference, DFO-led sampling provided 82 CTD profiles in 2019 (mostly from March and October/November) and 122 profiles in 2024 (a well-sampled year through many PSSI projects), while this project's Nation-led sampling in 2024 provided 150 profiles (mostly monthly from March to December). Beyond the scientific benefits, these collaborations were essential for building long-term relationships with First Nations partners, fostering mutual trust, and creating a framework for ongoing knowledge exchange between Indigenous knowledge systems and western scientific approaches.
-In terms of modelling, the WCVI model has been developed and run for 2019, 2024 (to take advantage of the intensive PSSI-related sampling) and one future scenario centered in 2055. Simulations for 2019 and 2024 have been compared against observations and show good agreement, particularly temperature and salinity. Biogeochemical variables (e.g., oxygen, nitrate) show good performance on the shelf, but some further calibration is needed to reach the desired performance inside the inlets. Figure 1 shows the model domain and bathymetry.
-Analyses of model outputs in Clayoquot Sound indicate that the inlets towards the south are warmer and fresher than those on the north at all levels of the water column and all three seasons analyzed (spring, summer, autumn). These conditions are due to stronger freshwater inputs, shallower bathymetry and a less direct connection with the shelf waters in southern inlets (Tofino to Bedwell) compared with northern inlets (Herbert to Sydney). In particular, model results allowed to study the role of the sills (particularly the shallow one outside of Herbert Inlet), which play a leading role modulating the deeper waters of the inlets (due to strong mixing at the sill and strong tidal advection).
-When comparing model results against temperature values that result in stress responses by Chinook salmon (above 16 to 18Â°C, personal communication by PSSI colleague Christoph Deeg), we find that the surface waters of all inlets may exceed these thresholds in summer under present-day conditions (Figure 2a). Furthermore, Tofino Inlet shows waters above these thresholds at all depths (Figure 3). When analyzing the same thresholds under the future scenario, they are exceeded mostly everywhere in the Sound in the top 5 meters (Figure 2b,c), and exceeded at depth in the southern inlets (from Bedwell to Tofino).
-Once the performance of the biogeochemical module of the WCVI is deemed appropriate, a similar analysis will be performed with oxygen, considering that salmon show signs of stress at environmental values lower than 6 to 8 mg L-1 (Christoph Deeg, personal communication). Nevertheless, from the observational record we find that Clayoquot Sound shows throughout the year oxygen concentrations that fall below these thresholds, even near the surface from spring to autumn (Figure 4).
-Two peer-reviewed publications are being prepared to discuss these results, while two manuscripts are already published discussing the low near-surface oxygen conditions (Rosen et al, 2022) and describing the model (Foreman et al, 2024). Informal presentations and updates were provided regularly to Gemma Macfarlane, the Stewardship Biologist from Maaqutusiis Hahoulthee Stewardship Society from Ahousaht Nation, as well as to project collaborators. A formal presentation was provided at the last Pacific Salmon Science Symposium in December 2025 and two other ones are scheduled in January and March 2026 to the Maa-nuult Joint Fisheries Committee (JFC) Technical Meeting Series and the State of the Pacific Ocean meeting, respectively. A presentation at a scientific meeting was planned for February 2026, but travel was not approved.</t>
-  </si>
-  <si>
-    <t>Figure 1. West coast Vancouver Island (WCVI) model domain. Colourscale shows the model bathymetry (in meters)
-Figure 2. Maps of Clayoquot Sound showing the percentage of the top 5m of the water column exceeding 17Â°C in summer (July, August and September) in the (a) simulation for 2024 and (b) future scenario. Panel (c) shows the difference between both (future scenario minus 2024 simulation), highlighting the additional percentage of the surface waters that can exceed the temperature threshold in the future scenario.
-Figure 3. Time series of the percentage of water volume that exceeds 17Â°C in Tofino inlet at different depth ranges and different simulations. Bold colours indicate the future scenario, while paler colours indicate the 2024 simulation. Green colours indicate the volume in the surface depth range (0 to 5 m), blue colours represent upper waters below the surface (5 to 20 m) and black/grey represent deep waters (20 to 100 m). At surface, both simulations exceed the threshold between spring and autumn, while below 5 m the threshold is exceeded mostly in the future scenario.
-Figure 4. Location of the CTD profiles with oxygen data from 2024. The oxygen histograms show the distribution of oxygen data for the whole 2024 year and four seasons (winter: Jan-Mar, spring: Apr-Jun, summer: Jul-Sep, and winter: Oct-Dec). The different colours show the histograms for four different depth ranges: the whole water column (blue), top 50 meters (orange), top 20 meters (yellow) and top 5 meters (purple).</t>
   </si>
   <si>
     <t>*Overview of the model*
@@ -2087,13 +2041,6 @@
 Peterman, R.M., Dorner, B. 2012. A widespread decrease in productivity of sockeye salmon (*Oncorhynchus nerka*) populations in western North America. Can. J. Fish. Aquat. Sci. 69: 1255-1260.
 Peterson, W.T., Schwing, F.B. 2003. A new climate regime in northeast Pacific ecosystems. Geo. Res. Lett. 30: 1896.
 Werner, A.T., Schnorbus, M.A., Shrestha, R.R., Cannon, A.J., Zwiers, F.W., Dayon G. Anslow, F. 2019. A long-term, temporally consistent, gridded daily meteorological dataset for northwestern North America,Â Scientific Data, 6:180299.</t>
-  </si>
-  <si>
-    <t>This project mainly used sediment cores, with water samples and electronic (CTD) data profiles to support the interpretation of environmental conditions.
-SEDIMENT CORES: Fourteen new sediment cores 40-50 cm long were collected in BC mainland inlets in 2022-2025 (Figure 1), using a box corer (0.1 m2 cross-sectional area). Cores were subsampled into 1-cm intervals over the top 10 cm, 2-cm intervals for 10-20 cm and 5-cm intervals from 20 cm to the bottom. The sampling resolution was highest near the surface to help define the surface mixed layer. The sediment accumulation rate and mixed layer depth for each core were determined using depth profiles of the radioisotopes Pb-210 and Ra-226. Radioisotopes were analyzed by Flett Research Ltd., in Manitoba, following the procedure of Eakins and Morrison (1978) and Mathieu et al. (1988). The composition of organic matter was determined by analysis of organic carbon and nitrogen at the University of British Columbia, using a CHN analyzer (following Calvert and Pedersen, 1995). Stable isotopes of carbon and nitrogen were determined at the University of British Columbia or at the University of Windsor, using mass spectrometry (Calvert et al., 2001). The proportions of marine-derived and terrigenous organic matter were calculated based on isotopic endmembers previously determined in BC coastal waters (Johannessen et al., 2021; Johannessen et al., 2019). The fluxes of marine and terrigenous organic matter were determined by multiplying the proportions of each by the % total organic carbon and by the sediment accumulation rate. The fluxes were used to determine trends in each type of organic matter over time.
-CTD PROFILES AND WATER SAMPLING: Profile data were collected using a SeaBird SBE911 CTD with sensors for temperature, salinity, dissolved oxygen, transmissivity (red: 660nm, green: 550 nm) and chlorophyll fluorescence. Water samples were collected using a standard 24-bottle rosette collected on the up-cast. Water samples were analyzed unfiltered for nutrients (nitrate, phosphate, silicate) at the Institute of Ocean Sciences, using a Technicon AutoAnalyzerâ„¢ II (Barwell-Clarke and Whitney, 1996). Nutrient data will be interpreted by calculating molar ratios of Si:N:P and comparing the ratios with those calculated for the Strait of Georgia and Puget Sound. (In Puget Sound, the Si:N ratio has declined since the 1990s, affecting the phytoplankton species assemblage, while the ratio has remained stable in the Strait of Georgia (unpublished data)).
-DATA ARCHIVING: Following quality control, data were archived in the OSD Data Archive at the Institute of Ocean Sciences and made available through the Waterproperties.ca website.
-DELAYS: There were some unforeseen delays in field work and sample analysis. Two sampling cruises were cancelled, and a change in Coast Guard policy that made it impossible to collect sediment cores and water samples during the same cruise, which meant that the field work portion of the project took longer than anticipated. In addition, three labs that had previously analyzed stable isotopes all stopped offering that service, and it took some time to identify a new lab. As a result, some data were only received this month, with the rest of the outstanding data due by March 31. Consequently, only a preliminary interpretation is possible at this time. Interpretation will be completed in the coming fiscal year.</t>
   </si>
   <si>
     <t>Figure 1. Chinook-bearing river systems on the WCVI that have been genetically sequenced and included in the library for stock assignment with GSI and PBT. Color coding indicates how populations were aggregated for individual stock assignments and shapes indicate how river systems fall in the South-West Vancouver Island (SWVI), Nootka-Kyuquot (NoKy) and North-West Vancouver Island (NWVI) Conservation Units.
@@ -2125,194 +2072,11 @@
     <t>Kyle Garver, DFO; Ahmed Siah, BC Centre for Aquatic Health Sciences</t>
   </si>
   <si>
-    <t>Validation and transfer of diagnostic assays for endemic pathogens
-In consultation with SEP veterinarians and fish health staff, the project identified seven endemic pathogens for which there was a need for improved diagnostic assays. Due to the need for high-capacity and rapid diagnostics, quantitative PCR (qPCR) assays were chosen for their accuracy and reliability. The targeted pathogens were as follows: *Tetracapsuloides bryosalmonae* (Bettge et al., 2009), *Flavobacterium columnare* (Gibbs et al., 2020), *Flavobacterium psychrophilum* (Ma et al., 2019; Marancik &amp; Wiens, 2013), *Renibacterium salmoninarum* (Richmond &amp; Plant, 2021), *Ichthyophthirius multifiliis* (Howell et al., 2019), IHNV (Purcell et al., 2013), and *Nucleospora salmonis* (Badil et al., 2011). Where pathogen nucleic acids were unavailable, synthetic double-stranded DNA fragments (gBlocksâ„¢) were used for validation work, e.g. limits of detection and quantification. In collaboration with BC Centre for Aquatic Health Sciences, the *R. salmoninarum* qPCR assay underwent interlaboratory validation in which both labs screened 170 samples. The results showed substantial agreement between labs (Cohen's Îº=0.68), confirming the reliability of assay transfer. Post-validation, assays were implemented to assist the FDL in disease investigations.
-To ensure effective knowledge transfer, standard operating procedures were developed by the AAH team and shared with FDL staff. Training sessions covered all aspects of assay implementation, enabling FDL personnel to independently conduct analyses.
-Deployment of assays for pathogen surveillance
-In addition to assay validation and technology transfer, this project also focused on collection and analysis of longitudinal data on two high-priority pathogens: *F. psychrophilum* and *R. salmoninarum*. *F. psychrophilum* is the causative agent of bacterial coldwater disease and infections can cause significant disease and mortality in juvenile, hatchery-reared salmonids. Identified knowledge gaps for *F. psychrophilum* in BC include overall prevalence in broodstock, and the linkage between female broodstock bacterial load and outbreaks in fry. While outbreaks are common at most SEP facilities rearing salmonids, outbreaks are notably acute in Harrison River Chinook salmon (HRCS).
-Surveillance conducted between 2023 and 2025 determined that prevalence was approximately 40% in HRCS broodstock during 2023-2024, with a significant reduction in 2025 (Ï‡2=12.6, *p* &lt; 0.01) (Table 1). It is possible that prevalence is cyclical in this stock but additional screening is necessary. Chehalis River broodstock, reared under similar conditions, showed comparable infection rates to HRCS in 2024, suggesting genetic differences between stocks may influence outbreak intensity.
-Both kidney and spleen were collected to determine which tissue would be best for routine sampling. Agreement between the two tissues was slight (Cohen's Îº=0.16). The number of positive fish based on spleen results was more than double that of kidney indicating that spleen is more likely to result in a positive detection. Tissues were also streaked on bacterial agar and evaluated for growth of yellow-pigmented bacteria morphologically similar to *F. psychrophilum*. Using novel sequencing techniques, we identified unexpected genetic heterogeneity within *F. psychrophilum* isolates from BC.
-In 2024, the SEP Fish Health group conducted a pilot study to evaluate the effectiveness of pre-fertilization egg disinfection in reducing bacterial loads. Unfertilized eggs from 20 HRCS females were treated in an OvadineÂ®:saline solution (100 ppm:0.75%) for 15 minutes. Egg disinfection is typically carried out post-fertilization; however, iodophor cannot penetrate eggs to eliminate bacteria already present within. A previous study by Lennox et al. (2023) suggested that pre-fertilization disinfection in an iodophor:saline solution may decrease intra-egg bacterial concentrations, supporting the basis for this pilot. Eggs from each female were sampled at three key stages (pre-fertilization and pre-treatment, pre-fertilization and post-treatment, and post-fertilization and post-treatment) and screened for *F. psychrophilum* by AAH staff. The number of positive samples decreased from eight (pre-treatment and pre-fertilization) to one (post-treatment and post-fertilization). Fish were not monitored post-hatch, so long-term effectiveness of the treatment could not be assessed, though no adverse impacts on fertilization or hatching were noted.
-The study was repeated in fall 2025, expanding to include all HRCS eggs as well as all chum salmon eggs at the Tenderfoot hatchery. Samples from the HRCS eggs were collected and will be analyzed using qPCR before the end of the fiscal year to further evaluate the efficacy of this treatment approach.
-*R. salmoninarum* is the causative agent of Bacterial Kidney Disease (BKD), and is vertically transmitted from female broodstock to progeny. As such, kidney is collected from spawning female broodstock and submitted to the FDL for BKD screening using an enzyme-linked immunosorbent assay (ELISA). In the current study, 637 samples were screened by ELISA and qPCR. Assay agreement was slight (Cohen's Îº=0.20), and overall, more samples were positive by ELISA as compared to qPCR. The ELISA measures bacterial antigen concentrations and serves as a proxy for previous *R. salmoninarum* exposure. Conversely, the qPCR measures the total amount of nucleic acid present, i.e. an active infection. Therefore, although the *R. salmoninarum* qPCR assay is sensitive and specific, the ELISA remains the gold standard method for broodstock screening. Longitudinal surveillance of select stocks was also conducted from 2023 through 2025 (Table 2). Prevalence, as determined by ELISA, is high at these facilities every year. Results from 2025 are pending but will be available by the end of this fiscal year.
-This project also explored the use of non-lethal sampling methods for *R. salmoninarum*. To do so, lethal (kidney) and non-lethal (mucus, gill clip, anal fin clip, and ventral swab) samples were collected from female broodstock at Nitinat and Big Q hatcheries. All samples were screened by the qPCR assay and kidney was also screened by ELISA (Table 3). In 2024, results showed limited agreement between non-lethal samples and kidney, with mucus samples providing the highest detection rates. Given the amount of handling during the spawning process, mucus also has the highest risk of contamination. Consequently, mucus sampling was excluded in 2025, with evaluation ongoing for gill clip and anal fin sampling methods.</t>
-  </si>
-  <si>
-    <t>Table 1. Longitudinal surveillance results for *Flavobacterium psychrophilum*. Broodstock were classified as positive if the bacterium was re-isolated from tissue samples or if tissues tested positive by qPCR. Total prevalence was calculated as the number of unique positive broodstock identified by qPCR and/or culture divided by the total number of samples collected. Subscripts denote statistically significant differences in prevalence among years (Ï‡2=12.6, *P* &lt; 0.01).
-Stock
-Year
-Total prevalence (No. screened)
-Harrison River
-2023
-0.43a (121)
-2024
-0.44a (122)
-2025
-0.25b (125)
-Chehalis River
-2024
-0.2 (60)
-Table 2. Longitudinal surveillance results for *R. salmoninarum* at select facilities. Broodstock were classified as positive if the ELISA optical density value was greater than the mean optical density of the negative control or kidney tested positive by qPCR. ELISA prevalence estimates included samples classified as 'low level of detection' as these samples are considered positive but are often kept by facilities.
-Facility
-Species
-2023
-2024
-No. of samples
-ELISA prevalence
-qPCR prevalence
-No. of samples
-ELISA prevalence
-qPCR prevalence
-Big Q
-Coho
-30
-0.93
-0.03
-60
-0.83
-0.05
-Chehalis
-Coho
-30
-0.93
-0.13
-60
-1
-0.07
-Inch Creek
-Coho
-20
-0.95
-0.05
-60
-1
-0.02
-Nitinat
-Coho
-40
-1
-0.55
-45
-1
-0.18
-Puntledge
-Coho
-20
-1
-0.35
-88
-0.86
-0.25
-Puntledge summer
-Chinook
-11
-1
-0.09
-18
-0.94
-0
-Table 3. Non-lethal BKD screening samples. Female Coho salmon broodstock were sampled at both facilities. Agreement values were calculated using Cohen's kappa analysis and all tissues were compared to kidney.
-Year
-Facility
-No. sampled
-Samples collected
-Sample agreement
-2024
-Nitinat
-40
-Kidney
-Gill clip
-Mucus
-Ventral swab
-Anal fin clip
-Gill: &lt;0
-Mucus: 0.11
-Ventral swab: 0.085
-Anal fin clip: &lt;0
-2025
-Nitinat
-40
-Kidney
-Gill clip
-Anal fin
-NA
-Big Q
-40
-Kidney
-Gill clip
-Anal fin
-NA
-Table 4. Stock and species sampled.
-Stock
-Species
-Big Q
-Coho
-Chehalis
-Coho
-Chehalis
-Chinook
-Chilko
-Chinook
-Chilliwack
-Coho
-Fraser
-Sockeye
-Fulton
-Sockeye
-Inch
-Coho
-Kitimat
-Coho
-Maria Slough
-Chinook
-Nanaimo River
-Chinook
-Nitinat
-Coho
-Norrish (Inch)
-Coho
-Puntledge
-Coho
-Puntledge Fall
-Chinook
-Puntledge Summer
-Chinook
-Quatse
-Coho
-Robertson
-Chinook
-Skeena
-Sockeye
-Sooke
-Chinook
-Thornton
-Chinook
-Viner River
-Chum</t>
-  </si>
-  <si>
-    <t>Badil, S., Elliott, D. G., Kurobe, T., Hedrick, R. P., Clemens, K., Blair, M., Purcell, M. K. 2011. Comparative evaluation of molecular diagnostic tests for *Nucleospora salmonis* and prevalence in migrating juvenile salmonids from the Snake River, USA. J. Aquat. Anim. Health. 23:19-29. doi:10.1080/08997659.2011.559418.
-Bettge, K., Wahli, T., Segner, H., &amp; Schmidt-Posthaus, H. 2009. Proliferative kidney disease in rainbow trout: time- and temperature-related renal pathology and parasite distribution. Dis. Aquat. Org. 83:67-76. doi: 10.3354/dao01989.
-Gibbs, G. D., Griffin, M. J., Mauel, M. J., &amp; Lawrence, M. L. 2020. Validation of a quantitative PCR assay for the detection of 2 *Flavobacterium columnare* genomovars. J.Â Vet. Diagn. Investig. 32:356-362. doi:10.1177/104063872091576.
-Howell, C. K., Atkinson, S. D., Bartholomew, J. L., &amp; Hallett, S. L. 2019. Development and application of a qPCR assay targeting *Ichthyophthirius multifiliis* in environmental water samples. Dis. Aquat. Org. 134:43-55. doi: 10.3354/dao03351.
-Lennox, S.M.G., Shavalier, M.A., Brenden, T.O., Knupp, C.K., &amp; Loch, T.P. 2023. Developing an improved egg disinfection method to reduce *Flavobacterium psychrophilum* transmission risk in rainbow trout (*Oncorhynchus mykiss*). American Fisheries Society - Fish Health Section Summer Seminar Series. https://sites.google.com/umn.edu/fishhealthseminar/archived-seminars/2023-seminar-series/lennox
-Ma, J., Bruce, T. J., Oliver, L. P., &amp; Cain, K. D. 2019. Co-infection of rainbow trout (*Oncorhynchus mykiss*) with infectious hematopoietic necrosis virus and *Flavobacterium psychrophilum*. J. Fish Dis. 42:1065-1076. doi:10.1111/jfd.13012.
-Marancik, D. P., &amp; Wiens, G. D. 2013. A real-time polymerase chain reaction assay for identification and quantification of *Flavobacterium psychrophilum* and application to disease resistance studies in selectively bred rainbow trout *Oncorhynchus mykiss*. FEMS Microbiol. Lett. 339:122-129. doi:10.1111/1574-6968.12061.
-Purcell, M. K., Thompson, R. L., Garver, K. A., Hawley, L. M., Batts, W. N., Sprague, L., Sampson, C. and Winton, J. R. 2013. Universal reverse-transcriptase real-time PCR for infectious hematopoietic necrosis virus (IHNV). Dis. Aquat. Org. 106: 103-115. doi: 10.3354/dao02644.
-Richmond, Z., &amp; Plant, K. 2021. Quantitative PCR (RT-qPCR) for Detection of *R.sal* using AgPath-ID One-Step RT-qPCR kit in Multiorgan tissue of Finfish Species. BC Centre For Aquatic Health Sciences, SOP 83-v5.1.</t>
-  </si>
-  <si>
     <t>Province of British Columbia, Pacific Salmon Commission</t>
   </si>
   <si>
     <t>Under global climate change, co-occurrence of gradual physical changes in seawater and extreme events pose a substantial threat to marine ecosystems (IPCC, 2023). This PSSI-funded project focused on the Strait of Georgia (SOG) within the Northeast Pacific coastal region where steady rises in mean seasonal seawater temperatures and *p*CO2 levels, and increasingly prevalent acute stressor events such as heatwaves and low-pH upwellings, are already occurring (Bylhouwer et al., 2013; Evans et al., 2019; Okey et al., 2024; Raymond et al., 2022; Talloni-Alvarez et al., 2014). Moreover, the SOG is distinctive as conditions of high *p*CO2 and aragonite undersaturation persist year-round across a wide extent of the water column (Moore-Maley et al., 2016; Simpson et al., 2024). *Limacina helicina*, a cold-water pteropod well-represented within the region's zooplankton communities, is highly susceptible to climate change stressors, with documented impacts of ocean warming and ocean acidification (OA) on shell development, growth, and survival (BednarÅ¡ek et al., 2016, 2022; Lischka et al., 2022; Lischka &amp; Riebesell, 2012). However, there has been minimal investigation of climate change effects on the species' nutritional status (*e.g.* fatty acid (FA) composition) under regionally-relevant conditions. Given the importance of *L. helicina* as a dietary item for some populations of juvenile Pacific salmon species in the Northeast Pacific (Brodeur et al., 2007; Doubleday &amp; Hopcroft, 2015; Sturdevant et al., 2012), it was proposed that any change in the nutritive status of *L. helicina* under climate stressor conditions could have carry-over impacts to juvenile salmon growth, health, and survival.
 The project involved cross-program collaboration between DFO researchers based at the Pacific Biological Station (PBS) and the Pacific Science Enterprise Centre (PSEC) for investigation of the impacts of warming and OA conditions (representative of future conditions in the SOG) on FA profiles of *L. helicina* populations in the region. *Limacina helicina* samples were collected and processed as part of juvenile Pacific salmon survey fieldwork carried out in the SOG during 2014âˆ’2023 by the *Salmon Marine Interactions Program* at PBS (Lead: Neville). The program also supported live collection (within the SOG) of *L. helicina* for a climate change experiment (2023). Subsequent field sample sorting (*i.e.* extraction of whole pteropods from historical size-fractionated plankton samples) and laboratory experimentation (*i.e.* conducting of a climate change experiment in the Fisheries and Oceans Climate Change and Ocean Acidification Laboratory (FOCCOAL)), and nutritional analyses (*i.e.* FA analyses via gas chromatography) were carried out by the *Sustainable Invertebrate Aquaculture Program* at PBS (Lead: Pearce) and *Nutrition Program* at PSEC (Lead: Forster), respectively.</t>
-  </si>
-  <si>
-    <t>*Climate Change Experiment*
-Live *L. helicina* (Figure 1) were collected from the SOG in early October 2023 for use in a climate stressor experiment. Collection of approximately 800 pteropods was carried out over a 7-h period across a centrally-located area of the SOG via a series of vertical tows (N=9) using a bongo net collar assembly with two 58-cm diameter Nitex nets (253-Âµm mesh) deployed to a maximum depth of 300 m. Following, jars with animals were kept in a temperature-controlled cool box (~12Â°C, dark conditions). Within 24 h of collection, all pteropods were transported to the FOCCOAL at PBS for application to a climate change experiment. A full factorial design was applied to the experiment, resulting in four treatments: *Control,* *OA*, *Warming*, *OA+Warming* (*n*=6 tanks per treatment). Treatment conditions were achieved via use of the FOCCOAL, which employs a programmable logic controller and automated seawater and gas mixing systems to tightly control seawater temperature and *p*CO2, respectively. Pteropods were exposed to singular and coinciding warming (mean summer seawater temperature + 4Â°C) and OA (Î©aragonite &lt; 1) conditions, with subsequent FA analyses carried out on 48-h and 5-d timepoint samples via gas chromatography (at PSEC). Results indicated a significant impact of OA on nutritional status at 48 h (Figure 2) and a significant impact of temperature on survival at 5 d (Figure 3).
-*Time-series Analyses (Field Samples)*
-Additionally, FA analyses of *L. helicina* picked from historical plankton samples collected in the SOG as part of juvenile Pacific salmon survey work (Neville et al., 2025, 2026a, 2026b, 2026c, 2026d, 2026e; Neville &amp; Spencer, 2026) were carried out to examine time-series changes in FA profiles in relation to regional temperature records (*e.g.* DFO British Columbia Shore Station Oceanographic Program*,* Chrome Island Lightstation temperature dataset). A subset (N=35) of frozen 1-mm size-fractioned samples covering a 10-year time series (2014-2023) were compiled to carry out pteropod FA profiling. Within a given year (N=7), five sampling stations were selected according to target tow depth and location. Sub-samples of the 1-mm size class samples from each station were used to obtain whole pteropods for FA analyses. FA analyses was carried out at PSEC via gas chromatography with results indicating significant differences in a number of fractions between year groups and in the overall FA profiles of a number of year groups (2016 and 2019; 2018 and 2021) (Figure 4), the latter findings parallelled by minor to moderate divergences in seasonal temperature conditions.</t>
   </si>
   <si>
     <t>Figure 1. Photograph of *Limacina helicina* (M. Poerner Loureiro, Vancouver Island University).
@@ -2586,11 +2350,6 @@
     <t>Province of British Columbia; Simon Fraser University</t>
   </si>
   <si>
-    <t>Figure 1. Â Map of Cultus Lake electrofishing quadrants.
-Figure 2. Lengths and Weights of all bass sampled between 2023-2025 (n=3,654).
-Figure 3. SMB gut contents from a subsample of biological samples taken between 2023-2025.</t>
-  </si>
-  <si>
     <t>Follow The fish</t>
   </si>
   <si>
@@ -2643,10 +2402,6 @@
   </si>
   <si>
     <t>Dr. T. Brown, SFU; Dr. Rachel Scholes, Dr. Tim Rodgers, UBC; Dr. Edward Kolodziej; Tsawwassen First Nation; Tsleil-Waututh Nation; Musqueam Nation; Cowichan Tribes; Redd fish Restoration; Vancouver Island University; BC conservation Foundation; World fisheries Trust; The Pacific Streamkeepers Federation; BC Ministry of Transportation; and Somenos Marsh Wildlife Society</t>
-  </si>
-  <si>
-    <t>Dr. T. Brown, SFU
-*Follow the Fish Program and associated partners and nations/organizations*: Huu-ay-aht First Nation; Toquaht Nation; Uchucklesaht Tribe; HupaÄasath First *Nation*; YuuÅ‚uÊ”iÅ‚Ê”atá¸¥ Government; Tseshaht First Nation</t>
   </si>
   <si>
     <t>*Field collections*:
@@ -2675,25 +2430,6 @@
   <si>
     <t>- We have characterized, for The First time, contaminant concentrations in juvenile Chinook salmon from The west coast of Vancouver Island. Our results indicate a low Risk of contaminant associated health impacts for certain compounds and contaminant classes. however, while concentrations in WCVI juvenile Chinook are lower relative to other regions in B.C. and Washington State, it remains important to evaluate contaminant associated risks in juvenile Chinook inhabiting these waters.
 - management questions addressed by This project include those related to Understanding and mitigating a significant stressor (i.e., contaminants) on at-Risk salmon populations. Similarly, The recovery of *endangered* southern Resident killer whales and *Threatened* Northern Resident killer whales requires identifying and mitigating The significant threat posed by contaminants, and largely delivered via their priority prey, Chinook salmon.</t>
-  </si>
-  <si>
-    <t>Anzalone, S. E., Fuller, N. W., Hartz, K. E. H., Fulton, C. A., Whitledge, G. W., Magnuson, J. T., ... &amp; Lydy, M. J. (2022). Pesticide residues in juvenile Chinook salmon and prey items of the Sacramento River watershed, California-a comparison of riverine and floodplain habitats.Â *Environmental Pollution*,Â *303*, 119102.
-Arkoosh, M. R., Van Gaest, A. L., Strickland, S. A., Hutchinson, G. P., Krupkin, A. B., &amp; Dietrich, J. P. (2017). Alteration of thyroid hormone concentrations in juvenile Chinook salmon (Oncorhynchus tshawytscha) exposed to polybrominated diphenyl ethers, BDE-47 and BDE-99.Â *Chemosphere*,Â *171*, 1-8.
-Beacham, T.D, Wallace, C., MacConnachie, C., Jonsen, K., McIntosh, B., Candy, J.R., &amp; Whitler, R.E. (2018). Population and individual identification of Chinook salmon in British Columbia through parentage-based tagging and genetic stock identification with single nucleotide polymorphisms. *Canadian Journal of Fisheries and Aquatic Sciences*, 75(7), 1096-1105.
-Beckvar, N., Dillon, T. M., &amp; Read, L. B. (2005). Approaches for linking wholeâ€body fish tissue residues of mercury or DDT to biological effects thresholds.Â *Environmental Toxicology and Chemistry*,Â *24*(8), 2094-2105.
-Berninger, J. P., &amp; Tillitt, D. E. (2019). Polychlorinated biphenyl tissueâ€concentration thresholds for survival, growth, and reproduction in fish.Â *Environmental toxicology and chemistry*,Â *38*(4), 712-736.
-Holbert, S., Colbourne, K., Fisk, A. T., Ross, P. S., MacDuffee, M., Gobas, F. A. P. C., &amp; Brown, T. M. (2024). Polychlorinated biphenyl and polybrominated diphenyl ether profiles vary with feeding ecology and marine rearing distribution among 10 Chinook salmon (Oncorhynchus tshawytscha) stocks in the North Pacific Ocean.Â *Environmental Research*,Â *241*, 117476.
-Johnson, L. L., Ylitalo, G. M., Sloan, C. A., Anulacion, B. F., Kagley, A. N., Arkoosh, M. R., ... &amp; Collier, T. K. (2007). Persistent organic pollutants in outmigrant juvenile Chinook salmon from the Lower Columbia Estuary, USA.Â *Science of the Total Environment*,Â *374*(2-3), 342-366.
-Lundin, J. I., Spromberg, J. A., Jorgensen, J. C., Myers, J. M., Chittaro, P. M., Zabel, R. W., ... &amp; Scholz, N. L. (2019). Legacy habitat contamination as a limiting factor for Chinook salmon recovery in the Willamette Basin, Oregon, USA.Â *PLoS One*,Â *14*(3), e0214399.
-Lundin, J. I., Chittaro, P. M., Ylitalo, G. M., Kern, J. W., Kuligowski, D. R., Sol, S. Y., ... &amp; Scholz, N. L. (2021). Decreased growth rate associated with tissue contaminants in juvenile Chinook salmon out-migrating through an industrial waterway.Â *Environmental Science &amp; Technology*,Â *55*(14), 9968-9978.
-Lundin, J. I., Chittaro, P. M., Schultz, I. R., Arkoosh, M. R., Baker, M. C., Baldwin, D. H., ... &amp; Dietrich, J. P. (2023). Dietary Exposure to Environmentally Relevant Levels of Chemical Contaminants Reduces Growth and Survival in Juvenile Chinook Salmon.Â *Environmental Science &amp; Technology*,Â *58*(1), 132-142.
-Meador, J. P., Collier, T. K., &amp; Stein, J. E. (2002). Use of tissue and sedimentâ€based threshold concentrations of polychlorinated biphenyls (PCBs) to protect juvenile salmonids listed under the US Endangered Species Act.Â *Aquatic Conservation: Marine and Freshwater Ecosystems*,Â *12*(5), 493-516.
-Meador, J. P. (2014). Do chemically contaminated river estuaries in Puget Sound (Washington, USA) affect the survival rate of hatchery-reared Chinook salmon?.Â *Canadian Journal of Fisheries and Aquatic Sciences*,Â *71*(1), 162-180.
-O'Neill, S. M., Carey, A. J., Lanksbury, J. A., Niewolny, L. A., Ylitalo, G., Johnson, L., &amp; West, J. E. (2015). Toxic contaminants in juvenile Chinook salmon (Oncorhynchus tshawytscha) migrating through estuary, nearshore and offshore habitats of Puget Sound.Â *Washington Department of Fish and Wildlife Report FBT*, 2-16.
-O'Neill, S. M., Carey, A. J., Harding, L. B., West, J. E., Ylitalo, G. M., &amp; Chamberlin, J. W. (2020). Chemical tracers guide identification of the location and source of persistent organic pollutants in juvenile Chinook salmon (Oncorhynchus tshawytscha), migrating seaward through an estuary with multiple contaminant inputs.Â *Science of the Total Environment*,Â *712*, 135516.
-Quinn, T.P., 2018. The abundance and diversity of salmon and trout: Past, present, future. In: The Behavior and Ecology of Pacific Salmon and Trout. University of Washington Press.
-Rosenberg, B., Neumann, D., &amp; Loseto, L. (2015).Â *Freshwater Institute (DFO Winnipeg) Stable Isotope Laboratory Quality Assurance/Quality Control and Inter-lab Comparison Report*. Fisheries and Oceans Canada= PÃªches et ocÃ©ans Canada.
-Zabel, R. W., &amp; Achord, S. (2004). Relating size of juveniles to survival within and among populations of Chinook salmon.Â *Ecology*,Â *85*(3), 795-806.</t>
   </si>
   <si>
     <t>Arbeider, M., Ritchie, L., Braun, D., Jenewein, B., Rickards, K., Dionne, K., Holt, C., Labelle, M., Nicklin, P., Mozin, P., Grant, P., Parken, C., and Bailey, R. 2020. Interior Fraser Coho Salmon Recovery Potential Assessment. Fisheries and Oceans Canada.
@@ -3189,6 +2925,112 @@
 Welch, D.W., Futia, M.H., Rinchard, J., Teffer, A.K., Miller, K.M., Hinch, S.G., and Honeyfield, D.C. 2018. Thiamine Levels in Muscle and Eggs of Adult Pacific Salmon from the Fraser River, British Columbia. J. Aquat. Anim. Health 30(3): 191–200. doi:10.1002/aah.10024.
 Whitfield, K.C., Bourassa, M.W., Adamolekun, B., Bergeron, G., Bettendorff, L., Brown, K.H., Cox, L., Fattal-Valevski, A., Fischer, P.R., Frank, E.L., Hiffler, L., Hlaing, L.M., Jefferds, M.E., Kapner, H., Kounnavong, S., Mousavi, M.P.S., Roth, D.E., Tsaloglou, M.N., Wieringa, F., and Combs, G.F. 2018. Thiamine deficiency disorders: diagnosis, prevalence, and a roadmap for global control programs. Ann. N. Y. Acad. Sci. 1430(1): 3–43. doi:10.1111/nyas.13919.
 Wright, G.M., Brown, S.B., Brown, L.R., Moore, K., Villella, M., Zajicek, J.L., Tillitt, D.E., Fitzsimons, J.D., and Honeyfield, D.C. 2005. Effect of sample handling on thiamine and thiaminolytic activity in alewife. J. Aquat. Anim. Health 17(1): 77–81. doi:10.1577/H03-074.1.</t>
+  </si>
+  <si>
+    <t>Chris Pearce, Clara Mackenzie, Ian Forster</t>
+  </si>
+  <si>
+    <t>Dr. T. Brown, SFU; **Follow the Fish Program and associated partners and nations/organizations**: Huu-ay-aht First Nation, Toquaht Nation, Uchucklesaht Tribe, Hupačasath First Nation, Yuułuʔiłʔatḥ Government, Tseshaht First Nation</t>
+  </si>
+  <si>
+    <t>- The goal of the project was to better characterize contaminant levels and evaluate their potential impacts on the health of juvenile Chinook from the West Coast of Vancouver Island.
+- 12 contaminant classes were analyzed in two composite samples collected in 2022 from Barkley Sound (completed) and polychlorinated biphenyls (PCBs), polycyclic aromatic hydrocarbons (PAHs) and metals were analyzed in individual fish collected in 2023 and 2024 in Clayoquot Sound and Barkley Sound (in progress).
+- Metals, PAHs, and PCBs were the top three contaminant classes detected with the highest concentrations in the two composite samples from Barkley Sound.
+- Comparing our results to established effects thresholds, juvenile Chinook salmon from Barkley Sound may be at low risk of exposure to contaminants, specifically PCBs, PBDEs, Dichlorodiphenyltrichloroethane (DDT), PAHs and mercury.
+- Concentrations of contaminant classes measured in WCVI juvenile Chinook salmon range from 3 to 100x lower than levels of contaminant classes documented in juvenile Chinook in the Fraser River. As such contaminant levels in WCVI juvenile provide a benchmark of 'lower' levels reflecting lower urban and industrial associated sources.</t>
+  </si>
+  <si>
+    <t>Anzalone, S. E., Fuller, N. W., Hartz, K. E. H., Fulton, C. A., Whitledge, G. W., Magnuson, J. T., ... &amp; Lydy, M. J. (2022). Pesticide residues in juvenile Chinook salmon and prey items of the Sacramento River watershed, California–a comparison of riverine and floodplain habitats. Environmental Pollution, 303, 119102.
+Arkoosh, M. R., Van Gaest, A. L., Strickland, S. A., Hutchinson, G. P., Krupkin, A. B., &amp; Dietrich, J. P. (2017). Alteration of thyroid hormone concentrations in juvenile Chinook salmon (Oncorhynchus tshawytscha) exposed to polybrominated diphenyl ethers, BDE-47 and BDE-99. Chemosphere, 171, 1-8.
+Beacham, T.D, Wallace, C., MacConnachie, C., Jonsen, K., McIntosh, B., Candy, J.R., &amp; Whitler, R.E. (2018). Population and individual identification of Chinook salmon in British Columbia through parentage-based tagging and genetic stock identification with single nucleotide polymorphisms. Canadian Journal of Fisheries and Aquatic Sciences, 75(7), 1096-1105.
+Beckvar, N., Dillon, T. M., &amp; Read, L. B. (2005). Approaches for linking whole‐body fish tissue residues of mercury or DDT to biological effects thresholds. Environmental Toxicology and Chemistry, 24(8), 2094-2105.
+Berninger, J. P., &amp; Tillitt, D. E. (2019). Polychlorinated biphenyl tissue‐concentration thresholds for survival, growth, and reproduction in fish. Environmental toxicology and chemistry, 38(4), 712-736.
+Holbert, S., Colbourne, K., Fisk, A. T., Ross, P. S., MacDuffee, M., Gobas, F. A. P. C., &amp; Brown, T. M. (2024). Polychlorinated biphenyl and polybrominated diphenyl ether profiles vary with feeding ecology and marine rearing distribution among 10 Chinook salmon (Oncorhynchus tshawytscha) stocks in the North Pacific Ocean. Environmental Research, 241, 117476.
+Johnson, L. L., Ylitalo, G. M., Sloan, C. A., Anulacion, B. F., Kagley, A. N., Arkoosh, M. R., ... &amp; Collier, T. K. (2007). Persistent organic pollutants in outmigrant juvenile Chinook salmon from the Lower Columbia Estuary, USA. Science of the Total Environment, 374(2-3), 342-366.
+Lundin, J. I., Spromberg, J. A., Jorgensen, J. C., Myers, J. M., Chittaro, P. M., Zabel, R. W., ... &amp; Scholz, N. L. (2019). Legacy habitat contamination as a limiting factor for Chinook salmon recovery in the Willamette Basin, Oregon, USA. PLoS One, 14(3), e0214399.
+Lundin, J. I., Chittaro, P. M., Ylitalo, G. M., Kern, J. W., Kuligowski, D. R., Sol, S. Y., ... &amp; Scholz, N. L. (2021). Decreased growth rate associated with tissue contaminants in juvenile Chinook salmon out-migrating through an industrial waterway. Environmental Science &amp; Technology, 55(14), 9968-9978.
+Lundin, J. I., Chittaro, P. M., Schultz, I. R., Arkoosh, M. R., Baker, M. C., Baldwin, D. H., ... &amp; Dietrich, J. P. (2023). Dietary Exposure to Environmentally Relevant Levels of Chemical Contaminants Reduces Growth and Survival in Juvenile Chinook Salmon. Environmental Science &amp; Technology, 58(1), 132-142.
+Meador, J. P., Collier, T. K., &amp; Stein, J. E. (2002). Use of tissue and sediment‐based threshold concentrations of polychlorinated biphenyls (PCBs) to protect juvenile salmonids listed under the US Endangered Species Act. Aquatic Conservation: Marine and Freshwater Ecosystems, 12(5), 493-516.
+Meador, J. P. (2014). Do chemically contaminated river estuaries in Puget Sound (Washington, USA) affect the survival rate of hatchery-reared Chinook salmon?. Canadian Journal of Fisheries and Aquatic Sciences, 71(1), 162-180.
+O’Neill, S. M., Carey, A. J., Lanksbury, J. A., Niewolny, L. A., Ylitalo, G., Johnson, L., &amp; West, J. E. (2015). Toxic contaminants in juvenile Chinook salmon (Oncorhynchus tshawytscha) migrating through estuary, nearshore and offshore habitats of Puget Sound. Washington Department of Fish and Wildlife Report FBT, 2-16.
+O'Neill, S. M., Carey, A. J., Harding, L. B., West, J. E., Ylitalo, G. M., &amp; Chamberlin, J. W. (2020). Chemical tracers guide identification of the location and source of persistent organic pollutants in juvenile Chinook salmon (Oncorhynchus tshawytscha), migrating seaward through an estuary with multiple contaminant inputs. Science of the Total Environment, 712, 135516.
+Quinn, T.P., 2018. The abundance and diversity of salmon and trout: Past, present, future. In: The Behavior and Ecology of Pacific Salmon and Trout. University of Washington Press.
+Rosenberg, B., Neumann, D., &amp; Loseto, L. (2015). Freshwater Institute (DFO Winnipeg) Stable Isotope Laboratory Quality Assurance/Quality Control and Inter-lab Comparison Report. Fisheries and Oceans Canada= Pêches et océans Canada.
+Zabel, R. W., &amp; Achord, S. (2004). Relating size of juveniles to survival within and among populations of Chinook salmon. Ecology, 85(3), 795-806.</t>
+  </si>
+  <si>
+    <t>Kristi Saunders (retired), 
+Christoph Deeg, Arthur Bass, Carl Llewellyn</t>
+  </si>
+  <si>
+    <t>*Validation and transfer of diagnostic assays for endemic pathogens*
+In consultation with SEP veterinarians and fish health staff, the project identified seven endemic pathogens for which there was a need for improved diagnostic assays. Due to the need for high-capacity and rapid diagnostics, quantitative PCR (qPCR) assays were chosen for their accuracy and reliability. The targeted pathogens were as follows: Tetracapsuloides bryosalmonae (Bettge et al., 2009), Flavobacterium columnare (Gibbs et al., 2020), Flavobacterium psychrophilum (Ma et al., 2019; Marancik &amp; Wiens, 2013), Renibacterium salmoninarum (Richmond &amp; Plant, 2021), Ichthyophthirius multifiliis (Howell et al., 2019), IHNV (Purcell et al., 2013), and Nucleospora salmonis (Badil et al., 2011). Where pathogen nucleic acids were unavailable, synthetic double-stranded DNA fragments (gBlocks™) were used for validation work, e.g. limits of detection and quantification. In collaboration with BC Centre for Aquatic Health Sciences, the R. salmoninarum qPCR assay underwent interlaboratory validation in which both labs screened 170 samples. The results showed substantial agreement between labs (Cohen’s κ=0.68), confirming the reliability of assay transfer. Post-validation, assays were implemented to assist the FDL in disease investigations.
+To ensure effective knowledge transfer, standard operating procedures were developed by the AAH team and shared with FDL staff. Training sessions covered all aspects of assay implementation, enabling FDL personnel to independently conduct analyses. 
+*Deployment of assays for pathogen surveillance* 
+In addition to assay validation and technology transfer, this project also focused on collection and analysis of longitudinal data on two high-priority pathogens: F. psychrophilum and R. salmoninarum. F. psychrophilum is the causative agent of bacterial coldwater disease and infections can cause significant disease and mortality in juvenile, hatchery-reared salmonids. Identified knowledge gaps for F. psychrophilum in BC include overall prevalence in broodstock, and the linkage between female broodstock bacterial load and outbreaks in fry. While outbreaks are common at most SEP facilities rearing salmonids, outbreaks are notably acute in Harrison River Chinook salmon (HRCS). 
+Surveillance conducted between 2023 and 2025 determined that prevalence was approximately 40% in HRCS broodstock during 2023–2024, with a significant reduction in 2025 (χ2=12.6, p &lt; 0.01) (Table 1). It is possible that prevalence is cyclical in this stock but additional screening is necessary. Chehalis River broodstock, reared under similar conditions, showed comparable infection rates to HRCS in 2024, suggesting genetic differences between stocks may influence outbreak intensity.
+Both kidney and spleen were collected to determine which tissue would be best for routine sampling. Agreement between the two tissues was slight (Cohen’s κ=0.16). The number of positive fish based on spleen results was more than double that of kidney indicating that spleen is more likely to result in a positive detection. Tissues were also streaked on bacterial agar and evaluated for growth of yellow-pigmented bacteria morphologically similar to F. psychrophilum. Using novel sequencing techniques, we identified unexpected genetic heterogeneity within F. psychrophilum isolates from BC. 
+In 2024, the SEP Fish Health group conducted a pilot study to evaluate the effectiveness of pre-fertilization egg disinfection in reducing bacterial loads. Unfertilized eggs from 20 HRCS females were treated in an Ovadine®:saline solution (100 ppm:0.75%) for 15 minutes. Egg disinfection is typically carried out post-fertilization; however, iodophor cannot penetrate eggs to eliminate bacteria already present within. A previous study by Lennox et al. (2023) suggested that pre-fertilization disinfection in an iodophor:saline solution may decrease intra-egg bacterial concentrations, supporting the basis for this pilot. Eggs from each female were sampled at three key stages (pre-fertilization and pre-treatment, pre-fertilization and post-treatment, and post-fertilization and post-treatment) and screened for F. psychrophilum by AAH staff. The number of positive samples decreased from eight (pre-treatment and pre-fertilization) to one (post-treatment and post-fertilization). Fish were not monitored post-hatch, so long-term effectiveness of the treatment could not be assessed, though no adverse impacts on fertilization or hatching were noted.
+The study was repeated in fall 2025, expanding to include all HRCS eggs as well as all chum salmon eggs at the Tenderfoot hatchery. Samples from the HRCS eggs were collected and will be analyzed using qPCR before the end of the fiscal year to further evaluate the efficacy of this treatment approach.
+*R. salmoninarum* is the causative agent of Bacterial Kidney Disease (BKD), and is vertically transmitted from female broodstock to progeny. As such, kidney is collected from spawning female broodstock and submitted to the FDL for BKD screening using an enzyme-linked immunosorbent assay (ELISA). In the current study, 637 samples were screened by ELISA and qPCR. Assay agreement was slight (Cohen’s κ=0.20), and overall, more samples were positive by ELISA as compared to qPCR. The ELISA measures bacterial antigen concentrations and serves as a proxy for previous R. salmoninarum exposure. Conversely, the qPCR measures the total amount of nucleic acid present, i.e. an active infection. Therefore, although the R. salmoninarum qPCR assay is sensitive and specific, the ELISA remains the gold standard method for broodstock screening. Longitudinal surveillance of select stocks was also conducted from 2023 through 2025 (Table 2). Prevalence, as determined by ELISA, is high at these facilities every year. Results from 2025 are pending but will be available by the end of this fiscal year. 
+This project also explored the use of non-lethal sampling methods for R. salmoninarum. To do so, lethal (kidney) and non-lethal (mucus, gill clip, anal fin clip, and ventral swab) samples were collected from female broodstock at Nitinat and Big Q hatcheries. All samples were screened by the qPCR assay and kidney was also screened by ELISA (Table 3). In 2024, results showed limited agreement between non-lethal samples and kidney, with mucus samples providing the highest detection rates. Given the amount of handling during the spawning process, mucus also has the highest risk of contamination. Consequently, mucus sampling was excluded in 2025, with evaluation ongoing for gill clip and anal fin sampling methods.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 1. Longitudinal surveillance results for Flavobacterium psychrophilum. Broodstock were classified as positive if the bacterium was re-isolated from tissue samples or if tissues tested positive by qPCR. Total prevalence was calculated as the number of unique positive broodstock identified by qPCR and/or culture divided by the total number of samples collected. Subscripts denote statistically significant differences in prevalence among years (χ2=12.6, P &lt; 0.01). 
+Table 2. Longitudinal surveillance results for R. salmoninarum at select facilities. Broodstock were classified as positive if the ELISA optical density value was greater than the mean optical density of the negative control or kidney tested positive by qPCR. ELISA prevalence estimates included samples classified as ‘low level of detection’ as these samples are considered positive but are often kept by facilities. 
+Table 3. Non-lethal BKD screening samples. Female coho salmon broodstock were sampled at both facilities. Agreement values were calculated using Cohen’s kappa analysis and all tissues were compared to kidney.
+Table 4. Stock and species sampled. </t>
+  </si>
+  <si>
+    <t>Badil, S., Elliott, D. G., Kurobe, T., Hedrick, R. P., Clemens, K., Blair, M., Purcell, M. K. 2011. Comparative evaluation of molecular diagnostic tests for Nucleospora salmonis and prevalence in migrating juvenile salmonids from the Snake River, USA. J. Aquat. Anim. Health. 23:19–29. doi:10.1080/08997659.2011.559418.
+Bettge, K., Wahli, T., Segner, H., &amp; Schmidt-Posthaus, H. 2009. Proliferative kidney disease in rainbow trout: time- and temperature-related renal pathology and parasite distribution. Dis. Aquat. Org. 83:67–76. doi: 10.3354/dao01989.
+Gibbs, G. D., Griffin, M. J., Mauel, M. J., &amp; Lawrence, M. L. 2020. Validation of a quantitative PCR assay for the detection of 2 Flavobacterium columnare genomovars. J. Vet. Diagn. Investig. 32:356–362. doi:10.1177/104063872091576.
+Howell, C. K., Atkinson, S. D., Bartholomew, J. L., &amp; Hallett, S. L. 2019. Development and application of a qPCR assay targeting Ichthyophthirius multifiliis in environmental water samples. Dis. Aquat. Org. 134:43–55. doi: 10.3354/dao03351.
+Lennox, S.M.G., Shavalier, M.A., Brenden, T.O., Knupp, C.K., &amp; Loch, T.P. 2023. Developing an improved egg disinfection method to reduce Flavobacterium psychrophilum transmission risk in rainbow trout (Oncorhynchus mykiss). American Fisheries Society – Fish Health Section Summer Seminar Series. https://sites.google.com/umn.edu/fishhealthseminar/archived-seminars/2023-seminar-series/lennox
+Ma, J., Bruce, T. J., Oliver, L. P., &amp; Cain, K. D. 2019. Co-infection of rainbow trout (Oncorhynchus mykiss) with infectious hematopoietic necrosis virus and Flavobacterium psychrophilum. J. Fish Dis. 42:1065–1076. doi:10.1111/jfd.13012.
+Marancik, D. P., &amp; Wiens, G. D. 2013. A real-time polymerase chain reaction assay for identification and quantification of *Flavobacterium psychrophilum* and application to disease resistance studies in selectively bred rainbow trout Oncorhynchus mykiss. FEMS Microbiol. Lett. 339:122–129. doi:10.1111/1574-6968.12061.
+Purcell, M. K., Thompson, R. L., Garver, K. A., Hawley, L. M., Batts, W. N., Sprague, L., Sampson, C. and Winton, J. R. 2013. Universal reverse-transcriptase real-time PCR for infectious hematopoietic necrosis virus (IHNV). Dis. Aquat. Org. 106: 103-115. doi: 10.3354/dao02644.
+Richmond, Z., &amp; Plant, K. 2021. Quantitative PCR (RT-qPCR) for Detection of R.sal using AgPath-ID One-Step RT-qPCR kit in Multiorgan tissue of Finfish Species. BC Centre For Aquatic Health Sciences, SOP 83-v5.1.</t>
+  </si>
+  <si>
+    <t>Christoph Deeg, Kristi Miller-Saunders (retired), 
+Karia Kaukinen, Arthur Bass</t>
+  </si>
+  <si>
+    <t>Figure 1.  Map of Cultus Lake electrofishing quadrants.
+Figure 2. Lengths and Weights of all bass sampled between 2023-2025 (n=3,654).
+Figure 3. SMB gut contents from a subsample of biological samples taken between 2023-2025.</t>
+  </si>
+  <si>
+    <t>Our observational methods are traditionally used in oceanographic research, e.g. sampling temperature, salinity and oxygen profiles with a CTD instrument as well as deploying moorings and weather stations. However, the innovative aspect is the collaboration with local communities. These collaborations allowed for sampling at a much higher frequency (~monthly) than anything achievable by DFO alone, but still maintaining DFO’s high-quality data standards (thanks to training and data post-processing and quality control by DFO). As a reference, DFO-led sampling provided 82 CTD profiles in 2019 (mostly from March and October/November) and 122 profiles in 2024 (a well-sampled year through many PSSI projects), while this project’s Nation-led sampling in 2024 provided 150 profiles (mostly monthly from March to December). Beyond the scientific benefits, these collaborations were essential for building long-term relationships with First Nations partners, fostering mutual trust, and creating a framework for ongoing knowledge exchange between Indigenous knowledge systems and western scientific approaches.
+In terms of modelling, the WCVI model has been developed and run for 2019, 2024 (to take advantage of the intensive PSSI-related sampling) and one future scenario centered in 2055. Simulations for 2019 and 2024 have been compared against observations and show good agreement, particularly temperature and salinity. Biogeochemical variables (e.g., oxygen, nitrate) show good performance on the shelf, but some further calibration is needed to reach the desired performance inside the inlets. Figure 1 shows the model domain and bathymetry.
+Analyses of model outputs in Clayoquot Sound indicate that the inlets towards the south are warmer  and fresher than those on the north at all levels of the water column and all three seasons analyzed (spring, summer, autumn). These conditions are due to stronger freshwater inputs, shallower bathymetry and a less direct connection with the shelf waters in southern inlets (Tofino to Bedwell) compared with northern inlets (Herbert to Sydney). In particular, model results allowed to study the role of the sills (particularly the shallow one outside of Herbert Inlet), which play a leading role modulating the deeper waters of the inlets (due to strong mixing at the sill and strong tidal advection).
+When comparing model results against temperature values that result in stress responses by Chinook salmon (above 16 to 18°C, personal communication by PSSI colleague Christoph Deeg), we find that the surface waters of all inlets may exceed these thresholds in summer under present-day conditions (Figure 2a). Furthermore, Tofino Inlet shows waters above these thresholds at all depths (Figure 3). When analyzing the same thresholds under the future scenario, they are exceeded mostly everywhere in the Sound in the top 5 meters (Figure 2b,c), and exceeded at depth in the southern inlets (from Bedwell to Tofino). 
+Once the performance of the biogeochemical module of the WCVI is deemed appropriate, a similar analysis will be performed with oxygen, considering that salmon show signs of stress at environmental values lower than 6 to 8 mg L-1 (Christoph Deeg, personal communication). Nevertheless, from the observational record we find that Clayoquot Sound shows throughout the year oxygen concentrations that fall below these thresholds, even near the surface from spring to autumn (Figure 4). 
+Two peer-reviewed publications are being prepared to discuss these results, while two manuscripts are already published discussing the low near-surface oxygen conditions (Rosen et al, 2022) and describing the model (Foreman et al, 2024). Informal presentations and updates were provided regularly to Gemma Macfarlane, the Stewardship Biologist from Maaqutusiis Hahoulthee Stewardship Society from Ahousaht Nation, as well as to project collaborators. A formal presentation was provided at the last Pacific Salmon Science Symposium in December 2025 and two other ones are scheduled in January and March 2026 to the Maa-nuult Joint Fisheries Committee (JFC) Technical Meeting Series and the State of the Pacific Ocean meeting, respectively. A presentation at a scientific meeting was planned for February 2026, but travel was not approved.</t>
+  </si>
+  <si>
+    <t>Figure 1. West coast Vancouver Island (WCVI) model domain. Colourscale shows the model bathymetry (in meters)
+Figure 2. Maps of Clayoquot Sound showing the percentage of the top 5m of the water column exceeding 17°C in summer (July, August and September) in the (a) simulation for 2024 and (b) future scenario. Panel (c) shows the difference between both (future scenario minus 2024 simulation), highlighting the additional percentage of the surface waters that can exceed the temperature threshold in the future scenario. 
+Figure 3. Time series of the percentage of water volume that exceeds 17°C in Tofino inlet at different depth ranges and different simulations. Bold colours indicate the future scenario, while paler colours indicate the 2024 simulation. Green colours indicate the volume in the surface depth range (0 to 5 m), blue colours represent upper waters below the surface (5 to 20 m) and black/grey represent deep waters (20 to 100 m). At surface, both simulations exceed the threshold between spring and autumn, while below 5 m the threshold is exceeded mostly in the future scenario. 
+Figure 4. Location of the CTD profiles with oxygen data from 2024. The oxygen histograms show the distribution of oxygen data for the whole 2024 year and four seasons (winter: Jan-Mar, spring: Apr-Jun, summer: Jul-Sep, and winter: Oct-Dec). The different colours show the histograms for four different depth ranges: the whole water column (blue), top 50 meters (orange), top 20 meters (yellow) and top 5 meters (purple).</t>
+  </si>
+  <si>
+    <t>This project mainly used sediment cores, with water samples and electronic (CTD) data profiles to support the interpretation of environmental conditions.
+*Sediment cores*
+Fourteen new sediment cores 40-50 cm long were collected in BC mainland inlets in 2022-2025 (Figure 1), using a box corer (0.1 m2 cross-sectional area). Cores were subsampled into 1-cm intervals over the top 10 cm, 2-cm intervals for 10-20 cm and 5-cm intervals from 20 cm to the bottom. The sampling resolution was highest near the surface to help define the surface mixed layer. The sediment accumulation rate and mixed layer depth for each core were determined using depth profiles of the radioisotopes Pb-210 and Ra-226. Radioisotopes were analyzed by Flett Research Ltd., in Manitoba, following the procedure of Eakins and Morrison (1978) and Mathieu et al. (1988). The composition of organic matter was determined by analysis of organic carbon and nitrogen at the University of British Columbia, using a CHN analyzer (following Calvert and Pedersen, 1995). Stable isotopes of carbon and nitrogen were determined at the University of British Columbia or at the University of Windsor, using mass spectrometry (Calvert et al., 2001). The proportions of marine-derived and terrigenous organic matter were calculated based on isotopic endmembers previously determined in BC coastal waters (Johannessen et al., 2021; Johannessen et al., 2019). The fluxes of marine and terrigenous organic matter were determined by multiplying the proportions of each by the % total organic carbon and by the sediment accumulation rate. The fluxes were used to determine trends in each type of organic matter over time.
+*CTD profiles and water sampling*
+Profile data were collected using a SeaBird SBE911 CTD with sensors for temperature, salinity, dissolved oxygen, transmissivity (red: 660nm, green: 550 nm) and chlorophyll fluorescence. Water samples were collected using a standard 24-bottle rosette collected on the up-cast. Water samples were analyzed unfiltered for nutrients (nitrate, phosphate, silicate) at the Institute of Ocean Sciences, using a Technicon AutoAnalyzer™ II (Barwell-Clarke and Whitney, 1996). Nutrient data will be interpreted by calculating molar ratios of Si:N:P and comparing the ratios with those calculated for the Strait of Georgia and Puget Sound. (In Puget Sound, the Si:N ratio has declined since the 1990s, affecting the phytoplankton species assemblage, while the ratio has remained stable in the Strait of Georgia (unpublished data)). 
+*Data archiving* 
+Following quality control, data were archived in the OSD Data Archive at the Institute of Ocean Sciences and made available through the Waterproperties.ca website. 
+*Delays*
+There were some unforeseen delays in field work and sample analysis. Two sampling cruises were cancelled, and a change in Coast Guard policy that made it impossible to collect sediment cores and water samples during the same cruise, which meant that the field work portion of the project took longer than anticipated. In addition, three labs that had previously analyzed stable isotopes all stopped offering that service, and it took some time to identify a new lab. As a result, some data were only received this month, with the rest of the outstanding data due by March 31. Consequently, only a preliminary interpretation is possible at this time. Interpretation will be completed in the coming fiscal year.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*Climate Change Experiment*
+Live *L. helicina* (Figure 1) were collected from the SOG in early October 2023 for use in a climate stressor experiment. Collection of approximately 800 pteropods was carried out over a 7-h period across a centrally-located area of the SOG via a series of vertical tows (N=9) using a bongo net collar assembly with two 58-cm diameter Nitex nets (253-µm mesh) deployed to a maximum depth of 300 m. Following, jars with animals were kept in a temperature-controlled cool box (~12°C, dark conditions). Within 24 h of collection, all pteropods were transported to the FOCCOAL at PBS for application to a climate change experiment. A full factorial design was applied to the experiment, resulting in four treatments: Control, OA, Warming, OA+Warming (n=6 tanks per treatment). Treatment conditions were achieved via use of the FOCCOAL, which employs a programmable logic controller and automated seawater and gas mixing systems to tightly control seawater temperature and pCO2, respectively. Pteropods were exposed to singular and coinciding warming (mean summer seawater temperature + 4°C) and OA (Ωaragonite &lt; 1) conditions, with subsequent FA analyses carried out on 48-h and 5-d timepoint samples via gas chromatography (at PSEC). Results indicated a significant impact of OA on nutritional status at 48 h (Figure 2) and a significant impact of temperature on survival at 5 d (Figure 3). 
+*Time-series Analyses (Field Samples)*
+Additionally, FA analyses of *L. helicina* picked from historical plankton samples collected in the SOG as part of juvenile Pacific salmon survey work (Neville et al., 2025, 2026a, 2026b, 2026c, 2026d, 2026e; Neville &amp; Spencer, 2026) were carried out to examine time-series changes in FA profiles in relation to regional temperature records (e.g. DFO British Columbia Shore Station Oceanographic Program, Chrome Island Lightstation temperature dataset). A subset (N=35) of frozen 1-mm size-fractioned samples covering a 10-year time series (2014–2023) were compiled to carry out pteropod FA profiling. Within a given year (N=7), five sampling stations were selected according to target tow depth and location. Sub-samples of the 1-mm size class samples from each station were used to obtain whole pteropods for FA analyses. FA analyses was carried out at PSEC via gas chromatography with results indicating significant differences in a number of fractions between year groups and in the overall FA profiles of a number of year groups (2016 and 2019; 2018 and 2021) (Figure 4), the latter findings parallelled by minor to moderate divergences in seasonal temperature conditions. </t>
   </si>
 </sst>
 </file>
@@ -3245,13 +3087,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3694,7 +3539,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C1235FC-468F-46C3-9676-E136DE729105}" name="Table1" displayName="Table1" ref="A1:U44" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
-  <autoFilter ref="A1:U44" xr:uid="{9C1235FC-468F-46C3-9676-E136DE729105}"/>
+  <autoFilter ref="A1:U44" xr:uid="{9C1235FC-468F-46C3-9676-E136DE729105}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="2412"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{21F25E78-D457-418F-9F78-7DE13AE8CD93}" name="source_file" dataDxfId="20"/>
     <tableColumn id="2" xr3:uid="{B8BCB027-8A7D-4FCE-803F-A296662A280E}" name="extraction_date" dataDxfId="19"/>
@@ -4091,7 +3942,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>21</v>
       </c>
@@ -4102,7 +3953,7 @@
         <v>22</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>570</v>
+        <v>552</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>23</v>
@@ -4132,7 +3983,7 @@
         <v>31</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>32</v>
@@ -4156,7 +4007,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>39</v>
       </c>
@@ -4182,7 +4033,7 @@
         <v>44</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>45</v>
@@ -4191,13 +4042,13 @@
         <v>46</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>47</v>
@@ -4221,7 +4072,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>54</v>
       </c>
@@ -4232,22 +4083,22 @@
         <v>2400</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>580</v>
+        <v>562</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>622</v>
+        <v>604</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>57</v>
@@ -4259,34 +4110,34 @@
         <v>58</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>623</v>
+        <v>605</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>624</v>
+        <v>606</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>627</v>
+        <v>609</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>626</v>
+        <v>608</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>625</v>
+        <v>607</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>59</v>
       </c>
@@ -4297,16 +4148,16 @@
         <v>2401</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>571</v>
+        <v>553</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>60</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>61</v>
@@ -4315,43 +4166,43 @@
         <v>62</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>607</v>
+        <v>589</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>612</v>
+        <v>594</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>608</v>
+        <v>590</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>609</v>
+        <v>591</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>610</v>
+        <v>592</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>611</v>
+        <v>593</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>63</v>
       </c>
@@ -4389,7 +4240,7 @@
         <v>71</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>72</v>
@@ -4401,7 +4252,7 @@
         <v>74</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="R6" s="2" t="s">
         <v>75</v>
@@ -4416,7 +4267,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>79</v>
       </c>
@@ -4427,7 +4278,7 @@
         <v>2403</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>572</v>
+        <v>554</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>80</v>
@@ -4448,40 +4299,40 @@
         <v>85</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>559</v>
+        <v>541</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>86</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>614</v>
+        <v>596</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>560</v>
+        <v>542</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>615</v>
+        <v>597</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>87</v>
       </c>
@@ -4498,31 +4349,31 @@
         <v>89</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>90</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>91</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>92</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>93</v>
@@ -4530,8 +4381,8 @@
       <c r="P8" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="Q8" s="2" t="s">
-        <v>496</v>
+      <c r="Q8" s="6" t="s">
+        <v>628</v>
       </c>
       <c r="R8" s="2" t="s">
         <v>95</v>
@@ -4539,14 +4390,14 @@
       <c r="S8" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="T8" s="2" t="s">
-        <v>497</v>
+      <c r="T8" s="6" t="s">
+        <v>629</v>
       </c>
       <c r="U8" s="3" t="s">
-        <v>583</v>
+        <v>565</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>97</v>
       </c>
@@ -4560,19 +4411,19 @@
         <v>98</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>566</v>
+        <v>548</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>99</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>61</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>100</v>
@@ -4581,13 +4432,13 @@
         <v>101</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>102</v>
@@ -4596,7 +4447,7 @@
         <v>103</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="R9" s="2" t="s">
         <v>104</v>
@@ -4608,10 +4459,10 @@
         <v>106</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:21" ht="409.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>107</v>
       </c>
@@ -4628,40 +4479,40 @@
         <v>109</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>110</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>111</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>112</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="Q10" s="2" t="s">
-        <v>500</v>
+      <c r="Q10" s="6" t="s">
+        <v>630</v>
       </c>
       <c r="R10" s="2" t="s">
         <v>114</v>
@@ -4676,7 +4527,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>118</v>
       </c>
@@ -4687,13 +4538,13 @@
         <v>2407</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>581</v>
+        <v>563</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>119</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>568</v>
+        <v>550</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>120</v>
@@ -4711,10 +4562,10 @@
         <v>56</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>124</v>
@@ -4735,13 +4586,13 @@
         <v>129</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>130</v>
       </c>
@@ -4752,57 +4603,63 @@
         <v>2408</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>573</v>
+        <v>555</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="I12" s="2"/>
+        <v>492</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>483</v>
+      </c>
       <c r="J12" s="2" t="s">
         <v>57</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="L12" s="2" t="s">
+      <c r="L12" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="P12" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2" t="s">
+      <c r="Q12" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="R12" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="P12" s="2" t="s">
+      <c r="S12" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="Q12" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="R12" s="2" t="s">
+      <c r="T12" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="S12" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="T12" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="U12" s="2" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>137</v>
       </c>
       <c r="B13" s="4">
         <v>46083</v>
@@ -4811,61 +4668,61 @@
         <v>2409</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="3" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="I13" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="K13" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="L13" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="M13" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="N13" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="L13" s="2" t="s">
+      <c r="O13" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="M13" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="N13" s="2" t="s">
+      <c r="P13" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="O13" s="2" t="s">
+      <c r="Q13" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="R13" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="P13" s="2" t="s">
+      <c r="S13" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="Q13" s="3" t="s">
-        <v>599</v>
-      </c>
-      <c r="R13" s="2" t="s">
+      <c r="T13" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="U13" s="3" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="S13" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="T13" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="U13" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="B14" s="4">
         <v>46083</v>
@@ -4874,63 +4731,63 @@
         <v>2410</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>153</v>
-      </c>
       <c r="J14" s="3" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>43</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="O14" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q14" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="P14" s="2" t="s">
+      <c r="R14" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="Q14" s="2" t="s">
+      <c r="S14" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="R14" s="2" t="s">
+      <c r="T14" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="S14" s="2" t="s">
+      <c r="U14" s="3" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="T14" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="B15" s="4">
         <v>46083</v>
@@ -4939,63 +4796,63 @@
         <v>2412</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="E15" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>164</v>
-      </c>
       <c r="J15" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>56</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="O15" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="Q15" s="6" t="s">
+        <v>631</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="S15" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="T15" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="U15" s="2" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="B16" s="4">
         <v>46083</v>
@@ -5004,63 +4861,63 @@
         <v>2413</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>574</v>
+        <v>556</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="G16" s="2" t="s">
+      <c r="K16" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="L16" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="O16" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="I16" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="J16" s="2" t="s">
+      <c r="P16" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="Q16" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="L16" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="O16" s="2" t="s">
+      <c r="R16" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="P16" s="2" t="s">
+      <c r="S16" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="Q16" s="2" t="s">
+      <c r="T16" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="U16" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="R16" s="2" t="s">
+    </row>
+    <row r="17" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="S16" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="T16" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="U16" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
-        <v>180</v>
       </c>
       <c r="B17" s="4">
         <v>46083</v>
@@ -5069,63 +4926,63 @@
         <v>2416</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="I17" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="G17" s="2" t="s">
+      <c r="J17" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>186</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>92</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>92</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>515</v>
+        <v>500</v>
       </c>
       <c r="P17" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="S17" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="Q17" s="2" t="s">
+      <c r="T17" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="R17" s="2" t="s">
+      <c r="U17" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="S17" s="2" t="s">
+    </row>
+    <row r="18" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="T17" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="U17" s="2" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
-        <v>194</v>
       </c>
       <c r="B18" s="4">
         <v>46083</v>
@@ -5134,63 +4991,63 @@
         <v>2417</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="H18" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="I18" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="J18" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="K18" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="L18" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="I18" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="J18" s="2" t="s">
+      <c r="M18" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="O18" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="P18" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="L18" s="2" t="s">
+      <c r="Q18" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="S18" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="M18" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="O18" s="2" t="s">
+      <c r="T18" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="U18" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="S18" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="T18" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="U18" s="2" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
-        <v>206</v>
       </c>
       <c r="B19" s="4">
         <v>46083</v>
@@ -5199,63 +5056,63 @@
         <v>2418</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>575</v>
+        <v>557</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>629</v>
+        <v>611</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>520</v>
+        <v>505</v>
       </c>
       <c r="G19" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="T19" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="U19" s="3" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>630</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>628</v>
-      </c>
-      <c r="P19" s="3" t="s">
-        <v>632</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>633</v>
-      </c>
-      <c r="R19" s="3" t="s">
-        <v>634</v>
-      </c>
-      <c r="S19" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="T19" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="U19" s="3" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="B20" s="4">
         <v>46083</v>
@@ -5264,63 +5121,63 @@
         <v>2421</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>576</v>
+        <v>558</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>521</v>
+        <v>506</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>56</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="O20" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="S20" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="P20" s="2" t="s">
+      <c r="T20" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="U20" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="R20" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="S20" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="T20" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="U20" s="2" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="B21" s="4">
         <v>46083</v>
@@ -5329,63 +5186,63 @@
         <v>2422</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="J21" s="2" t="s">
         <v>218</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>221</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>92</v>
       </c>
       <c r="L21" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q21" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="M21" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="O21" s="2" t="s">
+      <c r="R21" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="P21" s="2" t="s">
+      <c r="S21" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="Q21" s="2" t="s">
+      <c r="T21" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="R21" s="2" t="s">
+      <c r="U21" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="S21" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="T21" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="U21" s="2" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
-        <v>229</v>
       </c>
       <c r="B22" s="4">
         <v>46083</v>
@@ -5394,63 +5251,63 @@
         <v>2424</v>
       </c>
       <c r="D22" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="J22" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="K22" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="Q22" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="G22" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="J22" s="2" t="s">
+      <c r="R22" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="K22" s="2" t="s">
+      <c r="S22" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="L22" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="O22" s="2" t="s">
+      <c r="T22" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>587</v>
-      </c>
-      <c r="R22" s="2" t="s">
+      <c r="U22" s="3" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
         <v>237</v>
-      </c>
-      <c r="S22" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="T22" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
-        <v>240</v>
       </c>
       <c r="B23" s="4">
         <v>46083</v>
@@ -5459,63 +5316,63 @@
         <v>2425</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>558</v>
+        <v>540</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="J23" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="G23" s="2" t="s">
+      <c r="K23" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="N23" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="O23" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="I23" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="J23" s="2" t="s">
+      <c r="P23" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="N23" s="2" t="s">
+      <c r="Q23" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="R23" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="O23" s="2" t="s">
+      <c r="S23" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="U23" s="3" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="R23" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="U23" s="3" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
-        <v>249</v>
       </c>
       <c r="B24" s="4">
         <v>46083</v>
@@ -5524,63 +5381,63 @@
         <v>2426</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>562</v>
+        <v>544</v>
       </c>
       <c r="E24" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="G24" s="2" t="s">
+      <c r="J24" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="K24" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="I24" s="2" t="s">
+      <c r="L24" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="J24" s="2" t="s">
+      <c r="M24" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="K24" s="2" t="s">
+      <c r="N24" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="L24" s="2" t="s">
+      <c r="O24" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="M24" s="2" t="s">
+      <c r="P24" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="R24" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="N24" s="2" t="s">
+      <c r="S24" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="O24" s="2" t="s">
+      <c r="T24" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="P24" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="Q24" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="R24" s="2" t="s">
+      <c r="U24" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
         <v>260</v>
-      </c>
-      <c r="S24" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="T24" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="U24" s="2" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
-        <v>263</v>
       </c>
       <c r="B25" s="4">
         <v>46083</v>
@@ -5589,63 +5446,63 @@
         <v>2427</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="K25" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="G25" s="2" t="s">
+      <c r="L25" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="O25" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="H25" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="J25" s="2" t="s">
+      <c r="P25" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="K25" s="2" t="s">
+      <c r="Q25" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="R25" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="L25" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="O25" s="2" t="s">
+      <c r="S25" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="P25" s="2" t="s">
+      <c r="T25" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="Q25" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="R25" s="2" t="s">
+      <c r="U25" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="S25" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="T25" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="U25" s="2" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A26" s="2" t="s">
-        <v>273</v>
       </c>
       <c r="B26" s="4">
         <v>46083</v>
@@ -5654,63 +5511,63 @@
         <v>2430</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>556</v>
+        <v>538</v>
       </c>
       <c r="E26" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="K26" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="I26" s="2" t="s">
+      <c r="L26" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="J26" s="2" t="s">
+      <c r="M26" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="N26" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="K26" s="2" t="s">
+      <c r="O26" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="S26" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="L26" s="2" t="s">
+      <c r="T26" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="U26" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
         <v>278</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="N26" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>602</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>557</v>
-      </c>
-      <c r="S26" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="U26" s="2" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A27" s="2" t="s">
-        <v>281</v>
       </c>
       <c r="B27" s="4">
         <v>46083</v>
@@ -5719,63 +5576,63 @@
         <v>2432</v>
       </c>
       <c r="D27" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="P27" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="G27" s="2" t="s">
+      <c r="Q27" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="H27" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="M27" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="N27" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="O27" s="2" t="s">
+      <c r="R27" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="P27" s="2" t="s">
+      <c r="S27" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="Q27" s="2" t="s">
+      <c r="T27" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="R27" s="2" t="s">
+      <c r="U27" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
         <v>287</v>
-      </c>
-      <c r="S27" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="T27" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="U27" s="2" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A28" s="2" t="s">
-        <v>290</v>
       </c>
       <c r="B28" s="4">
         <v>46083</v>
@@ -5784,63 +5641,63 @@
         <v>2433</v>
       </c>
       <c r="D28" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="P28" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="F28" s="2" t="s">
+      <c r="Q28" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="R28" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="H28" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="N28" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="O28" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="P28" s="2" t="s">
+      <c r="S28" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="Q28" s="2" t="s">
+      <c r="T28" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="R28" s="2" t="s">
+      <c r="U28" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
         <v>296</v>
-      </c>
-      <c r="S28" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="T28" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="U28" s="2" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A29" s="2" t="s">
-        <v>299</v>
       </c>
       <c r="B29" s="4">
         <v>46083</v>
@@ -5849,63 +5706,63 @@
         <v>2434</v>
       </c>
       <c r="D29" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="H29" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="J29" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="K29" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N29" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="H29" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="I29" s="2" t="s">
+      <c r="O29" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="R29" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="J29" s="2" t="s">
+      <c r="S29" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="T29" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="K29" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="N29" s="2" t="s">
+      <c r="U29" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>592</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>593</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>594</v>
-      </c>
-      <c r="R29" s="2" t="s">
+    </row>
+    <row r="30" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="T29" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="U29" s="2" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A30" s="2" t="s">
-        <v>310</v>
       </c>
       <c r="B30" s="4">
         <v>46083</v>
@@ -5914,63 +5771,63 @@
         <v>2435</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="E30" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="I30" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="J30" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="H30" s="2" t="s">
+      <c r="K30" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="I30" s="2" t="s">
+      <c r="L30" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="M30" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="J30" s="2" t="s">
+      <c r="N30" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="K30" s="2" t="s">
+      <c r="O30" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="P30" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="Q30" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="R30" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="S30" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="T30" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="U30" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="M30" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="N30" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="O30" s="3" t="s">
-        <v>618</v>
-      </c>
-      <c r="P30" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="Q30" s="3" t="s">
-        <v>620</v>
-      </c>
-      <c r="R30" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="S30" s="3" t="s">
-        <v>617</v>
-      </c>
-      <c r="T30" s="3" t="s">
-        <v>621</v>
-      </c>
-      <c r="U30" s="2" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A31" s="2" t="s">
-        <v>320</v>
       </c>
       <c r="B31" s="4">
         <v>46083</v>
@@ -5979,63 +5836,63 @@
         <v>2436</v>
       </c>
       <c r="D31" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="I31" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="G31" s="2" t="s">
+      <c r="J31" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="H31" s="2" t="s">
+      <c r="K31" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="I31" s="2" t="s">
+      <c r="L31" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="N31" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="J31" s="2" t="s">
+      <c r="O31" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="K31" s="2" t="s">
+      <c r="P31" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="L31" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="N31" s="2" t="s">
+      <c r="Q31" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="O31" s="2" t="s">
+      <c r="R31" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="P31" s="2" t="s">
+      <c r="S31" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="Q31" s="2" t="s">
+      <c r="T31" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="R31" s="2" t="s">
+      <c r="U31" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
         <v>332</v>
-      </c>
-      <c r="S31" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="T31" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="U31" s="2" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A32" s="2" t="s">
-        <v>335</v>
       </c>
       <c r="B32" s="4">
         <v>46083</v>
@@ -6044,63 +5901,63 @@
         <v>2437</v>
       </c>
       <c r="D32" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="I32" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="J32" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="F32" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="H32" s="2" t="s">
+      <c r="K32" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="I32" s="2" t="s">
+      <c r="L32" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="J32" s="2" t="s">
+      <c r="M32" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="K32" s="2" t="s">
+      <c r="N32" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="L32" s="2" t="s">
+      <c r="O32" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="P32" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="M32" s="2" t="s">
+      <c r="Q32" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="N32" s="2" t="s">
+      <c r="R32" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="O32" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="P32" s="2" t="s">
+      <c r="S32" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="Q32" s="2" t="s">
+      <c r="T32" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="R32" s="2" t="s">
+      <c r="U32" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="S32" s="2" t="s">
+    </row>
+    <row r="33" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
         <v>348</v>
-      </c>
-      <c r="T32" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="U32" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A33" s="2" t="s">
-        <v>351</v>
       </c>
       <c r="B33" s="4">
         <v>46083</v>
@@ -6109,63 +5966,63 @@
         <v>2439</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>577</v>
+        <v>559</v>
       </c>
       <c r="E33" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="K33" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="F33" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="G33" s="2" t="s">
+      <c r="L33" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="O33" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="H33" s="2" t="s">
+      <c r="P33" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="Q33" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="I33" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="K33" s="2" t="s">
+      <c r="R33" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="L33" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="N33" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="O33" s="2" t="s">
+      <c r="S33" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="P33" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="Q33" s="2" t="s">
+      <c r="T33" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="R33" s="2" t="s">
+      <c r="U33" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
         <v>358</v>
-      </c>
-      <c r="S33" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="T33" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="U33" s="2" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A34" s="2" t="s">
-        <v>361</v>
       </c>
       <c r="B34" s="4">
         <v>46083</v>
@@ -6174,63 +6031,63 @@
         <v>2442</v>
       </c>
       <c r="D34" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="J34" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="K34" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="F34" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="I34" s="2" t="s">
+      <c r="L34" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N34" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="J34" s="2" t="s">
+      <c r="O34" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="K34" s="2" t="s">
+      <c r="P34" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="L34" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="N34" s="2" t="s">
+      <c r="Q34" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="R34" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="O34" s="2" t="s">
+      <c r="S34" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="P34" s="2" t="s">
+      <c r="T34" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="U34" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" ht="261" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
         <v>369</v>
-      </c>
-      <c r="Q34" s="3" t="s">
-        <v>585</v>
-      </c>
-      <c r="R34" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="S34" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="T34" s="3" t="s">
-        <v>591</v>
-      </c>
-      <c r="U34" s="2" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A35" s="2" t="s">
-        <v>372</v>
       </c>
       <c r="B35" s="4">
         <v>46083</v>
@@ -6239,63 +6096,63 @@
         <v>2443</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>541</v>
+        <v>526</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>61</v>
       </c>
       <c r="I35" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="O35" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="J35" s="2" t="s">
+      <c r="P35" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="K35" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="N35" s="2" t="s">
+      <c r="Q35" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="R35" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="O35" s="2" t="s">
+      <c r="S35" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="P35" s="2" t="s">
+      <c r="T35" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="U35" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>584</v>
-      </c>
-      <c r="R35" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="S35" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="T35" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="U35" s="2" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A36" s="2" t="s">
-        <v>383</v>
       </c>
       <c r="B36" s="4">
         <v>46083</v>
@@ -6304,25 +6161,25 @@
         <v>2447</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>384</v>
+        <v>560</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>622</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>68</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>92</v>
@@ -6331,36 +6188,36 @@
         <v>92</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="N36" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q36" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="R36" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="O36" s="2" t="s">
+      <c r="S36" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="P36" s="2" t="s">
+      <c r="T36" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="Q36" s="2" t="s">
+      <c r="U36" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="2" t="s">
         <v>390</v>
-      </c>
-      <c r="R36" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="S36" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="T36" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="U36" s="2" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A37" s="2" t="s">
-        <v>394</v>
       </c>
       <c r="B37" s="4">
         <v>46083</v>
@@ -6369,63 +6226,63 @@
         <v>2448</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>395</v>
+        <v>561</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>626</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>56</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I37" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="P37" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="J37" s="2" t="s">
+      <c r="Q37" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="K37" s="2" t="s">
+      <c r="R37" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="S37" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="L37" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="M37" s="2" t="s">
+      <c r="T37" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="N37" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="O37" s="2" t="s">
+      <c r="U37" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="P37" s="2" t="s">
+    </row>
+    <row r="38" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="2" t="s">
         <v>402</v>
-      </c>
-      <c r="Q37" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="R37" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="S37" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="T37" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="U37" s="2" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A38" s="2" t="s">
-        <v>407</v>
       </c>
       <c r="B38" s="4">
         <v>46083</v>
@@ -6434,63 +6291,63 @@
         <v>2449</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>565</v>
+        <v>547</v>
       </c>
       <c r="E38" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="M38" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="F38" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="H38" s="2" t="s">
+      <c r="N38" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="J38" s="2" t="s">
+      <c r="O38" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="K38" s="2" t="s">
+      <c r="P38" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="L38" s="2" t="s">
+      <c r="Q38" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="M38" s="2" t="s">
+      <c r="R38" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="N38" s="2" t="s">
+      <c r="S38" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="O38" s="2" t="s">
+      <c r="T38" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="P38" s="2" t="s">
+      <c r="U38" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="Q38" s="2" t="s">
+    </row>
+    <row r="39" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="2" t="s">
         <v>417</v>
-      </c>
-      <c r="R38" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="S38" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="T38" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="U38" s="2" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A39" s="2" t="s">
-        <v>422</v>
       </c>
       <c r="B39" s="4">
         <v>46083</v>
@@ -6499,63 +6356,63 @@
         <v>2451</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>68</v>
       </c>
       <c r="I39" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="Q39" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="R39" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="S39" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="J39" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="M39" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="N39" s="2" t="s">
+      <c r="T39" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="O39" s="2" t="s">
+      <c r="U39" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="2" t="s">
         <v>426</v>
-      </c>
-      <c r="P39" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="Q39" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="R39" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="S39" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="T39" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="U39" s="2" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A40" s="2" t="s">
-        <v>431</v>
       </c>
       <c r="B40" s="4">
         <v>46083</v>
@@ -6564,63 +6421,63 @@
         <v>2452</v>
       </c>
       <c r="D40" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="P40" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="I40" s="2" t="s">
+      <c r="Q40" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="R40" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="J40" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="K40" s="2" t="s">
+      <c r="S40" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="L40" s="2" t="s">
+      <c r="T40" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="M40" s="2" t="s">
+      <c r="U40" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="2" t="s">
         <v>436</v>
-      </c>
-      <c r="N40" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="O40" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="P40" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="Q40" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="R40" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="S40" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="T40" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="U40" s="2" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A41" s="2" t="s">
-        <v>443</v>
       </c>
       <c r="B41" s="4">
         <v>46083</v>
@@ -6629,63 +6486,63 @@
         <v>2504</v>
       </c>
       <c r="D41" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="L41" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="M41" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="F41" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="G41" s="2" t="s">
+      <c r="N41" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="O41" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="H41" s="2" t="s">
+      <c r="P41" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="I41" s="2" t="s">
+      <c r="Q41" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="J41" s="2" t="s">
+      <c r="R41" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="K41" s="2" t="s">
+      <c r="S41" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="L41" s="2" t="s">
+      <c r="T41" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="M41" s="2" t="s">
+      <c r="U41" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="N41" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="O41" s="2" t="s">
+    </row>
+    <row r="42" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="2" t="s">
         <v>453</v>
-      </c>
-      <c r="P41" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="Q41" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="R41" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="S41" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="T41" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="U41" s="2" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A42" s="2" t="s">
-        <v>460</v>
       </c>
       <c r="B42" s="4">
         <v>46083</v>
@@ -6694,63 +6551,63 @@
         <v>2513</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>551</v>
+        <v>438</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>619</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>92</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="O42" s="2" t="s">
-        <v>464</v>
+        <v>483</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>620</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>552</v>
+        <v>535</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>553</v>
+        <v>536</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="U42" s="2" t="s">
-        <v>554</v>
+        <v>459</v>
+      </c>
+      <c r="U42" s="3" t="s">
+        <v>621</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="B43" s="4">
         <v>46083</v>
@@ -6759,22 +6616,22 @@
         <v>2545</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>31</v>
@@ -6792,30 +6649,30 @@
         <v>31</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="T43" s="2" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="U43" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="B44" s="4">
         <v>46083</v>
@@ -6824,56 +6681,56 @@
         <v>3682</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="3" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>56</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="N44" s="3" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>596</v>
+        <v>578</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="U44" s="2" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/pssi_form_data_altered.xlsx
+++ b/data/processed/pssi_form_data_altered.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://086gc-my.sharepoint.com/personal/cory_lagasse_dfo-mpo_gc_ca/Documents/0.Workspace/PSSI-final-tech-report/data/processed/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://086gc-my.sharepoint.com/personal/cory_lagasse_dfo-mpo_gc_ca/Documents/1. Projects/PSSI Final Reporting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="250" documentId="13_ncr:1_{72209C9B-6B2A-454B-AB74-0C9975FB44EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9656DA6-090A-4E89-876A-13E6B23390F7}"/>
+  <xr:revisionPtr revIDLastSave="252" documentId="13_ncr:1_{72209C9B-6B2A-454B-AB74-0C9975FB44EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECA39BCA-17C6-43DA-994E-31A76E6DFCE4}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1620,9 +1620,6 @@
   </si>
   <si>
     <t>Christoph Deeg, Kristi Miller-Saunders (retired), Karia Kaukinen, Arthur Bass</t>
-  </si>
-  <si>
-    <t>**SEP Hatcheries**: Nitinat River Hatchery, Robertson Creek Hatchery, Chehalis River Hatchery, Tenderfoot Hatchery, and Puntledge Creek Hatchery.</t>
   </si>
   <si>
     <t>Nitinat, Sarita, Robertson, Maria Slough (Chehalis), Puntledge, and Tenderfoot</t>
@@ -3302,6 +3299,9 @@
   </si>
   <si>
     <t>Queen Charlotte Strait, Johnstone Strait, Strait of Georgia</t>
+  </si>
+  <si>
+    <t>SEP Hatcheries: Nitinat River Hatchery, Robertson Creek Hatchery, Chehalis River Hatchery, Tenderfoot Hatchery, and Puntledge Creek Hatchery.</t>
   </si>
 </sst>
 </file>
@@ -4196,8 +4196,7 @@
     <col min="1" max="1" width="13" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.140625" style="5" customWidth="1"/>
     <col min="3" max="3" width="12.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="96.140625" style="1" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="96.140625" style="1" customWidth="1"/>
+    <col min="4" max="5" width="96.140625" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.140625" style="1" customWidth="1"/>
     <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="9" width="11.42578125" style="1" customWidth="1"/>
@@ -4231,7 +4230,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -4255,10 +4254,10 @@
         <v>10</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>670</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>671</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>11</v>
@@ -4302,10 +4301,10 @@
         <v>22</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>23</v>
@@ -4320,7 +4319,7 @@
         <v>177</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>26</v>
@@ -4332,7 +4331,7 @@
         <v>25</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>27</v>
@@ -4341,7 +4340,7 @@
         <v>28</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>29</v>
@@ -4379,7 +4378,7 @@
         <v>37</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>38</v>
@@ -4391,10 +4390,10 @@
         <v>40</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>41</v>
@@ -4403,19 +4402,19 @@
         <v>42</v>
       </c>
       <c r="M3" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="N3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="R3" s="2" t="s">
         <v>43</v>
@@ -4450,16 +4449,16 @@
         <v>2400</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>52</v>
@@ -4468,7 +4467,7 @@
         <v>309</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>53</v>
@@ -4477,7 +4476,7 @@
         <v>52</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>54</v>
@@ -4486,19 +4485,19 @@
         <v>54</v>
       </c>
       <c r="P4" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="R4" s="2" t="s">
         <v>477</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>478</v>
       </c>
       <c r="S4" s="2" t="s">
         <v>55</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="U4" s="2" t="s">
         <v>56</v>
@@ -4507,10 +4506,10 @@
         <v>57</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
@@ -4524,19 +4523,19 @@
         <v>2401</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>59</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>246</v>
@@ -4547,7 +4546,7 @@
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="3" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="N5" s="3"/>
       <c r="O5" s="2"/>
@@ -4572,7 +4571,7 @@
         <v>66</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
@@ -4589,7 +4588,7 @@
         <v>68</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>69</v>
@@ -4622,7 +4621,7 @@
         <v>74</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>75</v>
@@ -4634,7 +4633,7 @@
         <v>77</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="U6" s="2" t="s">
         <v>78</v>
@@ -4660,10 +4659,10 @@
         <v>2403</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>83</v>
@@ -4675,7 +4674,7 @@
         <v>85</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>86</v>
@@ -4699,7 +4698,7 @@
         <v>88</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>89</v>
@@ -4708,19 +4707,19 @@
         <v>90</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
@@ -4737,25 +4736,25 @@
         <v>92</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>94</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>95</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>166</v>
@@ -4765,13 +4764,13 @@
       </c>
       <c r="N8" s="3"/>
       <c r="O8" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="R8" s="2" t="s">
         <v>97</v>
@@ -4780,7 +4779,7 @@
         <v>98</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="U8" s="2" t="s">
         <v>99</v>
@@ -4789,10 +4788,10 @@
         <v>100</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
@@ -4809,41 +4808,41 @@
         <v>102</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>246</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>103</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="N9" s="3"/>
       <c r="O9" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="R9" s="2" t="s">
         <v>104</v>
@@ -4852,7 +4851,7 @@
         <v>105</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="U9" s="2" t="s">
         <v>106</v>
@@ -4864,7 +4863,7 @@
         <v>108</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
@@ -4881,50 +4880,50 @@
         <v>110</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>111</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>112</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>113</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>114</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="N10" s="3"/>
       <c r="O10" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="S10" s="2" t="s">
         <v>115</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="U10" s="2" t="s">
         <v>116</v>
@@ -4950,16 +4949,16 @@
         <v>2407</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>121</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>122</v>
@@ -4980,13 +4979,13 @@
         <v>166</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q11" s="2" t="s">
         <v>125</v>
@@ -5007,10 +5006,10 @@
         <v>130</v>
       </c>
       <c r="W11" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="X11" s="2" t="s">
         <v>489</v>
-      </c>
-      <c r="X11" s="2" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
@@ -5024,25 +5023,25 @@
         <v>2408</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>51</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>52</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>53</v>
@@ -5051,11 +5050,11 @@
         <v>52</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="N12" s="3"/>
       <c r="O12" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
@@ -5066,7 +5065,7 @@
         <v>133</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="U12" s="2" t="s">
         <v>134</v>
@@ -5075,10 +5074,10 @@
         <v>135</v>
       </c>
       <c r="W12" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="X12" s="2" t="s">
         <v>493</v>
-      </c>
-      <c r="X12" s="2" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="13" spans="1:24" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5095,20 +5094,20 @@
         <v>137</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="3" t="s">
         <v>246</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>138</v>
@@ -5117,14 +5116,14 @@
         <v>139</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="N13" s="3"/>
       <c r="O13" s="2" t="s">
         <v>140</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q13" s="2" t="s">
         <v>141</v>
@@ -5145,10 +5144,10 @@
         <v>146</v>
       </c>
       <c r="W13" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="X13" s="2" t="s">
         <v>495</v>
-      </c>
-      <c r="X13" s="2" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="14" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
@@ -5165,41 +5164,41 @@
         <v>148</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>149</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>40</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="N14" s="3"/>
       <c r="O14" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="R14" s="2" t="s">
         <v>150</v>
@@ -5220,7 +5219,7 @@
         <v>155</v>
       </c>
       <c r="X14" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="15" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
@@ -5234,53 +5233,53 @@
         <v>2412</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>157</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>52</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="N15" s="3"/>
       <c r="O15" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="R15" s="2" t="s">
         <v>159</v>
       </c>
       <c r="S15" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="T15" s="2" t="s">
         <v>498</v>
-      </c>
-      <c r="T15" s="2" t="s">
-        <v>499</v>
       </c>
       <c r="U15" s="2" t="s">
         <v>160</v>
@@ -5289,10 +5288,10 @@
         <v>161</v>
       </c>
       <c r="W15" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="X15" s="2" t="s">
         <v>500</v>
-      </c>
-      <c r="X15" s="2" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="16" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
@@ -5306,16 +5305,16 @@
         <v>2413</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>163</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>164</v>
@@ -5337,13 +5336,13 @@
       </c>
       <c r="N16" s="3"/>
       <c r="O16" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="R16" s="2" t="s">
         <v>167</v>
@@ -5361,7 +5360,7 @@
         <v>171</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="X16" s="2" t="s">
         <v>172</v>
@@ -5381,13 +5380,13 @@
         <v>174</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>175</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>176</v>
@@ -5417,10 +5416,10 @@
         <v>96</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="S17" s="2" t="s">
         <v>181</v>
@@ -5455,7 +5454,7 @@
         <v>188</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>189</v>
@@ -5470,7 +5469,7 @@
         <v>177</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>192</v>
@@ -5479,7 +5478,7 @@
         <v>193</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>194</v>
@@ -5488,10 +5487,10 @@
         <v>194</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="R18" s="2" t="s">
         <v>195</v>
@@ -5500,19 +5499,19 @@
         <v>196</v>
       </c>
       <c r="T18" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="U18" s="2" t="s">
         <v>506</v>
-      </c>
-      <c r="U18" s="2" t="s">
-        <v>507</v>
       </c>
       <c r="V18" s="2" t="s">
         <v>197</v>
       </c>
       <c r="W18" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="X18" s="2" t="s">
         <v>508</v>
-      </c>
-      <c r="X18" s="2" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="19" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
@@ -5526,25 +5525,25 @@
         <v>2418</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>189</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>199</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>200</v>
@@ -5553,7 +5552,7 @@
         <v>193</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>201</v>
@@ -5562,31 +5561,31 @@
         <v>201</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="R19" s="2" t="s">
         <v>202</v>
       </c>
       <c r="S19" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="T19" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="T19" s="2" t="s">
+      <c r="U19" s="2" t="s">
         <v>512</v>
-      </c>
-      <c r="U19" s="2" t="s">
-        <v>513</v>
       </c>
       <c r="V19" s="2" t="s">
         <v>203</v>
       </c>
       <c r="W19" s="3" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
@@ -5600,25 +5599,25 @@
         <v>2421</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>205</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>177</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>206</v>
@@ -5627,17 +5626,17 @@
         <v>52</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="N20" s="3"/>
       <c r="O20" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="R20" s="2" t="s">
         <v>207</v>
@@ -5646,7 +5645,7 @@
         <v>208</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="U20" s="2" t="s">
         <v>209</v>
@@ -5655,10 +5654,10 @@
         <v>210</v>
       </c>
       <c r="W20" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="X20" s="2" t="s">
         <v>516</v>
-      </c>
-      <c r="X20" s="2" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="21" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
@@ -5675,13 +5674,13 @@
         <v>212</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>213</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>176</v>
@@ -5708,10 +5707,10 @@
         <v>216</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="R21" s="2" t="s">
         <v>217</v>
@@ -5732,7 +5731,7 @@
         <v>222</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="22" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
@@ -5749,16 +5748,16 @@
         <v>224</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>225</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>226</v>
@@ -5773,26 +5772,26 @@
         <v>229</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="N22" s="3"/>
       <c r="O22" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="R22" s="2" t="s">
         <v>230</v>
       </c>
       <c r="S22" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="T22" s="3" t="s">
         <v>576</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>577</v>
       </c>
       <c r="U22" s="2" t="s">
         <v>231</v>
@@ -5804,7 +5803,7 @@
         <v>233</v>
       </c>
       <c r="X22" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="23" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
@@ -5818,22 +5817,22 @@
         <v>2425</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>235</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>236</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>140</v>
@@ -5842,17 +5841,17 @@
         <v>237</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q23" s="2" t="s">
         <v>238</v>
@@ -5870,13 +5869,13 @@
         <v>242</v>
       </c>
       <c r="V23" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="W23" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="X23" s="3" t="s">
         <v>580</v>
-      </c>
-      <c r="W23" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="X23" s="3" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="24" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
@@ -5890,16 +5889,16 @@
         <v>2426</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>244</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>245</v>
@@ -5917,7 +5916,7 @@
         <v>249</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>252</v>
@@ -5935,10 +5934,10 @@
         <v>253</v>
       </c>
       <c r="S24" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="T24" s="2" t="s">
         <v>518</v>
-      </c>
-      <c r="T24" s="2" t="s">
-        <v>519</v>
       </c>
       <c r="U24" s="2" t="s">
         <v>254</v>
@@ -5950,7 +5949,7 @@
         <v>256</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
@@ -5967,19 +5966,19 @@
         <v>258</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>163</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>259</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>158</v>
@@ -5995,13 +5994,13 @@
       </c>
       <c r="N25" s="3"/>
       <c r="O25" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="R25" s="2" t="s">
         <v>262</v>
@@ -6010,7 +6009,7 @@
         <v>263</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="U25" s="2" t="s">
         <v>264</v>
@@ -6022,7 +6021,7 @@
         <v>266</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="26" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
@@ -6036,19 +6035,19 @@
         <v>2430</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>268</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>246</v>
@@ -6063,16 +6062,16 @@
         <v>271</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>272</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q26" s="2" t="s">
         <v>273</v>
@@ -6081,22 +6080,22 @@
         <v>274</v>
       </c>
       <c r="S26" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="T26" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="U26" s="2" t="s">
         <v>546</v>
-      </c>
-      <c r="T26" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="U26" s="2" t="s">
-        <v>547</v>
       </c>
       <c r="V26" s="2" t="s">
         <v>275</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="27" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
@@ -6113,22 +6112,22 @@
         <v>277</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>278</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>228</v>
@@ -6141,13 +6140,13 @@
       </c>
       <c r="N27" s="3"/>
       <c r="O27" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="R27" s="2" t="s">
         <v>279</v>
@@ -6168,7 +6167,7 @@
         <v>284</v>
       </c>
       <c r="X27" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="28" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
@@ -6185,10 +6184,10 @@
         <v>286</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>287</v>
@@ -6197,32 +6196,32 @@
         <v>288</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>228</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M28" s="3" t="s">
         <v>158</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="S28" s="2" t="s">
         <v>289</v>
@@ -6240,7 +6239,7 @@
         <v>293</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="29" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
@@ -6257,7 +6256,7 @@
         <v>295</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>296</v>
@@ -6281,34 +6280,34 @@
         <v>261</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q29" s="2" t="s">
         <v>301</v>
       </c>
       <c r="R29" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="S29" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="S29" s="3" t="s">
+      <c r="T29" s="3" t="s">
         <v>584</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>585</v>
       </c>
       <c r="U29" s="2" t="s">
         <v>302</v>
       </c>
       <c r="V29" s="3" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="W29" s="2" t="s">
         <v>303</v>
@@ -6328,10 +6327,10 @@
         <v>2435</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>306</v>
@@ -6355,7 +6354,7 @@
         <v>312</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="3" t="s">
@@ -6386,7 +6385,7 @@
         <v>320</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="31" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
@@ -6403,13 +6402,13 @@
         <v>322</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>323</v>
@@ -6433,10 +6432,10 @@
         <v>328</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q31" s="2" t="s">
         <v>328</v>
@@ -6460,7 +6459,7 @@
         <v>334</v>
       </c>
       <c r="X31" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="32" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
@@ -6477,31 +6476,31 @@
         <v>336</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>337</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>308</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>338</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="N32" s="3"/>
       <c r="O32" s="2" t="s">
@@ -6514,7 +6513,7 @@
         <v>341</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="S32" s="2" t="s">
         <v>342</v>
@@ -6546,48 +6545,48 @@
         <v>2439</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>349</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>350</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="M33" s="3"/>
       <c r="N33" s="3"/>
       <c r="O33" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="R33" s="2" t="s">
         <v>351</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="T33" s="2" t="s">
         <v>352</v>
@@ -6602,7 +6601,7 @@
         <v>355</v>
       </c>
       <c r="X33" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="34" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
@@ -6619,16 +6618,16 @@
         <v>357</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>177</v>
@@ -6646,13 +6645,13 @@
         <v>360</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q34" s="2" t="s">
         <v>361</v>
@@ -6664,7 +6663,7 @@
         <v>363</v>
       </c>
       <c r="T34" s="3" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="U34" s="2" t="s">
         <v>364</v>
@@ -6673,10 +6672,10 @@
         <v>365</v>
       </c>
       <c r="W34" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="X34" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="35" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
@@ -6693,13 +6692,13 @@
         <v>367</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>368</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>369</v>
@@ -6714,19 +6713,19 @@
         <v>371</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>370</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q35" s="2" t="s">
         <v>372</v>
@@ -6738,7 +6737,7 @@
         <v>374</v>
       </c>
       <c r="T35" s="3" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="U35" s="2" t="s">
         <v>375</v>
@@ -6747,10 +6746,10 @@
         <v>376</v>
       </c>
       <c r="W35" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="X35" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="36" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
@@ -6764,16 +6763,16 @@
         <v>2447</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>378</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>379</v>
@@ -6794,13 +6793,13 @@
         <v>166</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>96</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q36" s="2" t="s">
         <v>381</v>
@@ -6824,7 +6823,7 @@
         <v>387</v>
       </c>
       <c r="X36" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="37" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
@@ -6838,16 +6837,16 @@
         <v>2448</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>389</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>390</v>
+        <v>673</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>52</v>
@@ -6856,54 +6855,54 @@
         <v>177</v>
       </c>
       <c r="J37" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="K37" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="K37" s="2" t="s">
+      <c r="L37" s="2" t="s">
         <v>392</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>393</v>
       </c>
       <c r="M37" s="3" t="s">
         <v>25</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="P37" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="Q37" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="R37" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="Q37" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="R37" s="2" t="s">
+      <c r="S37" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="S37" s="2" t="s">
+      <c r="T37" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="T37" s="2" t="s">
+      <c r="U37" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="V37" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="U37" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="V37" s="2" t="s">
+      <c r="W37" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="W37" s="2" t="s">
+      <c r="X37" s="2" t="s">
         <v>399</v>
-      </c>
-      <c r="X37" s="2" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="38" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B38" s="4">
         <v>46083</v>
@@ -6912,72 +6911,72 @@
         <v>2449</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F38" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="K38" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="K38" s="2" t="s">
+      <c r="L38" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="L38" s="2" t="s">
+      <c r="M38" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="O38" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="M38" s="3" t="s">
-        <v>659</v>
-      </c>
-      <c r="N38" s="3" t="s">
-        <v>668</v>
-      </c>
-      <c r="O38" s="2" t="s">
+      <c r="P38" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="P38" s="2" t="s">
+      <c r="Q38" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="Q38" s="2" t="s">
+      <c r="R38" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="R38" s="2" t="s">
+      <c r="S38" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="S38" s="2" t="s">
+      <c r="T38" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="T38" s="2" t="s">
+      <c r="U38" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="U38" s="2" t="s">
+      <c r="V38" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="V38" s="2" t="s">
+      <c r="W38" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="W38" s="2" t="s">
+      <c r="X38" s="2" t="s">
         <v>413</v>
-      </c>
-      <c r="X38" s="2" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="39" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B39" s="4">
         <v>46083</v>
@@ -6986,16 +6985,16 @@
         <v>2451</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>337</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>308</v>
@@ -7004,7 +7003,7 @@
         <v>177</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>300</v>
@@ -7016,42 +7015,42 @@
         <v>166</v>
       </c>
       <c r="N39" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="Q39" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="O39" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="P39" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="Q39" s="2" t="s">
+      <c r="R39" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="R39" s="2" t="s">
+      <c r="S39" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="S39" s="2" t="s">
+      <c r="T39" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="T39" s="2" t="s">
+      <c r="U39" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="V39" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="U39" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="V39" s="2" t="s">
+      <c r="W39" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="W39" s="2" t="s">
-        <v>423</v>
-      </c>
       <c r="X39" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="40" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B40" s="4">
         <v>46083</v>
@@ -7060,10 +7059,10 @@
         <v>2452</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>337</v>
@@ -7078,54 +7077,54 @@
         <v>177</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>300</v>
       </c>
       <c r="L40" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="O40" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="M40" s="3" t="s">
-        <v>659</v>
-      </c>
-      <c r="N40" s="2" t="s">
+      <c r="P40" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="Q40" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="O40" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="P40" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="Q40" s="2" t="s">
+      <c r="R40" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="R40" s="2" t="s">
+      <c r="S40" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="S40" s="2" t="s">
+      <c r="T40" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="U40" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="T40" s="2" t="s">
+      <c r="V40" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="W40" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="X40" s="2" t="s">
         <v>538</v>
-      </c>
-      <c r="U40" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="V40" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="W40" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="X40" s="2" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="41" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B41" s="4">
         <v>46083</v>
@@ -7134,28 +7133,28 @@
         <v>2504</v>
       </c>
       <c r="D41" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="H41" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="E41" s="6" t="s">
-        <v>628</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>637</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="H41" s="2" t="s">
+      <c r="I41" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="K41" s="2" t="s">
         <v>438</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>439</v>
       </c>
       <c r="L41" s="3" t="s">
         <v>25</v>
@@ -7165,39 +7164,39 @@
       </c>
       <c r="N41" s="3"/>
       <c r="O41" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="P41" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="P41" s="2" t="s">
+      <c r="Q41" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="R41" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="Q41" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="R41" s="2" t="s">
+      <c r="S41" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="S41" s="2" t="s">
+      <c r="T41" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="T41" s="2" t="s">
+      <c r="U41" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="U41" s="2" t="s">
+      <c r="V41" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="V41" s="2" t="s">
+      <c r="W41" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="W41" s="2" t="s">
+      <c r="X41" s="2" t="s">
         <v>447</v>
-      </c>
-      <c r="X41" s="2" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="42" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B42" s="4">
         <v>46083</v>
@@ -7206,19 +7205,19 @@
         <v>2513</v>
       </c>
       <c r="D42" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="H42" s="2" t="s">
         <v>450</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>629</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>637</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>648</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>451</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>177</v>
@@ -7236,42 +7235,42 @@
         <v>166</v>
       </c>
       <c r="N42" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="Q42" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="R42" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="O42" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="P42" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="Q42" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="R42" s="2" t="s">
+      <c r="S42" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="S42" s="2" t="s">
+      <c r="T42" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="U42" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="V42" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="T42" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="U42" s="2" t="s">
+      <c r="W42" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="X42" s="2" t="s">
         <v>542</v>
-      </c>
-      <c r="V42" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="W42" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="X42" s="2" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="43" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B43" s="4">
         <v>46083</v>
@@ -7280,25 +7279,25 @@
         <v>2545</v>
       </c>
       <c r="D43" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>629</v>
+      </c>
+      <c r="F43" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="E43" s="6" t="s">
-        <v>630</v>
-      </c>
-      <c r="F43" s="2" t="s">
+      <c r="G43" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="H43" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>460</v>
-      </c>
       <c r="I43" s="3" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>28</v>
@@ -7307,7 +7306,7 @@
         <v>52</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="N43" s="3"/>
       <c r="O43" s="2" t="s">
@@ -7320,30 +7319,30 @@
         <v>28</v>
       </c>
       <c r="R43" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="S43" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="S43" s="2" t="s">
+      <c r="T43" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="T43" s="2" t="s">
+      <c r="U43" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="U43" s="2" t="s">
+      <c r="V43" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="V43" s="2" t="s">
+      <c r="W43" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="W43" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="X43" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="44" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B44" s="4">
         <v>46083</v>
@@ -7352,63 +7351,63 @@
         <v>3682</v>
       </c>
       <c r="D44" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>630</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="E44" s="6" t="s">
-        <v>631</v>
-      </c>
-      <c r="F44" s="2" t="s">
+      <c r="G44" s="2" t="s">
         <v>469</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>470</v>
       </c>
       <c r="H44" s="2"/>
       <c r="I44" s="3" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>52</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="N44" s="3"/>
       <c r="O44" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q44" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="S44" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="T44" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="T44" s="2" t="s">
+      <c r="U44" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="U44" s="2" t="s">
+      <c r="V44" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="V44" s="2" t="s">
+      <c r="W44" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="W44" s="2" t="s">
-        <v>475</v>
-      </c>
       <c r="X44" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
   </sheetData>
@@ -7421,4 +7420,264 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010061C374DCBC74724F8F9F44A4072F6AF4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6b8805a1b0743e175fd13f66dd395df7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b86e46b4-8cb4-4c9b-af91-82a4fe689175" xmlns:ns3="4ea98688-c254-4620-a63b-978b805c7ea0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71283a69954235b0ea5e31879caacbc8" ns2:_="" ns3:_="">
+    <xsd:import namespace="b86e46b4-8cb4-4c9b-af91-82a4fe689175"/>
+    <xsd:import namespace="4ea98688-c254-4620-a63b-978b805c7ea0"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b86e46b4-8cb4-4c9b-af91-82a4fe689175" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="11" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="6cca27c4-1c34-4d50-97f2-be840b0de0b4" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="12" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="18" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="19" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="21" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="22" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="4ea98688-c254-4620-a63b-978b805c7ea0" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="15" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="16" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b86e46b4-8cb4-4c9b-af91-82a4fe689175">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4878528-07E6-4A26-A0DF-E8ED128CCB49}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{775D00EA-857E-4AC8-A2C2-489AFEF93D59}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B2FEEE9-4F2F-47A3-957D-FBD655627B0F}"/>
 </file>
--- a/data/processed/pssi_form_data_altered.xlsx
+++ b/data/processed/pssi_form_data_altered.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://086gc-my.sharepoint.com/personal/cory_lagasse_dfo-mpo_gc_ca/Documents/1. Projects/PSSI Final Reporting/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ennsj\Documents\PSSI-final-tech-report\data\processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="252" documentId="13_ncr:1_{72209C9B-6B2A-454B-AB74-0C9975FB44EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECA39BCA-17C6-43DA-994E-31A76E6DFCE4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61796103-14A3-4B64-9062-0CB9F57A783F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="674">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="711">
   <si>
     <t>source_file</t>
   </si>
@@ -3303,6 +3303,177 @@
   <si>
     <t>SEP Hatcheries: Nitinat River Hatchery, Robertson Creek Hatchery, Chehalis River Hatchery, Tenderfoot Hatchery, and Puntledge Creek Hatchery.</t>
   </si>
+  <si>
+    <t>2398</t>
+  </si>
+  <si>
+    <t>2414</t>
+  </si>
+  <si>
+    <t>2398 - PSSI Science Project Reporting Jan 2026.docx</t>
+  </si>
+  <si>
+    <t>WCVI sediment transport and redd scour assessment</t>
+  </si>
+  <si>
+    <t>Redd scour monitoring</t>
+  </si>
+  <si>
+    <t>Diana McHugh</t>
+  </si>
+  <si>
+    <t>Tla-o-qui-aht First Nation, Redd Fish Restoration: Daphnee Tuzlak, J. Hutchinson</t>
+  </si>
+  <si>
+    <t>Tranquil Creek</t>
+  </si>
+  <si>
+    <t>South West Vancouver Island Chinook</t>
+  </si>
+  <si>
+    <t>- The freshwater risk assessment process triggered by the listing of WCVI Chinook listing as threatened in 2020 identified the time between being laid as an egg and hatching as extremely data deficient.
+- Redd scour was singled out as a priority data gap, so this study as well as work in the San Juan and Sarita were implemented  to study the issue.
+- So far, surplus sediment has been more of an issue than redd scour in Tranquil.</t>
+  </si>
+  <si>
+    <t>Balfour, T., &amp; Hutchinson, J. (2019). Fisheries Habitat Assessment Tranquil River (Hiłsyaqƛis). Central Westcoast Forest Society.
+Bradford, M. J. (1996). Comparative review of Pacific salmon survival rates. Oceanographic Literature Review, 6(43), 608. https://doi.org/10.1139/f95-129
+Clayoquot Sound Technical Planning Commttee (CSTPC), (2006). Watershed Planning in Clayoquot Sound, Volume: Tofino-Tranquil (Onadsilth-Eelsseuklis) Watershed Plan.
+Department of Fisheries and Oceans (DFO). (2024). South Coast Salmon West Coast of Vancouver Island Stock Assessment November 15, 2024; Escapement Bulletin #9 – all salmon species (Preliminary).
+DeVries, P., Burges, S. J., Daigneau, J., &amp; Stearns, D. (2001). Measurement of the temporal progression of scour in a pool-riffle sequence in a gravel bed stream using an electronic scour monitor. Water Resources Research, 37(11), 2805-2816.
+Gendaszek, A. S., Magirl, C. S., Czuba, C. R., &amp; Konrad, C. P. (2013). The timing of scour and fill in a gravel-bedded river measured with buried accelerometers. Journal of Hydrology, 495, 186-196.
+Gendaszek, A.S., 2021, Streambed scour of salmon (Oncorhynchus spp.) redds in the Sauk River, Northwestern Washington: U.S. Geological Survey Scientific Investigations Report 2021–5133, 19 p., https://doi.org/ 10.3133/ sir20215133.
+Hutchinson, J., Tuzlak, D., &amp; Pearson, A. (2020). The Legacy of Salmonid Habitat Degradation from Forestry Operations – Hiłsyaqƛis (Tranquil River). Ucluelet, BC: Central Westcoast Forest Society.
+Kwasnecha, K. Schaerer, S., &amp; Balfour T. (2024). Rotary Screw Trap Hiłsyaqƛis (Tranquil Creek). Prepared for ƛaʔuukʷiʔath (Tla-o-qui-aht) First Nation and Department of Fisheries and Oceans Canada.
+Montgomery, D. R., Buffington, J. M., Peterson, N. P., Schue􀆩-Hames, D., &amp; Quinn, T. P. (1996). Stream-bed scour, egg burial depths, and the influence of salmonid spawning on bed surface mobility and embryo survival. Canadian Journal of Fisheries and Aquatic Sciences, 53(5), 1061-1070.
+Patalano, A., García, C.M., Rodríguez, A., 2017. Rectification of Image Velocity Results (RIVeR ): A simple and user-friendly toolbox for large scale water surface Particle Image Velocimetry ( PIV ) and Particle Tracking Velocimetry ( PTV ) 109, 323–330. doi:10.1016/j.cageo.2017.07.0093 33
+Rennie, C. D., &amp; Millar, R. G. (2000). Spatial variability of stream bed scour and fill: a comparison of scour depth in chum salmon (Oncorhynchus keta) redds and adjacent bed. Canadian Journal of Fisheries and Aquatic Sciences, 57(5), 928-938.
+Roni, P., Johnson, C., De Boer, T., Press, G., Ditman, A., &amp; Sear, D. (2016). Interannual variability in the effects of physical habitat and parentage on Chinook salmon egg-to-fry survival. Canadian Journal of Fisheries and Aquatic Sciences, 73(7), 1047–1059.
+Saletti, M. 2024. Salmon Habitat Restoration Center of Expertise Technical Bulletin Vol. 1. Estimating Surface Flow Velocity in River Channels Using High Resolu􀆟on Drone Videos: Large-Scale Particle Image Velocimetry (LSPIV). Fisheries and Oceans Canada.
+Wolman, M. G. (1954). A method of sampling coarse river-bed material. EOS, Transactions American Geophysical Union, 35(6), 951-956.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Methodology
+-	Install hydromets (to monitor water levels and build a discharge curve to relate discharge to the observed scour)
+-	Field surveys of spawning locations, installation of accelerometer scour monitors (ASMs) at surveyed locations
+-	Use bed disturbance data along with a 2D hydraulic model of hiłsyaqƛis (Tranquil) to estimate the spatial extent of bed disturbance in key Chinook and chum spawning areas.
+Work Completed
+-	 ASMs installed at two sites for three consecutive years
+-	Field surveys collected particle size distribution, channel cross sections, and drone orthomosaics in the summer during low water
+&gt;&gt;&gt;&gt;&gt;&gt;&gt;AI Content
+The study used three integrated methods. DFO staff installed a hydrometric station on hiłsyaqƛis in September 2022 to record rainfall, air temperature, water temperature, and water depth at hourly intervals. Redd Fish staff measured discharge using an acoustic doppler current profiler (ADCP), a SonTek Flow Tracker2 velocimeter, and large-scale particle image velocimetry (LSPIV) from trail camera and drone videos. These measurements will produce a discharge rating curve to link observed water levels to flood magnitude.
+Accelerometer scour monitors (ASMs) were deployed at two sites in Reach 2—Site 1 (5–8 ASMs) and Site 2 (8–10 ASMs)—prior to each flood season from 2022 to 2024. Each ASM is a chain of three HOBO Pendant-G accelerometers set at 0, 15, and 35 cm depth, designed to align with the surface, top, and mid-point of a Chinook egg pocket. A tilt change greater than 15 degrees signals scour at that depth. ASMs were retrieved each summer using a PIT tag reader, and post-flood bed elevations were resurveyed with RTK-GPS. Geomorphic surveys—including Wolman pebble counts, channel cross-sections, and drone orthomosaics—were collected alongside ASM retrieval. In 2024, bulk sediment samples were also collected at each site. A 2D hydraulic model of hiłsyaqƛis (Tranquil Creek) is being calibrated with the ASM bed-disturbance data to produce reach-scale estimates of scour and deposition; this work will be complete in fall 2025.
+Results from 2022–2023 showed minimal scour at both sites, but 18.5 to 30.5 cm of sediment deposition at Site 2. A shift in grain size (D50 from 59 mm to 46 mm) suggests fine sediments mobilized from upstream. In 2023–2024, scour was recorded at two Site 1 locations (maximum depth up to 44 cm) with consecutive infill; at Site 2, two ASMs were disturbed by chum salmon during peak spawning rather than by high flows. Deposition continued at both sites but at a smaller scale than in the prior year. Engineered log jams were installed at Site 2 in summer 2024 as a large-scale restoration intervention. The 2024–2025 ASM data will be retrieved in summer 2025 and will capture the first-year effects of this restoration on bed dynamics.
+</t>
+  </si>
+  <si>
+    <t>&gt;&gt;&gt;&gt;&gt;&gt;AI Content
+In 2020, West Coast Vancouver Island (WCVI) Chinook were listed as “Threatened” by Canada’s Committee on the Status of Endangered Wildlife, triggering a freshwater risk assessment (FWRA) conducted with DFO and 16 First Nations. The FWRA found the incubation life history phase to be extremely data deficient across WCVI watersheds. Chinook egg-to-fry mortality is already estimated at 91.4%—even small improvements in incubation survival can meaningfully increase population productivity. Redd scour was identified as a high-priority data gap across 22 indicator watersheds. In hiłsyaqƛis (Tranquil Creek), industrial logging beginning in the 1960s increased sediment supply, widened the channel, reduced pool habitat, and degraded key Chinook and chum spawning habitat in Reach 2.
+In 2022, Redd Fish Restoration Society launched a three-year redd scour study in hiłsyaqƛis in partnership with ƛaʔuukʷiʔath (Tla-o-qui-aht) First Nation, DFO, BGC Engineering, and the University of British Columbia. The study aims to quantify redd scour, sediment dynamics, and hydrological conditions at two known spawning sites, and to develop a monitoring protocol that can be replicated across WCVI.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Findings
+-	Some scour was observed, followed by in-filling.
+-	Sediment deposition observed at both sites and may be a higher concern than redd scour in hiłsyaqƛis
+&gt;&gt;&gt;&gt;&gt;&gt;&gt;&gt;&gt;&gt;&gt;&gt;&gt;&gt;AI Content
+Across three flood seasons, very little redd scour was observed in hiłsyaqƛis (Tranquil Creek). Where scour did occur, it rarely exceeded 15 cm and was followed by infill. By contrast, sediment deposition—up to 30 cm at Site 2 in 2022–2023—was substantial. These results indicate that sediment surplus, most likely driven by decades of industrial logging, is a greater threat to incubating salmon in this watershed than redd scour.
+For salmon management, the findings shift the focus from peak flows and scour to sediment dynamics as a key limiting factor for incubation survival. Management actions that reduce upstream sediment delivery—such as road deactivation, slide remediation, and riparian restoration—may improve egg-to-fry survival more effectively than measures targeting scour alone. The study also confirms that ASMs can detect redd excavation by spawning salmon, providing an additional data stream for monitoring spawner-substrate interactions.
+Key uncertainties remain: the discharge rating curve is not yet complete, the 2024–2025 ASM data have not been retrieved, and the 2D hydraulic model is still being calibrated. Starting in September 2025, a UBC master’s student will quantify the sediment budget of hiłsyaqƛis to better characterize the role of industrial forestry in sediment supply. The results from this study will also be synthesized with parallel redd scour studies on the Sarita and San Juan Rivers to provide a broader picture of incubation risk across WCVI.
+</t>
+  </si>
+  <si>
+    <t>Pending (Report should be available in March 2026)
+-	Discharge curve
+-	Results from the 2024-25 winter season
+-	2D hydraulic model calibrated with the bed disturbance data
+-	Tie in the juvenile abundance (RST) data (2024 and 2025)
+-	Tie in to the two other redd scour project results (Sarita and San Juan)
+Next Steps
+-	Given the identification of surplus sediment as an issue, Redd Fish plans to partner with Dr. Marwan Hassan and a master’s student at UBC to quantify the sediment budget and look at the influence of industrial forestry on the sediment supply.</t>
+  </si>
+  <si>
+    <t>2414 PSSI EcoIndicators Project Reporting Jan 2026.docx</t>
+  </si>
+  <si>
+    <t>South Coast freshwater ecological indicator pilot</t>
+  </si>
+  <si>
+    <t>South Coast freshwater ecological indicators</t>
+  </si>
+  <si>
+    <t>Vancouver Island</t>
+  </si>
+  <si>
+    <t>Sarita, Sugsaw, Nahmint, Clemens, Bedwell, Ursus, Tranquil, Conuma, Leiner, Kaouk, Marble, Colonial, Cayeghle, Nimpkish</t>
+  </si>
+  <si>
+    <t>Freshwater (adult spawners, egg to smolt)</t>
+  </si>
+  <si>
+    <t>West Vancouver Island-South – CK-31; West Vancouver Island-Nootka &amp; Kyuquot – CK-32; West Vancouver Island-North – CK-33; East Vancouver Island-North – CK-29;</t>
+  </si>
+  <si>
+    <t>Water quality experienced by Chinook during freshwater life stages was identified as a gap in the RAMS process, undertaken to start understanding why wild WCVI Chinook returns are down even to seemingly pristine watersheds .  The eco-indicator project was designed to start filling in those gaps.  Periodic and opportunistic water quality data collected in roughly 550 sampling events in 13 watersheds, so far no major water quality issues have been identified.</t>
+  </si>
+  <si>
+    <t>The core of the program is collecting environmental data from river systems on Vancouver Island’s west coast to start filling in some gaps identified in the RAMS (Risk-Assessment Methodology for Salmon) process. The purpose of the data is to assess the health of river systems in respect to salmon habitat quality. For the most part, one or two rivers in every major inlet is monitored to try and gain the best idea possible of the health of salmon bearing systems up the west coast.</t>
+  </si>
+  <si>
+    <t>We maintained a network of water quality monitoring stations (water temperature, air temperature, water level, rain gauge) and collected periodic water quality and discharge measurements as well as putting together a few detailed photo surveys using drone footage.</t>
+  </si>
+  <si>
+    <t>- Temperatures in the monitored systems were generally cool enough for returning adults during return migration and spawning.
+- pH isn’t particularly seasonal, and observed range was within the range preferred by salmon.</t>
+  </si>
+  <si>
+    <t>Figure 1. ADD CAPTION - Day 100 April 10, Day 200 July 19, Day 300 Oct 27?
+Figure 2. ADD CAPTION
+Figure 3. ADD CAPTION</t>
+  </si>
+  <si>
+    <t>2493 PSSI Science Project Reporting Template Oct2025 Patterson Braun.docx</t>
+  </si>
+  <si>
+    <t>Improved understanding of cumulative impacts on salmon survival across freshwater life-stages; tools and approaches for mechanistic assessments</t>
+  </si>
+  <si>
+    <t>Freshwater cumulative impacts mechanistic assessments</t>
+  </si>
+  <si>
+    <t>David Patterson</t>
+  </si>
+  <si>
+    <t>David Patterson, Doug Braun, Josephine Iacarella, Kendra Robinson, Sean Naman, Daniel Selbie, Lucas Pon, Jeremy Venditti, Erika Eliason, Kim Birnie-Gauvin, Jon Moore</t>
+  </si>
+  <si>
+    <t>Developed and validated bioindicators related to multiple stressors (e.g. thermal stress, hypoxia, starvation, indicators of cardiac stress) for use in field and laboratory studies on Pacific salmon; for use in acute studies of environmental impacts (e.g. climate change projections, thermal thresholds, food deprivation)
+Developed novel biotelemetry and eco-hydraulic methods to evaluate physiological and behavioural responses to environmental stressors, for use in adult migration estimates of swim performance, mortality and effectiveness of different mitigation actions
+Increased understanding of the relationship of juvenile fish condition across different freshwater habitats to different biophysical factors (e.g. Coho wetlands, Sockeye Lakes); for use in setting escapement goals and valuations of habitat quality.</t>
+  </si>
+  <si>
+    <t>Landscape level assessments of stressors on aquatic habitats, climate change projections, and population dynamics models can provide cautionary flags that identify potentially stressed or vulnerable watersheds and/or populations (e.g., RPA status assessment, Pacific Salmon Explorer). These approaches are useful for initial watershed or population prioritization. However, in most cases these approaches are limited in their ability to accurately describe the cumulative impact that multiple stressors can have on individuals and specific populations because they lack a mechanistic approach that can verify the complex interacting pathways of effects on fish. This complexity makes it difficult to understand how future landscape alterations and climate change will affect salmon in a given watershed; thus limiting our ability to provide specific advice to managers on how to predict which mitigation or recovery actions (e.g. habitat restoration, harvest reductions) will most effectively recover salmon populations. We proposed to link in situ ecophysiology information with other biophysical habitat monitoring data to develop mechanistic relationships that address management issues around habitat-population modeling, assessment of restoration function, and fish responses to climate change. The specific management questions are: Q1) What multi-factor stressors limit stage specific freshwater habitat distribution? Q2) What are the key drivers of stage-specific survival and growth for life-cycle modelling? Q3) What is the role of temperature in combination with other key factors in predicting climate change impacts on salmon growth and survival in a given habitat (e.g. lake, river, wetlands)? Q4) What are major habitat factors that affect salmon growth and survival to consider in planning and assessment of habitat mitigation, restoration, and offsetting effectiveness?
+This project is distinct in that we are proposing a mechanistic approach to test the cumulative impact of multiple factors directly on individual fish response (i.e. growth, survival, stress) in their native habitats, leveraging multiple program expertise both within the freshwater section and beyond. Our experience is that science advice to major management decisions are best supported by a mechanistic understanding how environmental and physiological processes directly impact fish themselves. This is foundational work that can then be used to generate population responses were appropriate. However, we acknowledge that not all management questions to science require such an in-depth experimental approach, which is why we are proposing the guideline development to help managers and researchers prioritize how best to approach assessing cumulative impacts, as well as work with the other related projects.</t>
+  </si>
+  <si>
+    <t>Methods: We took a multifaceted approach to knowledge generation. The bioindicator development component combined a major literature review with the development and testing of new assays relevant to salmon in the lab. These were further validated using lab experiments and field surveys.
+The work on cumulative impact projects included : 1) development of in situ stage specific mechanistic relationships among biophysical factors (dissolved oxygen (DO), temperature, flow, conspecific competition), distribution, physiological condition metrics, growth, and survival for juvenile salmonids - all measure in situ, 2) continue to develop and evaluate ecophysiology tools related to evaluating fish condition. Life-stage specific mechanistic relationships were examined using samples in-hand from three large scale field programs (Lakes, E-Watch, North Thompson Salmon Ecosystem Program) within the Freshwater Ecosystems Section. All three programs generate unique multi-year population data on multiple biophysical factors influencing juvenile salmon condition, growth, and survival such as, water quality, conspecific density, temperature, food availability, primary productivity, DO and water level in lakes, wetlands, and flows in rivers. Models examining the effects of multiple biophysical factors on condition were used to understand how interacting biophysical drivers (including stressors) shape fish condition. Concomitant lab work included the development of ecophysiology tools, such as growth hormones (IgF) for freshwater salmon growth, troponin for oxygen/cardiac stress, and triglycerides (TAG) for nutritional status, that can be used as potential indicators of habitat quality.
+Products: The major products from the project include publications, new bioindicator assays, and development of subject matter expertise.
+Advancements: Increased capacity for new lab assays, such as IgF were developed as well as
+Bioindicator Development - Major literature and lab review of the best methods to e
+Lit. reviews, lab experiments, lab assay development, field experiments
+Advancements Communication- A major part of the project was to increase collaboration amongst the programs within the freshwater ecosystems section. Each of these programs have there own connections to different DFO branches, First Nation groups, and industry partners. In addition, we sought out expertise both within DFO, such as the genomics lab to validate biomarkers, and academia for help with ecohydraulics and swim performance. These relationships will extend past the life of the project.
+Key results: Publications, development of subject matter expertise in assessing cumulative effects.</t>
+  </si>
+  <si>
+    <t>Knowledge: The project focused on knowledge generation of individual responses to environmental stressors. Scaling this work up to the population level will be the next major task, now that we have a better biological understanding of how fish interact with their environment. Both the wetland and lake work has help improve our understanding of how ecosystems effect individual salmon condition.
+Salmon Management: The adult migration work has helped to provide a much stronger biological rationale for making predictions of in-river mortality. This information is then communicated to management is their decisions regarding harvest adjustments to accommodate the expected losses. Adult swim performance work can directly inform future mitigation activities related to passage success. The juvenile coho works supports advice regarding the importance of . Juvenile sockeye work has direct implications on setting spawning escapement targets based on lake carrying capacity. Juvenile thermal tolerance work that includes sub-lethal indicators of stress supports long term planning regarding identification of temperature sensitive streams.
+Understanding: The overall project was focused on an improved mechanistic understanding of how interact with the multiple stressors they experience.</t>
+  </si>
+  <si>
+    <t>Knowledge Gaps/Future/Recommendations:
+Continue to focus on 2-3-factor lab experiments that use ecological relevant values for the stressors, such as temperature and dissolved oxygen, as well as ecologically relevant behavioural (preference, avoidance) and physiological responses (e.g. growth). Match this work with bioindicator development and then test these relationships in the field. The choice of species or habitat stressors can be informed by closer cooperation with managers.
+Operationalization: Most of the activities within this overall project already had connections to salmon and habitat management groups. The next stage is to continue to share these results and the expertise with these respective managers. However, we recognize that a lot of this work could be value to those outside of our current network. We need to explore how best to share both within and outside of science.</t>
+  </si>
 </sst>
 </file>
 
@@ -3364,7 +3535,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
@@ -3374,9 +3545,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3876,10 +4048,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C1235FC-468F-46C3-9676-E136DE729105}" name="Table1" displayName="Table1" ref="A1:X44" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
-  <autoFilter ref="A1:X44" xr:uid="{9C1235FC-468F-46C3-9676-E136DE729105}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X44">
-    <sortCondition ref="C1:C44"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C1235FC-468F-46C3-9676-E136DE729105}" name="Table1" displayName="Table1" ref="A1:X47" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
+  <autoFilter ref="A1:X47" xr:uid="{9C1235FC-468F-46C3-9676-E136DE729105}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X46">
+    <sortCondition ref="C1:C46"/>
   </sortState>
   <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{21F25E78-D457-418F-9F78-7DE13AE8CD93}" name="source_file" dataDxfId="23"/>
@@ -4190,14 +4362,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X44"/>
+  <dimension ref="A1:X47"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.140625" style="5" customWidth="1"/>
     <col min="3" max="3" width="12.140625" style="1" customWidth="1"/>
-    <col min="4" max="5" width="96.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="54.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="59.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="33.5703125" style="1" customWidth="1"/>
     <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="9" width="11.42578125" style="1" customWidth="1"/>
     <col min="10" max="10" width="14.28515625" style="1" customWidth="1"/>
@@ -4206,7 +4379,7 @@
     <col min="15" max="15" width="11.42578125" style="1" customWidth="1"/>
     <col min="16" max="16" width="12.85546875" style="1" customWidth="1"/>
     <col min="17" max="17" width="11.42578125" style="1"/>
-    <col min="18" max="18" width="11.85546875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="34.42578125" style="1" customWidth="1"/>
     <col min="19" max="19" width="13.42578125" style="1" customWidth="1"/>
     <col min="20" max="20" width="47.85546875" style="1" customWidth="1"/>
     <col min="21" max="21" width="11.42578125" style="1"/>
@@ -4292,150 +4465,150 @@
     </row>
     <row r="2" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B2" s="4">
         <v>46083</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>559</v>
+      <c r="C2" s="2">
+        <v>2394</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="I2" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>657</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>676</v>
+      </c>
+      <c r="B3" s="9">
+        <v>46086</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>674</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>677</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>678</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>680</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="I3" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>671</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="4">
-        <v>46083</v>
-      </c>
-      <c r="C3" s="2">
-        <v>2394</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>589</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M3" t="s">
-        <v>657</v>
-      </c>
-      <c r="N3" t="s">
-        <v>476</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>49</v>
+      <c r="J3" s="8" t="s">
+        <v>681</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>682</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="Q3" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="R3" s="8" t="s">
+        <v>683</v>
+      </c>
+      <c r="S3" s="8" t="s">
+        <v>686</v>
+      </c>
+      <c r="T3" s="8" t="s">
+        <v>685</v>
+      </c>
+      <c r="U3" s="8" t="s">
+        <v>687</v>
+      </c>
+      <c r="V3" s="8" t="s">
+        <v>688</v>
+      </c>
+      <c r="W3" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="X3" s="8" t="s">
+        <v>684</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
@@ -5080,7 +5253,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>136</v>
       </c>
@@ -5099,7 +5272,7 @@
       <c r="F13" s="3" t="s">
         <v>632</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="3" t="s">
         <v>639</v>
       </c>
       <c r="H13" s="2"/>
@@ -5366,187 +5539,187 @@
         <v>172</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>689</v>
+      </c>
+      <c r="B17" s="9">
+        <v>46086</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>690</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>691</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>692</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>693</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>694</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="N17" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="O17" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="P17" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="Q17" s="8" t="s">
+        <v>695</v>
+      </c>
+      <c r="R17" s="8" t="s">
+        <v>696</v>
+      </c>
+      <c r="S17" s="8" t="s">
+        <v>697</v>
+      </c>
+      <c r="T17" s="8" t="s">
+        <v>698</v>
+      </c>
+      <c r="U17" s="8" t="s">
+        <v>699</v>
+      </c>
+      <c r="V17" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="W17" s="8" t="s">
+        <v>700</v>
+      </c>
+      <c r="X17" s="8" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="B17" s="4">
-        <v>46083</v>
-      </c>
-      <c r="C17" s="2">
-        <v>2416</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="S17" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="T17" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="U17" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="V17" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="W17" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="X17" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="B18" s="4">
         <v>46083</v>
       </c>
       <c r="C18" s="2">
-        <v>2417</v>
+        <v>2416</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>604</v>
+        <v>174</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>603</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>190</v>
+        <v>503</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="I18" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>177</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>192</v>
+        <v>178</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>193</v>
+        <v>96</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>658</v>
+        <v>166</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>476</v>
+        <v>96</v>
       </c>
       <c r="Q18" s="2" t="s">
         <v>476</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>195</v>
+        <v>504</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>505</v>
+        <v>182</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>506</v>
+        <v>183</v>
       </c>
       <c r="V18" s="2" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>507</v>
+        <v>185</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>508</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="B19" s="4">
         <v>46083</v>
       </c>
       <c r="C19" s="2">
-        <v>2418</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>564</v>
+        <v>2417</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>188</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>189</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>509</v>
+        <v>190</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>651</v>
+        <v>177</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>476</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>193</v>
@@ -5555,10 +5728,10 @@
         <v>658</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>476</v>
@@ -5567,70 +5740,72 @@
         <v>476</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>510</v>
+        <v>196</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="U19" s="2" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="V19" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="W19" s="3" t="s">
-        <v>551</v>
+        <v>197</v>
+      </c>
+      <c r="W19" s="2" t="s">
+        <v>507</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B20" s="4">
         <v>46083</v>
       </c>
       <c r="C20" s="2">
-        <v>2421</v>
+        <v>2418</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>565</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>606</v>
+        <v>564</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>605</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>641</v>
+        <v>189</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>509</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>177</v>
+        <v>199</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>651</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>476</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>52</v>
+        <v>193</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>658</v>
       </c>
-      <c r="N20" s="3"/>
+      <c r="N20" s="2" t="s">
+        <v>201</v>
+      </c>
       <c r="O20" s="2" t="s">
-        <v>476</v>
+        <v>201</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>476</v>
@@ -5639,72 +5814,70 @@
         <v>476</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>208</v>
+        <v>510</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="U20" s="2" t="s">
-        <v>209</v>
+        <v>512</v>
       </c>
       <c r="V20" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="W20" s="2" t="s">
-        <v>515</v>
+        <v>203</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>551</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="B21" s="4">
         <v>46083</v>
       </c>
       <c r="C21" s="2">
-        <v>2422</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>607</v>
+        <v>2421</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>606</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="I21" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>177</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>214</v>
+        <v>476</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>216</v>
-      </c>
+        <v>658</v>
+      </c>
+      <c r="N21" s="3"/>
       <c r="O21" s="2" t="s">
-        <v>216</v>
+        <v>476</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>476</v>
@@ -5713,70 +5886,72 @@
         <v>476</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>219</v>
+        <v>514</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="V21" s="2" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>222</v>
+        <v>515</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>476</v>
+        <v>516</v>
       </c>
     </row>
     <row r="22" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="B22" s="4">
         <v>46083</v>
       </c>
       <c r="C22" s="2">
-        <v>2424</v>
+        <v>2422</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>226</v>
+        <v>176</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>177</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>229</v>
+        <v>96</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>660</v>
-      </c>
-      <c r="N22" s="3"/>
+        <v>166</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>216</v>
+      </c>
       <c r="O22" s="2" t="s">
-        <v>476</v>
+        <v>216</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>476</v>
@@ -5785,63 +5960,63 @@
         <v>476</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>575</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>576</v>
+        <v>217</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>219</v>
       </c>
       <c r="U22" s="2" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="V22" s="2" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="X22" s="3" t="s">
-        <v>577</v>
+        <v>222</v>
+      </c>
+      <c r="X22" s="2" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="23" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="B23" s="4">
         <v>46083</v>
       </c>
       <c r="C23" s="2">
-        <v>2425</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>548</v>
+        <v>2424</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>224</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>476</v>
+        <v>643</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>651</v>
+        <v>476</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>226</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>140</v>
+        <v>227</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>476</v>
+        <v>228</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>229</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>660</v>
@@ -5854,317 +6029,317 @@
         <v>476</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>238</v>
+        <v>476</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="S23" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="T23" s="2" t="s">
-        <v>241</v>
+        <v>230</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>576</v>
       </c>
       <c r="U23" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="V23" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="W23" s="3" t="s">
-        <v>578</v>
+        <v>231</v>
+      </c>
+      <c r="V23" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="W23" s="2" t="s">
+        <v>233</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="24" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="B24" s="4">
         <v>46083</v>
       </c>
       <c r="C24" s="2">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>552</v>
+        <v>476</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>246</v>
+        <v>236</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>651</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>247</v>
+        <v>140</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>249</v>
+        <v>237</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>476</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>661</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>252</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="N24" s="3"/>
       <c r="O24" s="2" t="s">
-        <v>250</v>
+        <v>476</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>252</v>
+        <v>476</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>238</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>517</v>
+        <v>240</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>518</v>
+        <v>241</v>
       </c>
       <c r="U24" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="V24" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="W24" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="X24" s="2" t="s">
-        <v>519</v>
+        <v>242</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="B25" s="4">
         <v>46083</v>
       </c>
       <c r="C25" s="2">
-        <v>2427</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>258</v>
+        <v>2426</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>553</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>476</v>
+        <v>244</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>552</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>476</v>
+        <v>246</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>158</v>
+        <v>247</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="N25" s="3"/>
+        <v>661</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>252</v>
+      </c>
       <c r="O25" s="2" t="s">
-        <v>476</v>
+        <v>250</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="Q25" s="2" t="s">
-        <v>476</v>
+        <v>251</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>252</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>263</v>
+        <v>517</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="U25" s="2" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="V25" s="2" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="26" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="B26" s="4">
         <v>46083</v>
       </c>
       <c r="C26" s="2">
-        <v>2430</v>
+        <v>2427</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>544</v>
+        <v>258</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>644</v>
+        <v>163</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>476</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>476</v>
+        <v>259</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>246</v>
+        <v>476</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>269</v>
+        <v>158</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>660</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>664</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N26" s="3"/>
       <c r="O26" s="2" t="s">
-        <v>272</v>
+        <v>476</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>476</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>273</v>
+        <v>476</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>545</v>
+        <v>263</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="U26" s="2" t="s">
-        <v>546</v>
+        <v>264</v>
       </c>
       <c r="V26" s="2" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>547</v>
+        <v>266</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>476</v>
+        <v>521</v>
       </c>
     </row>
     <row r="27" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="B27" s="4">
         <v>46083</v>
       </c>
       <c r="C27" s="2">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>277</v>
+        <v>544</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>557</v>
+        <v>612</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>268</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>278</v>
+        <v>476</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>476</v>
+        <v>246</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>476</v>
+        <v>269</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>166</v>
+        <v>271</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="N27" s="3"/>
+        <v>660</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>664</v>
+      </c>
       <c r="O27" s="2" t="s">
-        <v>476</v>
+        <v>272</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>476</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>476</v>
+        <v>273</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>280</v>
+        <v>545</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>281</v>
+        <v>522</v>
       </c>
       <c r="U27" s="2" t="s">
-        <v>282</v>
+        <v>546</v>
       </c>
       <c r="V27" s="2" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="W27" s="2" t="s">
-        <v>284</v>
+        <v>547</v>
       </c>
       <c r="X27" s="2" t="s">
         <v>476</v>
@@ -6172,28 +6347,28 @@
     </row>
     <row r="28" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="B28" s="4">
         <v>46083</v>
       </c>
       <c r="C28" s="2">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>287</v>
+      <c r="G28" s="3" t="s">
+        <v>645</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>476</v>
@@ -6204,11 +6379,11 @@
       <c r="K28" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="L28" s="3" t="s">
-        <v>476</v>
+      <c r="L28" s="2" t="s">
+        <v>166</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="2" t="s">
@@ -6221,22 +6396,22 @@
         <v>476</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>523</v>
+        <v>279</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="U28" s="2" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="V28" s="2" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="X28" s="2" t="s">
         <v>476</v>
@@ -6244,509 +6419,507 @@
     </row>
     <row r="29" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="B29" s="4">
         <v>46083</v>
       </c>
       <c r="C29" s="2">
-        <v>2434</v>
+        <v>2433</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>615</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>296</v>
+        <v>614</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>557</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>177</v>
+        <v>476</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>299</v>
+        <v>476</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>261</v>
+        <v>228</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>476</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>668</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="P29" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="N29" s="3"/>
+      <c r="O29" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="P29" s="2" t="s">
         <v>476</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>584</v>
+        <v>476</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="T29" s="2" t="s">
+        <v>290</v>
       </c>
       <c r="U29" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>585</v>
+        <v>291</v>
+      </c>
+      <c r="V29" s="2" t="s">
+        <v>292</v>
       </c>
       <c r="W29" s="2" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>304</v>
+        <v>476</v>
       </c>
     </row>
     <row r="30" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="B30" s="4">
         <v>46083</v>
       </c>
       <c r="C30" s="2">
-        <v>2435</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>555</v>
+        <v>2434</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>295</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>309</v>
+        <v>177</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>311</v>
+        <v>299</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>300</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>312</v>
+        <v>261</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>658</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>662</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>668</v>
+      </c>
       <c r="O30" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="P30" s="2" t="s">
-        <v>313</v>
+        <v>476</v>
+      </c>
+      <c r="P30" s="3" t="s">
+        <v>476</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="R30" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="S30" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="T30" s="2" t="s">
-        <v>317</v>
+        <v>301</v>
+      </c>
+      <c r="R30" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="S30" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="T30" s="3" t="s">
+        <v>584</v>
       </c>
       <c r="U30" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="V30" s="2" t="s">
-        <v>319</v>
+        <v>302</v>
+      </c>
+      <c r="V30" s="3" t="s">
+        <v>585</v>
       </c>
       <c r="W30" s="2" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>476</v>
+        <v>304</v>
       </c>
     </row>
     <row r="31" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="B31" s="4">
         <v>46083</v>
       </c>
       <c r="C31" s="2">
-        <v>2436</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>322</v>
+        <v>2435</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>555</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>617</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>634</v>
+        <v>616</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>306</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>476</v>
+        <v>307</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>326</v>
+        <v>310</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>311</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N31" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="O31" s="2" t="s">
-        <v>476</v>
+        <v>658</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="3" t="s">
+        <v>313</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>476</v>
+        <v>313</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="U31" s="2" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="V31" s="2" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="W31" s="2" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="X31" s="2" t="s">
-        <v>524</v>
+        <v>476</v>
       </c>
     </row>
     <row r="32" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="B32" s="4">
         <v>46083</v>
       </c>
       <c r="C32" s="2">
-        <v>2437</v>
+        <v>2436</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>618</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>646</v>
+        <v>617</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>476</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>476</v>
+        <v>323</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>325</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>654</v>
+        <v>326</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>327</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>659</v>
-      </c>
-      <c r="N32" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>328</v>
+      </c>
       <c r="O32" s="2" t="s">
-        <v>339</v>
+        <v>476</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>340</v>
+        <v>476</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>525</v>
+        <v>329</v>
       </c>
       <c r="S32" s="2" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="U32" s="2" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="V32" s="2" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="W32" s="2" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="X32" s="2" t="s">
-        <v>347</v>
+        <v>524</v>
       </c>
     </row>
     <row r="33" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="B33" s="4">
         <v>46083</v>
       </c>
       <c r="C33" s="2">
-        <v>2439</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>566</v>
+        <v>2437</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>526</v>
+        <v>646</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>350</v>
+        <v>308</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="J33" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="J33" s="3" t="s">
         <v>476</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>476</v>
+        <v>338</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>654</v>
       </c>
-      <c r="M33" s="3"/>
+      <c r="M33" s="3" t="s">
+        <v>659</v>
+      </c>
       <c r="N33" s="3"/>
       <c r="O33" s="2" t="s">
-        <v>476</v>
+        <v>339</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>476</v>
+        <v>340</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>476</v>
+        <v>341</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>351</v>
+        <v>525</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>527</v>
+        <v>342</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="U33" s="2" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="V33" s="2" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="X33" s="2" t="s">
-        <v>528</v>
+        <v>347</v>
       </c>
     </row>
     <row r="34" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="B34" s="4">
         <v>46083</v>
       </c>
       <c r="C34" s="2">
-        <v>2442</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>357</v>
+        <v>2439</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>566</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>620</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>635</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>177</v>
+        <v>619</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>652</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>358</v>
+        <v>476</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="N34" s="3" t="s">
-        <v>666</v>
-      </c>
-      <c r="O34" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="P34" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+      <c r="O34" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="P34" s="2" t="s">
         <v>476</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>361</v>
+        <v>476</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="T34" s="3" t="s">
-        <v>574</v>
+        <v>527</v>
+      </c>
+      <c r="T34" s="2" t="s">
+        <v>352</v>
       </c>
       <c r="U34" s="2" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="V34" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="W34" s="3" t="s">
-        <v>581</v>
+        <v>354</v>
+      </c>
+      <c r="W34" s="2" t="s">
+        <v>355</v>
       </c>
       <c r="X34" s="2" t="s">
-        <v>476</v>
+        <v>528</v>
       </c>
     </row>
     <row r="35" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="B35" s="4">
         <v>46083</v>
       </c>
       <c r="C35" s="2">
-        <v>2443</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>367</v>
+        <v>2442</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>357</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>621</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>368</v>
+        <v>620</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>635</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>246</v>
+        <v>529</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>177</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>655</v>
+        <v>359</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>360</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>660</v>
+        <v>360</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>665</v>
-      </c>
-      <c r="O35" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="P35" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="P35" s="3" t="s">
         <v>476</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="T35" s="3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="U35" s="2" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="V35" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="W35" s="2" t="s">
-        <v>531</v>
+        <v>365</v>
+      </c>
+      <c r="W35" s="3" t="s">
+        <v>581</v>
       </c>
       <c r="X35" s="2" t="s">
         <v>476</v>
@@ -6754,660 +6927,878 @@
     </row>
     <row r="36" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="B36" s="4">
         <v>46083</v>
       </c>
       <c r="C36" s="2">
-        <v>2447</v>
+        <v>2443</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>567</v>
+        <v>367</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>177</v>
+        <v>246</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>96</v>
+        <v>371</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>655</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>166</v>
+        <v>660</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>96</v>
+        <v>370</v>
       </c>
       <c r="P36" s="2" t="s">
         <v>476</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="T36" s="2" t="s">
-        <v>384</v>
+        <v>374</v>
+      </c>
+      <c r="T36" s="3" t="s">
+        <v>573</v>
       </c>
       <c r="U36" s="2" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="V36" s="2" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="W36" s="2" t="s">
-        <v>387</v>
+        <v>531</v>
       </c>
       <c r="X36" s="2" t="s">
-        <v>533</v>
+        <v>476</v>
       </c>
     </row>
     <row r="37" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="B37" s="4">
         <v>46083</v>
       </c>
       <c r="C37" s="2">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>673</v>
+        <v>378</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>532</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I37" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>177</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>392</v>
+        <v>96</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N37" s="2" t="s">
-        <v>390</v>
+        <v>166</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>663</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>390</v>
+        <v>96</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>393</v>
+        <v>476</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>476</v>
+        <v>381</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="U37" s="2" t="s">
-        <v>534</v>
+        <v>385</v>
       </c>
       <c r="V37" s="2" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="W37" s="2" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="X37" s="2" t="s">
-        <v>399</v>
+        <v>533</v>
       </c>
     </row>
     <row r="38" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="B38" s="4">
         <v>46083</v>
       </c>
       <c r="C38" s="2">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>535</v>
+        <v>389</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>673</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>651</v>
+        <v>52</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>177</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>476</v>
+        <v>390</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>658</v>
-      </c>
-      <c r="N38" s="3" t="s">
-        <v>667</v>
+        <v>25</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>390</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>406</v>
+        <v>476</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="U38" s="2" t="s">
-        <v>410</v>
+        <v>534</v>
       </c>
       <c r="V38" s="2" t="s">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="W38" s="2" t="s">
-        <v>412</v>
+        <v>398</v>
       </c>
       <c r="X38" s="2" t="s">
-        <v>413</v>
+        <v>399</v>
       </c>
     </row>
     <row r="39" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="B39" s="4">
         <v>46083</v>
       </c>
       <c r="C39" s="2">
-        <v>2451</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>415</v>
+        <v>2449</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>556</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>337</v>
+        <v>401</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>476</v>
+        <v>535</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>308</v>
+        <v>476</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>177</v>
+        <v>651</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>416</v>
+        <v>476</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>300</v>
+        <v>402</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>166</v>
+        <v>403</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="N39" s="2" t="s">
-        <v>416</v>
+        <v>658</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>667</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="U39" s="2" t="s">
-        <v>536</v>
+        <v>410</v>
       </c>
       <c r="V39" s="2" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="W39" s="2" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="X39" s="2" t="s">
-        <v>476</v>
+        <v>413</v>
       </c>
     </row>
     <row r="40" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="B40" s="4">
         <v>46083</v>
       </c>
       <c r="C40" s="2">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>337</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>297</v>
+        <v>476</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="I40" s="2" t="s">
+      <c r="I40" s="3" t="s">
         <v>177</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>300</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>426</v>
+        <v>166</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>658</v>
+        <v>166</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>537</v>
+        <v>420</v>
       </c>
       <c r="U40" s="2" t="s">
-        <v>432</v>
+        <v>536</v>
       </c>
       <c r="V40" s="2" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="W40" s="2" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="X40" s="2" t="s">
-        <v>538</v>
+        <v>476</v>
       </c>
     </row>
     <row r="41" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="B41" s="4">
         <v>46083</v>
       </c>
       <c r="C41" s="2">
-        <v>2504</v>
+        <v>2452</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>627</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>636</v>
+        <v>626</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>539</v>
+        <v>297</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>476</v>
+        <v>308</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>425</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>25</v>
+        <v>300</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>426</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N41" s="3"/>
+        <v>658</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>428</v>
+      </c>
       <c r="O41" s="2" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>443</v>
+        <v>537</v>
       </c>
       <c r="U41" s="2" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="V41" s="2" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="W41" s="2" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="X41" s="2" t="s">
-        <v>447</v>
+        <v>538</v>
       </c>
     </row>
     <row r="42" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="B42" s="4">
         <v>46083</v>
       </c>
       <c r="C42" s="2">
-        <v>2513</v>
+        <v>2504</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>636</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>647</v>
+      <c r="G42" s="2" t="s">
+        <v>539</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>164</v>
+        <v>437</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>476</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>96</v>
+        <v>438</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="N42" s="2" t="s">
-        <v>451</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="N42" s="3"/>
       <c r="O42" s="2" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>476</v>
+        <v>440</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>476</v>
+        <v>440</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>540</v>
+        <v>443</v>
       </c>
       <c r="U42" s="2" t="s">
-        <v>541</v>
+        <v>444</v>
       </c>
       <c r="V42" s="2" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="W42" s="2" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="X42" s="2" t="s">
-        <v>542</v>
+        <v>447</v>
       </c>
     </row>
     <row r="43" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="B43" s="4">
         <v>46083</v>
       </c>
       <c r="C43" s="2">
-        <v>2545</v>
+        <v>2513</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>629</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>458</v>
+        <v>628</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>636</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>476</v>
+        <v>450</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>164</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>28</v>
+        <v>228</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>659</v>
-      </c>
-      <c r="N43" s="3"/>
+        <v>166</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>451</v>
+      </c>
       <c r="O43" s="2" t="s">
-        <v>28</v>
+        <v>451</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>28</v>
+        <v>476</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>28</v>
+        <v>476</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="T43" s="2" t="s">
-        <v>462</v>
+        <v>540</v>
       </c>
       <c r="U43" s="2" t="s">
-        <v>463</v>
+        <v>541</v>
       </c>
       <c r="V43" s="2" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="W43" s="2" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="X43" s="2" t="s">
-        <v>476</v>
+        <v>542</v>
       </c>
     </row>
     <row r="44" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="B44" s="4">
         <v>46083</v>
       </c>
       <c r="C44" s="2">
-        <v>3682</v>
+        <v>2545</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="H44" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>459</v>
+      </c>
       <c r="I44" s="3" t="s">
         <v>651</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>476</v>
+      <c r="K44" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>52</v>
       </c>
       <c r="M44" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="N44" s="3"/>
+      <c r="O44" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P44" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q44" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="R44" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="S44" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="T44" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="U44" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="V44" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="W44" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="X44" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B45" s="4">
+        <v>46083</v>
+      </c>
+      <c r="C45" s="2">
+        <v>3682</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>630</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="H45" s="2"/>
+      <c r="I45" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M45" s="3" t="s">
         <v>658</v>
       </c>
-      <c r="N44" s="3"/>
-      <c r="O44" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="Q44" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="R44" s="3" t="s">
+      <c r="N45" s="3"/>
+      <c r="O45" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="R45" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="S44" s="2" t="s">
+      <c r="S45" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="T44" s="2" t="s">
+      <c r="T45" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="U44" s="2" t="s">
+      <c r="U45" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="V44" s="2" t="s">
+      <c r="V45" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="W44" s="2" t="s">
+      <c r="W45" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="X44" s="2" t="s">
+      <c r="X45" s="2" t="s">
         <v>543</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B46" s="4">
+        <v>46083</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="O46" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P46" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q46" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="R46" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="S46" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="T46" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="U46" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="V46" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W46" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="X46" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="B47" s="4">
+        <v>46087</v>
+      </c>
+      <c r="C47" s="1">
+        <v>2493</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M47" s="2"/>
+      <c r="N47" s="3"/>
+      <c r="O47" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="W47" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>476</v>
       </c>
     </row>
   </sheetData>
@@ -7423,6 +7814,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b86e46b4-8cb4-4c9b-af91-82a4fe689175">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010061C374DCBC74724F8F9F44A4072F6AF4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6b8805a1b0743e175fd13f66dd395df7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b86e46b4-8cb4-4c9b-af91-82a4fe689175" xmlns:ns3="4ea98688-c254-4620-a63b-978b805c7ea0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71283a69954235b0ea5e31879caacbc8" ns2:_="" ns3:_="">
     <xsd:import namespace="b86e46b4-8cb4-4c9b-af91-82a4fe689175"/>
@@ -7651,33 +8061,39 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b86e46b4-8cb4-4c9b-af91-82a4fe689175">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4878528-07E6-4A26-A0DF-E8ED128CCB49}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B2FEEE9-4F2F-47A3-957D-FBD655627B0F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b86e46b4-8cb4-4c9b-af91-82a4fe689175"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{775D00EA-857E-4AC8-A2C2-489AFEF93D59}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{775D00EA-857E-4AC8-A2C2-489AFEF93D59}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B2FEEE9-4F2F-47A3-957D-FBD655627B0F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4878528-07E6-4A26-A0DF-E8ED128CCB49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b86e46b4-8cb4-4c9b-af91-82a4fe689175"/>
+    <ds:schemaRef ds:uri="4ea98688-c254-4620-a63b-978b805c7ea0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/processed/pssi_form_data_altered.xlsx
+++ b/data/processed/pssi_form_data_altered.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ennsj\Documents\PSSI-final-tech-report\data\processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61796103-14A3-4B64-9062-0CB9F57A783F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{564ED53F-2486-4C71-95DC-89CCDD6EC782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1485" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="724">
   <si>
     <t>source_file</t>
   </si>
@@ -3473,6 +3473,50 @@
     <t>Knowledge Gaps/Future/Recommendations:
 Continue to focus on 2-3-factor lab experiments that use ecological relevant values for the stressors, such as temperature and dissolved oxygen, as well as ecologically relevant behavioural (preference, avoidance) and physiological responses (e.g. growth). Match this work with bioindicator development and then test these relationships in the field. The choice of species or habitat stressors can be informed by closer cooperation with managers.
 Operationalization: Most of the activities within this overall project already had connections to salmon and habitat management groups. The next stage is to continue to share these results and the expertise with these respective managers. However, we recognize that a lot of this work could be value to those outside of our current network. We need to explore how best to share both within and outside of science.</t>
+  </si>
+  <si>
+    <t>9001 PSSI Science Reporting CVIS CLagasse.docx</t>
+  </si>
+  <si>
+    <t>Climate Vulnerability Indicators for Salmon (CVIS)</t>
+  </si>
+  <si>
+    <t>Cory Lagasse</t>
+  </si>
+  <si>
+    <t>Fraser Basin</t>
+  </si>
+  <si>
+    <t>Oncorhynchus spp.</t>
+  </si>
+  <si>
+    <t>50 CUs within the Fraser Basin</t>
+  </si>
+  <si>
+    <t>- We developed the *Climate Vulnerability Indicators for Salmon (CVIS)* framework, an indicator-based, quantitative approach that integrates freshwater, migration, nearshore marine, demographic, and genetic mechanisms into 17 standardized indicators to evaluate relative climate vulnerability across Pacific salmon conservation units (CUs). The framework provides a transparent and reproducible basis for comparing climate-related risk among CUs that supports prioritization and planning by identifying which mechanisms and life stages most differentiate vulnerability.
+- CVIS was applied to 5 species and 50 Pacific salmon CUs in the Fraser River basin, using downscaled climate projections, cumulative habitat stressor models, life-history timing, status assessments, and niche/genomic modelling to characterize multi-mechanism, life-stage-specific climate risk and the sensitivity of CU vulnerability rankings to emissions scenarios and scoring methods.
+- Results summary -</t>
+  </si>
+  <si>
+    <t>Climate change is contributing to declines and increasing variability in Pacific salmon productivity across their Canadian range, but impacts are heterogeneous across species and among the &gt;450 Pacific salmon conservation units (CUs). Despite substantial scientific understanding of climate stressors in freshwater and marine environments, broad-scale, quantitative assessments that compare climate vulnerability across multiple species and wide geographic areas remain limited for Canadian Pacific salmon. This gap constrains systematic incorporation of climate considerations into conservation investment, rebuilding actions, and management planning, which may limit their effectiveness since any benefits of these activities can be moderated or outweighed by climate-driven changes.
+The CVIS assessment was developed to address this need through a quantitative, indicator-based climate change vulnerability assessment (CCVA) framework. The approach integrates multiple data products and modelling efforts, including downscaled climate models in freshwater and marine domains, cumulative habitat stressors models, Wild Salmon Policy (WSP) status assessments, CU-specific life history timing, and environmental niche and genetic analyses. The framework is designed to be scientifically robust, transparent, and reproducible to support decision-making. The application presented in the report focuses on the Fraser River basin, an area of high life-history diversity where climate change is recognized as a major threat for several populations (e.g., Fraser sockeye and Interior Fraser Chinook).</t>
+  </si>
+  <si>
+    <t>Framework and indicators. CVIS consists of 17 quantitative indicators grouped into five categories aligned with mechanisms and life stages: (1) freshwater spawning and rearing, (2) upstream migration, (3) nearshore marine, (4) demographics, and (5) genetics. Each indicator is derived from a quantitative or categorical metric (e.g., projected August stream temperature, proportional change in seasonal flow, migration distance, projected nearshore SST, cumulative habitat impacts, WSP status category, heterozygosity, genomic offset). Indicators are standardized to a common 0-1 risk scale using response functions, enabling comparison of risk across indicators and CUs. Where applicable, physiological/ecological thresholds (e.g., 15Â°C lower thresholds used for some temperature risk normalizations) are used to map changes into risk scores. Uncertainty and variability are represented using 80% quantile ranges across global climate models.
+Data integration and spatial methods. Freshwater indicators use the BC Freshwater Atlas stream network, filtered to accessible habitat with BCFishPass accessibility and habitat models. Hydrologic variables primarily draw from PCIC VIC-GL downscaled projections (with an additional statistical downscaling flow product used for comparison for August flows). Upstream migration indicators combine CU run/spawn timing with a migration-path approach (river mouth to spawning sites) and apply an upstream movement model to estimate temperature and flow exposure along the migration route. Nearshore marine indicators use sea surface temperature projections averaged over a 6month window around ocean entry within the relevant marine adaptive zone (for Fraser CUs, the Strait of Georgia MAZ is used), and incorporate an additive cumulative impacts model for nearshore habitats.
+Scoring and sensitivity analysis. To translate individual indicators into overall vulnerability, the report evaluates multiple aggregation approaches reflecting different assumptions about how mechanisms combine, including: (i) sum-of-averages by category, (ii) average across all indicators, (iii) sum-of-cubic means by category (up-weighting high indicator values), and (iv) a logic model that bins indicators into low/moderate/high risk. Results are presented with emphasis on midcentury (2041-2060) under RCP 4.5, with additional evaluation of sensitivity to emissions scenarios (RCP 4.5 vs 8.5), time periods (mid- vs endcentury), global climate models, and scoring frameworks. The report also examines indicator correlations to evaluate overlap among mechanisms.</t>
+  </si>
+  <si>
+    <t>Insights content to be added.</t>
+  </si>
+  <si>
+    <t>Next steps content to be added.</t>
+  </si>
+  <si>
+    <t>Tables and figures to be added.</t>
+  </si>
+  <si>
+    <t>DFO: Michael Arbeider, Colin Bailey, Josephine Iacarella, Timothy Healy; External:Pacific Salmon Foundation, Pacific Climate Impacts Consortium, ECCC, University of Victoria</t>
   </si>
 </sst>
 </file>
@@ -4048,8 +4092,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C1235FC-468F-46C3-9676-E136DE729105}" name="Table1" displayName="Table1" ref="A1:X47" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
-  <autoFilter ref="A1:X47" xr:uid="{9C1235FC-468F-46C3-9676-E136DE729105}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C1235FC-468F-46C3-9676-E136DE729105}" name="Table1" displayName="Table1" ref="A1:X48" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
+  <autoFilter ref="A1:X48" xr:uid="{9C1235FC-468F-46C3-9676-E136DE729105}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X46">
     <sortCondition ref="C1:C46"/>
   </sortState>
@@ -4362,34 +4406,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X47"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:X48"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.140625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="54.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="59.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="33.5703125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
-    <col min="8" max="9" width="11.42578125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="48.42578125" style="1" customWidth="1"/>
-    <col min="12" max="14" width="44.7109375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="12.85546875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="11.42578125" style="1"/>
-    <col min="18" max="18" width="34.42578125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="47.85546875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="11.42578125" style="1"/>
-    <col min="22" max="22" width="12.85546875" style="1" customWidth="1"/>
-    <col min="23" max="23" width="15.7109375" style="1" customWidth="1"/>
-    <col min="24" max="24" width="126.85546875" style="1" customWidth="1"/>
-    <col min="25" max="16384" width="11.42578125" style="1"/>
+    <col min="2" max="2" width="17.1796875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="54.81640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="59.1796875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="33.54296875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7265625" style="1" customWidth="1"/>
+    <col min="8" max="9" width="11.453125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.26953125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="48.453125" style="1" customWidth="1"/>
+    <col min="12" max="14" width="44.7265625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="11.453125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="12.81640625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="11.453125" style="1"/>
+    <col min="18" max="18" width="34.453125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="13.453125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="47.81640625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="11.453125" style="1"/>
+    <col min="22" max="22" width="12.81640625" style="1" customWidth="1"/>
+    <col min="23" max="23" width="15.7265625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="126.81640625" style="1" customWidth="1"/>
+    <col min="25" max="16384" width="11.453125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4463,7 +4507,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>36</v>
       </c>
@@ -4537,7 +4581,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>676</v>
       </c>
@@ -4611,7 +4655,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>50</v>
       </c>
@@ -4685,7 +4729,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>58</v>
       </c>
@@ -4747,7 +4791,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>67</v>
       </c>
@@ -4821,7 +4865,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>82</v>
       </c>
@@ -4895,7 +4939,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>91</v>
       </c>
@@ -4967,7 +5011,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>101</v>
       </c>
@@ -5039,7 +5083,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>109</v>
       </c>
@@ -5111,7 +5155,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>120</v>
       </c>
@@ -5185,7 +5229,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>131</v>
       </c>
@@ -5253,7 +5297,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>136</v>
       </c>
@@ -5323,7 +5367,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>147</v>
       </c>
@@ -5395,7 +5439,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>156</v>
       </c>
@@ -5467,7 +5511,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>162</v>
       </c>
@@ -5539,7 +5583,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
         <v>689</v>
       </c>
@@ -5613,7 +5657,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>173</v>
       </c>
@@ -5687,7 +5731,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>187</v>
       </c>
@@ -5761,7 +5805,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>198</v>
       </c>
@@ -5835,7 +5879,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>204</v>
       </c>
@@ -5907,7 +5951,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>211</v>
       </c>
@@ -5981,7 +6025,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="23" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>223</v>
       </c>
@@ -6053,7 +6097,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>234</v>
       </c>
@@ -6125,7 +6169,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>243</v>
       </c>
@@ -6199,7 +6243,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>257</v>
       </c>
@@ -6271,7 +6315,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>267</v>
       </c>
@@ -6345,7 +6389,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="28" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>276</v>
       </c>
@@ -6417,7 +6461,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>285</v>
       </c>
@@ -6489,7 +6533,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>294</v>
       </c>
@@ -6563,7 +6607,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>305</v>
       </c>
@@ -6635,7 +6679,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="32" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>321</v>
       </c>
@@ -6709,7 +6753,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="33" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>335</v>
       </c>
@@ -6781,7 +6825,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="34" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>348</v>
       </c>
@@ -6851,7 +6895,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="35" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>356</v>
       </c>
@@ -6925,7 +6969,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="36" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>366</v>
       </c>
@@ -6999,7 +7043,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="37" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>377</v>
       </c>
@@ -7073,7 +7117,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="38" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>388</v>
       </c>
@@ -7147,7 +7191,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="39" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>400</v>
       </c>
@@ -7221,7 +7265,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="40" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>414</v>
       </c>
@@ -7295,7 +7339,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="41" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>423</v>
       </c>
@@ -7369,7 +7413,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="42" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>435</v>
       </c>
@@ -7441,7 +7485,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="43" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>448</v>
       </c>
@@ -7515,7 +7559,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="44" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>456</v>
       </c>
@@ -7587,7 +7631,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="45" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>466</v>
       </c>
@@ -7657,7 +7701,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="46" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>21</v>
       </c>
@@ -7731,7 +7775,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>701</v>
       </c>
@@ -7798,6 +7842,66 @@
         <v>476</v>
       </c>
       <c r="X47" s="3" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A48" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="B48" s="4">
+        <v>46092</v>
+      </c>
+      <c r="C48" s="2">
+        <v>9001</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="M48" s="2"/>
+      <c r="N48" s="3"/>
+      <c r="O48" s="2"/>
+      <c r="P48" s="2"/>
+      <c r="Q48" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="R48" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="S48" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="T48" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="U48" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="V48" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="W48" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="X48" s="3" t="s">
         <v>476</v>
       </c>
     </row>
